--- a/data/mel_database.xlsx
+++ b/data/mel_database.xlsx
@@ -1177,7 +1177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS157"/>
+  <dimension ref="A1:AS156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -15045,6 +15045,16 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>To relate oyster-farm performance to environmental conditions over several crop years, pair simple in-situ measurements with satellite data. Record daily sea-surface temperature at a fixed station (manual thermometer at about 0.5 m) and obtain remote-sensing temperature and ocean-colour chlorophyll-a for the farming area from a satellite database, validating the satellite values against your in-situ readings by linear regression (satellite chlorophyll is often overestimated in shallow, sediment- or CDOM-rich water). Track farm records - survival and the duration of each rearing phase (seed-to-juvenile, juvenile-to-adult, adult-to-market) from routine grading of lantern-net stock - and flag wind direction, cold-front passages and El Nino/La Nina periods, computing the change in chlorophyll during cold fronts as a productivity signal. Regress survival and phase duration against mean water temperature and chlorophyll to identify the conditions driving crop performance, testing significance with Pearson correlation.</t>
+        </is>
+      </c>
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AM69" s="18" t="inlineStr">
         <is>
           <t>mizuta_2012</t>
@@ -15060,7 +15070,7 @@
       </c>
       <c r="AS69" s="16" t="inlineStr">
         <is>
-          <t>Underrepresented climate zone in v11 (subtropical SW Atlantic). Strong demonstration that satellite-derived chl-a is a usable predictor of commercial oyster yield — directly transferable to siting and climate-adaptation planning elsewhere.</t>
+          <t>Underrepresented climate zone in v11 (subtropical SW Atlantic). Strong demonstration that satellite-derived chl-a is a usable predictor of commercial oyster yield — directly transferable to siting and climate-adaptation planning elsewhere. | v38: filled at High from pasted Methods (Mizuta); Source Read set to Full PDF.</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15166,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>https://link.springer.com/journal/11179</t>
+          <t>https://doi.org/10.1007/s11179-005-0036-3</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -15232,6 +15242,16 @@
       <c r="AJ70" t="inlineStr">
         <is>
           <t>Sheltered</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>To monitor the phytoplankton community around a shellfish farm - for food-supply assessment and early warning of harmful blooms - collect water through the year at roughly monthly intervals with a bottle sampler (for example a 4 L Molchanov). Concentrate and settle the samples in Utermohl sedimentation chambers (with fine, around 2 um, filtration as needed), then identify and count cells under a light microscope using a counting chamber, converting counts to abundance and to biomass from cell-volume estimates. Describe the seasonal succession and track the taxa and density build-ups that precede harmful or toxic blooms, which are common around mariculture installations.</t>
+        </is>
+      </c>
+      <c r="AL70" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
       <c r="AM70" s="18" t="inlineStr">
@@ -15249,7 +15269,7 @@
       </c>
       <c r="AS70" s="16" t="inlineStr">
         <is>
-          <t>Uses the newly-added vocab entry Bay mussel (Mytilus trossulus) — exactly the species this v1.2→v1.3 vocab addition was for. Replicable HAB-detection-oriented monitoring protocol; bridges to the Schmidt 2018 Dinophysis use case.</t>
+          <t>Uses the newly-added vocab entry Bay mussel (Mytilus trossulus) — exactly the species this v1.2→v1.3 vocab addition was for. Replicable HAB-detection-oriented monitoring protocol; bridges to the Schmidt 2018 Dinophysis use case. | v38: filled at Med from database methods notes (supplied file contained background text only for this paper). | v39: DOI added (10.1007/s11179-005-0036-3); prior value was a journal homepage only.</t>
         </is>
       </c>
     </row>
@@ -16347,12 +16367,12 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Abstract + DOI metadata</t>
+          <t>Full PDF</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jembe.2005.05.005</t>
+          <t>https://doi.org/10.1016/j.jembe.2005.06.003</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -16437,12 +16457,12 @@
       </c>
       <c r="AK76" s="16" t="inlineStr">
         <is>
-          <t>Although developed at finfish farms, this broad-scale benthic method transfers to mollusc-farm monitoring. Sample sediment at farms and matched reference sites with grabs, identify the infaunal community, and measure sediment chemistry (total organic carbon, sulphides, redox). Compare farm against reference with multivariate community analysis and ANOVA across a range of farms to characterise the typical footprint and its extent.</t>
+          <t>Although developed at finfish farms, this broad-scale benthic-impact design transfers directly to bivalve or seaweed farm seabed monitoring. Lay out sites along a farm-impact gradient - directly under the structures (&lt;10 m), within the lease but away from them (&gt;20 m), just outside the lease boundary (~35 m), and reference sites 1-2 km away in a similar physical setting - with several sites per level and farm location treated as a blocking factor. At each site take triplicate Van Veen grabs (0.07 m2), sieve in the field at 1 mm and fix in buffered formalin, then in the lab wash the sample through a stacked sieve series (1 to 4 mm), sort, identify and count the infauna; estimate biomass non-destructively as ash-free dry weight using the sieve size-class method (multiplying the count on each sieve by the mean AFDW for that size class) so specimens are retained. Alongside, take triplicate corer samples for sediment: redox potential at the surface and at 10 and 40 mm within a few hours of collection, and the top 30 mm for organic content (loss-on-ignition), %C, %N and delta-13-C / delta-15-N (elemental-analyser IRMS, run unacidified to favour nitrogen accuracy), plus particle-size distribution (median grain size and %silt-clay). Analyse by aggregating replicates to a mean per impact level per farm (to avoid unequal-replication bias), run ANOVA with farm location as a block and sequential reference-vs-cage, reference-vs-lease and reference-vs-compliance contrasts, and for community structure use constrained ordination (CAP) with NPMANOVA on fourth-root-transformed Bray-Curtis similarities, using Pearson correlations to link ordination axes to sediment variables and to individual species and pinpoint the taxa driving the gradient.</t>
         </is>
       </c>
       <c r="AL76" s="17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AM76" s="18" t="inlineStr">
@@ -16465,7 +16485,7 @@
       </c>
       <c r="AS76" s="16" t="inlineStr">
         <is>
-          <t>Original system is Atlantic salmon (Finfish); benthic-impact methodology is directly transferable to mollusk farm monitoring (Rule 2). Multi-tagged Mollusk + Finfish — applies to both aquaculture types. Strong methodological template for broad-scale benthic + sediment monitoring at farm vs reference sites.</t>
+          <t>Original system is Atlantic salmon (Finfish); benthic-impact methodology is directly transferable to mollusk farm monitoring (Rule 2). Multi-tagged Mollusk + Finfish — applies to both aquaculture types. Strong methodological template for broad-scale benthic + sediment monitoring at farm vs reference sites. | v35: lifted Low-&gt;High from full pasted Methods (Edgar 2005); Source Read set to Full PDF; DOI corrected to 10.1016/j.jembe.2005.06.003 (prior 2005.05.005).</t>
         </is>
       </c>
     </row>
@@ -16769,7 +16789,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Abstract + DOI metadata</t>
+          <t>Full PDF</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -16859,12 +16879,12 @@
       </c>
       <c r="AK78" s="16" t="inlineStr">
         <is>
-          <t>This is a modelling contribution rather than a field method: it couples a shellfish-production model (likely of the ShellSIM/FARM family) with a benthic-impact framework to explore trade-offs between production and benthic-biodiversity outcomes under different scenarios. To use it, parameterise the production model for your site and run scenarios, then validate the outputs against field data; it supports siting and stocking decisions but does not itself measure an indicator.</t>
+          <t>This is a modelling framework (WISE) for finding the sustainable ceiling on shellfish culture given the food demand of naturally-occurring filter feeders, not a field-measurement protocol. First map the wild benthic filter-feeder community - via acoustic seabed mapping, benthic grabs, ROV/diver/video surveys - and use GIS interpolation constrained by habitat, sediment and depth to estimate each species' abundance across the system. Then build a resource-partitioning budget: multiply each species' abundance by its clearance rate to get the volume cleared per day and the phytoplankton (chlorophyll) and detrital organic matter removed, doing the same for the cultivated stock, and derive a simple mass-balance threshold for when the food resource starts to deplete. Finally, integrate wild and cultivated filter feeders into a dynamic ecosystem model (for example EcoWin2000, or FARM at farm scale) to simulate the chlorophyll drawdown and production trade-offs of different stocking scenarios. Use it for carrying-capacity and siting decisions rather than to measure an ecosystem-service indicator directly.</t>
         </is>
       </c>
       <c r="AL78" s="17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AM78" s="18" t="inlineStr">
@@ -16887,7 +16907,7 @@
       </c>
       <c r="AS78" s="16" t="inlineStr">
         <is>
-          <t>Modelling framework paper. Likely uses FARM or ShellSIM models given co-authorship; confirm specifics from full text. WQ 1.1.1 may apply if the model couples bioextraction explicitly — defer until full PDF read.</t>
+          <t>Modelling framework paper. Likely uses FARM or ShellSIM models given co-authorship; confirm specifics from full text. WQ 1.1.1 may apply if the model couples bioextraction explicitly — defer until full PDF read. | v36: lifted Low-&gt;High from full pasted Methods; Source Read set to Full PDF.</t>
         </is>
       </c>
     </row>
@@ -17186,7 +17206,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Abstract + DOI metadata</t>
+          <t>Full PDF</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -17271,12 +17291,12 @@
       </c>
       <c r="AK80" s="16" t="inlineStr">
         <is>
-          <t>To compare the seabed impact of bottom versus suspended (longline) mussel culture, sample sediment along distance transects at both culture types and at reference sites, identifying infauna and measuring sediment chemistry. Compare across culture method and distance with ANOVA and multivariate community analysis to see which mode leaves the larger benthic footprint and how far it extends.</t>
+          <t>To test how mussel culture (bottom or suspended) reshapes the sediment and macrobenthic community, compare a mussel site against a nearby control of similar depth and hydrography, ideally replicating across several contrasting systems rather than only within one. Collect box cores at each site; take the top 1 cm with a syringe (frozen, kept dark) for sediment properties and photopigments, and sieve the rest at 1 mm (fixed in formaldehyde) for macrofauna, adding diver video transects to record mussel distribution and large epibenthos. In the lab, identify macrofauna to the lowest level and assign feeding groups (deposit and suspension feeders, predators), estimating biomass as ash-free dry weight; measure grain size (laser diffraction), particulate organic carbon and nitrogen (elemental analyser), sediment phosphorus (ICP-OES) and chlorophyll-a/phaeopigments (HPLC on acetone extracts). Test mussel-vs-control differences within each system with t-tests and compare community structure with nMDS, ANOSIM and SIMPER on Bray-Curtis similarities (double-square-root-transformed data).</t>
         </is>
       </c>
       <c r="AL80" s="17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AM80" s="18" t="inlineStr">
@@ -17299,7 +17319,7 @@
       </c>
       <c r="AS80" s="16" t="inlineStr">
         <is>
-          <t>Strong methodological template for culture-method-comparison benthic studies (bottom vs suspended). Companion to Murray 2007 (row 79) and Crawford 2003 (row 82). North Sea / Wadden context.</t>
+          <t>Strong methodological template for culture-method-comparison benthic studies (bottom vs suspended). Companion to Murray 2007 (row 79) and Crawford 2003 (row 82). North Sea / Wadden context. | v36: lifted Low-&gt;High from full pasted Methods; Source Read set to Full PDF.</t>
         </is>
       </c>
     </row>
@@ -17593,7 +17613,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>Abstract + DOI metadata</t>
+          <t>Full PDF</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -17678,12 +17698,12 @@
       </c>
       <c r="AK82" s="16" t="inlineStr">
         <is>
-          <t>To assess a shellfish farm's benthic footprint, sample sediment at the farm and matched reference sites with grabs, identify infauna and measure sediment chemistry, comparing with ANOVA and multivariate community analysis. A standard replicated paired-site benthic-impact design suitable for oyster or mussel farms.</t>
+          <t>To assess a longline oyster/mussel farm's benthic footprint, run several transects across the farm parallel to the current, from about 100 m upstream to 100 m downstream, with sample sites from the farm centre out past the lease boundary (grouped as inside / boundary / outside). At each site take diver cores - small Perspex cores for redox potential and sulphide at 1 and 4 cm depth and the top 2 cm for grain size and organic carbon - plus wider PVC cores (to 10 cm, 1 mm sieve) for infauna, a near-bottom Niskin sample for turbidity, and sediment traps deployed a few days for biodeposition; film diver-video transects for a visual seabed record. Measure redox and sulphide with calibrated ion-selective probes and organic carbon by CHNS analyser after acid removal of carbonate, and identify and count the infauna. Compare inside/boundary/outside with two-way mixed-model ANOVA (farm random, site fixed) for chemistry and univariate indices (richness, abundance, Shannon), and community structure with PRIMER clustering, MDS and ANOSIM on square-root Bray-Curtis data.</t>
         </is>
       </c>
       <c r="AL82" s="17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AM82" s="18" t="inlineStr">
@@ -17706,7 +17726,7 @@
       </c>
       <c r="AS82" s="16" t="inlineStr">
         <is>
-          <t>Tasmanian shellfish-farm context (likely oysters and possibly mussels); confirm species mix from full PDF.</t>
+          <t>Tasmanian shellfish-farm context (likely oysters and possibly mussels); confirm species mix from full PDF. | v36: lifted Low-&gt;High from full pasted Methods; Source Read set to Full PDF.</t>
         </is>
       </c>
     </row>
@@ -18409,7 +18429,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>Abstract + DOI metadata</t>
+          <t>Full PDF</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -18494,12 +18514,12 @@
       </c>
       <c r="AK86" s="16" t="inlineStr">
         <is>
-          <t>To quantify a longline mussel farm's effect on sediment oxygen and nitrogen cycling, collect intact sediment cores at the farm and a reference site across seasons and incubate them (with oxygen microelectrodes where possible) to measure oxygen uptake and nitrogen fluxes, alongside infaunal sampling. Compare farm against reference with mass-balance and ANOVA; close in method to the other intact-core mussel-farm nitrogen-cycle studies.</t>
+          <t>To quantify how a longline mussel farm alters sediment oxygen and nitrogen cycling, sample stations under and away from the farm (plus a reference) and combine benthic flux incubations with community and microprofile work. Collect diver cores (~5 cm diameter); measure porosity, loss-on-ignition and C/N down the profile, sediment chlorophyll-a on the top 5 mm (90% acetone, spectrophotometer with phaeopigment correction), and the microphytobenthos community (sieved, counted in Utermohl chambers), and sieve additional cores at 0.5 mm for macrofauna. Measure total oxygen, ammonium and nitrate fluxes by whole-core incubation (in situ or in the lab, stirred, dark and light), with oxygen by Winkler titration, and quantify denitrification by adding 15N-nitrate and measuring 15N-labelled N2 by isotope-ratio mass spectrometry (isotope pairing); optionally resolve diffusive oxygen uptake with Clark-type microelectrode profiles. Farm sediments typically show elevated oxygen demand and shifted nitrogen cycling, and free sulphide under the farm can suppress nitrate reduction - a mechanism testable with sediment-slurry incubations.</t>
         </is>
       </c>
       <c r="AL86" s="17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AM86" s="18" t="inlineStr">
@@ -18522,7 +18542,7 @@
       </c>
       <c r="AS86" s="16" t="inlineStr">
         <is>
-          <t>Companion paper to Nizzoli 2005/2006/2011 (rows 67/66/68) and Kaspar 1985 (row 65) for mussel-farm N-cycle synthesis. WQ 1.1.1 not assigned per Rule 1a (impact-detection framing); confirm from full PDF. | v1.4 refinement: Added WQ 1.1.2 (Rate of denitrification) — intact-core sediment incubations under longline mussel farming (canonical Danish methodology, Glud + Dalsgaard co-authors). Mollusc-specific indicator added in v1.4.</t>
+          <t>Companion paper to Nizzoli 2005/2006/2011 (rows 67/66/68) and Kaspar 1985 (row 65) for mussel-farm N-cycle synthesis. WQ 1.1.1 not assigned per Rule 1a (impact-detection framing); confirm from full PDF. | v1.4 refinement: Added WQ 1.1.2 (Rate of denitrification) — intact-core sediment incubations under longline mussel farming (canonical Danish methodology, Glud + Dalsgaard co-authors). Mollusc-specific indicator added in v1.4. | v36: lifted Low-&gt;High from full pasted Methods; Source Read set to Full PDF.</t>
         </is>
       </c>
     </row>
@@ -18615,7 +18635,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>Abstract + DOI metadata</t>
+          <t>Full PDF</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -18705,12 +18725,12 @@
       </c>
       <c r="AK87" s="16" t="inlineStr">
         <is>
-          <t>This foundational multidisciplinary design combines several benthic measurements at a mussel farm and reference: sediment chemistry, infaunal identification, biodeposition traps, and foraminiferal analysis as a sensitive enrichment indicator. Deploy traps to quantify biodeposition, grab sediment for infauna and chemistry, and compare farm against reference with ANOVA and community analysis - the multi-method approach is its enduring value.</t>
+          <t>This foundational multidisciplinary design evaluates a mussel farm's benthic impact against a nearby reference of matched depth and bottom type. Quantify biodeposition with bottom-mounted sediment traps (acrylic tubes) deployed seasonally, and characterise the sediment - organic carbon and nitrogen, C/N ratio, chlorophyll-a, grain size and porosity - alongside the infaunal community. Its distinctive element is adding foraminifera as a sensitive, fast-responding bioindicator of organic enrichment, which can register a farm effect earlier than the macrofauna does. Compare farm against reference across the full suite of measures; the multi-method, multi-indicator approach is what makes it robust, and it pairs naturally with the flux and erosion methods.</t>
         </is>
       </c>
       <c r="AL87" s="17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AM87" s="18" t="inlineStr">
@@ -18733,7 +18753,7 @@
       </c>
       <c r="AS87" s="16" t="inlineStr">
         <is>
-          <t>Foundational 1990s mussel-farm benthic-impact paper; methodology influential for subsequent Atlantic Canada / mussel-farm studies including the Cranford 2007 (row 64) tradition.</t>
+          <t>Foundational 1990s mussel-farm benthic-impact paper; methodology influential for subsequent Atlantic Canada / mussel-farm studies including the Cranford 2007 (row 64) tradition. | v36: lifted Low-&gt;High from full pasted Methods; Source Read set to Full PDF.</t>
         </is>
       </c>
     </row>
@@ -18821,7 +18841,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>Abstract + DOI metadata</t>
+          <t>Full PDF</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -18906,12 +18926,12 @@
       </c>
       <c r="AK88" s="16" t="inlineStr">
         <is>
-          <t>To document a farm's influence on water-column chemistry, sample farm-zone and non-farm-zone stations across seasons with Niskin bottles, analysing nitrogen, phosphorus and silicon nutrients and chlorophyll-a (fluorometer) and identifying phytoplankton by microscopy. Compare zones along a spatial gradient to reveal how dense oyster culture reshapes nutrient stoichiometry and phytoplankton structure.</t>
+          <t>To document how dense oyster culture changes water-column chemistry, sample stations inside the shellfish-farming blocks and in the surrounding corridors and open water across seasons (with an intensive short-period campaign to capture day-to-day variability). Collect water and, after a 200 um pre-screen, filter through pre-combusted GF/F filters; measure ammonium (Koroleff method), nitrate and soluble reactive phosphorus on a segmented-flow analyser, particulate organic carbon and nitrogen on a CHN analyser, and chlorophyll-a by fluorometry. Contrast farm zones against corridors and reference water to reveal the phytoplankton depletion and the shift in nutrient stoichiometry (for example altered N:P and ammonium enrichment) driven by oyster filtration and excretion.</t>
         </is>
       </c>
       <c r="AL88" s="17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AM88" s="18" t="inlineStr">
@@ -18934,7 +18954,7 @@
       </c>
       <c r="AS88" s="16" t="inlineStr">
         <is>
-          <t>Thau Lagoon Pacific-oyster (table/trestle) culture context. WQ 1.1.1 not assigned per Rule 1a (composition-influence framing); confirm bioextraction calc presence from full PDF. | v1.4 refinement: WQ 1.2.1 (Dissolved oxygen) removed — I-col confirms paper measures N/P/Si nutrients, Chl-a, and phytoplankton structure; DO is not listed among the measurements. v1.3 broad-usage WQ 1.2.1 tag narrowed to actual DO papers under v1.4. Flag for PDF confirm if needed.</t>
+          <t>Thau Lagoon Pacific-oyster (table/trestle) culture context. WQ 1.1.1 not assigned per Rule 1a (composition-influence framing); confirm bioextraction calc presence from full PDF. | v1.4 refinement: WQ 1.2.1 (Dissolved oxygen) removed — I-col confirms paper measures N/P/Si nutrients, Chl-a, and phytoplankton structure; DO is not listed among the measurements. v1.3 broad-usage WQ 1.2.1 tag narrowed to actual DO papers under v1.4. Flag for PDF confirm if needed. | v36: lifted Low-&gt;High from full pasted Methods; Source Read set to Full PDF.</t>
         </is>
       </c>
     </row>
@@ -19650,7 +19670,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>Abstract + DOI metadata</t>
+          <t>Full PDF</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
@@ -19735,12 +19755,12 @@
       </c>
       <c r="AK92" s="16" t="inlineStr">
         <is>
-          <t>To measure sediment stability and resuspension under mussel gear, use an erosion device (for example a Gust microcosm erosion chamber) to determine the critical shear stress and erosion rate of the bed, deploy sediment traps to capture resuspended and deposited material, and analyse grain size. Compare farm against reference to see whether biodeposition and gear alter bed erodibility.</t>
+          <t>To measure whether mussel biodeposition changes how erodible the seabed is, compare an impacted muddy site under intensive culture with a coarser reference site. Collect undisturbed sediment in Plexiglas cores (about 98 cm2 surface) by diver, with an Ekman grab as a low-disturbance alternative, then run each core in a portable oscillating-grid erosion device (Particle Erosion Simulator / BEAST): step up the grid frequency and track the suspended-sediment response optically (transmission/turbidity calibrated to suspended matter by filtration) to derive the critical shear velocity for erosion onset and the erosion rate. Characterise the bed with grain size, organic content (loss-on-ignition), total organic carbon and nitrogen, chlorophyll-a and sediment carbohydrates (the colloidal fraction indexes the microbial-biofilm EPS that stabilises sediment). Contrast the two sites to link biodeposition and biofilm to bed stability.</t>
         </is>
       </c>
       <c r="AL92" s="17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AM92" s="18" t="inlineStr">
@@ -19763,7 +19783,7 @@
       </c>
       <c r="AS92" s="16" t="inlineStr">
         <is>
-          <t>Useful for sediment-stability monitoring around mussel farms; companion to Grant 1995 (row 87) tradition.</t>
+          <t>Useful for sediment-stability monitoring around mussel farms; companion to Grant 1995 (row 87) tradition. | v36: lifted Low-&gt;High from full pasted Methods; Source Read set to Full PDF.</t>
         </is>
       </c>
     </row>
@@ -19851,12 +19871,12 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>Abstract + DOI metadata</t>
+          <t>Full PDF</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.aquaculture.2018.12.052</t>
+          <t>https://doi.org/10.1016/j.aquaculture.2018.11.001</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -19941,12 +19961,12 @@
       </c>
       <c r="AK93" s="16" t="inlineStr">
         <is>
-          <t>This is a modelling method for predicting where bivalve biodeposits (faeces and pseudofaeces) settle: couple a hydrodynamic model with Lagrangian particle-tracking of settling particles to map the deposition footprint, ideally validating against sediment-trap field data. Use it to anticipate the spatial extent of benthic loading for siting and monitoring design rather than as a direct measurement.</t>
+          <t>This is a hydrodynamic-modelling method for predicting where bivalve biodeposits settle, not a field measurement. Set up a 2D hydrodynamic model (here MOHID) over the embayment on a regular grid, force it with tide-gauge water levels at the open boundaries plus river inputs, and validate against in-situ current and tide records. Then release Lagrangian particles representing faeces and pseudofaeces from the farm areas and track their dispersion and settling to map the deposition footprint and accumulation zones, comparing contrasting forcing (for example neap versus spring tides). Use it to anticipate where benthic loading will concentrate - for siting and for targeting where to place benthic monitoring - rather than to measure deposition directly.</t>
         </is>
       </c>
       <c r="AL93" s="17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AM93" s="18" t="inlineStr">
@@ -19969,7 +19989,7 @@
       </c>
       <c r="AS93" s="16" t="inlineStr">
         <is>
-          <t>Strong template for biodeposit-footprint prediction; Santa Catarina (subtropical Brazil) oyster + mussel context.</t>
+          <t>Strong template for biodeposit-footprint prediction; Santa Catarina (subtropical Brazil) oyster + mussel context. | v36: lifted Low-&gt;High from full pasted Methods; Source Read set to Full PDF. | v37: DOI corrected to paper's own 10.1016/j.aquaculture.2018.11.001 (prior 10.1016/j.aquaculture.2018.12.052).</t>
         </is>
       </c>
     </row>
@@ -20673,7 +20693,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>Abstract + DOI metadata</t>
+          <t>Full PDF</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
@@ -20763,12 +20783,12 @@
       </c>
       <c r="AK97" s="16" t="inlineStr">
         <is>
-          <t>To assess whether intertidal clam farming with predator-exclusion netting changes the infaunal community, sample seeded and netted clam beds and reference flats with sediment cores across seasons and, ideally, across several regions, identifying and weighing the infauna. Compare farm against reference with ANOVA and community analysis; site-scale effects may be limited even where regional-scale cumulative effects warrant a broader baseline.</t>
+          <t>To assess whether intertidal clam farming (seeding plus predator-exclusion netting) changes the infaunal bivalve community, use a paired design: match each farm site to a nearby reference of similar sediment type, slope, size and wave exposure, and ideally sample across several regions and farm ages. Sample on daytime low tides, stratifying by tidal height (for example a lower band and an upper band up to the top of the netted area), and collect infauna by quadrat/core following a standard intertidal-clam sampling method, identifying and counting (bivalves usually dominate the infauna). Compare farm against reference with paired univariate tests and multivariate community analysis; note that farm-scale effects can be modest and may not scale simply to the largest leases, so a broad baseline helps.</t>
         </is>
       </c>
       <c r="AL97" s="17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AM97" s="18" t="inlineStr">
@@ -20791,7 +20811,7 @@
       </c>
       <c r="AS97" s="16" t="inlineStr">
         <is>
-          <t>BC Canada intertidal Manila clam farms with predator-exclusion netting on seeded clam beds. Reports limited site-scale impact on bivalve community structure but flags potential regional-scale cumulative impacts. Calls for regional-scale baseline + monitoring. Reference benchmark for intertidal clam-bed netting context. AC = Bottom culture chosen as closest vocab; the gear is laid-net-over-substrate rather than rack-and-bag — minor vocab gap to log for v1.4.</t>
+          <t>BC Canada intertidal Manila clam farms with predator-exclusion netting on seeded clam beds. Reports limited site-scale impact on bivalve community structure but flags potential regional-scale cumulative impacts. Calls for regional-scale baseline + monitoring. Reference benchmark for intertidal clam-bed netting context. AC = Bottom culture chosen as closest vocab; the gear is laid-net-over-substrate rather than rack-and-bag — minor vocab gap to log for v1.4. | v36: lifted Low-&gt;High from full pasted Methods; Source Read set to Full PDF.</t>
         </is>
       </c>
     </row>
@@ -21086,12 +21106,12 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>Abstract + Methods (fetched)</t>
+          <t>Full PDF</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aqc.973</t>
+          <t>https://doi.org/10.1002/aqc.977</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -21172,6 +21192,16 @@
       <c r="AJ99" t="inlineStr">
         <is>
           <t>Sheltered</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>To test whether off-bottom shellfish aquaculture changes how molluscivorous sea ducks use winter habitat, survey birds along the shore and relate their densities to habitat features including aquaculture extent. Divide the coast into survey polygons (here 34, each covering water out to about 250 m from shore) and, two to three times a month through the wintering season, count all target ducks (for example surf scoter and Barrow's goldeneye) from a slow-moving boat about 100 m offshore, marking each sighting by GPS with bearing and distance so counts can be mapped in GIS; sum counts per polygon and express as birds per km2. Characterise each polygon's habitat - percentage area under aquaculture structures (delineated by boat GPS), intertidal width, presence of reefs, percent rocky shore, and intertidal mussel density (measured on shore-parallel transects with 1 m2 quadrats and small mussel-count subquadrats). Relate bird densities to the habitat variables with multiple regression and an information-theoretic model-selection approach (AICc, model averaging, parameter likelihoods) to see whether aquaculture displaces birds from natural foraging habitat or supplements their food via fouling mussels.</t>
+        </is>
+      </c>
+      <c r="AL99" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="AM99" s="18" t="inlineStr">
@@ -21189,7 +21219,7 @@
       </c>
       <c r="AS99" s="16" t="inlineStr">
         <is>
-          <t>Documents that off-bottom suspended oyster aquaculture provides winter foraging habitat for molluscivorous sea ducks (concentrated, energetically-rich prey). H&amp;B 1.2.1 (Mobile fauna — vertebrate top predators) is the focal indicator. Demonstrates positive habitat-function interaction (aquaculture supports sea-duck winter survival). Farm Structure: off-bottom suspended oyster — vocab is imperfect; 'Not gear-specific' chosen since the Mollusk-vocab suspended-oyster options (lantern net, longline) don't quite fit BC off-bottom oyster culture. Minor vocab gap to log for v1.4.  [v22] Methods confirmed: structured sea-duck density surveys (surf scoter, Barrow's goldeneye) vs habitat variables + statistical habitat-selection modelling. Field counts practitioner-doable with ID training; model selection needs partner -&gt; T3 Partnership.</t>
+          <t>Documents that off-bottom suspended oyster aquaculture provides winter foraging habitat for molluscivorous sea ducks (concentrated, energetically-rich prey). H&amp;B 1.2.1 (Mobile fauna — vertebrate top predators) is the focal indicator. Demonstrates positive habitat-function interaction (aquaculture supports sea-duck winter survival). Farm Structure: off-bottom suspended oyster — vocab is imperfect; 'Not gear-specific' chosen since the Mollusk-vocab suspended-oyster options (lantern net, longline) don't quite fit BC off-bottom oyster culture. Minor vocab gap to log for v1.4.  [v22] Methods confirmed: structured sea-duck density surveys (surf scoter, Barrow's goldeneye) vs habitat variables + statistical habitat-selection modelling. Field counts practitioner-doable with ID training; model selection needs partner -&gt; T3 Partnership. | v38: filled at High from pasted Methods (Zydelis); Source Read set to Full PDF; DOI corrected to paper's own 10.1002/aqc.977 (prior aqc.973).</t>
         </is>
       </c>
     </row>
@@ -21900,7 +21930,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>Abstract + DOI metadata</t>
+          <t>Full PDF</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -21990,12 +22020,12 @@
       </c>
       <c r="AK103" s="16" t="inlineStr">
         <is>
-          <t>To assess the habitat value of structured oyster culture, compare the farm (for example concrete posts with attached oysters) against adjacent unstructured mudflat, sampling resident macrobenthos with cores across seasons and quantifying density, biomass and diversity. Contrast structured against unstructured habitat to reveal the biodiversity uplift the oyster structure provides, and watch for invasive species when interpreting.</t>
+          <t>To measure the habitat value of structured oyster culture, compare the oyster habitat (for example rows of concrete posts with attached oysters) against adjacent unstructured mudflat as a control, sampling in both a wet and a dry season at low tide. In replicate 0.25 m2 quadrats, collect and measure all oysters (abundance and shell-length size-frequency) and remove all associated epifauna from live and dead shells; take a 10 cm-deep core (10 cm diameter) at each quadrat for infauna, sampling the control mudflat the same way (infauna only). Compute abundance, biomass, density, species richness, Shannon diversity and evenness, test habitat and season effects with two-way ANOVA, and compare community structure with PERMANOVA and nMDS on square-root-transformed Bray-Curtis dissimilarities. Watch for non-native species when interpreting the biodiversity gains.</t>
         </is>
       </c>
       <c r="AL103" s="17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AM103" s="18" t="inlineStr">
@@ -22018,7 +22048,7 @@
       </c>
       <c r="AS103" s="16" t="inlineStr">
         <is>
-          <t>Subtropical Pearl River Delta context; traditional benthic oyster farms left fallow develop into complex habitats with biodiversity comparable to natural oyster reefs. Documents one invasive species (Xenostrobus securis) at lower densities than artificial-substrate controls. Cites D'Amours 2008 (R81) as comparator. AB = Pacific oyster used as closest vocab match; HK oysters are typically Magallana hongkongensis — minor vocab-gap to log for v1.4.</t>
+          <t>Subtropical Pearl River Delta context; traditional benthic oyster farms left fallow develop into complex habitats with biodiversity comparable to natural oyster reefs. Documents one invasive species (Xenostrobus securis) at lower densities than artificial-substrate controls. Cites D'Amours 2008 (R81) as comparator. AB = Pacific oyster used as closest vocab match; HK oysters are typically Magallana hongkongensis — minor vocab-gap to log for v1.4. | v36: lifted Low-&gt;High from full pasted Methods; Source Read set to Full PDF.</t>
         </is>
       </c>
     </row>
@@ -25093,88 +25123,88 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Wu, S., et al.</t>
+          <t>George, M. N., et al.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Multiplexed printed sensors for in situ monitoring in bivalve aquaculture</t>
+          <t>Microscale pH and dissolved oxygen fluctuations within mussel aggregations and their implications for mussel attachment and raft aquaculture</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Nanoscale</t>
+          <t>Journal of Shellfish Research</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>16110-16119</t>
+          <t>795-809</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Royal Society of Chemistry</t>
+          <t>National Shellfisheries Association</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Sensor-development paper presenting a thin, flexible, multiplexed sensor tag for attachment to bivalves. Three co-located sensing modalities: (i) dissolved-oxygen electrochemical sensor (0.5–6 ppm range), (ii) salinity sensor (4–40 g kg⁻¹ range), (iii) curvature/strain sensor based on electrodeposited semiconducting fibers, resolving oyster gape down to sub-mm. Fabricated by low-cost printed-electronics techniques. DO + salinity ranges chosen to match bivalve-farm-relevant conditions. Maps to MEL WQ 1.2.1 (DO + salinity) — methodology-development paper.</t>
+          <t>In-farm sensors monitoring pH and dissolved oxygen at microscale (within mussel aggregations) and ambient (1 m + 7 m vertical sondes) at a Penn Cove (WA, USA) raft mussel farm (Mytilus trossulus). Aggregation sensors: Durafet III pH electrode (±0.01) + Honeywell DirectLine DL5000 DO probe (±0.1 mg L⁻¹), inserted in mesh bags hung from rope lines. Logged hourly via Honeywell UDA2182 analyzer with 4–20 mA Lascar data logger. Observed pH 7.14–8.58; DO 0.1–18.5 mg L⁻¹. Lab experiments paired extreme pH + DO excursions with byssus-plaque adhesion curing. Maps narrowly to MEL WQ 1.2.1 (DO measurement) — Sub-rule 1b narrow retention (parallel to Fernández 2019 / R94 precedent).</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Protocol (sensor design, fabrication, and bench/aquarium-scale characterisation)</t>
+          <t>Protocol (in-situ pH + DO microsensor deployment + paired lab plaque curing experiments)</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Partial — DO and salinity sensor ranges are bench-validated against standards; sea-deployment performance is not reported in the published abstract/methods snippets and would need to be established before operational MEL use.</t>
+          <t>Partial for MEL purposes — DO logging is methodologically robust and useful as a WQ 1.2.1 approach; the paper's primary deliverable (plaque-curing chemistry) sits outside the MEL indicator set.</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Partial — once the platform is sea-validated, low-cost tags could be deployed by trained farmers.</t>
+          <t>Partial — sonde deployment + maintenance is feasible for trained farmers; Durafet pH calibration is more specialist.</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Yes (sensor development requires research-grade fabrication facility)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Printed electrochemical DO + salinity electrodes; electrodeposited semiconducting fibre curvature/strain sensor; multiplexed PCB; portable readout</t>
+          <t>Durafet III pH electrode + Honeywell DL5000 DO probe; UDA2182 analyzer; Lascar 4–20 mA logger; 12-V AGM battery</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Low (per-tag, once developed) – High (R&amp;D fabrication setup)</t>
+          <t>Medium — sensor + logger ~$2–3K per node; multiple nodes for vertical + within-aggregation array</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Continuous (in-situ tag deployment, intended)</t>
+          <t>Multi-season (hourly logging across farming cycle)</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>Calibration regressions vs reference sensors; range/linearity/sensitivity characterisation</t>
+          <t>Time-series; correlations between pH and DO; threshold-exceedance event extraction</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>Yes — Open access via UC eScholarship deposit; journal article paywalled</t>
+          <t>No — Paywalled (BioOne / NSA)</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -25184,12 +25214,12 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1039/d2nr04382c</t>
+          <t>https://doi.org/10.2983/035.038.0329</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>A printed in-situ sensor platform, still at development stage - no sea-deployment performance reported yet.</t>
+          <t>Captures the extreme acidification and hypoxia the animals actually experience within clumps, beyond ambient readings.</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
@@ -25214,32 +25244,32 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>WQ 1.2.1 — Inorganic chemistry (DO, salinity)</t>
+          <t>WQ 1.2.1 — Inorganic chemistry (DO)</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>Cross-zone / global (methodology paper)</t>
+          <t>Temperate Pacific</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>Multi-species / mixed (oyster gape sensor specified)</t>
+          <t>Bay mussel (Mytilus trossulus)</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Not specified (sensor-development paper)</t>
+          <t>Raft / hanging rope</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>Bench / sensor-development</t>
+          <t>Single farm</t>
         </is>
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Variable / seasonal</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -25249,7 +25279,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>Sensor / wearable tag, Water chemistry</t>
+          <t>Water chemistry, In-situ sensors</t>
         </is>
       </c>
       <c r="AH119" t="inlineStr">
@@ -25259,88 +25289,103 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Not depth-specific</t>
+          <t>Shallow nearshore (2–10 m)</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>Not exposure-specific</t>
+          <t>Sheltered</t>
+        </is>
+      </c>
+      <c r="AK119" s="16" t="inlineStr">
+        <is>
+          <t>To characterise the pH and dissolved-oxygen conditions a raft mussel crop actually experiences, suspend water-quality sondes (logging temperature, salinity, pH, DO and chlorophyll) at more than one depth (for example 1 and 7 m) in the centre of the raft and log hourly over an extended period, calibrating monthly. To capture the microenvironment inside mussel clumps, embed a pH electrode and an oxygen probe in the centre of mesh bags of mussels hung beside the sondes. Test season and depth effects with two-way ANOVA (rank-transformed), and run a threshold/excursion analysis - counting sustained drops below critical pH or DO limits (for example two consecutive hours below a set threshold) and comparing their frequency and duration across season and depth. This captures both ambient conditions and the more extreme acidification and hypoxia excursions the animals endure within aggregations.</t>
+        </is>
+      </c>
+      <c r="AL119" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="AM119" s="18" t="inlineStr">
         <is>
-          <t>wu_2022</t>
+          <t>george_2019</t>
         </is>
       </c>
       <c r="AN119" s="19" t="n"/>
       <c r="AO119" s="19" t="n"/>
       <c r="AP119" s="19" t="n"/>
+      <c r="AQ119" s="16" t="inlineStr">
+        <is>
+          <t>Microscale pH &amp; Oxygen Inside Mussel Aggregations</t>
+        </is>
+      </c>
       <c r="AR119" s="16" t="inlineStr">
         <is>
-          <t>Wu, Shuo-En; Phongphaew, Napasorn; Zhai, Yichen; Yao, Lulu; Hsu, Hsun-Hao; Shiller, Alan; Azoulay, Jason D; Ng, Tse Nga</t>
+          <t>George, Matthew N; Andino, Jessie; Huie, Jonathan; Carrington, Emily</t>
         </is>
       </c>
       <c r="AS119" s="16" t="inlineStr">
         <is>
-          <t>Rule 10 caveat: the available abstract and introduction describe a sensor-development paper, explicitly framed as 'platform for aquaculture studies', without yet reporting sea-deployment performance. Retaining per the methodology-paper precedent (cf. Outinen 2019 / R106) because (a) DO and salinity ranges are matched to bivalve-farm conditions, (b) the gape sensor targets oyster behavior in-farm. v1.4 log: a 'Sensor / wearable tag' entry would be useful in Method Category vocab. Companion to the broader open-source bivalve-tag literature (Burnett &amp; Carrington open-source review, 2022).</t>
+          <t>Sub-rule 1b narrow retention parallel to Fernández 2019 (R94): pH is not in the closed MEL indicator set, but DO (WQ 1.2.1) is robustly measured. The microscale in-aggregation deployment is an unusual and useful methodological contribution — embedding aggregation sensors among cultured mussels allows DO/pH at the site of physiological action rather than only at ambient sonde depth. Companion to Carrington's broader OA/mussel-attachment program. v1.4 log: pH stays off the indicator set; if reconsidered, this paper would upgrade to 2.1.x candidate.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>George, M. N., et al.</t>
+          <t>Nizzoli, D., et al.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Microscale pH and dissolved oxygen fluctuations within mussel aggregations and their implications for mussel attachment and raft aquaculture</t>
+          <t>Oxygen and ammonium dynamics during a farming cycle of the bivalve Tapes philippinarum</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Journal of Shellfish Research</t>
+          <t>Hydrobiologia</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>38</v>
+        <v>587</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>795-809</t>
+          <t>25-36</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>2019</v>
+        <v>2007</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>National Shellfisheries Association</t>
+          <t>Springer</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>In-farm sensors monitoring pH and dissolved oxygen at microscale (within mussel aggregations) and ambient (1 m + 7 m vertical sondes) at a Penn Cove (WA, USA) raft mussel farm (Mytilus trossulus). Aggregation sensors: Durafet III pH electrode (±0.01) + Honeywell DirectLine DL5000 DO probe (±0.1 mg L⁻¹), inserted in mesh bags hung from rope lines. Logged hourly via Honeywell UDA2182 analyzer with 4–20 mA Lascar data logger. Observed pH 7.14–8.58; DO 0.1–18.5 mg L⁻¹. Lab experiments paired extreme pH + DO excursions with byssus-plaque adhesion curing. Maps narrowly to MEL WQ 1.2.1 (DO measurement) — Sub-rule 1b narrow retention (parallel to Fernández 2019 / R94 precedent).</t>
+          <t>Benthic flux measurements of dissolved oxygen and ammonium across the water-sediment interface at a control site and a Manila-clam-farmed (Tapes / Ruditapes philippinarum) experimental site in Sacca di Goro (Po Delta, Italy), spanning the full farming cycle (young-to-harvest cohort). Companion to Nizzoli 2006 MEPS (R115, ¹⁵N-pairing emphasis) — same site, same group, but here the temporal axis is the farming-cycle progression rather than instantaneous pathway partitioning. Maps to MEL WQ 1.2.1 (DO + NH4 fluxes) and H&amp;B 1.4.1 (sediment biogeochemistry under clam farming).</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Protocol (in-situ pH + DO microsensor deployment + paired lab plaque curing experiments)</t>
+          <t>Protocol (paired benthic incubation across farming cycle)</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Partial for MEL purposes — DO logging is methodologically robust and useful as a WQ 1.2.1 approach; the paper's primary deliverable (plaque-curing chemistry) sits outside the MEL indicator set.</t>
+          <t>Yes — paired farm-vs-control sediment-core incubations with standard solute-flux methodology.</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Partial — sonde deployment + maintenance is feasible for trained farmers; Durafet pH calibration is more specialist.</t>
+          <t>No — laboratory core incubation is research-only.</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -25350,27 +25395,27 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Durafet III pH electrode + Honeywell DL5000 DO probe; UDA2182 analyzer; Lascar 4–20 mA logger; 12-V AGM battery</t>
+          <t>Plexiglas core tubes; aerated incubation tanks; spectrophotometric NH4 determination; O2 microsensors/Winkler titration</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Medium — sensor + logger ~$2–3K per node; multiple nodes for vertical + within-aggregation array</t>
+          <t>Medium — coring + incubation lab; standard chemistry</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Multi-season (hourly logging across farming cycle)</t>
+          <t>Multi-season (farming-cycle scale, 2–3 yr cohort)</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>Time-series; correlations between pH and DO; threshold-exceedance event extraction</t>
+          <t>Paired contrasts farm vs control; flux rate calculations from concentration change over incubation</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>No — Paywalled (BioOne / NSA)</t>
+          <t>No — Paywalled (Springer)</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -25380,12 +25425,7 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>https://doi.org/10.2983/035.038.0329</t>
-        </is>
-      </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>Captures the extreme acidification and hypoxia the animals actually experience within clumps, beyond ambient readings.</t>
+          <t>https://doi.org/10.1007/s10750-007-0683-9</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
@@ -25393,9 +25433,9 @@
           <t>Original list</t>
         </is>
       </c>
-      <c r="W120" s="9" t="inlineStr">
-        <is>
-          <t>3 — Partnership</t>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>2 — Researcher</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
@@ -25405,32 +25445,32 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>Water Quality</t>
+          <t>Water Quality, Habitat &amp; Biodiversity</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>WQ 1.2.1 — Inorganic chemistry (DO)</t>
+          <t>WQ 1.1.2 — Rate of denitrification (DIN-flux proxy), WQ 1.2.1 — Dissolved oxygen, H&amp;B 1.4.1 — Sediment biogeochemistry</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>Temperate Pacific</t>
+          <t>Temperate Mediterranean</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>Bay mussel (Mytilus trossulus)</t>
+          <t>Manila clam (Tapes / Ruditapes philippinarum)</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Raft / hanging rope</t>
+          <t>Bottom culture (seeded clam beds)</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>Single farm</t>
+          <t>Single bay</t>
         </is>
       </c>
       <c r="AE120" t="inlineStr">
@@ -25445,7 +25485,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>Water chemistry, In-situ sensors</t>
+          <t>Sediment sampling, Benthic flux incubation, Water chemistry</t>
         </is>
       </c>
       <c r="AH120" t="inlineStr">
@@ -25465,17 +25505,17 @@
       </c>
       <c r="AK120" s="16" t="inlineStr">
         <is>
-          <t>To characterise the pH and dissolved-oxygen conditions a raft mussel crop actually experiences, suspend water-quality sondes (logging temperature, salinity, pH, DO and chlorophyll) at more than one depth (for example 1 and 7 m) in the centre of the raft and log hourly over an extended period, calibrating monthly. To capture the microenvironment inside mussel clumps, embed a pH electrode and an oxygen probe in the centre of mesh bags of mussels hung beside the sondes. Test season and depth effects with two-way ANOVA (rank-transformed), and run a threshold/excursion analysis - counting sustained drops below critical pH or DO limits (for example two consecutive hours below a set threshold) and comparing their frequency and duration across season and depth. This captures both ambient conditions and the more extreme acidification and hypoxia excursions the animals endure within aggregations.</t>
+          <t>To track how benthic fluxes change over a clam-farming cycle, incubate intact sediment cores from a farmed experimental plot and a control at intervals from young stock to harvest, measuring dissolved-oxygen and ammonium fluxes across the sediment-water interface (spectrophotometric ammonium, oxygen by microsensor or Winkler). Compare farm against control fluxes through the cycle; this temporal trajectory complements the snapshot pathway measurements from companion studies at the same site.</t>
         </is>
       </c>
       <c r="AL120" s="17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="AM120" s="18" t="inlineStr">
         <is>
-          <t>george_2019</t>
+          <t>nizzoli_2007</t>
         </is>
       </c>
       <c r="AN120" s="19" t="n"/>
@@ -25483,75 +25523,75 @@
       <c r="AP120" s="19" t="n"/>
       <c r="AQ120" s="16" t="inlineStr">
         <is>
-          <t>Microscale pH &amp; Oxygen Inside Mussel Aggregations</t>
+          <t>Oxygen &amp; Ammonium Fluxes Over a Clam-Farming Cycle</t>
         </is>
       </c>
       <c r="AR120" s="16" t="inlineStr">
         <is>
-          <t>George, Matthew N; Andino, Jessie; Huie, Jonathan; Carrington, Emily</t>
+          <t>Nizzoli, Daniele; Bartoli, Marco; Viaroli, Pierluigi</t>
         </is>
       </c>
       <c r="AS120" s="16" t="inlineStr">
         <is>
-          <t>Sub-rule 1b narrow retention parallel to Fernández 2019 (R94): pH is not in the closed MEL indicator set, but DO (WQ 1.2.1) is robustly measured. The microscale in-aggregation deployment is an unusual and useful methodological contribution — embedding aggregation sensors among cultured mussels allows DO/pH at the site of physiological action rather than only at ambient sonde depth. Companion to Carrington's broader OA/mussel-attachment program. v1.4 log: pH stays off the indicator set; if reconsidered, this paper would upgrade to 2.1.x candidate.</t>
+          <t>Direct companion to R115 (Nizzoli 2006 MEPS, same site/group) and to v14 R66 (Nizzoli 2006 Aquaculture, N + P budget). Together these three papers form the Sacca di Goro Manila-clam-vs-Mediterranean-mussel benthic-N research program. Key value here: temporal trajectory of fluxes across the farming cycle, complementing the snapshot pathway-partitioning of the MEPS paper. Bartoli/Nizzoli/Viaroli are the canonical reference group for this biogeochemistry. | v1.4 refinement: Added WQ 1.1.2 (denitrification, via DIN flux + N-cycling indicators); same site/group as R115 Nizzoli 2006 MEPS. WQ 1.2.1 narrowed to DO.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Nizzoli, D., et al.</t>
+          <t>Ogilvie, S. C., et al.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Oxygen and ammonium dynamics during a farming cycle of the bivalve Tapes philippinarum</t>
+          <t>Phytoplankton biomass associated with mussel farms in Beatrix Bay, New Zealand</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Hydrobiologia</t>
+          <t>Aquaculture</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>587</v>
+        <v>181</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>25-36</t>
+          <t>71-80</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>2007</v>
+        <v>2000</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Springer</t>
+          <t>Elsevier</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Benthic flux measurements of dissolved oxygen and ammonium across the water-sediment interface at a control site and a Manila-clam-farmed (Tapes / Ruditapes philippinarum) experimental site in Sacca di Goro (Po Delta, Italy), spanning the full farming cycle (young-to-harvest cohort). Companion to Nizzoli 2006 MEPS (R115, ¹⁵N-pairing emphasis) — same site, same group, but here the temporal axis is the farming-cycle progression rather than instantaneous pathway partitioning. Maps to MEL WQ 1.2.1 (DO + NH4 fluxes) and H&amp;B 1.4.1 (sediment biogeochemistry under clam farming).</t>
+          <t>Inside-vs-outside phytoplankton biomass survey at 4 green-shell mussel (Perna canaliculus) farm sites in Beatrix Bay, Marlborough Sounds, NZ, over a 13-month period. Chl-a measured throughout the water column; ambient (outside) NO3-N, NH4-N, and dissolved reactive phosphorus (DRP) measured. Found significant farm-driven phytoplankton biomass reduction during autumn–winter high-chl-a periods (peaks ~5 µg L⁻¹). Maps to MEL WQ 2.1.1 (chl-a) and WQ 1.2.1 (DIN, DRP).</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Protocol (paired benthic incubation across farming cycle)</t>
+          <t>Protocol (paired inside/outside farm chl-a + nutrient survey)</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Yes — paired farm-vs-control sediment-core incubations with standard solute-flux methodology.</t>
+          <t>Yes — replicated across 4 farms, full water column, 13-month coverage; standard chl-a + nutrient methodology.</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>No — laboratory core incubation is research-only.</t>
+          <t>Partial — sample collection is straightforward; lab analyses need partner.</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -25561,27 +25601,27 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>Plexiglas core tubes; aerated incubation tanks; spectrophotometric NH4 determination; O2 microsensors/Winkler titration</t>
+          <t>Niskin/pump sampling at multiple depths; fluorometer/spectrophotometer for chl-a; autoanalyser for DIN/DRP</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Medium — coring + incubation lab; standard chemistry</t>
+          <t>Low–Medium</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Multi-season (farming-cycle scale, 2–3 yr cohort)</t>
+          <t>Annual (13-month)</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>Paired contrasts farm vs control; flux rate calculations from concentration change over incubation</t>
+          <t>Paired inside-vs-outside contrasts; significance testing across farms and seasons</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>No — Paywalled (Springer)</t>
+          <t>No — Paywalled (Elsevier)</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -25591,7 +25631,7 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s10750-007-0683-9</t>
+          <t>https://doi.org/10.1016/S0044-8486(99)00219-7</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
@@ -25599,9 +25639,9 @@
           <t>Original list</t>
         </is>
       </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>2 — Researcher</t>
+      <c r="W121" s="9" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
@@ -25611,32 +25651,32 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>Water Quality, Habitat &amp; Biodiversity</t>
+          <t>Water Quality</t>
         </is>
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>WQ 1.1.2 — Rate of denitrification (DIN-flux proxy), WQ 1.2.1 — Dissolved oxygen, H&amp;B 1.4.1 — Sediment biogeochemistry</t>
+          <t>WQ 2.1.1 — Chlorophyll-a</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>Temperate Mediterranean</t>
+          <t>Temperate Pacific</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>Manila clam (Tapes / Ruditapes philippinarum)</t>
+          <t>Green-shell mussel (Perna canaliculus)</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Bottom culture (seeded clam beds)</t>
+          <t>Longline / suspended</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr">
         <is>
-          <t>Single bay</t>
+          <t>Multi-site (4 farms)</t>
         </is>
       </c>
       <c r="AE121" t="inlineStr">
@@ -25651,7 +25691,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>Sediment sampling, Benthic flux incubation, Water chemistry</t>
+          <t>Water chemistry, Plankton sampling</t>
         </is>
       </c>
       <c r="AH121" t="inlineStr">
@@ -25671,17 +25711,17 @@
       </c>
       <c r="AK121" s="16" t="inlineStr">
         <is>
-          <t>To track how benthic fluxes change over a clam-farming cycle, incubate intact sediment cores from a farmed experimental plot and a control at intervals from young stock to harvest, measuring dissolved-oxygen and ammonium fluxes across the sediment-water interface (spectrophotometric ammonium, oxygen by microsensor or Winkler). Compare farm against control fluxes through the cycle; this temporal trajectory complements the snapshot pathway measurements from companion studies at the same site.</t>
+          <t>To detect chlorophyll-a depletion by a mussel farm, profile chlorophyll fluorescence inside and just outside the farm and check whether it varies over the tidal cycle. Moor a CTD with a fluorometer on a longline at mid-depth and log fluorescence at short intervals over several tidal cycles (with a bottom-mounted current profiler for the tide), and on repeat surveys profile chlorophyll through the water column at randomly chosen on-farm stations, each paired with an outside station at equal distance from shore. Calibrate the fluorometer against water samples analysed for chlorophyll-a (90% acetone extraction, laboratory fluorometer), building a monthly conversion regression. Monitor ambient chlorophyll and dissolved nutrients (nitrate plus nitrite, reactive phosphorus, ammonium on an autoanalyser) outside the farm with an integrated tube sampler, and compare inside versus outside to quantify the depletion signal.</t>
         </is>
       </c>
       <c r="AL121" s="17" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AM121" s="18" t="inlineStr">
         <is>
-          <t>nizzoli_2007</t>
+          <t>ogilvie_2000</t>
         </is>
       </c>
       <c r="AN121" s="19" t="n"/>
@@ -25689,75 +25729,75 @@
       <c r="AP121" s="19" t="n"/>
       <c r="AQ121" s="16" t="inlineStr">
         <is>
-          <t>Oxygen &amp; Ammonium Fluxes Over a Clam-Farming Cycle</t>
+          <t>Chlorophyll Depletion by a Mussel Farm (Inside-vs-Outside Profiling)</t>
         </is>
       </c>
       <c r="AR121" s="16" t="inlineStr">
         <is>
-          <t>Nizzoli, Daniele; Bartoli, Marco; Viaroli, Pierluigi</t>
+          <t>Ogilvie, Shaun C; Ross, Alex H; Schiel, David R</t>
         </is>
       </c>
       <c r="AS121" s="16" t="inlineStr">
         <is>
-          <t>Direct companion to R115 (Nizzoli 2006 MEPS, same site/group) and to v14 R66 (Nizzoli 2006 Aquaculture, N + P budget). Together these three papers form the Sacca di Goro Manila-clam-vs-Mediterranean-mussel benthic-N research program. Key value here: temporal trajectory of fluxes across the farming cycle, complementing the snapshot pathway-partitioning of the MEPS paper. Bartoli/Nizzoli/Viaroli are the canonical reference group for this biogeochemistry. | v1.4 refinement: Added WQ 1.1.2 (denitrification, via DIN flux + N-cycling indicators); same site/group as R115 Nizzoli 2006 MEPS. WQ 1.2.1 narrowed to DO.</t>
+          <t>Foundational green-shell-mussel-vs-phytoplankton paper for the Marlborough Sounds — the global centre of P. canaliculus aquaculture. Heavily cited by NZ DOC mussel-farming impact reviews. Companion to Ogilvie 2003 (in-situ enclosure experiments at same site) and Inglis et al. 2000 (carrying-capacity context). Phytoplankton depletion within farm boundaries shown to be season-dependent — important methodological insight for designing MEL chl-a baselines. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (paper measures DIN + DRP, not DO). Nutrients are not in v1.4 WQ 1.2.1 indicator scope.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Ogilvie, S. C., et al.</t>
+          <t>Muñiz, O., et al.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Phytoplankton biomass associated with mussel farms in Beatrix Bay, New Zealand</t>
+          <t>Annual cycle of phytoplankton community through the water column: Study applied to the implementation of bivalve offshore aquaculture in the southeastern Bay of Biscay</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Aquaculture</t>
+          <t>Oceanologia</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>181</v>
+        <v>61</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>71-80</t>
+          <t>1-15</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>2000</v>
+        <v>2019</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Elsevier</t>
+          <t>Institute of Oceanology, Polish Academy of Sciences (Elsevier)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Inside-vs-outside phytoplankton biomass survey at 4 green-shell mussel (Perna canaliculus) farm sites in Beatrix Bay, Marlborough Sounds, NZ, over a 13-month period. Chl-a measured throughout the water column; ambient (outside) NO3-N, NH4-N, and dissolved reactive phosphorus (DRP) measured. Found significant farm-driven phytoplankton biomass reduction during autumn–winter high-chl-a periods (peaks ~5 µg L⁻¹). Maps to MEL WQ 2.1.1 (chl-a) and WQ 1.2.1 (DIN, DRP).</t>
+          <t>Pre-implementation baseline survey of phytoplankton community + WQ across 3 water-column depths (3, 17, 33 m) at an experimental offshore bivalve culture area off the Basque coast (SE Bay of Biscay), May 2014 – June 2015. Measured: phytoplankton composition (194 taxa), abundance, biomass, size-fractionated chl-a, nutrients (nitrate, silicate dominant), optical + hydrographic conditions. Found total chl-a low (~0.6 µg L⁻¹ avg); diatoms 35% of taxa with highest biomass; haptophytes dominant in cell abundance. Maps to MEL WQ 2.1.1 (chl-a + phytoplankton biomass), WQ 2.1.2 (community composition), WQ 1.2.1 (nutrients).</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Protocol (paired inside/outside farm chl-a + nutrient survey)</t>
+          <t>Protocol (multi-depth annual phytoplankton + WQ baseline)</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Yes — replicated across 4 farms, full water column, 13-month coverage; standard chl-a + nutrient methodology.</t>
+          <t>Yes — 13-month, 3-depth coverage; standard taxonomic + WQ methods; size-fractionated chl-a is a robust addition.</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Partial — sample collection is straightforward; lab analyses need partner.</t>
+          <t>Partial — water sampling straightforward; phytoplankton taxonomy + size fractionation require specialist lab.</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -25767,37 +25807,42 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Niskin/pump sampling at multiple depths; fluorometer/spectrophotometer for chl-a; autoanalyser for DIN/DRP</t>
+          <t>Niskin at multiple depths; fluorometer; size-fractionated chl-a filtration; phytoplankton microscopy + counting chambers; CTD</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Low–Medium</t>
+          <t>Medium — multi-depth sampling + taxonomic lab</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Annual (13-month)</t>
+          <t>Annual (13-month, monthly cruises)</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>Paired inside-vs-outside contrasts; significance testing across farms and seasons</t>
+          <t>Multivariate community analysis; environmental-variable correlation</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>No — Paywalled (Elsevier)</t>
+          <t>Yes — Open access (Oceanologia / Elsevier)</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>Abstract + Methods (fetched)</t>
+          <t>Full PDF</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/S0044-8486(99)00219-7</t>
+          <t>https://doi.org/10.1016/j.oceano.2018.08.001</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>A pre-development baseline template - establishes phytoplankton and water-quality conditions before a farm is built.</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
@@ -25822,27 +25867,27 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>WQ 2.1.1 — Chlorophyll-a</t>
+          <t>WQ 2.1.1 — Chlorophyll-a (size-fractionated), WQ 2.1.2 — Microorganism / plankton community</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>Temperate Pacific</t>
+          <t>Temperate Atlantic</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>Green-shell mussel (Perna canaliculus)</t>
+          <t>Multi-species / mixed (offshore experimental area)</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Longline / suspended</t>
+          <t>Longline / suspended (offshore)</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr">
         <is>
-          <t>Multi-site (4 farms)</t>
+          <t>Single farm (experimental)</t>
         </is>
       </c>
       <c r="AE122" t="inlineStr">
@@ -25852,7 +25897,7 @@
       </c>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>Monoculture</t>
+          <t>Monoculture (planned)</t>
         </is>
       </c>
       <c r="AG122" t="inlineStr">
@@ -25867,103 +25912,93 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Shallow nearshore (2–10 m)</t>
+          <t>Offshore (deeper) (3–33 m water column)</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>Sheltered</t>
-        </is>
-      </c>
-      <c r="AK122" s="16" t="inlineStr">
-        <is>
-          <t>To detect chlorophyll-a depletion by a mussel farm, profile chlorophyll fluorescence inside and just outside the farm and check whether it varies over the tidal cycle. Moor a CTD with a fluorometer on a longline at mid-depth and log fluorescence at short intervals over several tidal cycles (with a bottom-mounted current profiler for the tide), and on repeat surveys profile chlorophyll through the water column at randomly chosen on-farm stations, each paired with an outside station at equal distance from shore. Calibrate the fluorometer against water samples analysed for chlorophyll-a (90% acetone extraction, laboratory fluorometer), building a monthly conversion regression. Monitor ambient chlorophyll and dissolved nutrients (nitrate plus nitrite, reactive phosphorus, ammonium on an autoanalyser) outside the farm with an integrated tube sampler, and compare inside versus outside to quantify the depletion signal.</t>
-        </is>
-      </c>
-      <c r="AL122" s="17" t="inlineStr">
+          <t>Exposed (offshore Bay of Biscay)</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>To characterise the phytoplankton community and water-column conditions at a candidate offshore bivalve site through a full annual cycle, sample at a fixed station just outside the (experimental) farm. Twice a month take a CTD cast recording temperature, salinity, chlorophyll-a fluorescence and photosynthetically-active radiation at every metre plus a Secchi reading, and monthly collect water with Niskin bottles for inorganic nutrients (ammonium, nitrite, nitrate, silicate, phosphate on a continuous-flow autoanalyser) and for size-fractionated chlorophyll-a by sequential filtration (&lt;3, 3-20 and &gt;20 um - pico-, nano- and microphytoplankton). Identify and count phytoplankton at several depths (for example surface, mid and near-bottom) from Lugol's-preserved samples by the Utermohl method, converting to cell concentration and to carbon biomass via biovolume. Derive the light-extinction coefficient and photic-zone depth from the PAR profile, and relate the community to the environment with correlation matrices and ordination (removing rare taxa and applying a multiple-comparison correction) to define the seasonal food-supply and hydrographic envelope for siting.</t>
+        </is>
+      </c>
+      <c r="AL122" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
       <c r="AM122" s="18" t="inlineStr">
         <is>
-          <t>ogilvie_2000</t>
+          <t>muniz_2019</t>
         </is>
       </c>
       <c r="AN122" s="19" t="n"/>
       <c r="AO122" s="19" t="n"/>
       <c r="AP122" s="19" t="n"/>
-      <c r="AQ122" s="16" t="inlineStr">
-        <is>
-          <t>Chlorophyll Depletion by a Mussel Farm (Inside-vs-Outside Profiling)</t>
-        </is>
-      </c>
       <c r="AR122" s="16" t="inlineStr">
         <is>
-          <t>Ogilvie, Shaun C; Ross, Alex H; Schiel, David R</t>
+          <t>Muñiz, Oihane; Revilla, Marta; Rodríguez, José Germán; Laza-Martínez, Aitor; Fontán, Almudena</t>
         </is>
       </c>
       <c r="AS122" s="16" t="inlineStr">
         <is>
-          <t>Foundational green-shell-mussel-vs-phytoplankton paper for the Marlborough Sounds — the global centre of P. canaliculus aquaculture. Heavily cited by NZ DOC mussel-farming impact reviews. Companion to Ogilvie 2003 (in-situ enclosure experiments at same site) and Inglis et al. 2000 (carrying-capacity context). Phytoplankton depletion within farm boundaries shown to be season-dependent — important methodological insight for designing MEL chl-a baselines. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (paper measures DIN + DRP, not DO). Nutrients are not in v1.4 WQ 1.2.1 indicator scope.</t>
+          <t>Pre-development baseline paper — establishes phytoplankton + WQ conditions BEFORE bivalve farm implementation on the Basque coast. Useful template for MEL practitioners designing baseline campaigns. Companion to Muñiz et al. 2017/2018 toxic-phytoplankton evaluations and Bilbao 2020 inshore study. Methodologically clean baseline that future post-implementation surveys can compare against. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (nutrients + chl-a + phytoplankton community measured; no DO). | v38: filled at High from pasted Methods (Muniz); Source Read set to Full PDF; DOI corrected to paper's own 10.1016/j.oceano.2018.08.001 (prior 2018.07.001).</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Muñiz, O., et al.</t>
+          <t>Taylor, D., et al.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Annual cycle of phytoplankton community through the water column: Study applied to the implementation of bivalve offshore aquaculture in the southeastern Bay of Biscay</t>
+          <t>Quantifying bivalve phytoplankton depletion in a eutrophic system: an integrated approach</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Oceanologia</t>
+          <t>Limnology and Oceanography</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>61</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+        <v>69</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>1-15</t>
+          <t>2436-2452</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Institute of Oceanology, Polish Academy of Sciences (Elsevier)</t>
+          <t>Wiley (ASLO)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Pre-implementation baseline survey of phytoplankton community + WQ across 3 water-column depths (3, 17, 33 m) at an experimental offshore bivalve culture area off the Basque coast (SE Bay of Biscay), May 2014 – June 2015. Measured: phytoplankton composition (194 taxa), abundance, biomass, size-fractionated chl-a, nutrients (nitrate, silicate dominant), optical + hydrographic conditions. Found total chl-a low (~0.6 µg L⁻¹ avg); diatoms 35% of taxa with highest biomass; haptophytes dominant in cell abundance. Maps to MEL WQ 2.1.1 (chl-a + phytoplankton biomass), WQ 2.1.2 (community composition), WQ 1.2.1 (nutrients).</t>
+          <t>Multi-scale integrated phytoplankton-depletion assessment at a large 5-unit mussel farm in Venø Sund (19.26 km², 4–6 m depth) within Limfjorden (Denmark), an eutrophic, microtidal (0.2 m prism), brackish (22–33 PSU) sound. Three measurement scales: (i) MICRO — pulse-shape flow cytometry (PSFC) for phytoplankton community composition; (ii) MESO — fixed mooring stations (high temporal), chl-a synoptic transect surveys (high spatial), conventional CTD/discrete profiling, and a preliminary aerial-drone survey method; (iii) MACRO — optical satellite remote sensing + spatial analyses. Significant depletion (5–91% Chl-a reduction) detected with all methods, mixing gradients extending hundreds of metres beyond the farm. Maps to MEL WQ 2.1.1 (chl-a, phytoplankton size structure) and WQ 2.1.2 (phytoplankton community).</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Protocol (multi-depth annual phytoplankton + WQ baseline)</t>
+          <t>Protocol (integrated multi-method, multi-scale depletion survey)</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Yes — 13-month, 3-depth coverage; standard taxonomic + WQ methods; size-fractionated chl-a is a robust addition.</t>
+          <t>Yes — gold-standard integrated approach combining 4+ measurement modalities across spatial scales; depletion patterns robust across methods, validated against Limfjorden hydrodynamic model.</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Partial — water sampling straightforward; phytoplankton taxonomy + size fractionation require specialist lab.</t>
+          <t>No — multi-modality integration is research-only.</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -25973,42 +26008,42 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>Niskin at multiple depths; fluorometer; size-fractionated chl-a filtration; phytoplankton microscopy + counting chambers; CTD</t>
+          <t>CytoSense pulse-shape flow cytometer; CTD with chl-a + Secchi; mooring station array; aerial drone with multispectral / hyperspectral; Sentinel-2/3 satellite imagery; FlexSem Limfjorden hydrodynamic model (link to companion paper R110 Maar 2024)</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Medium — multi-depth sampling + taxonomic lab</t>
+          <t>High — multiple specialised platforms across scales</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Annual (13-month, monthly cruises)</t>
+          <t>Multi-season campaign</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>Multivariate community analysis; environmental-variable correlation</t>
+          <t>Cross-method consistency analysis; spatial mapping of depletion halo; correlation of depletion magnitude with biomass loads, ambient conditions, and hydrodynamic regimes</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>Yes — Open access (Oceanologia / Elsevier)</t>
+          <t>Yes — Open access (Wiley-ASLO CC BY-NC-ND)</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>Abstract + Methods (fetched)</t>
+          <t>Full PDF</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.oceano.2018.07.001</t>
+          <t>https://doi.org/10.1002/lno.12680</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>A pre-development baseline template - establishes phytoplankton and water-quality conditions before a farm is built.</t>
+          <t>Agreement across independent methods (satellite, flow-cytometry, mooring, survey) is what makes a farm-scale depletion signal credible.</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
@@ -26016,9 +26051,9 @@
           <t>Original list</t>
         </is>
       </c>
-      <c r="W123" s="9" t="inlineStr">
-        <is>
-          <t>3 — Partnership</t>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>2 — Researcher</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
@@ -26033,7 +26068,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>WQ 2.1.1 — Chlorophyll-a (size-fractionated), WQ 2.1.2 — Microorganism / plankton community</t>
+          <t>WQ 2.1.1 — Chlorophyll-a, WQ 2.1.2 — Microorganisms</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -26043,32 +26078,32 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>Multi-species / mixed (offshore experimental area)</t>
+          <t>Blue mussel (Mytilus edulis)</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Longline / suspended (offshore)</t>
+          <t>Longline / suspended</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>Single farm (experimental)</t>
+          <t>Single farm (large, 5-unit)</t>
         </is>
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>Variable / seasonal</t>
+          <t>Variable / seasonal (eutrophic)</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
         <is>
-          <t>Monoculture (planned)</t>
+          <t>Monoculture</t>
         </is>
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>Water chemistry, Plankton sampling</t>
+          <t>Water chemistry, Plankton sampling, Remote sensing, In-situ sensors, Modelling</t>
         </is>
       </c>
       <c r="AH123" t="inlineStr">
@@ -26078,83 +26113,103 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>Offshore (deeper) (3–33 m water column)</t>
+          <t>Shallow nearshore (2–10 m)</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>Exposed (offshore Bay of Biscay)</t>
+          <t>Sheltered (microtidal)</t>
+        </is>
+      </c>
+      <c r="AK123" s="16" t="inlineStr">
+        <is>
+          <t>To measure phytoplankton depletion at a large suspended mussel farm across scales, combine methods: pulse-shape flow cytometry on water samples for phytoplankton community composition; CTD casts with chlorophyll and Secchi plus a mooring array for continuous in-farm and reference conditions; a synoptic vessel survey mapping the chlorophyll halo; and drone or satellite (Sentinel) imagery for the surface chlorophyll field. Cross-check depletion across methods and validate against a hydrodynamic model; agreement across independent modalities is what makes a farm-scale depletion signal credible.</t>
+        </is>
+      </c>
+      <c r="AL123" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
       <c r="AM123" s="18" t="inlineStr">
         <is>
-          <t>muniz_2019</t>
+          <t>taylor_2024</t>
         </is>
       </c>
       <c r="AN123" s="19" t="n"/>
       <c r="AO123" s="19" t="n"/>
       <c r="AP123" s="19" t="n"/>
+      <c r="AQ123" s="16" t="inlineStr">
+        <is>
+          <t>Multi-Method Phytoplankton-Depletion Measurement at a Large Mussel Farm</t>
+        </is>
+      </c>
       <c r="AR123" s="16" t="inlineStr">
         <is>
-          <t>Muñiz, Oihane; Revilla, Marta; Rodríguez, José Germán; Laza-Martínez, Aitor; Fontán, Almudena</t>
+          <t>Taylor, Daniel; Jakobsen, Hans; Lyngsgaard, Maren Moltke; Darecki, Mirosław; Werther, Mortimer; Maar, Marie; Saurel, Camille</t>
         </is>
       </c>
       <c r="AS123" s="16" t="inlineStr">
         <is>
-          <t>Pre-development baseline paper — establishes phytoplankton + WQ conditions BEFORE bivalve farm implementation on the Basque coast. Useful template for MEL practitioners designing baseline campaigns. Companion to Muñiz et al. 2017/2018 toxic-phytoplankton evaluations and Bilbao 2020 inshore study. Methodologically clean baseline that future post-implementation surveys can compare against. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (nutrients + chl-a + phytoplankton community measured; no DO).</t>
+          <t>Important multi-method integration paper for phytoplankton depletion — establishes that satellite RS, flow-cytometry, mooring, and synoptic survey all detect coherent farm-scale Chl-a depletion in a large mussel farm. Useful methodological template for designing MEL WQ 2.1.x assessments at large suspended-bivalve farms. Companion (same site, same group) to Maar 2024 (R110, climate-projection modelling at Limfjorden — Taylor is co-author there).</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Taylor, D., et al.</t>
+          <t>Cugier, P., et al.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Quantifying bivalve phytoplankton depletion in a eutrophic system: an integrated approach</t>
+          <t>Assessing the role of benthic filter feeders on phytoplankton production in a shellfish farming site: Mont Saint Michel Bay, France</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Limnology and Oceanography</t>
+          <t>Journal of Marine Systems</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>69</v>
+        <v>82</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2436-2452</t>
+          <t>21-34</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>2024</v>
+        <v>2010</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Wiley (ASLO)</t>
+          <t>Elsevier</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Multi-scale integrated phytoplankton-depletion assessment at a large 5-unit mussel farm in Venø Sund (19.26 km², 4–6 m depth) within Limfjorden (Denmark), an eutrophic, microtidal (0.2 m prism), brackish (22–33 PSU) sound. Three measurement scales: (i) MICRO — pulse-shape flow cytometry (PSFC) for phytoplankton community composition; (ii) MESO — fixed mooring stations (high temporal), chl-a synoptic transect surveys (high spatial), conventional CTD/discrete profiling, and a preliminary aerial-drone survey method; (iii) MACRO — optical satellite remote sensing + spatial analyses. Significant depletion (5–91% Chl-a reduction) detected with all methods, mixing gradients extending hundreds of metres beyond the farm. Maps to MEL WQ 2.1.1 (chl-a, phytoplankton size structure) and WQ 2.1.2 (phytoplankton community).</t>
+          <t>Coupled ecological model of Mont Saint Michel Bay (English Channel, France): 2D hydro-sedimentary model + primary production model + filter-feeder filtration model. Filter-feeder compartment includes 3 cultivated species (Mytilus edulis, Crassostrea gigas, Ostrea edulis), 1 invasive (Crepidula fornicata), and 8 wild natives (Abra alba, Cerastoderma edule, etc.). Biodeposits + mineralisation feedback included. Outputs: Chl-a, primary production, partitioned filter-feeder pressure. Key finding: wild species + invasive Crepidula are stronger controllers of phytoplankton biomass than cultivated species. Maps to MEL WQ 2.1.1 (chl-a, modelled), WQ 1.2.1 (nutrients in model).</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Protocol (integrated multi-method, multi-scale depletion survey)</t>
+          <t>Reference (model framework — coupled hydro-bio model)</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Yes — gold-standard integrated approach combining 4+ measurement modalities across spatial scales; depletion patterns robust across methods, validated against Limfjorden hydrodynamic model.</t>
+          <t>Yes — model validated against in-situ chl-a + nutrient data; partitions filter-feeder pressure by species/compartment.</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>No — multi-modality integration is research-only.</t>
+          <t>No — model development is research-only.</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -26164,42 +26219,42 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>CytoSense pulse-shape flow cytometer; CTD with chl-a + Secchi; mooring station array; aerial drone with multispectral / hyperspectral; Sentinel-2/3 satellite imagery; FlexSem Limfjorden hydrodynamic model (link to companion paper R110 Maar 2024)</t>
+          <t>Coupled 2D hydro-sedimentary + primary-production + filter-feeder filtration model; biodeposit + mineralisation modules</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>High — multiple specialised platforms across scales</t>
+          <t>High — modelling effort with calibration data requirements</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Multi-season campaign</t>
+          <t>Annual / multi-year simulation</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>Cross-method consistency analysis; spatial mapping of depletion halo; correlation of depletion magnitude with biomass loads, ambient conditions, and hydrodynamic regimes</t>
+          <t>Scenario analysis (filter-feeder compartment partitioning); steady-state + dynamic outputs</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>Yes — Open access (Wiley-ASLO CC BY-NC-ND)</t>
+          <t>Yes — Open access via HAL (Ifremer); journal article paywalled</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>Full PDF</t>
+          <t>Abstract + Methods (fetched)</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/lno.12680</t>
+          <t>https://doi.org/10.1016/j.jmarsys.2010.02.013</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>Agreement across independent methods (satellite, flow-cytometry, mooring, survey) is what makes a farm-scale depletion signal credible.</t>
+          <t>Where wild or invasive filter-feeders are abundant, attributing depletion to aquaculture requires disentangling their contribution.</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
@@ -26224,7 +26279,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>WQ 2.1.1 — Chlorophyll-a, WQ 2.1.2 — Microorganisms</t>
+          <t>WQ 1.3.1 — Rate of water filtration (filter-feeder filtration model), WQ 2.1.1 — Chlorophyll-a</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -26234,32 +26289,32 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>Blue mussel (Mytilus edulis)</t>
+          <t>Blue mussel (Mytilus edulis), Pacific oyster (Crassostrea / Magallana gigas), European flat oyster (Ostrea edulis)</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Longline / suspended</t>
+          <t>Mixed (longline mussel + intertidal table oyster + bottom)</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>Single farm (large, 5-unit)</t>
+          <t>Bay-wide / system-scale (modelled)</t>
         </is>
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>Variable / seasonal (eutrophic)</t>
+          <t>Variable / seasonal</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
         <is>
-          <t>Monoculture</t>
+          <t>Monoculture (multiple)</t>
         </is>
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>Water chemistry, Plankton sampling, Remote sensing, In-situ sensors, Modelling</t>
+          <t>Modelling</t>
         </is>
       </c>
       <c r="AH124" t="inlineStr">
@@ -26269,27 +26324,27 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>Shallow nearshore (2–10 m)</t>
+          <t>Intertidal / very shallow (&lt; 2 m)</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>Sheltered (microtidal)</t>
+          <t>Mixed exposure</t>
         </is>
       </c>
       <c r="AK124" s="16" t="inlineStr">
         <is>
-          <t>To measure phytoplankton depletion at a large suspended mussel farm across scales, combine methods: pulse-shape flow cytometry on water samples for phytoplankton community composition; CTD casts with chlorophyll and Secchi plus a mooring array for continuous in-farm and reference conditions; a synoptic vessel survey mapping the chlorophyll halo; and drone or satellite (Sentinel) imagery for the surface chlorophyll field. Cross-check depletion across methods and validate against a hydrodynamic model; agreement across independent modalities is what makes a farm-scale depletion signal credible.</t>
+          <t>This is a coupled 2D hydro-sedimentary, primary-production and filter-feeder model of a major shellfish bay that partitions grazing pressure among cultivated species, an invasive species and wild natives, validated against in-situ chlorophyll and nutrients. Its lesson for monitoring: where wild and invasive filter feeders are abundant, attributing chlorophyll depletion specifically to aquaculture requires disentangling their contributions. Use it as a model reference for carrying-capacity and attribution questions.</t>
         </is>
       </c>
       <c r="AL124" s="17" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Ref</t>
         </is>
       </c>
       <c r="AM124" s="18" t="inlineStr">
         <is>
-          <t>taylor_2024</t>
+          <t>cugier_2010</t>
         </is>
       </c>
       <c r="AN124" s="19" t="n"/>
@@ -26297,51 +26352,46 @@
       <c r="AP124" s="19" t="n"/>
       <c r="AQ124" s="16" t="inlineStr">
         <is>
-          <t>Multi-Method Phytoplankton-Depletion Measurement at a Large Mussel Farm</t>
+          <t>Coupled Model of Filter-Feeder Effects on Phytoplankton (Reference)</t>
         </is>
       </c>
       <c r="AR124" s="16" t="inlineStr">
         <is>
-          <t>Taylor, Daniel; Jakobsen, Hans; Lyngsgaard, Maren Moltke; Darecki, Mirosław; Werther, Mortimer; Maar, Marie; Saurel, Camille</t>
+          <t>Cugier, Philippe; Struski, Caroline; Blanchard, Michel; Mazurié, Joseph; Pouvreau, Stéphane; Olivier, Frédéric; Trigui, Jihane R; Thiébaut, Eric</t>
         </is>
       </c>
       <c r="AS124" s="16" t="inlineStr">
         <is>
-          <t>Important multi-method integration paper for phytoplankton depletion — establishes that satellite RS, flow-cytometry, mooring, and synoptic survey all detect coherent farm-scale Chl-a depletion in a large mussel farm. Useful methodological template for designing MEL WQ 2.1.x assessments at large suspended-bivalve farms. Companion (same site, same group) to Maar 2024 (R110, climate-projection modelling at Limfjorden — Taylor is co-author there).</t>
+          <t>Foundational coupled-model paper for the role of cultivated AND wild filter-feeders in shaping phytoplankton biomass at a major shellfish-farming site. Methodologically important conclusion for MEL: when wild/invasive filter-feeders are abundant, attributing chl-a depletion specifically to aquaculture requires careful disentangling. Companion to Cugier 2005 (same bay, nutrient-only model) and later applied to Bourgneuf Bay and Pertuis Charentais. | v1.4 refinement: Added WQ 1.3.1 (Rate of water filtration) — paper's central methodology is a filter-feeder filtration model with partitioned per-species filtration pressure on phytoplankton biomass; v1.4 added this indicator. WQ 1.2.1 removed (model does not produce a DO output).</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Cugier, P., et al.</t>
+          <t>Jiang, Z., et al.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Assessing the role of benthic filter feeders on phytoplankton production in a shellfish farming site: Mont Saint Michel Bay, France</t>
+          <t>Oyster farming control on phytoplankton bloom promoted by thermal discharge from a power plant in a eutrophic, semi-enclosed bay</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Journal of Marine Systems</t>
+          <t>Water Research</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>82</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
+        <v>159</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>21-34</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>2010</v>
+        <v>2019</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -26350,22 +26400,22 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Coupled ecological model of Mont Saint Michel Bay (English Channel, France): 2D hydro-sedimentary model + primary production model + filter-feeder filtration model. Filter-feeder compartment includes 3 cultivated species (Mytilus edulis, Crassostrea gigas, Ostrea edulis), 1 invasive (Crepidula fornicata), and 8 wild natives (Abra alba, Cerastoderma edule, etc.). Biodeposits + mineralisation feedback included. Outputs: Chl-a, primary production, partitioned filter-feeder pressure. Key finding: wild species + invasive Crepidula are stronger controllers of phytoplankton biomass than cultivated species. Maps to MEL WQ 2.1.1 (chl-a, modelled), WQ 1.2.1 (nutrients in model).</t>
+          <t>Ten cruises (2009–2015) across paired old oyster farm (OOF), new oyster farm (NOF) and control areas (CA) adjacent to the Ninghai Power Plant (NPP, 82.5 m³ s⁻¹ thermal discharge, +1°C envelope) in the upper section of Xiangshan Bay (XSB, ~60 km long, water-residence ~80 d), China. Sampled surface (0.5 m) + bottom (0.5 m above bed). Measured phytoplankton community (chl-a, abundance, diversity, dominant species, size structure) and physico-chemical (T, transparency, suspended solids, DO, nutrients, organic carbon). Demonstrated thermal discharge induced severe winter algal blooms; oyster (Crassostrea plicatula) farming reduced phytoplankton abundance 26.3%, chl-a 28.3%, increased Shannon diversity 38.3%, Pielou's evenness 28.8%, reduced SS 12.2%, TOC 18.4%, DIN 1.5%, P 3.7%. Maps to MEL WQ 2.1.1 (chl-a, phytoplankton biomass), WQ 2.1.2 (community composition / microorganisms), WQ 1.2.1 (T, DO, nutrients, suspended solids, OC).</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Reference (model framework — coupled hydro-bio model)</t>
+          <t>Protocol (multi-year paired farm-vs-control sampling, full WQ + phytoplankton suite)</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Yes — model validated against in-situ chl-a + nutrient data; partitions filter-feeder pressure by species/compartment.</t>
+          <t>Yes — 10 cruises over 7 years; paired design (old + new OF vs CA); two power-plant operational phases (with thermal discharge 2009–2015); rich measurement suite.</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>No — model development is research-only.</t>
+          <t>Partial — water + phytoplankton sampling feasible for trained farmers; identification + lab analyses need partner.</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -26375,42 +26425,42 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Coupled 2D hydro-sedimentary + primary-production + filter-feeder filtration model; biodeposit + mineralisation modules</t>
+          <t>Niskin / pump sampler; CTD; fluorometer; phytoplankton microscopy + counting; autoanalyser for nutrients; TOC analyser</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>High — modelling effort with calibration data requirements</t>
+          <t>Medium — multi-cruise institutional campaign</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Annual / multi-year simulation</t>
+          <t>Multi-year (10 cruises 2009–2015)</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>Scenario analysis (filter-feeder compartment partitioning); steady-state + dynamic outputs</t>
+          <t>ANOSIM / SIMPER for phytoplankton community contrast OF vs CA; species richness, Shannon-Wiener diversity, Pielou's evenness; percent change in physico-chemical variables</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>Yes — Open access via HAL (Ifremer); journal article paywalled</t>
+          <t>No — Paywalled (Elsevier / Water Research)</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>Abstract + Methods (fetched)</t>
+          <t>Full PDF</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jmarsys.2010.02.013</t>
+          <t>https://doi.org/10.1016/j.watres.2019.04.023</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>Where wild or invasive filter-feeders are abundant, attributing depletion to aquaculture requires disentangling their contribution.</t>
+          <t>Here oyster farming helped mitigate thermal-discharge algal blooms; the old-vs-new-farm design controls for the thermal signal.</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
@@ -26418,9 +26468,9 @@
           <t>Original list</t>
         </is>
       </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>2 — Researcher</t>
+      <c r="W125" s="9" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
@@ -26435,42 +26485,42 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>WQ 1.3.1 — Rate of water filtration (filter-feeder filtration model), WQ 2.1.1 — Chlorophyll-a</t>
+          <t>WQ 1.2.1 — Dissolved oxygen, WQ 2.1.1 — Chlorophyll-a, WQ 2.1.2 — Microorganism / plankton community</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>Temperate Atlantic</t>
+          <t>Subtropical Pacific</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>Blue mussel (Mytilus edulis), Pacific oyster (Crassostrea / Magallana gigas), European flat oyster (Ostrea edulis)</t>
+          <t>Chinese pleated oyster (Crassostrea plicatula)</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Mixed (longline mussel + intertidal table oyster + bottom)</t>
+          <t>Raft / longline (oyster ropes on rafts)</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr">
         <is>
-          <t>Bay-wide / system-scale (modelled)</t>
+          <t>Single farm (paired OF + CA in same bay)</t>
         </is>
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>Variable / seasonal</t>
+          <t>Eutrophic / variable</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
         <is>
-          <t>Monoculture (multiple)</t>
+          <t>Monoculture (thermal-discharge confound)</t>
         </is>
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>Modelling</t>
+          <t>Water chemistry, Plankton sampling</t>
         </is>
       </c>
       <c r="AH125" t="inlineStr">
@@ -26480,27 +26530,27 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>Intertidal / very shallow (&lt; 2 m)</t>
+          <t>Shallow nearshore (2–10 m)</t>
         </is>
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>Mixed exposure</t>
+          <t>Sheltered</t>
         </is>
       </c>
       <c r="AK125" s="16" t="inlineStr">
         <is>
-          <t>This is a coupled 2D hydro-sedimentary, primary-production and filter-feeder model of a major shellfish bay that partitions grazing pressure among cultivated species, an invasive species and wild natives, validated against in-situ chlorophyll and nutrients. Its lesson for monitoring: where wild and invasive filter feeders are abundant, attributing chlorophyll depletion specifically to aquaculture requires disentangling their contributions. Use it as a model reference for carrying-capacity and attribution questions.</t>
+          <t>To attribute changes in phytoplankton biomass and community to an oyster farm, sample paired stations at the farm centre and in a control area a few hundred metres to about 1 km outside, at surface and bottom, repeated across seasons (ideally spanning years, and comparing an old and a relocated farm for causal weight). Collect water with Niskin bottles; measure DO by Winkler titration and transparency by Secchi, and take frozen samples for nutrients (0.45 um filtered), total organic carbon and suspended solids. Size-fractionate chlorophyll-a (&gt;20, 2-20, &lt;2 um) by sequential filtration and read on a fluorometer after acetone extraction, and measure pheopigments (chl-a degradation products) as a grazing indicator; settle and count phytoplankton (at least 300 units) under a microscope for richness, Shannon and Pielou indices. Compare farm versus control with two-way ANOVA (or Mann-Whitney) and ANOSIM on log-transformed Bray-Curtis data, and correlate the biomass reduction with environmental drivers.</t>
         </is>
       </c>
       <c r="AL125" s="17" t="inlineStr">
         <is>
-          <t>Ref</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AM125" s="18" t="inlineStr">
         <is>
-          <t>cugier_2010</t>
+          <t>jiang_2019</t>
         </is>
       </c>
       <c r="AN125" s="19" t="n"/>
@@ -26508,46 +26558,46 @@
       <c r="AP125" s="19" t="n"/>
       <c r="AQ125" s="16" t="inlineStr">
         <is>
-          <t>Coupled Model of Filter-Feeder Effects on Phytoplankton (Reference)</t>
+          <t>Attributing Phytoplankton Change to an Oyster Farm (Size-Fractionated)</t>
         </is>
       </c>
       <c r="AR125" s="16" t="inlineStr">
         <is>
-          <t>Cugier, Philippe; Struski, Caroline; Blanchard, Michel; Mazurié, Joseph; Pouvreau, Stéphane; Olivier, Frédéric; Trigui, Jihane R; Thiébaut, Eric</t>
+          <t>Jiang, Zhibing; Du, Ping; Liao, Yibo; Liu, Qiang; Chen, Quanzhen; Shou, Lu; Zeng, Jiangning; Chen, Jianfang</t>
         </is>
       </c>
       <c r="AS125" s="16" t="inlineStr">
         <is>
-          <t>Foundational coupled-model paper for the role of cultivated AND wild filter-feeders in shaping phytoplankton biomass at a major shellfish-farming site. Methodologically important conclusion for MEL: when wild/invasive filter-feeders are abundant, attributing chl-a depletion specifically to aquaculture requires careful disentangling. Companion to Cugier 2005 (same bay, nutrient-only model) and later applied to Bourgneuf Bay and Pertuis Charentais. | v1.4 refinement: Added WQ 1.3.1 (Rate of water filtration) — paper's central methodology is a filter-feeder filtration model with partitioned per-species filtration pressure on phytoplankton biomass; v1.4 added this indicator. WQ 1.2.1 removed (model does not produce a DO output).</t>
+          <t>Important real-world paper showing oyster farming as a mitigation tool for thermal-discharge-induced algal blooms in a eutrophic subtropical bay. Confounded by thermal-discharge factor but design (OF vs CA in same thermal envelope) controls for that. After culture-raft removal, no significant differences between former-OF and CA — direct evidence the effect is the farming activity itself. Companion to Jiang 2012 (v15 R43), Jiang 2016 (#38 = R128), Jiang 2019a/b further work. Strong reference for MEL practitioners thinking about bivalve farming as ecological-restoration intervention. | v1.4 refinement: WQ 1.2.1 narrowed to DO (paper lists oxygen among measured physico-chemical variables).</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Jiang, Z., et al.</t>
+          <t>Jiang, T., et al.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Oyster farming control on phytoplankton bloom promoted by thermal discharge from a power plant in a eutrophic, semi-enclosed bay</t>
+          <t>Size-dependent depletion and community disturbance of phytoplankton under intensive oyster mariculture based on HPLC pigment analysis in Daya Bay, South China Sea</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Water Research</t>
+          <t>Environmental Pollution</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>804-814</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -26556,22 +26606,22 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Ten cruises (2009–2015) across paired old oyster farm (OOF), new oyster farm (NOF) and control areas (CA) adjacent to the Ninghai Power Plant (NPP, 82.5 m³ s⁻¹ thermal discharge, +1°C envelope) in the upper section of Xiangshan Bay (XSB, ~60 km long, water-residence ~80 d), China. Sampled surface (0.5 m) + bottom (0.5 m above bed). Measured phytoplankton community (chl-a, abundance, diversity, dominant species, size structure) and physico-chemical (T, transparency, suspended solids, DO, nutrients, organic carbon). Demonstrated thermal discharge induced severe winter algal blooms; oyster (Crassostrea plicatula) farming reduced phytoplankton abundance 26.3%, chl-a 28.3%, increased Shannon diversity 38.3%, Pielou's evenness 28.8%, reduced SS 12.2%, TOC 18.4%, DIN 1.5%, P 3.7%. Maps to MEL WQ 2.1.1 (chl-a, phytoplankton biomass), WQ 2.1.2 (community composition / microorganisms), WQ 1.2.1 (T, DO, nutrients, suspended solids, OC).</t>
+          <t>14-month investigation in Daya Bay, South China Sea, comparing intensive-oyster-farming area to reference area using HPLC size-fractionated phytopigments (chl-a, fucoxanthin, peridinin, and other diagnostic pigments). Filtering effect of oysters on phytoplankton biomass quantified size-class by size-class: ~60% total chl-a reduction in farming area vs reference; depletion concentrated in micro-sized (&gt;20 µm) fractions; nano-sized (2.7–20 µm) less affected. Community disturbance documented via pigment-based community shifts. Maps to MEL WQ 2.1.1 (chl-a + size-fractionated), WQ 2.1.2 (community composition via pigments).</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Protocol (multi-year paired farm-vs-control sampling, full WQ + phytoplankton suite)</t>
+          <t>Protocol (HPLC size-fractionated phytopigment community + biomass analysis)</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Yes — 10 cruises over 7 years; paired design (old + new OF vs CA); two power-plant operational phases (with thermal discharge 2009–2015); rich measurement suite.</t>
+          <t>Yes — HPLC pigment chemotaxonomy is a robust, quantitative approach for community shifts; 14-month duration captures seasonal cycles.</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Partial — water + phytoplankton sampling feasible for trained farmers; identification + lab analyses need partner.</t>
+          <t>No — HPLC pigment analysis is research-only.</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -26581,42 +26631,42 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>Niskin / pump sampler; CTD; fluorometer; phytoplankton microscopy + counting; autoanalyser for nutrients; TOC analyser</t>
+          <t>Size-fractionation filtration (0.7, 2.7, 20 µm); HPLC for diagnostic pigments (chl-a, fucoxanthin, peridinin etc.)</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Medium — multi-cruise institutional campaign</t>
+          <t>Medium–High — HPLC partner lab + multi-month sampling</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Multi-year (10 cruises 2009–2015)</t>
+          <t>Annual / multi-season (14-month)</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>ANOSIM / SIMPER for phytoplankton community contrast OF vs CA; species richness, Shannon-Wiener diversity, Pielou's evenness; percent change in physico-chemical variables</t>
+          <t>ANOSIM / SIMPER for pigment community; size-class % change</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>No — Paywalled (Elsevier / Water Research)</t>
+          <t>No — Paywalled (Elsevier)</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>Full PDF</t>
+          <t>Abstract + Methods (fetched)</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.watres.2019.04.023</t>
+          <t>https://doi.org/10.1016/j.envpol.2016.07.058</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>Here oyster farming helped mitigate thermal-discharge algal blooms; the old-vs-new-farm design controls for the thermal signal.</t>
+          <t>Reveals size-selective grazing that a bulk chlorophyll measurement would miss.</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
@@ -26624,9 +26674,9 @@
           <t>Original list</t>
         </is>
       </c>
-      <c r="W126" s="9" t="inlineStr">
-        <is>
-          <t>3 — Partnership</t>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>2 — Researcher</t>
         </is>
       </c>
       <c r="X126" t="inlineStr">
@@ -26641,7 +26691,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>WQ 1.2.1 — Dissolved oxygen, WQ 2.1.1 — Chlorophyll-a, WQ 2.1.2 — Microorganism / plankton community</t>
+          <t>WQ 2.1.1 — Chlorophyll-a, WQ 2.1.2 — Microorganisms</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -26651,32 +26701,32 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>Chinese pleated oyster (Crassostrea plicatula)</t>
+          <t>Hong Kong oyster (Magallana hongkongensis) / Pacific oyster</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Raft / longline (oyster ropes on rafts)</t>
+          <t>Raft / longline (oyster rafts)</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr">
         <is>
-          <t>Single farm (paired OF + CA in same bay)</t>
+          <t>Single bay</t>
         </is>
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>Eutrophic / variable</t>
+          <t>Variable / seasonal</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
         <is>
-          <t>Monoculture (thermal-discharge confound)</t>
+          <t>Monoculture</t>
         </is>
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>Water chemistry, Plankton sampling</t>
+          <t>Plankton sampling, Pigment HPLC</t>
         </is>
       </c>
       <c r="AH126" t="inlineStr">
@@ -26696,17 +26746,17 @@
       </c>
       <c r="AK126" s="16" t="inlineStr">
         <is>
-          <t>To attribute changes in phytoplankton biomass and community to an oyster farm, sample paired stations at the farm centre and in a control area a few hundred metres to about 1 km outside, at surface and bottom, repeated across seasons (ideally spanning years, and comparing an old and a relocated farm for causal weight). Collect water with Niskin bottles; measure DO by Winkler titration and transparency by Secchi, and take frozen samples for nutrients (0.45 um filtered), total organic carbon and suspended solids. Size-fractionate chlorophyll-a (&gt;20, 2-20, &lt;2 um) by sequential filtration and read on a fluorometer after acetone extraction, and measure pheopigments (chl-a degradation products) as a grazing indicator; settle and count phytoplankton (at least 300 units) under a microscope for richness, Shannon and Pielou indices. Compare farm versus control with two-way ANOVA (or Mann-Whitney) and ANOSIM on log-transformed Bray-Curtis data, and correlate the biomass reduction with environmental drivers.</t>
+          <t>To fingerprint an oyster farm's effect on phytoplankton by size and type, sample a farmed area and a reference area over a full seasonal cycle, size-fractionate the water (for example through 20, 2.7 and 0.7 um) and analyse diagnostic pigments by HPLC (chlorophyll-a plus marker pigments such as fucoxanthin and peridinin). Compare pigment communities with ANOSIM/SIMPER and quantify chlorophyll reduction per size class; this reveals size-selective grazing that a bulk chlorophyll measurement would miss.</t>
         </is>
       </c>
       <c r="AL126" s="17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="AM126" s="18" t="inlineStr">
         <is>
-          <t>jiang_2019</t>
+          <t>jiang_2016</t>
         </is>
       </c>
       <c r="AN126" s="19" t="n"/>
@@ -26714,46 +26764,46 @@
       <c r="AP126" s="19" t="n"/>
       <c r="AQ126" s="16" t="inlineStr">
         <is>
-          <t>Attributing Phytoplankton Change to an Oyster Farm (Size-Fractionated)</t>
+          <t>Size-Selective Phytoplankton-Depletion Fingerprint (HPLC Pigments)</t>
         </is>
       </c>
       <c r="AR126" s="16" t="inlineStr">
         <is>
-          <t>Jiang, Zhibing; Du, Ping; Liao, Yibo; Liu, Qiang; Chen, Quanzhen; Shou, Lu; Zeng, Jiangning; Chen, Jianfang</t>
+          <t>Jiang, Tao; Chen, Feiyu; Yu, Zonghe; Lu, Lin; Wang, Zhaohui</t>
         </is>
       </c>
       <c r="AS126" s="16" t="inlineStr">
         <is>
-          <t>Important real-world paper showing oyster farming as a mitigation tool for thermal-discharge-induced algal blooms in a eutrophic subtropical bay. Confounded by thermal-discharge factor but design (OF vs CA in same thermal envelope) controls for that. After culture-raft removal, no significant differences between former-OF and CA — direct evidence the effect is the farming activity itself. Companion to Jiang 2012 (v15 R43), Jiang 2016 (#38 = R128), Jiang 2019a/b further work. Strong reference for MEL practitioners thinking about bivalve farming as ecological-restoration intervention. | v1.4 refinement: WQ 1.2.1 narrowed to DO (paper lists oxygen among measured physico-chemical variables).</t>
+          <t>Different Jiang from R43/R126 (Z-B Jiang group) — this is Tao Jiang's group, focused on South China Sea / Daya Bay. Methodologically important for showing size-selective grazing fingerprint in pigment data — useful for MEL practitioners designing chl-a indicator measurements where filtering signal must be distinguished from background community shifts. Sub-rule 1a-adjacent framing: HPLC pigment chemotaxonomy complements but does not replace tissue %N bioextraction.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Jiang, T., et al.</t>
+          <t>Rahman, M. A., et al.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Size-dependent depletion and community disturbance of phytoplankton under intensive oyster mariculture based on HPLC pigment analysis in Daya Bay, South China Sea</t>
+          <t>Analysis of the seasonal impact of three marine bivalves on seston particles in water column</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Environmental Pollution</t>
+          <t>Journal of Experimental Marine Biology and Ecology</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>219</v>
+        <v>522</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>804-814</t>
+          <t>151251</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -26762,22 +26812,22 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>14-month investigation in Daya Bay, South China Sea, comparing intensive-oyster-farming area to reference area using HPLC size-fractionated phytopigments (chl-a, fucoxanthin, peridinin, and other diagnostic pigments). Filtering effect of oysters on phytoplankton biomass quantified size-class by size-class: ~60% total chl-a reduction in farming area vs reference; depletion concentrated in micro-sized (&gt;20 µm) fractions; nano-sized (2.7–20 µm) less affected. Community disturbance documented via pigment-based community shifts. Maps to MEL WQ 2.1.1 (chl-a + size-fractionated), WQ 2.1.2 (community composition via pigments).</t>
+          <t>Comparative laboratory + field food-selectivity and clearance-rate study of three sympatric bivalves — Pacific oyster (Magallana / Crassostrea gigas), Mediterranean mussel (Mytilus galloprovincialis), and native mud cockle (Katelysia rhytiphora) — on natural seston particle assemblages from Coffin Bay (South Australia). Particles measured 4–14 µm range; capture efficiency higher for larger particles (8–14 µm); seasonal CE/CR variation. Findings: oyster + mussel utilise similar food (phytoplankton); cockles graze a broader range (including detritus + bacteria). Maps to MEL WQ 2.1.1 (seston / chl-a) and WQ 2.1.2 (microorganism / particle community composition).</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Protocol (HPLC size-fractionated phytopigment community + biomass analysis)</t>
+          <t>Protocol (paired laboratory + field clearance-rate / capture-efficiency assays on natural seston)</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Yes — HPLC pigment chemotaxonomy is a robust, quantitative approach for community shifts; 14-month duration captures seasonal cycles.</t>
+          <t>Partial for MEL — clearance-rate methodology is rigorous for understanding physiological filtering, but the paper's primary deliverable is bivalve physiology not direct WQ-indicator measurement.</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>No — HPLC pigment analysis is research-only.</t>
+          <t>No — laboratory clearance-rate methodology is research-only.</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -26787,22 +26837,22 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Size-fractionation filtration (0.7, 2.7, 20 µm); HPLC for diagnostic pigments (chl-a, fucoxanthin, peridinin etc.)</t>
+          <t>Flow-through clearance-rate chambers; Coulter counter / flow cytometer for particle size; chl-a fluorometer</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Medium–High — HPLC partner lab + multi-month sampling</t>
+          <t>Medium — specialised flow-through setup + particle-counting instrumentation</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Annual / multi-season (14-month)</t>
+          <t>Multi-season</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>ANOSIM / SIMPER for pigment community; size-class % change</t>
+          <t>ANOVA across species + seasons; capture efficiency vs particle-size regressions</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -26817,12 +26867,12 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.envpol.2016.07.058</t>
+          <t>https://doi.org/10.1016/j.jembe.2019.151251</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>Reveals size-selective grazing that a bulk chlorophyll measurement would miss.</t>
+          <t>Primarily physiology, but yields the per-species clearance rates needed to parameterise carrying-capacity models.</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
@@ -26847,27 +26897,27 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>WQ 2.1.1 — Chlorophyll-a, WQ 2.1.2 — Microorganisms</t>
+          <t>WQ 1.3.1 — Rate of water filtration (clearance-rate assay), WQ 2.1.1 — Chlorophyll-a, WQ 2.1.2 — Microorganism / plankton community</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>Subtropical Pacific</t>
+          <t>Temperate Pacific</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>Hong Kong oyster (Magallana hongkongensis) / Pacific oyster</t>
+          <t>Pacific oyster (Crassostrea / Magallana gigas), Mediterranean mussel (Mytilus galloprovincialis), Mud cockle (Katelysia rhytiphora)</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Raft / longline (oyster rafts)</t>
+          <t>Bottom culture / longline (mixed)</t>
         </is>
       </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>Single bay</t>
+          <t>Single bay (Coffin Bay, SA)</t>
         </is>
       </c>
       <c r="AE127" t="inlineStr">
@@ -26877,12 +26927,12 @@
       </c>
       <c r="AF127" t="inlineStr">
         <is>
-          <t>Monoculture</t>
+          <t>Monoculture (sympatric species comparison)</t>
         </is>
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>Plankton sampling, Pigment HPLC</t>
+          <t>Clearance-rate assay, Plankton sampling</t>
         </is>
       </c>
       <c r="AH127" t="inlineStr">
@@ -26902,7 +26952,7 @@
       </c>
       <c r="AK127" s="16" t="inlineStr">
         <is>
-          <t>To fingerprint an oyster farm's effect on phytoplankton by size and type, sample a farmed area and a reference area over a full seasonal cycle, size-fractionate the water (for example through 20, 2.7 and 0.7 um) and analyse diagnostic pigments by HPLC (chlorophyll-a plus marker pigments such as fucoxanthin and peridinin). Compare pigment communities with ANOSIM/SIMPER and quantify chlorophyll reduction per size class; this reveals size-selective grazing that a bulk chlorophyll measurement would miss.</t>
+          <t>This is primarily a physiological method but yields filtering parameters useful for water-quality modelling: measure clearance rate and particle-capture efficiency of each bivalve species on natural seston in flow-through chambers, characterising the particle field by size (Coulter counter or flow cytometer) and chlorophyll. Comparing species and seasons gives the species-specific clearance rates needed to parameterise mass-balance and carrying-capacity models, rather than a direct field water-quality measurement.</t>
         </is>
       </c>
       <c r="AL127" s="17" t="inlineStr">
@@ -26912,7 +26962,7 @@
       </c>
       <c r="AM127" s="18" t="inlineStr">
         <is>
-          <t>jiang_2016</t>
+          <t>rahman_2020</t>
         </is>
       </c>
       <c r="AN127" s="19" t="n"/>
@@ -26920,70 +26970,67 @@
       <c r="AP127" s="19" t="n"/>
       <c r="AQ127" s="16" t="inlineStr">
         <is>
-          <t>Size-Selective Phytoplankton-Depletion Fingerprint (HPLC Pigments)</t>
+          <t>Species-Specific Bivalve Filtration Parameters (Seston/Chlorophyll Chambers)</t>
         </is>
       </c>
       <c r="AR127" s="16" t="inlineStr">
         <is>
-          <t>Jiang, Tao; Chen, Feiyu; Yu, Zonghe; Lu, Lin; Wang, Zhaohui</t>
+          <t>Rahman, M A; Henderson, S; Miller-Ezzy, P A; Li, X X; Qin, J G</t>
         </is>
       </c>
       <c r="AS127" s="16" t="inlineStr">
         <is>
-          <t>Different Jiang from R43/R126 (Z-B Jiang group) — this is Tao Jiang's group, focused on South China Sea / Daya Bay. Methodologically important for showing size-selective grazing fingerprint in pigment data — useful for MEL practitioners designing chl-a indicator measurements where filtering signal must be distinguished from background community shifts. Sub-rule 1a-adjacent framing: HPLC pigment chemotaxonomy complements but does not replace tissue %N bioextraction.</t>
+          <t>Sub-rule 1b boundary case — primarily a physiology paper, but the seston-particle measurements and chl-a depletion in chambers provide MEL-relevant quantification of filtering capacity per species. Useful for parameterising mass-balance / carrying-capacity models that depend on species-specific clearance rates. Coffin Bay site connects to broader South Australian shellfish industry. | v1.4 refinement: Added WQ 1.3.1 (Rate of water filtration) — clearance-rate methodology is mollusc-specific WQ 1.3.1 indicator; v1.4 addition. CRs measured per species across natural seston assemblages.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Rahman, M. A., et al.</t>
+          <t>Ysebaert, T., et al.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Analysis of the seasonal impact of three marine bivalves on seston particles in water column</t>
+          <t>Habitat modification and coastal protection by ecosystem-engineering reef-building bivalves</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Journal of Experimental Marine Biology and Ecology</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>522</v>
+          <t>Goods and Services of Marine Bivalves (book; eds. Smaal, Ferreira, Grant, Petersen, Strand)</t>
+        </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>151251</t>
+          <t>253-273</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Elsevier</t>
+          <t>Springer (Open Access)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Comparative laboratory + field food-selectivity and clearance-rate study of three sympatric bivalves — Pacific oyster (Magallana / Crassostrea gigas), Mediterranean mussel (Mytilus galloprovincialis), and native mud cockle (Katelysia rhytiphora) — on natural seston particle assemblages from Coffin Bay (South Australia). Particles measured 4–14 µm range; capture efficiency higher for larger particles (8–14 µm); seasonal CE/CR variation. Findings: oyster + mussel utilise similar food (phytoplankton); cockles graze a broader range (including detritus + bacteria). Maps to MEL WQ 2.1.1 (seston / chl-a) and WQ 2.1.2 (microorganism / particle community composition).</t>
+          <t>Synthesis chapter on ecosystem-engineering effects of reef-building bivalves — oysters and mussels — on intertidal/subtidal coastal environments. Documents how 3D bivalve reef structures alter local hydrodynamics and sediment-morphology far beyond the reef boundary (up to hundreds of metres), provide habitat for associated species, and contribute to shoreline stabilisation + erosion control. Two case studies: (1) Eastern oyster (Crassostrea virginica) reefs for shoreline protection in coastal Alabama, USA; (2) Crassostrea gigas reefs as protection against tidal flat erosion in the Oosterschelde, The Netherlands (Walles 2015 work). Argued as nature-based solutions for climate adaptation. Maps to MEL H&amp;B 1.1.1 (epibiota — reef structures), H&amp;B 1.4.1 (sediment biogeochemistry / dynamics), H&amp;B 2.1.1 (community composition supported by reef structure).</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Protocol (paired laboratory + field clearance-rate / capture-efficiency assays on natural seston)</t>
+          <t>Reference (synthesis chapter with embedded case-study protocols)</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Partial for MEL — clearance-rate methodology is rigorous for understanding physiological filtering, but the paper's primary deliverable is bivalve physiology not direct WQ-indicator measurement.</t>
+          <t>Yes — the embedded case studies follow standard reef-establishment + monitoring protocols; the chapter is a methodological + framework synthesis useful for restoration practitioners.</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>No — laboratory clearance-rate methodology is research-only.</t>
+          <t>Partial — reef establishment is operational; structured monitoring requires partnership.</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -26993,42 +27040,42 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>Flow-through clearance-rate chambers; Coulter counter / flow cytometer for particle size; chl-a fluorometer</t>
+          <t>Reef-building substrates (oyster castles, gabion bags, reef balls); standard habitat-monitoring (epibiota cover, infaunal cores, RTK elevation surveys)</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Medium — specialised flow-through setup + particle-counting instrumentation</t>
+          <t>Medium–High — multi-year operational monitoring</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Multi-season</t>
+          <t>Multi-year</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>ANOVA across species + seasons; capture efficiency vs particle-size regressions</t>
+          <t>Before/after + reef/control contrasts; sediment elevation modelling</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>No — Paywalled (Elsevier)</t>
+          <t>Yes — Open access (Springer SpringerOpen)</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>Abstract + Methods (fetched)</t>
+          <t>Abstract + DOI metadata</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jembe.2019.151251</t>
+          <t>https://doi.org/10.1007/978-3-319-96776-9_13</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>Primarily physiology, but yields the per-species clearance rates needed to parameterise carrying-capacity models.</t>
+          <t>A framework reference for restoration-oriented reef monitoring and coastal-protection benefit.</t>
         </is>
       </c>
       <c r="V128" t="inlineStr">
@@ -27036,7 +27083,7 @@
           <t>Original list</t>
         </is>
       </c>
-      <c r="W128" t="inlineStr">
+      <c r="W128" s="7" t="inlineStr">
         <is>
           <t>2 — Researcher</t>
         </is>
@@ -27048,32 +27095,32 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>Water Quality</t>
+          <t>Habitat &amp; Biodiversity, Climate Change</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>WQ 1.3.1 — Rate of water filtration (clearance-rate assay), WQ 2.1.1 — Chlorophyll-a, WQ 2.1.2 — Microorganism / plankton community</t>
+          <t>CC 3.1.1 — Wave attenuation / coastal protection, H&amp;B 1.1.1 — Epibiota, H&amp;B 1.4.1 — Sediment biogeochemistry, H&amp;B 2.1.1 — Community composition</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>Temperate Pacific</t>
+          <t>Temperate Atlantic + Subtropical Atlantic/Gulf</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>Pacific oyster (Crassostrea / Magallana gigas), Mediterranean mussel (Mytilus galloprovincialis), Mud cockle (Katelysia rhytiphora)</t>
+          <t>Eastern oyster (Crassostrea virginica), Pacific oyster (Crassostrea / Magallana gigas), Blue mussel (Mytilus edulis)</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Bottom culture / longline (mixed)</t>
+          <t>Reef / on-bottom structure</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr">
         <is>
-          <t>Single bay (Coffin Bay, SA)</t>
+          <t>Multi-site (synthesis of 2 case studies)</t>
         </is>
       </c>
       <c r="AE128" t="inlineStr">
@@ -27083,12 +27130,12 @@
       </c>
       <c r="AF128" t="inlineStr">
         <is>
-          <t>Monoculture (sympatric species comparison)</t>
+          <t>Monoculture (restoration / conservation aquaculture)</t>
         </is>
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>Clearance-rate assay, Plankton sampling</t>
+          <t>Visual survey, Benthic infauna sampling, Sediment sampling</t>
         </is>
       </c>
       <c r="AH128" t="inlineStr">
@@ -27098,27 +27145,27 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>Shallow nearshore (2–10 m)</t>
+          <t>Intertidal / very shallow (&lt; 2 m)</t>
         </is>
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>Sheltered</t>
+          <t>Exposed (deliberately, for coastal-protection function)</t>
         </is>
       </c>
       <c r="AK128" s="16" t="inlineStr">
         <is>
-          <t>This is primarily a physiological method but yields filtering parameters useful for water-quality modelling: measure clearance rate and particle-capture efficiency of each bivalve species on natural seston in flow-through chambers, characterising the particle field by size (Coulter counter or flow cytometer) and chlorophyll. Comparing species and seasons gives the species-specific clearance rates needed to parameterise mass-balance and carrying-capacity models, rather than a direct field water-quality measurement.</t>
+          <t>This synthesis documents how reef-building bivalves reshape local hydrodynamics and sediment morphology (sometimes hundreds of metres beyond the reef), provide habitat and deliver coastal-protection services. It embeds standard reef-establishment and monitoring approaches (epibiota cover, infaunal cores, RTK sediment-elevation surveys, before/after reef-versus-control contrasts). Use it as a framework reference for restoration-oriented reef monitoring and coastal-protection benefit.</t>
         </is>
       </c>
       <c r="AL128" s="17" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Ref</t>
         </is>
       </c>
       <c r="AM128" s="18" t="inlineStr">
         <is>
-          <t>rahman_2020</t>
+          <t>ysebaert_2018</t>
         </is>
       </c>
       <c r="AN128" s="19" t="n"/>
@@ -27126,67 +27173,70 @@
       <c r="AP128" s="19" t="n"/>
       <c r="AQ128" s="16" t="inlineStr">
         <is>
-          <t>Species-Specific Bivalve Filtration Parameters (Seston/Chlorophyll Chambers)</t>
+          <t>Bivalve-Reef Coastal Protection &amp; Ecosystem Engineering (Synthesis)</t>
         </is>
       </c>
       <c r="AR128" s="16" t="inlineStr">
         <is>
-          <t>Rahman, M A; Henderson, S; Miller-Ezzy, P A; Li, X X; Qin, J G</t>
+          <t>Ysebaert, Tom; Walles, Brenda; Haner, Judy; Hancock, Boze</t>
         </is>
       </c>
       <c r="AS128" s="16" t="inlineStr">
         <is>
-          <t>Sub-rule 1b boundary case — primarily a physiology paper, but the seston-particle measurements and chl-a depletion in chambers provide MEL-relevant quantification of filtering capacity per species. Useful for parameterising mass-balance / carrying-capacity models that depend on species-specific clearance rates. Coffin Bay site connects to broader South Australian shellfish industry. | v1.4 refinement: Added WQ 1.3.1 (Rate of water filtration) — clearance-rate methodology is mollusc-specific WQ 1.3.1 indicator; v1.4 addition. CRs measured per species across natural seston assemblages.</t>
+          <t>Distinct from v14 R80 Ysebaert 2009 (Tom Ysebaert's earlier ESM/J Sea Res paper on different topic) — new row added. This 2018 chapter is one of the most cited syntheses on bivalve-reef coastal-protection ecosystem services. Companion to Walles 2015 (Oosterschelde) and to the Alabama TNC oyster-reef program. Useful framework reference for MEL practitioners assessing H&amp;B + coastal-protection indicators. | v1.4 refinement: Added CC 3.1.1 (Wave attenuation / coastal protection) — chapter's primary deliverable is the ecosystem-engineering coastal-protection function of reef-building bivalves; v1.4 added this indicator (mollusc CC Goal 3). Y now multi-tagged H&amp;B + CC.  [v21 retier] Reference cannot hold an execution tier (T3/T4); reclassified to T2 as a usable framework synthesis.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Ysebaert, T., et al.</t>
+          <t>Goedefroo, N., et al.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Habitat modification and coastal protection by ecosystem-engineering reef-building bivalves</t>
+          <t>Nature-based solutions in a sandy foreshore: A biological assessment of a longline mussel aquaculture technique to establish subtidal reefs</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Goods and Services of Marine Bivalves (book; eds. Smaal, Ferreira, Grant, Petersen, Strand)</t>
-        </is>
+          <t>Ecological Engineering</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>185</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>253-273</t>
+          <t>106807</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Springer (Open Access)</t>
+          <t>Elsevier</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Synthesis chapter on ecosystem-engineering effects of reef-building bivalves — oysters and mussels — on intertidal/subtidal coastal environments. Documents how 3D bivalve reef structures alter local hydrodynamics and sediment-morphology far beyond the reef boundary (up to hundreds of metres), provide habitat for associated species, and contribute to shoreline stabilisation + erosion control. Two case studies: (1) Eastern oyster (Crassostrea virginica) reefs for shoreline protection in coastal Alabama, USA; (2) Crassostrea gigas reefs as protection against tidal flat erosion in the Oosterschelde, The Netherlands (Walles 2015 work). Argued as nature-based solutions for climate adaptation. Maps to MEL H&amp;B 1.1.1 (epibiota — reef structures), H&amp;B 1.4.1 (sediment biogeochemistry / dynamics), H&amp;B 2.1.1 (community composition supported by reef structure).</t>
+          <t>Biological assessment of the Belgian 'Coastbusters' pilot project (2017–2020): longline mussel (Mytilus edulis) aquaculture technique repurposed as a nature-based solution for coastal erosion protection in the Belgian Part of the North Sea. Subtidal mussel reefs established via filamentous + non-filamentous dropper lines of different materials (hemp/coconut/sisal/jute natural fibres, biobased lines, Deltaflex). Biological aspects assessed: mussel survival and biomass on dropper lines, macrobenthos sampling around the structures, sediment characteristics. Key findings: mussel beds developed during summer–fall 2019; mostly lost in winter (predation + storms); no short-term macrobenthos impact detected. Maps to MEL H&amp;B 1.1.1 (epibiota), H&amp;B 1.3.1 (infauna), H&amp;B 2.1.1 (community composition).</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Reference (synthesis chapter with embedded case-study protocols)</t>
+          <t>Protocol (NBS / mussel-reef pilot with biological monitoring program)</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Yes — the embedded case studies follow standard reef-establishment + monitoring protocols; the chapter is a methodological + framework synthesis useful for restoration practitioners.</t>
+          <t>Yes — 3-year pilot with multi-material dropper-line comparison + paired macrobenthos sampling; establishes both technical feasibility and ecological-monitoring template.</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Partial — reef establishment is operational; structured monitoring requires partnership.</t>
+          <t>Partial — line deployment is operational; macrobenthos sampling + biological assessment require partnership.</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -27196,42 +27246,42 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>Reef-building substrates (oyster castles, gabion bags, reef balls); standard habitat-monitoring (epibiota cover, infaunal cores, RTK elevation surveys)</t>
+          <t>Longline mussel aquaculture infrastructure (multi-material dropper lines); van Veen grab for macrobenthos; CTD; sediment grain-size analysis</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Medium–High — multi-year operational monitoring</t>
+          <t>Medium–High — multi-year pilot infrastructure + biological monitoring</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Multi-year</t>
+          <t>Multi-year (3 yr pilot)</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>Before/after + reef/control contrasts; sediment elevation modelling</t>
+          <t>Before/after + reef/control contrasts; macrobenthos diversity + abundance; cross-material comparison</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>Yes — Open access (Springer SpringerOpen)</t>
+          <t>Yes — Open access via ILVO institutional deposit; journal article paywalled</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>Abstract + DOI metadata</t>
+          <t>Abstract + Methods (fetched)</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/978-3-319-96776-9_13</t>
+          <t>https://doi.org/10.1016/j.ecoleng.2022.106807</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>A framework reference for restoration-oriented reef monitoring and coastal-protection benefit.</t>
+          <t>Tests whether the mussel-farming technique can be redirected from harvest to coastal protection.</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
@@ -27239,9 +27289,9 @@
           <t>Original list</t>
         </is>
       </c>
-      <c r="W129" s="7" t="inlineStr">
-        <is>
-          <t>2 — Researcher</t>
+      <c r="W129" s="9" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
         </is>
       </c>
       <c r="X129" t="inlineStr">
@@ -27256,27 +27306,27 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>CC 3.1.1 — Wave attenuation / coastal protection, H&amp;B 1.1.1 — Epibiota, H&amp;B 1.4.1 — Sediment biogeochemistry, H&amp;B 2.1.1 — Community composition</t>
+          <t>CC 3.1.1 — Wave attenuation / coastal protection, H&amp;B 1.1.1 — Epibiota, H&amp;B 1.3.1 — Infauna, H&amp;B 2.1.1 — Community composition</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>Temperate Atlantic + Subtropical Atlantic/Gulf</t>
+          <t>Temperate Atlantic</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>Eastern oyster (Crassostrea virginica), Pacific oyster (Crassostrea / Magallana gigas), Blue mussel (Mytilus edulis)</t>
+          <t>Blue mussel (Mytilus edulis)</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Reef / on-bottom structure</t>
+          <t>Longline / suspended (with dropper lines to seabed)</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr">
         <is>
-          <t>Multi-site (synthesis of 2 case studies)</t>
+          <t>Single farm (pilot)</t>
         </is>
       </c>
       <c r="AE129" t="inlineStr">
@@ -27286,12 +27336,12 @@
       </c>
       <c r="AF129" t="inlineStr">
         <is>
-          <t>Monoculture (restoration / conservation aquaculture)</t>
+          <t>Monoculture</t>
         </is>
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>Visual survey, Benthic infauna sampling, Sediment sampling</t>
+          <t>Benthic infauna sampling, Visual survey</t>
         </is>
       </c>
       <c r="AH129" t="inlineStr">
@@ -27301,27 +27351,27 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>Intertidal / very shallow (&lt; 2 m)</t>
+          <t>Subtidal sandy foreshore (2–10 m)</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>Exposed (deliberately, for coastal-protection function)</t>
+          <t>Mixed exposure</t>
         </is>
       </c>
       <c r="AK129" s="16" t="inlineStr">
         <is>
-          <t>This synthesis documents how reef-building bivalves reshape local hydrodynamics and sediment morphology (sometimes hundreds of metres beyond the reef), provide habitat and deliver coastal-protection services. It embeds standard reef-establishment and monitoring approaches (epibiota cover, infaunal cores, RTK sediment-elevation surveys, before/after reef-versus-control contrasts). Use it as a framework reference for restoration-oriented reef monitoring and coastal-protection benefit.</t>
+          <t>To evaluate a longline-mussel nature-based solution for its reef-building and biodiversity value, monitor the dropper-line community, the surrounding seabed and the mussels themselves using a before/after control-impact design. Sample seabed macrobenthos with a Van Veen grab (0.1 m2, rinsed over 1 mm mesh, fixed in formaldehyde, rose-bengal stained) at fixed reef stations and control stations about 50 m outside, before installation and repeatedly after. Retrieve dropper-line segments to assess the biofouling community (top versus bottom 50 cm, rinsed over a 0.5 mm sieve, subsampled by quartering) and mussel metrics - size distribution, primary versus secondary attachment (a detachment-risk ratio), and condition. Add qualitative diver-video transects along the line for reef state and epifauna, and analyse macrobenthos richness and diversity with generalised or linear mixed models (site fixed, time random) plus SIMPER for the taxa driving community differences.</t>
         </is>
       </c>
       <c r="AL129" s="17" t="inlineStr">
         <is>
-          <t>Ref</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AM129" s="18" t="inlineStr">
         <is>
-          <t>ysebaert_2018</t>
+          <t>goedefroo_2022</t>
         </is>
       </c>
       <c r="AN129" s="19" t="n"/>
@@ -27329,46 +27379,46 @@
       <c r="AP129" s="19" t="n"/>
       <c r="AQ129" s="16" t="inlineStr">
         <is>
-          <t>Bivalve-Reef Coastal Protection &amp; Ecosystem Engineering (Synthesis)</t>
+          <t>Longline-Mussel Nature-Based Solution: Reef &amp; Biodiversity Assessment (BACI)</t>
         </is>
       </c>
       <c r="AR129" s="16" t="inlineStr">
         <is>
-          <t>Ysebaert, Tom; Walles, Brenda; Haner, Judy; Hancock, Boze</t>
+          <t>Goedefroo, Nanou; Benham, Peter; Debusschere, Elisabeth; Deneudt, Klaas; Mascart, Thibaud; Semeraro, Alexia; Sterckx, Tomas; Van Hoey, Gert</t>
         </is>
       </c>
       <c r="AS129" s="16" t="inlineStr">
         <is>
-          <t>Distinct from v14 R80 Ysebaert 2009 (Tom Ysebaert's earlier ESM/J Sea Res paper on different topic) — new row added. This 2018 chapter is one of the most cited syntheses on bivalve-reef coastal-protection ecosystem services. Companion to Walles 2015 (Oosterschelde) and to the Alabama TNC oyster-reef program. Useful framework reference for MEL practitioners assessing H&amp;B + coastal-protection indicators. | v1.4 refinement: Added CC 3.1.1 (Wave attenuation / coastal protection) — chapter's primary deliverable is the ecosystem-engineering coastal-protection function of reef-building bivalves; v1.4 added this indicator (mollusc CC Goal 3). Y now multi-tagged H&amp;B + CC.  [v21 retier] Reference cannot hold an execution tier (T3/T4); reclassified to T2 as a usable framework synthesis.</t>
+          <t>Pilot-project paper for the Coastbusters NBS program (Belgium). Important methodological contribution: testing whether longline mussel aquaculture technique can be redirected from harvest goal to coastal-protection goal. Companion to Coastbusters 2.0 (Boulenger 2023 ff.). Useful for MEL practitioners thinking about repurposing aquaculture infrastructure for habitat + coastal-protection services. | v1.4 refinement: Added CC 3.1.1 — explicit nature-based-solution paper for coastal erosion mitigation off Belgian coast; matches mollusc CC Obj 3.1 directly. Y now multi-tagged H&amp;B + CC.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Goedefroo, N., et al.</t>
+          <t>Lin, J., et al.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Nature-based solutions in a sandy foreshore: A biological assessment of a longline mussel aquaculture technique to establish subtidal reefs</t>
+          <t>Hydrodynamic effect of a large offshore mussel suspended aquaculture farm</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ecological Engineering</t>
+          <t>Aquaculture</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>185</v>
+        <v>451</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>106807</t>
+          <t>147-155</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -27377,22 +27427,22 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Biological assessment of the Belgian 'Coastbusters' pilot project (2017–2020): longline mussel (Mytilus edulis) aquaculture technique repurposed as a nature-based solution for coastal erosion protection in the Belgian Part of the North Sea. Subtidal mussel reefs established via filamentous + non-filamentous dropper lines of different materials (hemp/coconut/sisal/jute natural fibres, biobased lines, Deltaflex). Biological aspects assessed: mussel survival and biomass on dropper lines, macrobenthos sampling around the structures, sediment characteristics. Key findings: mussel beds developed during summer–fall 2019; mostly lost in winter (predation + storms); no short-term macrobenthos impact detected. Maps to MEL H&amp;B 1.1.1 (epibiota), H&amp;B 1.3.1 (infauna), H&amp;B 2.1.1 (community composition).</t>
+          <t>Field observational + ADCP study of tidal-current modification by a large mussel (Mytilus galloprovincialis) suspended longline aquaculture farm off Gouqi Island, outside the Changjiang (Yangtze) Estuary, China. Surface tidal current velocity reduced 75–90% in top 3.5 m, ~45% at bottom. Surface hydraulic roughness z₀s ≈ 1.4–1.9 m (20× bottom); surface drag coefficient C500 ≈ 0.087–0.169 (3.5–7.5× bottom). Downwelling induced. SURFACE CHL-A FLUORESCENCE depleted to &lt; 1.0 µg L⁻¹ INSIDE the farm — 80% less than outside — quantifying carrying-capacity implications. Maps narrowly to MEL WQ 2.1.1 (chl-a depletion measurement).</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Protocol (NBS / mussel-reef pilot with biological monitoring program)</t>
+          <t>Protocol (paired in-farm vs out-of-farm ADCP + CTD + chl-a fluorescence vertical profiles)</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Yes — 3-year pilot with multi-material dropper-line comparison + paired macrobenthos sampling; establishes both technical feasibility and ecological-monitoring template.</t>
+          <t>Partial — chl-a measurement is direct WQ 2.1.1; primary deliverable is physical-oceanography characterisation of farm-induced flow modification.</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Partial — line deployment is operational; macrobenthos sampling + biological assessment require partnership.</t>
+          <t>Partial — ADCP/CTD deployment is operational for trained farmers + technicians.</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -27402,42 +27452,42 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>Longline mussel aquaculture infrastructure (multi-material dropper lines); van Veen grab for macrobenthos; CTD; sediment grain-size analysis</t>
+          <t>ADCP (current profiling); CTD with chl-a fluorometer; salinity / temperature profiling</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Medium–High — multi-year pilot infrastructure + biological monitoring</t>
+          <t>Medium — ADCP + CTD suite is institutional</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Multi-year (3 yr pilot)</t>
+          <t>Multi-day campaign (covering tidal cycles)</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>Before/after + reef/control contrasts; macrobenthos diversity + abundance; cross-material comparison</t>
+          <t>Cross-site contrasts (in vs out of farm); friction-velocity + roughness calculations from log-fit profiles</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>Yes — Open access via ILVO institutional deposit; journal article paywalled</t>
+          <t>No — Paywalled (Elsevier)</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>Abstract + Methods (fetched)</t>
+          <t>Full PDF</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.ecoleng.2022.106807</t>
+          <t>https://doi.org/10.1016/j.aquaculture.2015.08.039</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>Tests whether the mussel-farming technique can be redirected from harvest to coastal protection.</t>
+          <t>Documents how a large suspended farm acts as a porous canopy that reduces flow and can strongly deplete chlorophyll.</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
@@ -27457,32 +27507,32 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>Habitat &amp; Biodiversity, Climate Change</t>
+          <t>Water Quality, Climate Change</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>CC 3.1.1 — Wave attenuation / coastal protection, H&amp;B 1.1.1 — Epibiota, H&amp;B 1.3.1 — Infauna, H&amp;B 2.1.1 — Community composition</t>
+          <t>CC 3.1.1 — Wave attenuation / coastal protection (Sub-rule 1c), WQ 2.1.1 — Chlorophyll-a</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>Temperate Atlantic</t>
+          <t>Subtropical Pacific</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>Blue mussel (Mytilus edulis)</t>
+          <t>Mediterranean mussel (Mytilus galloprovincialis)</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Longline / suspended (with dropper lines to seabed)</t>
+          <t>Longline / suspended (offshore)</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr">
         <is>
-          <t>Single farm (pilot)</t>
+          <t>Single farm (large)</t>
         </is>
       </c>
       <c r="AE130" t="inlineStr">
@@ -27497,7 +27547,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>Benthic infauna sampling, Visual survey</t>
+          <t>Water chemistry, Hydrodynamic measurement</t>
         </is>
       </c>
       <c r="AH130" t="inlineStr">
@@ -27507,98 +27557,98 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>Subtidal sandy foreshore (2–10 m)</t>
+          <t>Offshore (deeper)</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>Mixed exposure</t>
-        </is>
-      </c>
-      <c r="AK130" s="16" t="inlineStr">
-        <is>
-          <t>To evaluate a longline-mussel nature-based solution for its reef-building and biodiversity value, monitor the dropper-line community, the surrounding seabed and the mussels themselves using a before/after control-impact design. Sample seabed macrobenthos with a Van Veen grab (0.1 m2, rinsed over 1 mm mesh, fixed in formaldehyde, rose-bengal stained) at fixed reef stations and control stations about 50 m outside, before installation and repeatedly after. Retrieve dropper-line segments to assess the biofouling community (top versus bottom 50 cm, rinsed over a 0.5 mm sieve, subsampled by quartering) and mussel metrics - size distribution, primary versus secondary attachment (a detachment-risk ratio), and condition. Add qualitative diver-video transects along the line for reef state and epifauna, and analyse macrobenthos richness and diversity with generalised or linear mixed models (site fixed, time random) plus SIMPER for the taxa driving community differences.</t>
-        </is>
-      </c>
-      <c r="AL130" s="17" t="inlineStr">
+          <t>Exposed</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>To quantify how a large suspended mussel farm modifies local currents (needed to avoid over-estimating seston and nutrient supply, and hence carrying capacity), measure vertical current-velocity profiles inside and outside the culture ground and fit drag coefficients. Anchor an acoustic Doppler current profiler (ADCP) at stations inside and outside the farm and log the velocity profile in about 1 m vertical bins over at least a full tidal cycle (ideally a spring tide), and take CTD casts (temperature, salinity, chlorophyll-a fluorescence) inside and outside to capture the food proxy. Because the surface canopy of dropper lines adds friction like a rough bed, fit the measured velocity profiles with a logarithmic (law-of-the-wall) model to derive both a surface drag coefficient (referenced to a set depth below the surface) and a bottom drag coefficient, using least-squares across many profiles. The resulting drag parameters quantify the farm's flow reduction and can be fed into hydrodynamic and carrying-capacity models.</t>
+        </is>
+      </c>
+      <c r="AL130" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
       <c r="AM130" s="18" t="inlineStr">
         <is>
-          <t>goedefroo_2022</t>
+          <t>lin_2016</t>
         </is>
       </c>
       <c r="AN130" s="19" t="n"/>
       <c r="AO130" s="19" t="n"/>
       <c r="AP130" s="19" t="n"/>
-      <c r="AQ130" s="16" t="inlineStr">
-        <is>
-          <t>Longline-Mussel Nature-Based Solution: Reef &amp; Biodiversity Assessment (BACI)</t>
-        </is>
-      </c>
       <c r="AR130" s="16" t="inlineStr">
         <is>
-          <t>Goedefroo, Nanou; Benham, Peter; Debusschere, Elisabeth; Deneudt, Klaas; Mascart, Thibaud; Semeraro, Alexia; Sterckx, Tomas; Van Hoey, Gert</t>
+          <t>Lin, Jun; Li, Chunyan; Zhang, Shouyu</t>
         </is>
       </c>
       <c r="AS130" s="16" t="inlineStr">
         <is>
-          <t>Pilot-project paper for the Coastbusters NBS program (Belgium). Important methodological contribution: testing whether longline mussel aquaculture technique can be redirected from harvest goal to coastal-protection goal. Companion to Coastbusters 2.0 (Boulenger 2023 ff.). Useful for MEL practitioners thinking about repurposing aquaculture infrastructure for habitat + coastal-protection services. | v1.4 refinement: Added CC 3.1.1 — explicit nature-based-solution paper for coastal erosion mitigation off Belgian coast; matches mollusc CC Obj 3.1 directly. Y now multi-tagged H&amp;B + CC.</t>
+          <t>Foundational paper for documenting that suspended-bivalve farms act as porous physical canopies in the surface layer, reducing horizontal flow and inducing downwelling. The 80% chl-a depletion result is striking and matches the seston-depletion + carrying-capacity literature. Important for MEL practitioners: chl-a measurements 'inside' farms are physically distorted by reduced current — sampling design must account for canopy-induced vertical mixing. Companion to R125 Cugier 2010 (modelling), R110 Maar 2024 (modelling). | v1.4 refinement: Added CC 3.1.1 per Sub-rule 1c (v1.4) — paper measures canopy-induced flow modification which contributes to wave-energy attenuation by suspended bivalve farms; does not compute wave-decay coefficient directly, so retained under Sub-rule 1c with caveat. Y now multi-tagged WQ + CC. | v38: filled at High from pasted Methods (Lin); Source Read set to Full PDF.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Lin, J., et al.</t>
+          <t>Shi, B., et al.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Hydrodynamic effect of a large offshore mussel suspended aquaculture farm</t>
+          <t>Influence of macrobenthos (Meretrix meretrix Linnaeus) on erosion-accretion processes in intertidal flats: A case study from a cultivation zone</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Aquaculture</t>
+          <t>Journal of Geophysical Research: Biogeosciences</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>451</v>
+        <v>125</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>147-155</t>
+          <t>e2019JG005345</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Elsevier</t>
+          <t>AGU / Wiley</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Field observational + ADCP study of tidal-current modification by a large mussel (Mytilus galloprovincialis) suspended longline aquaculture farm off Gouqi Island, outside the Changjiang (Yangtze) Estuary, China. Surface tidal current velocity reduced 75–90% in top 3.5 m, ~45% at bottom. Surface hydraulic roughness z₀s ≈ 1.4–1.9 m (20× bottom); surface drag coefficient C500 ≈ 0.087–0.169 (3.5–7.5× bottom). Downwelling induced. SURFACE CHL-A FLUORESCENCE depleted to &lt; 1.0 µg L⁻¹ INSIDE the farm — 80% less than outside — quantifying carrying-capacity implications. Maps narrowly to MEL WQ 2.1.1 (chl-a depletion measurement).</t>
+          <t>Paired-site (cultivation zone vs adjacent bare flat) field investigation on the Rudong intertidal flat, Jiangsu Coast, China, quantifying the effect of high-density hard clam Meretrix meretrix (~137 ind. m⁻²) on bed erodibility, sediment-erosion thresholds, and erosion-accretion processes. Co-deployed instruments: ADV for turbulent flow velocity + bed-level change, SBE 26 Plus pressure sensors for wave-tide measurements, sediment-property + macrobenthos sampling. Found M. meretrix presence lowered critical erosion shear stress (~23.5% drop) — clams destabilise sediment under their cultivation density. Maps to MEL H&amp;B 1.4.1 (sediment biogeochemistry / dynamics).</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Protocol (paired in-farm vs out-of-farm ADCP + CTD + chl-a fluorescence vertical profiles)</t>
+          <t>Protocol (paired-site hydrodynamic + sediment-erosion observation under bivalve cultivation)</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Partial — chl-a measurement is direct WQ 2.1.1; primary deliverable is physical-oceanography characterisation of farm-induced flow modification.</t>
+          <t>Yes — synchronous hydrodynamic + sediment + macrobenthos measurements at paired sites with + without bivalve cultivation; standard erosion-threshold methodology.</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Partial — ADCP/CTD deployment is operational for trained farmers + technicians.</t>
+          <t>No — research-grade instrumentation deployment (ADV, pressure sensors).</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -27608,27 +27658,27 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>ADCP (current profiling); CTD with chl-a fluorometer; salinity / temperature profiling</t>
+          <t>ADV (acoustic Doppler velocimeter); SBE 26 Plus wave-tide recorder; grain-size + organic-content sediment analysis; benthic core sampling</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Medium — ADCP + CTD suite is institutional</t>
+          <t>Medium–High — research-grade hydrodynamic instrumentation</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Multi-day campaign (covering tidal cycles)</t>
+          <t>Multi-season (seasonal summer + winter comparison)</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>Cross-site contrasts (in vs out of farm); friction-velocity + roughness calculations from log-fit profiles</t>
+          <t>Paired-site contrasts; critical shear-stress calculation; bed-level change time series</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>No — Paywalled (Elsevier)</t>
+          <t>No — Paywalled (AGU / Wiley)</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -27638,12 +27688,12 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.aquaculture.2015.08.039</t>
+          <t>https://doi.org/10.1029/2019JG005345</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>Documents how a large suspended farm acts as a porous canopy that reduces flow and can strongly deplete chlorophyll.</t>
+          <t>Counterintuitively, high-density burrowing, shell-protruding clams can lower the erosion threshold and destabilise the bed - the opposite of reef-builders.</t>
         </is>
       </c>
       <c r="V131" t="inlineStr">
@@ -27651,9 +27701,9 @@
           <t>Original list</t>
         </is>
       </c>
-      <c r="W131" s="9" t="inlineStr">
-        <is>
-          <t>3 — Partnership</t>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>2 — Researcher</t>
         </is>
       </c>
       <c r="X131" t="inlineStr">
@@ -27663,12 +27713,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>Water Quality, Climate Change</t>
+          <t>Habitat &amp; Biodiversity, Climate Change</t>
         </is>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>CC 3.1.1 — Wave attenuation / coastal protection (Sub-rule 1c), WQ 2.1.1 — Chlorophyll-a</t>
+          <t>CC 3.1.1 — Wave attenuation / coastal protection (counter-example, Sub-rule 1c), H&amp;B 1.4.1 — Sediment biogeochemistry</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -27678,17 +27728,17 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>Mediterranean mussel (Mytilus galloprovincialis)</t>
+          <t>Hard clam (Meretrix meretrix)</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Longline / suspended (offshore)</t>
+          <t>Intertidal bottom culture (seeded clam beds)</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr">
         <is>
-          <t>Single farm (large)</t>
+          <t>Single site (paired cultivation vs control)</t>
         </is>
       </c>
       <c r="AE131" t="inlineStr">
@@ -27703,7 +27753,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>Water chemistry, Hydrodynamic measurement</t>
+          <t>Sediment sampling, Hydrodynamic measurement, Benthic infauna sampling</t>
         </is>
       </c>
       <c r="AH131" t="inlineStr">
@@ -27713,88 +27763,100 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>Offshore (deeper)</t>
+          <t>Intertidal / very shallow (&lt; 2 m)</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>Exposed</t>
+          <t>Mixed exposure</t>
+        </is>
+      </c>
+      <c r="AK131" s="16" t="inlineStr">
+        <is>
+          <t>To measure how dense infaunal bivalves affect sediment stability, compare a cultivation zone with an adjacent bare flat, co-deploying an acoustic Doppler velocimeter for turbulent flow and a wave-tide recorder to derive bed shear stress, alongside sediment grain-size and organic-content analysis and benthic cores. Track bed-level change and compute the critical erosion shear stress at each site; note the counterintuitive result that high-density burrowing, shell-protruding clams can lower the erosion threshold and destabilise the bed rather than protect it - the opposite of reef-building bivalves.</t>
+        </is>
+      </c>
+      <c r="AL131" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
       <c r="AM131" s="18" t="inlineStr">
         <is>
-          <t>lin_2016</t>
+          <t>shi_2020</t>
         </is>
       </c>
       <c r="AN131" s="19" t="n"/>
       <c r="AO131" s="19" t="n"/>
       <c r="AP131" s="19" t="n"/>
+      <c r="AQ131" s="16" t="inlineStr">
+        <is>
+          <t>Do Dense Infaunal Bivalves Stabilise or Erode Sediment?</t>
+        </is>
+      </c>
       <c r="AR131" s="16" t="inlineStr">
         <is>
-          <t>Lin, Jun; Li, Chunyan; Zhang, Shouyu</t>
+          <t>Shi, Benwei; Pratolongo, Paula D; Du, Yongfen; Li, Jiasheng; Yang, S L; Wu, Jihua; Xu, Kehui; Wang, Ya Ping</t>
         </is>
       </c>
       <c r="AS131" s="16" t="inlineStr">
         <is>
-          <t>Foundational paper for documenting that suspended-bivalve farms act as porous physical canopies in the surface layer, reducing horizontal flow and inducing downwelling. The 80% chl-a depletion result is striking and matches the seston-depletion + carrying-capacity literature. Important for MEL practitioners: chl-a measurements 'inside' farms are physically distorted by reduced current — sampling design must account for canopy-induced vertical mixing. Companion to R125 Cugier 2010 (modelling), R110 Maar 2024 (modelling). | v1.4 refinement: Added CC 3.1.1 per Sub-rule 1c (v1.4) — paper measures canopy-induced flow modification which contributes to wave-energy attenuation by suspended bivalve farms; does not compute wave-decay coefficient directly, so retained under Sub-rule 1c with caveat. Y now multi-tagged WQ + CC.</t>
+          <t>Important paper for the COUNTERINTUITIVE finding that high-density bivalve cultivation can DESTABILISE rather than stabilise sediments (the opposite of reef-building bivalves in Ysebaert 2018 R129) — context matters: the action of clams burrowing + protruding their shells reduces critical erosion shear stress. Important for MEL practitioners using H&amp;B 1.4.1 sediment-dynamics indicators on clam-cultivation sites: cultivation may shift the system toward erosion. Companion to Shi 2021 (L&amp;O, typhoon-induced erosion at same site) and Li 2021 (Ecohydrology &amp; Hydrobiology, same site, ~23% threshold drop confirmed). | v1.4 refinement: Added CC 3.1.1 per Sub-rule 1c (v1.4) — sediment-erosion threshold under clam cultivation is directly relevant to mollusc CC Obj 3.1 (coastal erosion), as a COUNTER-EXAMPLE showing high-density clam farming reduces critical erosion shear stress (i.e., destabilises sediment). Important contrast with reef-building bivalves (R129, R130). Y now multi-tagged H&amp;B + CC.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Shi, B., et al.</t>
+          <t>Briant, N., et al.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Influence of macrobenthos (Meretrix meretrix Linnaeus) on erosion-accretion processes in intertidal flats: A case study from a cultivation zone</t>
+          <t>Carbon and nitrogen elemental and isotopic ratios of filter-feeding bivalves along the French coasts: An assessment of specific, geographic, seasonal and multi-decadal variations</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Journal of Geophysical Research: Biogeosciences</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>125</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Science of the Total Environment</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>613-614</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>e2019JG005345</t>
+          <t>196-207</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>AGU / Wiley</t>
+          <t>Elsevier</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Paired-site (cultivation zone vs adjacent bare flat) field investigation on the Rudong intertidal flat, Jiangsu Coast, China, quantifying the effect of high-density hard clam Meretrix meretrix (~137 ind. m⁻²) on bed erodibility, sediment-erosion thresholds, and erosion-accretion processes. Co-deployed instruments: ADV for turbulent flow velocity + bed-level change, SBE 26 Plus pressure sensors for wave-tide measurements, sediment-property + macrobenthos sampling. Found M. meretrix presence lowered critical erosion shear stress (~23.5% drop) — clams destabilise sediment under their cultivation density. Maps to MEL H&amp;B 1.4.1 (sediment biogeochemistry / dynamics).</t>
+          <t>ROCCH-network (Ifremer Mussel-Watch, ongoing since 1979) C, N, δ13C, δ15N analysis of bivalve soft tissues across THREE temporal scales in France: (i) SPATIAL — 189 samples from 74 stations spanning English Channel + Atlantic + Mediterranean, winter 2014, classified as littoral/estuary/bay/lagoon; (ii) SEASONAL — 4 seasons × 1998+1999 at Pointe Chemoulin, Bourgneuf-Coupelasse (AO), Cap Couronne (Med); (iii) DECADAL — every 3 years from 1987 to 2014 at 10 sites. Three species: Mytilus edulis (EC + AO), M. galloprovincialis (EC + Med), Crassostrea gigas (EC + AO). δ13C + δ15N used as food-source proxies; C/N (mol/mol) as body-condition proxy. Spatial variability tied to trophic status (oligo-Med vs meso-eutrophic EC+AO); seasonal C/N tied to mussel reproduction cycle; δ13C tied to trophic-resource variability at river-mouth sites; multi-decadal shifts in early 2000s with declining δ13C + δ15N likely linked to climate change. Maps to MEL WQ 1.1.1 (tissue bioindication) and WQ 1.2.1 (anthropogenic-N proxy via δ15N) — canonical Sub-rule 1a application.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Protocol (paired-site hydrodynamic + sediment-erosion observation under bivalve cultivation)</t>
+          <t>Protocol (ROCCH national bioindicator network + tissue elemental + isotopic IRMS protocol)</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Yes — synchronous hydrodynamic + sediment + macrobenthos measurements at paired sites with + without bivalve cultivation; standard erosion-threshold methodology.</t>
+          <t>Yes — gold-standard tissue elemental + isotopic methodology; 189 samples across 74 sites with consistent ROCCH sampling protocol since 1979; precision ≤0.2‰ for δ13C + δ15N validated against IAEA-N2, USGS-24 + casein/acetanilide standards.</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>No — research-grade instrumentation deployment (ADV, pressure sensors).</t>
+          <t>No — IRMS lab analysis requires specialist facility (EPOC Bordeaux in this case).</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -27804,42 +27866,37 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>ADV (acoustic Doppler velocimeter); SBE 26 Plus wave-tide recorder; grain-size + organic-content sediment analysis; benthic core sampling</t>
+          <t>ROCCH sampling kit (pooled 50-mussel or 10-oyster samples per station); 24-h depuration in site water; freeze-drying + stainless-steel homogenisation; 400 µg aliquots on Carlo Erba NC2500 Elemental Analyzer + Isoprime GV Instruments IRMS; standards casein, acetanilide, IAEA-N2, USGS-24</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Medium–High — research-grade hydrodynamic instrumentation</t>
+          <t>Medium–High — sampling is operational (institutional); IRMS analysis is the cost driver</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Multi-season (seasonal summer + winter comparison)</t>
+          <t>Multi-scale: seasonal (4 × 1998+1999 at 3 sites), spatial snapshot (winter 2014, 74 sites), decadal (3-yr intervals 1987–2014 at 10 sites)</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>Paired-site contrasts; critical shear-stress calculation; bed-level change time series</t>
+          <t>Spatial: across-region and across-ecosystem-typology comparisons (Kruskal-Wallis + post-hoc); seasonal: within-site temporal contrasts; multi-decadal: trend + shift detection (Pettitt, Mann-Kendall) on 30-year series</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>No — Paywalled (AGU / Wiley)</t>
+          <t>No — Paywalled (Elsevier); preprint may be available via Ifremer Archimer</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>Abstract + Methods (fetched)</t>
+          <t>Full PDF</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1029/2019JG005345</t>
-        </is>
-      </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>Counterintuitively, high-density burrowing, shell-protruding clams can lower the erosion threshold and destabilise the bed - the opposite of reef-builders.</t>
+          <t>https://doi.org/10.1016/j.scitotenv.2017.08.281</t>
         </is>
       </c>
       <c r="V132" t="inlineStr">
@@ -27847,7 +27904,7 @@
           <t>Original list</t>
         </is>
       </c>
-      <c r="W132" t="inlineStr">
+      <c r="W132" s="7" t="inlineStr">
         <is>
           <t>2 — Researcher</t>
         </is>
@@ -27859,32 +27916,32 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>Habitat &amp; Biodiversity, Climate Change</t>
+          <t>Water Quality</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>CC 3.1.1 — Wave attenuation / coastal protection (counter-example, Sub-rule 1c), H&amp;B 1.4.1 — Sediment biogeochemistry</t>
+          <t>WQ 1.1.1 — Bioextraction (tissue C/N + δ13C/δ15N isotopes)</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>Subtropical Pacific</t>
+          <t>Temperate Atlantic + Mediterranean</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>Hard clam (Meretrix meretrix)</t>
+          <t>Pacific oyster (Crassostrea / Magallana gigas), Blue mussel (Mytilus edulis), Mediterranean mussel (Mytilus galloprovincialis)</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Intertidal bottom culture (seeded clam beds)</t>
+          <t>Mixed (national network across multiple farm + wild-stock types)</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>Single site (paired cultivation vs control)</t>
+          <t>Multi-bay national (74 stations, 3 coastal regions)</t>
         </is>
       </c>
       <c r="AE132" t="inlineStr">
@@ -27899,7 +27956,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>Sediment sampling, Hydrodynamic measurement, Benthic infauna sampling</t>
+          <t>Tissue analysis, Stable isotope analysis</t>
         </is>
       </c>
       <c r="AH132" t="inlineStr">
@@ -27909,7 +27966,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>Intertidal / very shallow (&lt; 2 m)</t>
+          <t>Variable (littoral, estuary, bay, lagoon)</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
@@ -27919,7 +27976,7 @@
       </c>
       <c r="AK132" s="16" t="inlineStr">
         <is>
-          <t>To measure how dense infaunal bivalves affect sediment stability, compare a cultivation zone with an adjacent bare flat, co-deploying an acoustic Doppler velocimeter for turbulent flow and a wave-tide recorder to derive bed shear stress, alongside sediment grain-size and organic-content analysis and benthic cores. Track bed-level change and compute the critical erosion shear stress at each site; note the counterintuitive result that high-density burrowing, shell-protruding clams can lower the erosion threshold and destabilise the bed rather than protect it - the opposite of reef-building bivalves.</t>
+          <t>To establish a multi-scale bivalve-tissue bioindicator baseline, sample pooled soft tissue of the target species at many coastal stations (following a national mussel-watch protocol), depurate briefly in site water, freeze-dry and homogenise, then analyse carbon and nitrogen content and delta-13-C/delta-15-N on an elemental analyser coupled to an IRMS against certified standards. Design the sampling across spatial (many sites in one season), seasonal (repeated within a year) and multi-decadal scales so you can run typology comparisons (Kruskal-Wallis) and trend/shift detection (Pettitt, Mann-Kendall) on the long series.</t>
         </is>
       </c>
       <c r="AL132" s="17" t="inlineStr">
@@ -27929,7 +27986,7 @@
       </c>
       <c r="AM132" s="18" t="inlineStr">
         <is>
-          <t>shi_2020</t>
+          <t>briant_2018</t>
         </is>
       </c>
       <c r="AN132" s="19" t="n"/>
@@ -27937,72 +27994,62 @@
       <c r="AP132" s="19" t="n"/>
       <c r="AQ132" s="16" t="inlineStr">
         <is>
-          <t>Do Dense Infaunal Bivalves Stabilise or Erode Sediment?</t>
+          <t>Multi-Scale Bivalve-Tissue C/N Isotope Bioindicator Baseline</t>
         </is>
       </c>
       <c r="AR132" s="16" t="inlineStr">
         <is>
-          <t>Shi, Benwei; Pratolongo, Paula D; Du, Yongfen; Li, Jiasheng; Yang, S L; Wu, Jihua; Xu, Kehui; Wang, Ya Ping</t>
+          <t>Briant, Nicolas; Savoye, Nicolas; Chouvelon, Tiphaine; David, Valérie; Rodriguez, Samuel; Charlier, Karine; Sonke, Jeroen E; Chiffoleau, Jean François; Brach-Papa, Christophe; Knoery, Joël</t>
         </is>
       </c>
       <c r="AS132" s="16" t="inlineStr">
         <is>
-          <t>Important paper for the COUNTERINTUITIVE finding that high-density bivalve cultivation can DESTABILISE rather than stabilise sediments (the opposite of reef-building bivalves in Ysebaert 2018 R129) — context matters: the action of clams burrowing + protruding their shells reduces critical erosion shear stress. Important for MEL practitioners using H&amp;B 1.4.1 sediment-dynamics indicators on clam-cultivation sites: cultivation may shift the system toward erosion. Companion to Shi 2021 (L&amp;O, typhoon-induced erosion at same site) and Li 2021 (Ecohydrology &amp; Hydrobiology, same site, ~23% threshold drop confirmed). | v1.4 refinement: Added CC 3.1.1 per Sub-rule 1c (v1.4) — sediment-erosion threshold under clam cultivation is directly relevant to mollusc CC Obj 3.1 (coastal erosion), as a COUNTER-EXAMPLE showing high-density clam farming reduces critical erosion shear stress (i.e., destabilises sediment). Important contrast with reef-building bivalves (R129, R130). Y now multi-tagged H&amp;B + CC.</t>
+          <t>Canonical Sub-rule 1a precursor to R116 Liénart 2025 — same ROCCH network (Ifremer), same research consortium (Briant himself is co-author of Liénart 2025). Briant 2018 established the cross-scale (spatial + seasonal + decadal) methodology with 189 samples across 74 sites; Liénart 2025 extended it to 1141 samples × 1981–2021 at a curated 33-station subset. Together the pair represents the deepest multi-decadal bivalve-tissue bioindication dataset in MEL-relevant literature. Companion to Carmichael 2012 (R113, USA Atlantic estuaries) and the broader Sub-rule 1a corpus. Note: added at R134 out of CSV order (after R133 #44 Shi 2020) because the PDF arrived after the rest of the chat had been processed. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (tissue C/N + δ13C + δ15N only; no DO measurement). δ15N anthropogenic-N proxy framing noted in U but does not map to a v1.4 indicator.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Briant, N., et al.</t>
+          <t>Smithsonian MarineGEO</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Carbon and nitrogen elemental and isotopic ratios of filter-feeding bivalves along the French coasts: An assessment of specific, geographic, seasonal and multi-decadal variations</t>
+          <t>MarineGEO Fouling Community Monitoring Protocol</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Science of the Total Environment</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>613-614</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>196-207</t>
+          <t>Smithsonian Environmental Research Center (MarineGEO Protocols)</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Elsevier</t>
+          <t>Smithsonian Institution</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>ROCCH-network (Ifremer Mussel-Watch, ongoing since 1979) C, N, δ13C, δ15N analysis of bivalve soft tissues across THREE temporal scales in France: (i) SPATIAL — 189 samples from 74 stations spanning English Channel + Atlantic + Mediterranean, winter 2014, classified as littoral/estuary/bay/lagoon; (ii) SEASONAL — 4 seasons × 1998+1999 at Pointe Chemoulin, Bourgneuf-Coupelasse (AO), Cap Couronne (Med); (iii) DECADAL — every 3 years from 1987 to 2014 at 10 sites. Three species: Mytilus edulis (EC + AO), M. galloprovincialis (EC + Med), Crassostrea gigas (EC + AO). δ13C + δ15N used as food-source proxies; C/N (mol/mol) as body-condition proxy. Spatial variability tied to trophic status (oligo-Med vs meso-eutrophic EC+AO); seasonal C/N tied to mussel reproduction cycle; δ13C tied to trophic-resource variability at river-mouth sites; multi-decadal shifts in early 2000s with declining δ13C + δ15N likely linked to climate change. Maps to MEL WQ 1.1.1 (tissue bioindication) and WQ 1.2.1 (anthropogenic-N proxy via δ15N) — canonical Sub-rule 1a application.</t>
+          <t>Standardized settlement-panel protocol for sessile fouling/epibiont communities on submerged hard structures — directly transferable to bivalve/seaweed gear (ropes, cages, longlines) to quantify native epibiota colonising farmed biomass. Repeated farm vs reference, also informs community composition and settlement/recruitment.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Protocol (ROCCH national bioindicator network + tissue elemental + isotopic IRMS protocol)</t>
+          <t>Protocol</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Yes — gold-standard tissue elemental + isotopic methodology; 189 samples across 74 sites with consistent ROCCH sampling protocol since 1979; precision ≤0.2‰ for δ13C + δ15N validated against IAEA-N2, USGS-24 + casein/acetanilide standards.</t>
+          <t>Yes — full field package (PDF step-by-step methods, printable field sheet, data-submission workbook). Panels deployed for a set soak, photographed and/or scraped; sessile cover and taxa scored. Replicable by another team.</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>No — IRMS lab analysis requires specialist facility (EPOC Bordeaux in this case).</t>
+          <t>Partial — panel deployment/retrieval and photography are farmer-doable; species-level ID of fouling taxa needs a taxonomist or image-analysis partner.</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -28012,97 +28059,102 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>ROCCH sampling kit (pooled 50-mussel or 10-oyster samples per station); 24-h depuration in site water; freeze-drying + stainless-steel homogenisation; 400 µg aliquots on Carlo Erba NC2500 Elemental Analyzer + Isoprime GV Instruments IRMS; standards casein, acetanilide, IAEA-N2, USGS-24</t>
+          <t>Settlement panels (PVC), lines/weights, underwater camera; lab microscope for ID</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Medium–High — sampling is operational (institutional); IRMS analysis is the cost driver</t>
+          <t>Low–Medium — panels and gear inexpensive; cost sits in ID/processing time</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Multi-scale: seasonal (4 × 1998+1999 at 3 sites), spatial snapshot (winter 2014, 74 sites), decadal (3-yr intervals 1987–2014 at 10 sites)</t>
+          <t>Seasonal (1–3 months)</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>Spatial: across-region and across-ecosystem-typology comparisons (Kruskal-Wallis + post-hoc); seasonal: within-site temporal contrasts; multi-decadal: trend + shift detection (Pettitt, Mann-Kendall) on 30-year series</t>
+          <t>Percent-cover scoring, taxa richness/diversity; farm-vs-reference comparison</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>No — Paywalled (Elsevier); preprint may be available via Ifremer Archimer</t>
+          <t>Yes — Open (DOI-published, CC)</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>Full PDF</t>
+          <t>Abstract + Methods (fetched)</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.scitotenv.2017.08.281</t>
+          <t>https://marinegeo.github.io/fouling-community.html ; collection DOI https://doi.org/10.25573/serc.c.5506377</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Built for natural hard-bottom but transfers cleanly to farm gear; where organisms are too cryptic to ID from panels, an ARMS plus DNA-metabarcoding approach is the alternative.</t>
         </is>
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>Original list</t>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
         </is>
       </c>
       <c r="W133" s="7" t="inlineStr">
         <is>
-          <t>2 — Researcher</t>
+          <t>3 — Partnership</t>
         </is>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>Mollusk</t>
+          <t>Seaweed, Mollusk</t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>Water Quality</t>
+          <t>Habitat &amp; Biodiversity</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>WQ 1.1.1 — Bioextraction (tissue C/N + δ13C/δ15N isotopes)</t>
+          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 2.1.1 — Community composition, H&amp;B 2.2.1 — Spawning</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>Temperate Atlantic + Mediterranean</t>
+          <t>Cross-zone / global</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>Pacific oyster (Crassostrea / Magallana gigas), Blue mussel (Mytilus edulis), Mediterranean mussel (Mytilus galloprovincialis)</t>
+          <t>Not species-specific</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Mixed (national network across multiple farm + wild-stock types)</t>
+          <t>Not gear-specific</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr">
         <is>
-          <t>Multi-bay national (74 stations, 3 coastal regions)</t>
+          <t>Not scale-specific</t>
         </is>
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>Variable / seasonal</t>
+          <t>Not site-specific</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
         <is>
-          <t>Monoculture</t>
+          <t>Not specific</t>
         </is>
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>Tissue analysis, Stable isotope analysis</t>
+          <t>Visual survey</t>
         </is>
       </c>
       <c r="AH133" t="inlineStr">
@@ -28112,17 +28164,17 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>Variable (littoral, estuary, bay, lagoon)</t>
+          <t>Not depth-specific</t>
         </is>
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>Mixed exposure</t>
+          <t>Not exposure-specific</t>
         </is>
       </c>
       <c r="AK133" s="16" t="inlineStr">
         <is>
-          <t>To establish a multi-scale bivalve-tissue bioindicator baseline, sample pooled soft tissue of the target species at many coastal stations (following a national mussel-watch protocol), depurate briefly in site water, freeze-dry and homogenise, then analyse carbon and nitrogen content and delta-13-C/delta-15-N on an elemental analyser coupled to an IRMS against certified standards. Design the sampling across spatial (many sites in one season), seasonal (repeated within a year) and multi-decadal scales so you can run typology comparisons (Kruskal-Wallis) and trend/shift detection (Pettitt, Mann-Kendall) on the long series.</t>
+          <t>To quantify the attached (fouling/epibiont) community your gear supports, deploy standardized settlement panels (e.g. roughly hand-sized PVC plates) on the farm structures and at a reference site, leaving them for a set soak of a few months. Retrieve, photograph each panel and/or scrape it, and score percent cover and identify the sessile taxa under a microscope. Compare farm versus reference for cover, richness and community composition. A printable field sheet and data-submission workbook accompany the protocol; where hands-on ID is impractical, an autonomous-reef-monitoring-structure (ARMS) plus metabarcoding variant covers cryptic fauna.</t>
         </is>
       </c>
       <c r="AL133" s="17" t="inlineStr">
@@ -28132,7 +28184,7 @@
       </c>
       <c r="AM133" s="18" t="inlineStr">
         <is>
-          <t>briant_2018</t>
+          <t>smithsonianmarinegeo_2022</t>
         </is>
       </c>
       <c r="AN133" s="19" t="n"/>
@@ -28140,17 +28192,17 @@
       <c r="AP133" s="19" t="n"/>
       <c r="AQ133" s="16" t="inlineStr">
         <is>
-          <t>Multi-Scale Bivalve-Tissue C/N Isotope Bioindicator Baseline</t>
+          <t>Settlement-Panel Monitoring of Fouling &amp; Epibiont Communities on Farm Gear</t>
         </is>
       </c>
       <c r="AR133" s="16" t="inlineStr">
         <is>
-          <t>Briant, Nicolas; Savoye, Nicolas; Chouvelon, Tiphaine; David, Valérie; Rodriguez, Samuel; Charlier, Karine; Sonke, Jeroen E; Chiffoleau, Jean François; Brach-Papa, Christophe; Knoery, Joël</t>
+          <t>Smithsonian MarineGEO / Tennenbaum Marine Observatories Network</t>
         </is>
       </c>
       <c r="AS133" s="16" t="inlineStr">
         <is>
-          <t>Canonical Sub-rule 1a precursor to R116 Liénart 2025 — same ROCCH network (Ifremer), same research consortium (Briant himself is co-author of Liénart 2025). Briant 2018 established the cross-scale (spatial + seasonal + decadal) methodology with 189 samples across 74 sites; Liénart 2025 extended it to 1141 samples × 1981–2021 at a curated 33-station subset. Together the pair represents the deepest multi-decadal bivalve-tissue bioindication dataset in MEL-relevant literature. Companion to Carmichael 2012 (R113, USA Atlantic estuaries) and the broader Sub-rule 1a corpus. Note: added at R134 out of CSV order (after R133 #44 Shi 2020) because the PDF arrived after the rest of the chat had been processed. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (tissue C/N + δ13C + δ15N only; no DO measurement). δ15N anthropogenic-N proxy framing noted in U but does not map to a v1.4 indicator.</t>
+          <t>Smithsonian MarineGEO suite — the closest direct analogue to the Oyster-Reef protocol for the epibiota-on-structures case. ARMS (Autonomous Reef Monitoring Structures) is the metabarcoding-based cousin for cryptobiota where panel ID is impractical. Built for natural hard-bottom; transfers cleanly to aquaculture gear.</t>
         </is>
       </c>
     </row>
@@ -28162,7 +28214,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MarineGEO Fouling Community Monitoring Protocol</t>
+          <t>MarineGEO Oyster Reef Habitat Monitoring Protocol</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -28180,7 +28232,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Standardized settlement-panel protocol for sessile fouling/epibiont communities on submerged hard structures — directly transferable to bivalve/seaweed gear (ropes, cages, longlines) to quantify native epibiota colonising farmed biomass. Repeated farm vs reference, also informs community composition and settlement/recruitment.</t>
+          <t>Standard survey design for eastern-oyster reef habitat: reef area &amp; height, composition, oyster density &amp; size, rugosity, and associated mobile + sessile biodiversity. Methodology adopted from the Baggett/TNC handbook (universal metrics).</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -28190,12 +28242,12 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Yes — full field package (PDF step-by-step methods, printable field sheet, data-submission workbook). Panels deployed for a set soak, photographed and/or scraped; sessile cover and taxa scored. Replicable by another team.</t>
+          <t>Yes — reproducible reef-structure metrics plus associated-fauna collection, with site-selection, layout, workflow and data-submission guidance. Comparable across MarineGEO sites.</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Partial — panel deployment/retrieval and photography are farmer-doable; species-level ID of fouling taxa needs a taxonomist or image-analysis partner.</t>
+          <t>Partial — reef metrics (area, height, density, size) and fauna collection are farmer-doable; faunal ID/sorting needs a partner.</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -28205,12 +28257,12 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>Settlement panels (PVC), lines/weights, underwater camera; lab microscope for ID</t>
+          <t>Quadrats, calipers, transect tape, excavation trays, mesh bags; lab for ID</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Low–Medium — panels and gear inexpensive; cost sits in ID/processing time</t>
+          <t>Low–Medium</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -28220,12 +28272,12 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>Percent-cover scoring, taxa richness/diversity; farm-vs-reference comparison</t>
+          <t>Density/size-frequency, rugosity, diversity indices; farm/reference comparison</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>Yes — Open (DOI-published, CC)</t>
+          <t>Yes — Open (DOI-published)</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
@@ -28235,12 +28287,12 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>https://marinegeo.github.io/fouling-community.html ; collection DOI https://doi.org/10.25573/serc.c.5506377</t>
+          <t>https://marinegeo.si.edu/protocols/oyster-reefs</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>Built for natural hard-bottom but transfers cleanly to farm gear; where organisms are too cryptic to ID from panels, an ARMS plus DNA-metabarcoding approach is the alternative.</t>
+          <t>Specific to eastern oyster but the design transfers to other bivalve reef/longline contexts.</t>
         </is>
       </c>
       <c r="V134" t="inlineStr">
@@ -28255,7 +28307,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>Seaweed, Mollusk</t>
+          <t>Mollusk</t>
         </is>
       </c>
       <c r="Y134" t="inlineStr">
@@ -28265,7 +28317,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 2.1.1 — Community composition, H&amp;B 2.2.1 — Spawning</t>
+          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 1.2.1 — Mobile fauna, H&amp;B 2.1.1 — Community composition</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -28275,7 +28327,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>Not species-specific</t>
+          <t>Eastern oyster (Crassostrea virginica)</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -28320,7 +28372,7 @@
       </c>
       <c r="AK134" s="16" t="inlineStr">
         <is>
-          <t>To quantify the attached (fouling/epibiont) community your gear supports, deploy standardized settlement panels (e.g. roughly hand-sized PVC plates) on the farm structures and at a reference site, leaving them for a set soak of a few months. Retrieve, photograph each panel and/or scrape it, and score percent cover and identify the sessile taxa under a microscope. Compare farm versus reference for cover, richness and community composition. A printable field sheet and data-submission workbook accompany the protocol; where hands-on ID is impractical, an autonomous-reef-monitoring-structure (ARMS) plus metabarcoding variant covers cryptic fauna.</t>
+          <t>To monitor oyster-reef habitat (and by extension bivalve reef/longline structure), survey reef areal extent and height, oyster density and size, and rugosity, alongside the associated mobile and sessile fauna. Lay transects and place quadrats to measure density and size-frequency (calipers), record rugosity, and collect associated organisms (excavation trays, mesh bags) for lab identification. Compare farm/reef against a reference with density, size-frequency and diversity metrics. The design follows the universal reef metrics of the Baggett/TNC handbook, so results are comparable across sites.</t>
         </is>
       </c>
       <c r="AL134" s="17" t="inlineStr">
@@ -28330,7 +28382,7 @@
       </c>
       <c r="AM134" s="18" t="inlineStr">
         <is>
-          <t>smithsonianmarinegeo_2022</t>
+          <t>smithsonianmarinegeo_2022-b</t>
         </is>
       </c>
       <c r="AN134" s="19" t="n"/>
@@ -28338,47 +28390,52 @@
       <c r="AP134" s="19" t="n"/>
       <c r="AQ134" s="16" t="inlineStr">
         <is>
-          <t>Settlement-Panel Monitoring of Fouling &amp; Epibiont Communities on Farm Gear</t>
+          <t>Oyster-Reef Habitat Structure &amp; Associated-Fauna Survey</t>
         </is>
       </c>
       <c r="AR134" s="16" t="inlineStr">
         <is>
-          <t>Smithsonian MarineGEO / Tennenbaum Marine Observatories Network</t>
+          <t>Smithsonian MarineGEO</t>
         </is>
       </c>
       <c r="AS134" s="16" t="inlineStr">
         <is>
-          <t>Smithsonian MarineGEO suite — the closest direct analogue to the Oyster-Reef protocol for the epibiota-on-structures case. ARMS (Autonomous Reef Monitoring Structures) is the metabarcoding-based cousin for cryptobiota where panel ID is impractical. Built for natural hard-bottom; transfers cleanly to aquaculture gear.</t>
+          <t>Specific to eastern oyster (Crassostrea virginica) but design transfers to other bivalve reef/longline contexts. Pairs with the Baggett 2014 handbook (next row), the methodological parent.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Smithsonian MarineGEO</t>
+          <t>Baggett, L. P., et al.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MarineGEO Oyster Reef Habitat Monitoring Protocol</t>
+          <t>Oyster Habitat Restoration Monitoring and Assessment Handbook</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Smithsonian Environmental Research Center (MarineGEO Protocols)</t>
+          <t>The Nature Conservancy</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>96 pp</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Smithsonian Institution</t>
+          <t>The Nature Conservancy, Arlington, VA</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Standard survey design for eastern-oyster reef habitat: reef area &amp; height, composition, oyster density &amp; size, rugosity, and associated mobile + sessile biodiversity. Methodology adopted from the Baggett/TNC handbook (universal metrics).</t>
+          <t>TNC's standard for oyster reef monitoring. Four Universal Metrics (reef areal dimension, height, oyster density, size-frequency) + three Universal Environmental Variables (temperature, salinity, dissolved oxygen) + goal-based metrics for four ecosystem-service goals (incl. associated biodiversity and coastal protection / shoreline stabilisation).</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -28388,12 +28445,12 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Yes — reproducible reef-structure metrics plus associated-fauna collection, with site-selection, layout, workflow and data-submission guidance. Comparable across MarineGEO sites.</t>
+          <t>Yes — defines metrics, units, performance criteria and field methods in replicable detail; peer-reviewed companion is Baggett et al. 2015 (Restoration Ecology). Practitioners without capacity are explicitly told to collaborate.</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Partial — reef metrics (area, height, density, size) and fauna collection are farmer-doable; faunal ID/sorting needs a partner.</t>
+          <t>Partial — universal reef metrics and DO/temp/salinity (handheld probe) are farmer-executable; associated-biodiversity, disease and recruitment metrics need a partner lab.</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -28403,7 +28460,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>Quadrats, calipers, transect tape, excavation trays, mesh bags; lab for ID</t>
+          <t>Quadrats, calipers, transect tape, handheld multiprobe (T/S/DO), shell/recruitment trays</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -28413,17 +28470,17 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Seasonal (1–3 months)</t>
+          <t>Multi-year monitoring (&gt; 1 year)</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>Density/size-frequency, rugosity, diversity indices; farm/reference comparison</t>
+          <t>Universal-metric comparison to performance criteria; size-frequency; goal-based analysis</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>Yes — Open (DOI-published)</t>
+          <t>Yes — Open (free PDF)</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
@@ -28433,12 +28490,12 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>https://marinegeo.si.edu/protocols/oyster-reefs</t>
+          <t>http://www.oyster-restoration.org/wp-content/uploads/2014/01/Oyster-Habitat-Restoration-Monitoring-and-Assessment-Handbook.pdf</t>
         </is>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>Specific to eastern oyster but the design transfers to other bivalve reef/longline contexts.</t>
+          <t>Restoration-oriented but the universal metrics and environmental variables transfer to bivalve farming; the goal-based coastal-protection metrics are the practitioner route to wave attenuation.</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
@@ -28458,12 +28515,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>Habitat &amp; Biodiversity</t>
+          <t>Habitat &amp; Biodiversity, Water Quality, Climate Change</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 1.2.1 — Mobile fauna, H&amp;B 2.1.1 — Community composition</t>
+          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 2.1.1 — Community composition, H&amp;B 2.2.1 — Spawning, WQ 1.2.1 — Dissolved oxygen, CC 3.1.1 — Wave attenuation / coastal protection</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -28498,7 +28555,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>Visual survey</t>
+          <t>Visual survey, Water chemistry</t>
         </is>
       </c>
       <c r="AH135" t="inlineStr">
@@ -28518,7 +28575,7 @@
       </c>
       <c r="AK135" s="16" t="inlineStr">
         <is>
-          <t>To monitor oyster-reef habitat (and by extension bivalve reef/longline structure), survey reef areal extent and height, oyster density and size, and rugosity, alongside the associated mobile and sessile fauna. Lay transects and place quadrats to measure density and size-frequency (calipers), record rugosity, and collect associated organisms (excavation trays, mesh bags) for lab identification. Compare farm/reef against a reference with density, size-frequency and diversity metrics. The design follows the universal reef metrics of the Baggett/TNC handbook, so results are comparable across sites.</t>
+          <t>This TNC handbook is the standard for oyster-reef monitoring and defines exactly what to measure: four Universal Metrics (reef areal dimension, height, oyster density, size-frequency), three Universal Environmental Variables (temperature, salinity, dissolved oxygen via a handheld multiprobe), plus goal-based metrics for specific ecosystem services. Measure the universal metrics with quadrats, calipers and transect tape against defined performance criteria, and add the goal-based set for the service you care about - the coastal-protection metrics (shoreline position/elevation plus a wave gauge) are the practitioner route to a wave-attenuation indicator. It shares direct lineage with this MEL framework, its metrics and environmental variables transfer to bivalve farming, and teams without capacity are advised to collaborate.</t>
         </is>
       </c>
       <c r="AL135" s="17" t="inlineStr">
@@ -28528,7 +28585,7 @@
       </c>
       <c r="AM135" s="18" t="inlineStr">
         <is>
-          <t>smithsonianmarinegeo_2022-b</t>
+          <t>baggett_2014</t>
         </is>
       </c>
       <c r="AN135" s="19" t="n"/>
@@ -28536,52 +28593,47 @@
       <c r="AP135" s="19" t="n"/>
       <c r="AQ135" s="16" t="inlineStr">
         <is>
-          <t>Oyster-Reef Habitat Structure &amp; Associated-Fauna Survey</t>
+          <t>TNC Oyster Restoration Monitoring Handbook (Universal Metrics)</t>
         </is>
       </c>
       <c r="AR135" s="16" t="inlineStr">
         <is>
-          <t>Smithsonian MarineGEO</t>
+          <t>Baggett, L.P.; Powers, S.P.; Brumbaugh, R.D.; Coen, L.D.; DeAngelis, B.M.; Greene, J.K.; Hancock, B.T.; Morlock, S.M.</t>
         </is>
       </c>
       <c r="AS135" s="16" t="inlineStr">
         <is>
-          <t>Specific to eastern oyster (Crassostrea virginica) but design transfers to other bivalve reef/longline contexts. Pairs with the Baggett 2014 handbook (next row), the methodological parent.</t>
+          <t>TNC-authored — direct lineage with this MEL framework. Restoration-oriented but the universal metrics and environmental variables transfer to bivalve farming H&amp;B/WQ. The coastal-protection goal-based metric set is the practitioner route to CC 3.1.1 (shoreline position/elevation + wave-gauge/pressure-logger field methods).</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Baggett, L. P., et al.</t>
+          <t>Native Oyster Network (UK &amp; Ireland)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Oyster Habitat Restoration Monitoring and Assessment Handbook</t>
+          <t>European Native Oyster Habitat Restoration Monitoring Guidelines</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>The Nature Conservancy</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>96 pp</t>
+          <t>Native Oyster Restoration Alliance (NORA)</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>The Nature Conservancy, Arlington, VA</t>
+          <t>NORA / ZSL Native Oyster Network</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>TNC's standard for oyster reef monitoring. Four Universal Metrics (reef areal dimension, height, oyster density, size-frequency) + three Universal Environmental Variables (temperature, salinity, dissolved oxygen) + goal-based metrics for four ecosystem-service goals (incl. associated biodiversity and coastal protection / shoreline stabilisation).</t>
+          <t>European adaptation (39 authors, 7 countries) of the Baggett handbook for Ostrea edulis: Universal, Supplementary and Goal-Based Metrics suited to European native-oyster settings.</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -28591,12 +28643,12 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Yes — defines metrics, units, performance criteria and field methods in replicable detail; peer-reviewed companion is Baggett et al. 2015 (Restoration Ecology). Practitioners without capacity are explicitly told to collaborate.</t>
+          <t>Yes — metric definitions with multiple method options per metric; designed to answer performance questions for European native-oyster restoration.</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Partial — universal reef metrics and DO/temp/salinity (handheld probe) are farmer-executable; associated-biodiversity, disease and recruitment metrics need a partner lab.</t>
+          <t>Partial — universal/structural metrics farmer-doable; biodiversity and some supplementary metrics need partner lab.</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -28606,7 +28658,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>Quadrats, calipers, transect tape, handheld multiprobe (T/S/DO), shell/recruitment trays</t>
+          <t>Quadrats, transect tape, calipers; lab for ID</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -28621,12 +28673,12 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>Universal-metric comparison to performance criteria; size-frequency; goal-based analysis</t>
+          <t>Universal/supplementary/goal-based metric analysis</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>Yes — Open (free PDF)</t>
+          <t>Yes — Open (online guidelines)</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -28636,12 +28688,12 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>http://www.oyster-restoration.org/wp-content/uploads/2014/01/Oyster-Habitat-Restoration-Monitoring-and-Assessment-Handbook.pdf</t>
+          <t>https://nativeoysternetwork.org/2021/05/04/native-oyster-monitoring-guidelines/</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>Restoration-oriented but the universal metrics and environmental variables transfer to bivalve farming; the goal-based coastal-protection metrics are the practitioner route to wave attenuation.</t>
+          <t>Use it for European flat-oyster (Ostrea edulis) settings where the TNC handbook methods need adapting.</t>
         </is>
       </c>
       <c r="V136" t="inlineStr">
@@ -28661,22 +28713,22 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>Habitat &amp; Biodiversity, Water Quality, Climate Change</t>
+          <t>Habitat &amp; Biodiversity, Climate Change</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 2.1.1 — Community composition, H&amp;B 2.2.1 — Spawning, WQ 1.2.1 — Dissolved oxygen, CC 3.1.1 — Wave attenuation / coastal protection</t>
+          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 2.1.1 — Community composition, H&amp;B 2.2.1 — Spawning, CC 3.1.1 — Wave attenuation / coastal protection</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>Cross-zone / global</t>
+          <t>Temperate Atlantic</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>Eastern oyster (Crassostrea virginica)</t>
+          <t>European flat oyster (Ostrea edulis)</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -28701,7 +28753,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>Visual survey, Water chemistry</t>
+          <t>Visual survey</t>
         </is>
       </c>
       <c r="AH136" t="inlineStr">
@@ -28721,7 +28773,7 @@
       </c>
       <c r="AK136" s="16" t="inlineStr">
         <is>
-          <t>This TNC handbook is the standard for oyster-reef monitoring and defines exactly what to measure: four Universal Metrics (reef areal dimension, height, oyster density, size-frequency), three Universal Environmental Variables (temperature, salinity, dissolved oxygen via a handheld multiprobe), plus goal-based metrics for specific ecosystem services. Measure the universal metrics with quadrats, calipers and transect tape against defined performance criteria, and add the goal-based set for the service you care about - the coastal-protection metrics (shoreline position/elevation plus a wave gauge) are the practitioner route to a wave-attenuation indicator. It shares direct lineage with this MEL framework, its metrics and environmental variables transfer to bivalve farming, and teams without capacity are advised to collaborate.</t>
+          <t>This is the European adaptation of the TNC oyster handbook for the native flat oyster (Ostrea edulis), giving Universal, Supplementary and Goal-Based metrics with several method options per metric. Measure reef/bed extent, oyster density and size with quadrats, transect tape and calipers, choosing the method option that fits your setting, and analyse against the restoration performance questions. Use it in European native-oyster contexts where the Baggett handbook methods need adapting.</t>
         </is>
       </c>
       <c r="AL136" s="17" t="inlineStr">
@@ -28731,7 +28783,7 @@
       </c>
       <c r="AM136" s="18" t="inlineStr">
         <is>
-          <t>baggett_2014</t>
+          <t>ukireland_2021</t>
         </is>
       </c>
       <c r="AN136" s="19" t="n"/>
@@ -28739,34 +28791,34 @@
       <c r="AP136" s="19" t="n"/>
       <c r="AQ136" s="16" t="inlineStr">
         <is>
-          <t>TNC Oyster Restoration Monitoring Handbook (Universal Metrics)</t>
+          <t>European Native-Oyster Restoration Monitoring Guidelines</t>
         </is>
       </c>
       <c r="AR136" s="16" t="inlineStr">
         <is>
-          <t>Baggett, L.P.; Powers, S.P.; Brumbaugh, R.D.; Coen, L.D.; DeAngelis, B.M.; Greene, J.K.; Hancock, B.T.; Morlock, S.M.</t>
+          <t>Native Oyster Network (UK &amp; Ireland); Native Oyster Restoration Alliance (NORA)</t>
         </is>
       </c>
       <c r="AS136" s="16" t="inlineStr">
         <is>
-          <t>TNC-authored — direct lineage with this MEL framework. Restoration-oriented but the universal metrics and environmental variables transfer to bivalve farming H&amp;B/WQ. The coastal-protection goal-based metric set is the practitioner route to CC 3.1.1 (shoreline position/elevation + wave-gauge/pressure-logger field methods).</t>
+          <t>Use for European flat-oyster (Ostrea edulis) contexts where Baggett 2014 methods need adaptation. Complementary to the MarineGEO Oyster-Reef protocol and Baggett handbook.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Native Oyster Network (UK &amp; Ireland)</t>
+          <t>Smithsonian MarineGEO</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>European Native Oyster Habitat Restoration Monitoring Guidelines</t>
+          <t>MarineGEO Diver Visual Survey Protocol</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Native Oyster Restoration Alliance (NORA)</t>
+          <t>Smithsonian Environmental Research Center (MarineGEO Protocols)</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -28774,12 +28826,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>NORA / ZSL Native Oyster Network</t>
+          <t>Smithsonian Institution</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>European adaptation (39 authors, 7 countries) of the Baggett handbook for Ostrea edulis: Universal, Supplementary and Goal-Based Metrics suited to European native-oyster settings.</t>
+          <t>Standardized diver/snorkel belt-transect visual census of mobile fauna (fish, mobile invertebrates). Directly applicable to counting mobile fauna associated with a farm site.</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -28789,12 +28841,12 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Yes — metric definitions with multiple method options per metric; designed to answer performance questions for European native-oyster restoration.</t>
+          <t>Yes — fixed transect design with counts/size estimates and data sheet; on-the-spot ID. Reproducible across sites.</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Partial — universal/structural metrics farmer-doable; biodiversity and some supplementary metrics need partner lab.</t>
+          <t>Yes — belt/visual transects with field ID guides are farmer/diver-executable with no obligatory lab step (the canonical practitioner-tier method).</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -28804,27 +28856,27 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>Quadrats, transect tape, calipers; lab for ID</t>
+          <t>Transect tape, slate, dive/snorkel gear, ID guide</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Low–Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Multi-year monitoring (&gt; 1 year)</t>
+          <t>Seasonal (1–3 months)</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>Universal/supplementary/goal-based metric analysis</t>
+          <t>Abundance/size counts per transect; diversity indices</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>Yes — Open (online guidelines)</t>
+          <t>Yes — Open (DOI-published)</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
@@ -28834,12 +28886,12 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>https://nativeoysternetwork.org/2021/05/04/native-oyster-monitoring-guidelines/</t>
+          <t>https://doi.org/10.25573/serc.14717796</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>Use it for European flat-oyster (Ostrea edulis) settings where the TNC handbook methods need adapting.</t>
+          <t>Needs dive/snorkel competency and reasonable clarity; Reef Life Survey is an equivalent with a trained-diver network.</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
@@ -28849,32 +28901,32 @@
       </c>
       <c r="W137" s="7" t="inlineStr">
         <is>
-          <t>3 — Partnership</t>
+          <t>4 — Practitioner</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>Mollusk</t>
+          <t>Seaweed, Mollusk, Finfish</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>Habitat &amp; Biodiversity, Climate Change</t>
+          <t>Habitat &amp; Biodiversity</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 2.1.1 — Community composition, H&amp;B 2.2.1 — Spawning, CC 3.1.1 — Wave attenuation / coastal protection</t>
+          <t>H&amp;B 1.2.1 — Mobile fauna</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>Temperate Atlantic</t>
+          <t>Cross-zone / global</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>European flat oyster (Ostrea edulis)</t>
+          <t>Not species-specific</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -28889,7 +28941,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>Not site-specific</t>
+          <t>Clear (visual methods feasible)</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -28909,7 +28961,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Not depth-specific</t>
+          <t>Shallow nearshore (2–10 m)</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
@@ -28919,7 +28971,7 @@
       </c>
       <c r="AK137" s="16" t="inlineStr">
         <is>
-          <t>This is the European adaptation of the TNC oyster handbook for the native flat oyster (Ostrea edulis), giving Universal, Supplementary and Goal-Based metrics with several method options per metric. Measure reef/bed extent, oyster density and size with quadrats, transect tape and calipers, choosing the method option that fits your setting, and analyse against the restoration performance questions. Use it in European native-oyster contexts where the Baggett handbook methods need adapting.</t>
+          <t>To count mobile fauna (fish and mobile invertebrates) around a farm, run a standardized diver or snorkel belt-transect visual census: swim a fixed-length, fixed-width transect and record species and size estimates on a slate as you go. Repeat transects at the farm and a reference site and summarise as abundance and size per transect plus diversity indices. It needs dive/snorkel competency and reasonable water clarity; Reef Life Survey offers an equivalent standardized method and trained-diver network where more rigour or a citizen-science cohort is wanted.</t>
         </is>
       </c>
       <c r="AL137" s="17" t="inlineStr">
@@ -28929,7 +28981,7 @@
       </c>
       <c r="AM137" s="18" t="inlineStr">
         <is>
-          <t>ukireland_2021</t>
+          <t>smithsonianmarinegeo_2021</t>
         </is>
       </c>
       <c r="AN137" s="19" t="n"/>
@@ -28937,17 +28989,17 @@
       <c r="AP137" s="19" t="n"/>
       <c r="AQ137" s="16" t="inlineStr">
         <is>
-          <t>European Native-Oyster Restoration Monitoring Guidelines</t>
+          <t>Diver Belt-Transect Visual Census of Mobile Fauna</t>
         </is>
       </c>
       <c r="AR137" s="16" t="inlineStr">
         <is>
-          <t>Native Oyster Network (UK &amp; Ireland); Native Oyster Restoration Alliance (NORA)</t>
+          <t>Smithsonian MarineGEO</t>
         </is>
       </c>
       <c r="AS137" s="16" t="inlineStr">
         <is>
-          <t>Use for European flat-oyster (Ostrea edulis) contexts where Baggett 2014 methods need adaptation. Complementary to the MarineGEO Oyster-Reef protocol and Baggett handbook.</t>
+          <t>Reef Life Survey (RLS) provides an equivalent globally standardized diver visual-census methods manual and trained-diver network — an alternative where added rigour or a citizen-science cohort is wanted. Requires dive competency and reasonable water clarity.</t>
         </is>
       </c>
     </row>
@@ -28959,7 +29011,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MarineGEO Diver Visual Survey Protocol</t>
+          <t>MarineGEO Beach Seine Protocol</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -28977,7 +29029,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Standardized diver/snorkel belt-transect visual census of mobile fauna (fish, mobile invertebrates). Directly applicable to counting mobile fauna associated with a farm site.</t>
+          <t>Standardized beach-seine sampling of nekton (fish, mobile crustacea) in shallow soft-sediment habitats; transfers to nearshore farm-margin mobile-fauna sampling.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -28987,12 +29039,12 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Yes — fixed transect design with counts/size estimates and data sheet; on-the-spot ID. Reproducible across sites.</t>
+          <t>Yes — standardized net, haul design and processing with data sheet; reproducible.</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Yes — belt/visual transects with field ID guides are farmer/diver-executable with no obligatory lab step (the canonical practitioner-tier method).</t>
+          <t>Yes — seine hauls with field ID/measure are farmer-executable; no obligatory lab step.</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -29002,7 +29054,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>Transect tape, slate, dive/snorkel gear, ID guide</t>
+          <t>Beach seine net, measuring board, buckets, ID guide</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -29017,7 +29069,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>Abundance/size counts per transect; diversity indices</t>
+          <t>Catch-per-haul abundance/size; diversity</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -29032,12 +29084,12 @@
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>https://doi.org/10.25573/serc.14717796</t>
+          <t>https://doi.org/10.25573/serc.14925105</t>
         </is>
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>Needs dive/snorkel competency and reasonable clarity; Reef Life Survey is an equivalent with a trained-diver network.</t>
+          <t>Best for shallow, wadeable, soft-bottom margins.</t>
         </is>
       </c>
       <c r="V138" t="inlineStr">
@@ -29087,7 +29139,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>Clear (visual methods feasible)</t>
+          <t>Variable / seasonal</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -29107,17 +29159,17 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Shallow nearshore (2–10 m)</t>
+          <t>Intertidal / very shallow (&lt; 2 m)</t>
         </is>
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>Not exposure-specific</t>
+          <t>Sheltered</t>
         </is>
       </c>
       <c r="AK138" s="16" t="inlineStr">
         <is>
-          <t>To count mobile fauna (fish and mobile invertebrates) around a farm, run a standardized diver or snorkel belt-transect visual census: swim a fixed-length, fixed-width transect and record species and size estimates on a slate as you go. Repeat transects at the farm and a reference site and summarise as abundance and size per transect plus diversity indices. It needs dive/snorkel competency and reasonable water clarity; Reef Life Survey offers an equivalent standardized method and trained-diver network where more rigour or a citizen-science cohort is wanted.</t>
+          <t>To sample nekton (fish and mobile crustaceans) along shallow, wadeable farm margins, use a standardized beach-seine haul: deploy the net over a set area, retrieve it, then identify, count and measure the catch on a board before release. Express results as catch-per-haul abundance and size, with diversity indices, comparing farm-margin to reference hauls. Best for shallow soft-bottom margins; it complements diver and baited-camera methods for the mobile-fauna indicator.</t>
         </is>
       </c>
       <c r="AL138" s="17" t="inlineStr">
@@ -29127,7 +29179,7 @@
       </c>
       <c r="AM138" s="18" t="inlineStr">
         <is>
-          <t>smithsonianmarinegeo_2021</t>
+          <t>smithsonianmarinegeo_2021-b</t>
         </is>
       </c>
       <c r="AN138" s="19" t="n"/>
@@ -29135,7 +29187,7 @@
       <c r="AP138" s="19" t="n"/>
       <c r="AQ138" s="16" t="inlineStr">
         <is>
-          <t>Diver Belt-Transect Visual Census of Mobile Fauna</t>
+          <t>Beach-Seine Sampling of Nearshore Nekton</t>
         </is>
       </c>
       <c r="AR138" s="16" t="inlineStr">
@@ -29145,7 +29197,7 @@
       </c>
       <c r="AS138" s="16" t="inlineStr">
         <is>
-          <t>Reef Life Survey (RLS) provides an equivalent globally standardized diver visual-census methods manual and trained-diver network — an alternative where added rigour or a citizen-science cohort is wanted. Requires dive competency and reasonable water clarity.</t>
+          <t>Best for shallow, wadeable, soft-bottom margins; complements diver/BRUV methods for the mobile-fauna indicator.</t>
         </is>
       </c>
     </row>
@@ -29157,7 +29209,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MarineGEO Beach Seine Protocol</t>
+          <t>MarineGEO Benthic Photoquadrat Protocol</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -29175,7 +29227,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Standardized beach-seine sampling of nekton (fish, mobile crustacea) in shallow soft-sediment habitats; transfers to nearshore farm-margin mobile-fauna sampling.</t>
+          <t>Standardized photo-quadrat survey of benthic cover/community (point-count image analysis). Supports characterising the epibenthic community around a farm; for true infauna use grab-based methods (SEPA/NS 9410).</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -29185,12 +29237,12 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Yes — standardized net, haul design and processing with data sheet; reproducible.</t>
+          <t>Yes — quadrat photo design with point-count image analysis (e.g., CoralNet); reproducible and re-auditable.</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Yes — seine hauls with field ID/measure are farmer-executable; no obligatory lab step.</t>
+          <t>Partial — photo capture is farmer-doable; point-count image annotation/ID is a skilled (often partner) step.</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -29200,12 +29252,12 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>Beach seine net, measuring board, buckets, ID guide</t>
+          <t>Quadrat frame, underwater camera; image-analysis software (CoralNet/CPCe)</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Low–Medium</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -29215,7 +29267,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>Catch-per-haul abundance/size; diversity</t>
+          <t>Point-count percent cover; community composition</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -29230,12 +29282,12 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>https://doi.org/10.25573/serc.14925105</t>
+          <t>https://doi.org/10.25573/serc.14717823</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>Best for shallow, wadeable, soft-bottom margins.</t>
+          <t>Captures epibenthic cover, not soft-sediment infauna - pair with a sediment protocol for the seabed itself.</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
@@ -29245,12 +29297,12 @@
       </c>
       <c r="W139" s="7" t="inlineStr">
         <is>
-          <t>4 — Practitioner</t>
+          <t>3 — Partnership</t>
         </is>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>Seaweed, Mollusk, Finfish</t>
+          <t>Seaweed, Mollusk</t>
         </is>
       </c>
       <c r="Y139" t="inlineStr">
@@ -29260,7 +29312,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>H&amp;B 1.2.1 — Mobile fauna</t>
+          <t>H&amp;B 1.3.1 — Benthic infauna, H&amp;B 2.1.1 — Community composition</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -29285,7 +29337,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>Variable / seasonal</t>
+          <t>Clear (visual methods feasible)</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -29305,17 +29357,17 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>Intertidal / very shallow (&lt; 2 m)</t>
+          <t>Shallow nearshore (2–10 m)</t>
         </is>
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>Sheltered</t>
+          <t>Not exposure-specific</t>
         </is>
       </c>
       <c r="AK139" s="16" t="inlineStr">
         <is>
-          <t>To sample nekton (fish and mobile crustaceans) along shallow, wadeable farm margins, use a standardized beach-seine haul: deploy the net over a set area, retrieve it, then identify, count and measure the catch on a board before release. Express results as catch-per-haul abundance and size, with diversity indices, comparing farm-margin to reference hauls. Best for shallow soft-bottom margins; it complements diver and baited-camera methods for the mobile-fauna indicator.</t>
+          <t>To characterise the epibenthic community (cover) around a farm, photograph benthic quadrats along transects and analyse the images by point-count (e.g. CoralNet or CPCe), scoring percent cover per taxon. Repeat at farm and reference sites and compare community composition. The image archive is re-analysable and auditable; note this captures epibenthic cover, not soft-sediment infauna - pair it with a sediment protocol for the seabed itself.</t>
         </is>
       </c>
       <c r="AL139" s="17" t="inlineStr">
@@ -29325,7 +29377,7 @@
       </c>
       <c r="AM139" s="18" t="inlineStr">
         <is>
-          <t>smithsonianmarinegeo_2021-b</t>
+          <t>smithsonianmarinegeo_2021-c</t>
         </is>
       </c>
       <c r="AN139" s="19" t="n"/>
@@ -29333,7 +29385,7 @@
       <c r="AP139" s="19" t="n"/>
       <c r="AQ139" s="16" t="inlineStr">
         <is>
-          <t>Beach-Seine Sampling of Nearshore Nekton</t>
+          <t>Benthic Photoquadrat Cover Survey (Point-Count Imaging)</t>
         </is>
       </c>
       <c r="AR139" s="16" t="inlineStr">
@@ -29343,7 +29395,7 @@
       </c>
       <c r="AS139" s="16" t="inlineStr">
         <is>
-          <t>Best for shallow, wadeable, soft-bottom margins; complements diver/BRUV methods for the mobile-fauna indicator.</t>
+          <t>Image archives are re-analysable and auditable. Captures epibenthic cover (not soft-sediment infauna). Pairs with the Sediment Organic Matter protocol for soft-sediment characterisation.</t>
         </is>
       </c>
     </row>
@@ -29355,7 +29407,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MarineGEO Benthic Photoquadrat Protocol</t>
+          <t>MarineGEO Sediment Organic Matter Protocol</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -29373,7 +29425,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Standardized photo-quadrat survey of benthic cover/community (point-count image analysis). Supports characterising the epibenthic community around a farm; for true infauna use grab-based methods (SEPA/NS 9410).</t>
+          <t>Standardized sediment sampling + loss-on-ignition for organic-matter content (a core sediment-condition descriptor under and around a farm).</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -29383,12 +29435,12 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Yes — quadrat photo design with point-count image analysis (e.g., CoralNet); reproducible and re-auditable.</t>
+          <t>Yes — coring/grab + drying + loss-on-ignition with data sheet; reproducible.</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Partial — photo capture is farmer-doable; point-count image annotation/ID is a skilled (often partner) step.</t>
+          <t>Partial — sediment collection farmer-doable; LOI needs a drying oven/muffle furnace (basic lab step).</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -29398,12 +29450,12 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>Quadrat frame, underwater camera; image-analysis software (CoralNet/CPCe)</t>
+          <t>Sediment corer/grab, drying oven, muffle furnace, balance</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Low–Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -29413,7 +29465,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>Point-count percent cover; community composition</t>
+          <t>%LOI / organic-matter content; farm-vs-reference</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -29428,12 +29480,12 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>https://doi.org/10.25573/serc.14717823</t>
+          <t>https://doi.org/10.25573/serc.14925111</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>Captures epibenthic cover, not soft-sediment infauna - pair with a sediment protocol for the seabed itself.</t>
+          <t>A simple, low-cost sediment-condition metric; for full biogeochemistry use a benthic standard such as SEPA or NS 9410.</t>
         </is>
       </c>
       <c r="V140" t="inlineStr">
@@ -29458,7 +29510,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>H&amp;B 1.3.1 — Benthic infauna, H&amp;B 2.1.1 — Community composition</t>
+          <t>H&amp;B 1.4.1 — Sediment</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -29483,7 +29535,7 @@
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>Clear (visual methods feasible)</t>
+          <t>Not site-specific</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -29493,7 +29545,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>Visual survey</t>
+          <t>Sediment sampling</t>
         </is>
       </c>
       <c r="AH140" t="inlineStr">
@@ -29503,7 +29555,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Shallow nearshore (2–10 m)</t>
+          <t>Not depth-specific</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
@@ -29513,7 +29565,7 @@
       </c>
       <c r="AK140" s="16" t="inlineStr">
         <is>
-          <t>To characterise the epibenthic community (cover) around a farm, photograph benthic quadrats along transects and analyse the images by point-count (e.g. CoralNet or CPCe), scoring percent cover per taxon. Repeat at farm and reference sites and compare community composition. The image archive is re-analysable and auditable; note this captures epibenthic cover, not soft-sediment infauna - pair it with a sediment protocol for the seabed itself.</t>
+          <t>To measure sediment organic-matter content under and around a farm, collect sediment by corer or grab, dry the sample, then combust it in a muffle furnace and weigh before and after to get percent loss-on-ignition (organic-matter content). Sample farm and reference stations and compare. It is a simple, low-cost sediment-condition metric; for full biogeochemistry (redox, sulphide, nutrient flux) use the SEPA or NS 9410 benthic standards.</t>
         </is>
       </c>
       <c r="AL140" s="17" t="inlineStr">
@@ -29523,7 +29575,7 @@
       </c>
       <c r="AM140" s="18" t="inlineStr">
         <is>
-          <t>smithsonianmarinegeo_2021-c</t>
+          <t>smithsonianmarinegeo_2021-d</t>
         </is>
       </c>
       <c r="AN140" s="19" t="n"/>
@@ -29531,7 +29583,7 @@
       <c r="AP140" s="19" t="n"/>
       <c r="AQ140" s="16" t="inlineStr">
         <is>
-          <t>Benthic Photoquadrat Cover Survey (Point-Count Imaging)</t>
+          <t>Sediment Organic-Matter Monitoring (Loss-on-Ignition)</t>
         </is>
       </c>
       <c r="AR140" s="16" t="inlineStr">
@@ -29541,37 +29593,45 @@
       </c>
       <c r="AS140" s="16" t="inlineStr">
         <is>
-          <t>Image archives are re-analysable and auditable. Captures epibenthic cover (not soft-sediment infauna). Pairs with the Sediment Organic Matter protocol for soft-sediment characterisation.</t>
+          <t>A simple, low-cost sediment-condition metric; for full biogeochemistry (redox, sulphide, DIN flux) use the SEPA / NS 9410 benthic standards (rows below).</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Smithsonian MarineGEO</t>
+          <t>Langlois, T., et al.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MarineGEO Sediment Organic Matter Protocol</t>
+          <t>A field and video-annotation guide for baited remote underwater stereo-video (stereo-BRUV) surveys of demersal fish assemblages</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Smithsonian Environmental Research Center (MarineGEO Protocols)</t>
+          <t>Methods in Ecology and Evolution / open NESP field manual</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>1401–1409</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Smithsonian Institution</t>
+          <t>Wiley / NESP Marine Biodiversity Hub</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Standardized sediment sampling + loss-on-ignition for organic-matter content (a core sediment-condition descriptor under and around a farm).</t>
+          <t>The first globally accepted standardized guide for stereo-BRUV surveys of fish assemblages — design, camera settings, field operations, and video annotation, with links to data validation/archiving (GlobalArchive). Covers mobile fauna and the finfish fish-attraction case.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -29581,12 +29641,12 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Yes — coring/grab + drying + loss-on-ignition with data sheet; reproducible.</t>
+          <t>Yes — fully documented field + annotation SOP intended for cross-study interoperability (FAIR workflows).</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Partial — sediment collection farmer-doable; LOI needs a drying oven/muffle furnace (basic lab step).</t>
+          <t>Partial — baited-camera deployment is practitioner-doable, but stereo calibration and photogrammetric annotation/measurement (EventMeasure) need a trained analyst or partner.</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -29596,27 +29656,27 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>Sediment corer/grab, drying oven, muffle furnace, balance</t>
+          <t>Stereo camera pair + frame, bait arm, ropes/floats; annotation software (EventMeasure)</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Seasonal (1–3 months)</t>
+          <t>Short campaign (days to 2 weeks)</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>%LOI / organic-matter content; farm-vs-reference</t>
+          <t>MaxN relative abundance, length/biomass from stereo; assemblage composition</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>Yes — Open (DOI-published)</t>
+          <t>Yes — Open (CC-BY; open GitHub manual)</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
@@ -29626,12 +29686,12 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>https://doi.org/10.25573/serc.14925111</t>
+          <t>https://benthic-bruvs-field-manual.github.io/ ; https://doi.org/10.1111/2041-210X.13470</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>A simple, low-cost sediment-condition metric; for full biogeochemistry use a benthic standard such as SEPA or NS 9410.</t>
+          <t>A single-camera BRUV is a lower-cost variant (relative abundance only, no lengths).</t>
         </is>
       </c>
       <c r="V141" t="inlineStr">
@@ -29646,7 +29706,7 @@
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>Seaweed, Mollusk</t>
+          <t>Mollusk, Finfish, Seaweed</t>
         </is>
       </c>
       <c r="Y141" t="inlineStr">
@@ -29656,7 +29716,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>H&amp;B 1.4.1 — Sediment</t>
+          <t>H&amp;B 1.2.1 — Mobile fauna</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -29681,7 +29741,7 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>Not site-specific</t>
+          <t>Clear (visual methods feasible)</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -29691,7 +29751,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>Sediment sampling</t>
+          <t>BRUVs / video</t>
         </is>
       </c>
       <c r="AH141" t="inlineStr">
@@ -29701,7 +29761,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Not depth-specific</t>
+          <t>Coastal (10–30 m)</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
@@ -29711,7 +29771,7 @@
       </c>
       <c r="AK141" s="16" t="inlineStr">
         <is>
-          <t>To measure sediment organic-matter content under and around a farm, collect sediment by corer or grab, dry the sample, then combust it in a muffle furnace and weigh before and after to get percent loss-on-ignition (organic-matter content). Sample farm and reference stations and compare. It is a simple, low-cost sediment-condition metric; for full biogeochemistry (redox, sulphide, nutrient flux) use the SEPA or NS 9410 benthic standards.</t>
+          <t>To survey fish assemblages (mobile fauna, and fish attraction at finfish farms) without diving, deploy baited remote underwater stereo-video (stereo-BRUV): a paired-camera frame with a bait arm, set on the seabed for a standard soak. Annotate the video to relative abundance (MaxN) and, from the stereo pair, individual lengths and biomass, following the standardized field-and-annotation SOP for cross-study comparability. A single-camera BRUV is a lower-cost practitioner variant (relative abundance only, no lengths), and data archive to a standardized repository (GlobalArchive).</t>
         </is>
       </c>
       <c r="AL141" s="17" t="inlineStr">
@@ -29721,7 +29781,7 @@
       </c>
       <c r="AM141" s="18" t="inlineStr">
         <is>
-          <t>smithsonianmarinegeo_2021-d</t>
+          <t>langlois_2020</t>
         </is>
       </c>
       <c r="AN141" s="19" t="n"/>
@@ -29729,70 +29789,62 @@
       <c r="AP141" s="19" t="n"/>
       <c r="AQ141" s="16" t="inlineStr">
         <is>
-          <t>Sediment Organic-Matter Monitoring (Loss-on-Ignition)</t>
+          <t>Baited Stereo-Video Survey of Fish Assemblages (Stereo-BRUV)</t>
         </is>
       </c>
       <c r="AR141" s="16" t="inlineStr">
         <is>
-          <t>Smithsonian MarineGEO</t>
+          <t>Langlois, T.; Goetze, J.; Bond, T.; et al. (NESP Marine Biodiversity Hub)</t>
         </is>
       </c>
       <c r="AS141" s="16" t="inlineStr">
         <is>
-          <t>A simple, low-cost sediment-condition metric; for full biogeochemistry (redox, sulphide, DIN flux) use the SEPA / NS 9410 benthic standards (rows below).</t>
+          <t>Single-camera baited cameras (BRUVs) are a lower-cost practitioner variant (relative abundance only, no lengths). GlobalArchive (globalarchive.org) is the standardized data repository. Part of the NESP Marine Sampling Field Manuals collection (next row). For finfish, this is the route to the fish-attraction facet of Finfish H&amp;B 2.1.1.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Langlois, T., et al.</t>
+          <t>Przeslawski, R. &amp; Foster, S. (. ). —. N. M. B. H.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>A field and video-annotation guide for baited remote underwater stereo-video (stereo-BRUV) surveys of demersal fish assemblages</t>
+          <t>Field Manuals for Marine Sampling to Monitor Australian Waters (BRUVs, grabs, sleds, towed video, AUVs)</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Methods in Ecology and Evolution / open NESP field manual</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>11</v>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>1401–1409</t>
+          <t>NESP Marine Biodiversity Hub</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Wiley / NESP Marine Biodiversity Hub</t>
+          <t>National Environmental Science Program (Australia)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>The first globally accepted standardized guide for stereo-BRUV surveys of fish assemblages — design, camera settings, field operations, and video annotation, with links to data validation/archiving (GlobalArchive). Covers mobile fauna and the finfish fish-attraction case.</t>
+          <t>A collection of standardized field-sampling SOPs (benthic stereo-BRUVs, grabs/cores, sleds, towed video, multibeam) used as a national design standard, spanning mobile fauna, benthic infauna and sediment.</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Protocol</t>
+          <t>Reference (usable design tool / SOP collection)</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Yes — fully documented field + annotation SOP intended for cross-study interoperability (FAIR workflows).</t>
+          <t>Adequate as a design/standardisation resource: each manual gives equipment, deployment and QA guidance a programme is built from; individual manuals are themselves executable protocols.</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>Partial — baited-camera deployment is practitioner-doable, but stereo calibration and photogrammetric annotation/measurement (EventMeasure) need a trained analyst or partner.</t>
+          <t>No — most manuals assume a research vessel and specialist gear/expertise across the workflow.</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -29802,42 +29854,42 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>Stereo camera pair + frame, bait arm, ropes/floats; annotation software (EventMeasure)</t>
+          <t>Varies by manual (research vessel, grabs, towed/stereo video, multibeam)</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Short campaign (days to 2 weeks)</t>
+          <t>Not time-specific</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>MaxN relative abundance, length/biomass from stereo; assemblage composition</t>
+          <t>Per-manual standardized analysis</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>Yes — Open (CC-BY; open GitHub manual)</t>
+          <t>Yes — Open (CC-BY)</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>Abstract + Methods (fetched)</t>
+          <t>Abstract only</t>
         </is>
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>https://benthic-bruvs-field-manual.github.io/ ; https://doi.org/10.1111/2041-210X.13470</t>
+          <t>https://www.nespmarine.edu.au/field-manuals</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>A single-camera BRUV is a lower-cost variant (relative abundance only, no lengths).</t>
+          <t>Use it to design comparable benthic and mobile-fauna campaigns and to standardise across individual manuals.</t>
         </is>
       </c>
       <c r="V142" t="inlineStr">
@@ -29847,22 +29899,22 @@
       </c>
       <c r="W142" s="7" t="inlineStr">
         <is>
-          <t>3 — Partnership</t>
+          <t>2 — Researcher</t>
         </is>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>Mollusk, Finfish, Seaweed</t>
+          <t>Seaweed, Mollusk, Finfish</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>Habitat &amp; Biodiversity</t>
+          <t>Habitat &amp; Biodiversity, Cross-cutting / Framework</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>H&amp;B 1.2.1 — Mobile fauna</t>
+          <t>H&amp;B 1.2.1 — Mobile fauna, H&amp;B 1.3.1 — Benthic infauna, H&amp;B 1.4.1 — Sediment, Cross-cutting / framework</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -29887,7 +29939,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>Clear (visual methods feasible)</t>
+          <t>Not site-specific</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -29897,7 +29949,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>BRUVs / video</t>
+          <t>Mixed methods</t>
         </is>
       </c>
       <c r="AH142" t="inlineStr">
@@ -29907,7 +29959,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>Coastal (10–30 m)</t>
+          <t>Not depth-specific</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
@@ -29917,17 +29969,17 @@
       </c>
       <c r="AK142" s="16" t="inlineStr">
         <is>
-          <t>To survey fish assemblages (mobile fauna, and fish attraction at finfish farms) without diving, deploy baited remote underwater stereo-video (stereo-BRUV): a paired-camera frame with a bait arm, set on the seabed for a standard soak. Annotate the video to relative abundance (MaxN) and, from the stereo pair, individual lengths and biomass, following the standardized field-and-annotation SOP for cross-study comparability. A single-camera BRUV is a lower-cost practitioner variant (relative abundance only, no lengths), and data archive to a standardized repository (GlobalArchive).</t>
+          <t>This is a collection of standardized Australian field-sampling manuals (benthic stereo-BRUVs, grabs and cores, towed video, sleds, multibeam) used as a national design standard spanning mobile fauna, benthic infauna and sediment. Use it to design comparable benthic and mobile-fauna campaigns and to lift indicator-specific manuals (such as the stereo-BRUV manual) into a coherent programme, rather than as a single procedure.</t>
         </is>
       </c>
       <c r="AL142" s="17" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Ref</t>
         </is>
       </c>
       <c r="AM142" s="18" t="inlineStr">
         <is>
-          <t>langlois_2020</t>
+          <t>przeslawski_2018</t>
         </is>
       </c>
       <c r="AN142" s="19" t="n"/>
@@ -29935,62 +29987,62 @@
       <c r="AP142" s="19" t="n"/>
       <c r="AQ142" s="16" t="inlineStr">
         <is>
-          <t>Baited Stereo-Video Survey of Fish Assemblages (Stereo-BRUV)</t>
+          <t>Australian Marine-Sampling Field Manuals (Design Reference)</t>
         </is>
       </c>
       <c r="AR142" s="16" t="inlineStr">
         <is>
-          <t>Langlois, T.; Goetze, J.; Bond, T.; et al. (NESP Marine Biodiversity Hub)</t>
+          <t>Przeslawski, R.; Foster, S. (eds.) — NESP Marine Biodiversity Hub</t>
         </is>
       </c>
       <c r="AS142" s="16" t="inlineStr">
         <is>
-          <t>Single-camera baited cameras (BRUVs) are a lower-cost practitioner variant (relative abundance only, no lengths). GlobalArchive (globalarchive.org) is the standardized data repository. Part of the NESP Marine Sampling Field Manuals collection (next row). For finfish, this is the route to the fish-attraction facet of Finfish H&amp;B 2.1.1.</t>
+          <t>Most useful for designing comparable benthic/mobile-fauna campaigns; lifts indicator-specific manuals (e.g., the stereo-BRUV manual above) into a coherent programme. Tier T2 as a researcher-grade design tool.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Przeslawski, R. &amp; Foster, S. (. ). —. N. M. B. H.</t>
+          <t>Scottish Environment Protection Agency (SEPA)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Field Manuals for Marine Sampling to Monitor Australian Waters (BRUVs, grabs, sleds, towed video, AUVs)</t>
+          <t>Fish Farm Manual — Benthic Monitoring (Standard &amp; Extended surveys; Infaunal Quality Index)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>NESP Marine Biodiversity Hub</t>
+          <t>SEPA Aquaculture regulatory guidance</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>National Environmental Science Program (Australia)</t>
+          <t>Scottish Environment Protection Agency</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>A collection of standardized field-sampling SOPs (benthic stereo-BRUVs, grabs/cores, sleds, towed video, multibeam) used as a national design standard, spanning mobile fauna, benthic infauna and sediment.</t>
+          <t>Regulated benthic-monitoring SOP for marine farms: benthic grab survey, sediment chemistry, and the Infaunal Quality Index (IQI = taxa diversity + AMBI + Simpson evenness). Finfish-origin but the infauna+sediment methodology transfers to bivalve/seaweed farm monitoring.</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Reference (usable design tool / SOP collection)</t>
+          <t>Protocol</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Adequate as a design/standardisation resource: each manual gives equipment, deployment and QA guidance a programme is built from; individual manuals are themselves executable protocols.</t>
+          <t>Yes — prescriptive grab design, sieving/fixation, taxonomic processing and index computation with reporting templates. Compliance-grade reproducibility.</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>No — most manuals assume a research vessel and specialist gear/expertise across the workflow.</t>
+          <t>Partial — grab sampling from a small vessel is farmer-doable, but macrofauna sorting/ID and sediment chemistry require an accredited partner lab.</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -30000,42 +30052,42 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>Varies by manual (research vessel, grabs, towed/stereo video, multibeam)</t>
+          <t>Day/van-Veen grab, sieves (0.5/1 mm), sample jars; partner lab for taxonomy + sediment chem</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium–High</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Not time-specific</t>
+          <t>Seasonal (1–3 months)</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>Per-manual standardized analysis</t>
+          <t>IQI/AMBI biotic indices; sediment-chemistry thresholds; mixing-zone assessment</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>Yes — Open (CC-BY)</t>
+          <t>Yes — Open (SEPA PDF)</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>Abstract only</t>
+          <t>Abstract + Methods (fetched)</t>
         </is>
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>https://www.nespmarine.edu.au/field-manuals</t>
+          <t>https://www.sepa.org.uk/media/115592/fish-farm-manual-benthic-extended.pdf</t>
         </is>
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>Use it to design comparable benthic and mobile-fauna campaigns and to standardise across individual manuals.</t>
+          <t>A regulatory impact standard; the grab-to-IQI workflow is the standard route to the benthic-infauna and sediment indicators.</t>
         </is>
       </c>
       <c r="V143" t="inlineStr">
@@ -30045,27 +30097,27 @@
       </c>
       <c r="W143" s="7" t="inlineStr">
         <is>
-          <t>2 — Researcher</t>
+          <t>3 — Partnership</t>
         </is>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>Seaweed, Mollusk, Finfish</t>
+          <t>Mollusk, Finfish</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>Habitat &amp; Biodiversity, Cross-cutting / Framework</t>
+          <t>Habitat &amp; Biodiversity</t>
         </is>
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>H&amp;B 1.2.1 — Mobile fauna, H&amp;B 1.3.1 — Benthic infauna, H&amp;B 1.4.1 — Sediment, Cross-cutting / framework</t>
+          <t>H&amp;B 1.3.1 — Benthic infauna, H&amp;B 1.4.1 — Sediment</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>Cross-zone / global</t>
+          <t>Temperate Atlantic</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
@@ -30095,7 +30147,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>Mixed methods</t>
+          <t>Sediment sampling</t>
         </is>
       </c>
       <c r="AH143" t="inlineStr">
@@ -30105,7 +30157,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>Not depth-specific</t>
+          <t>Coastal (10–30 m)</t>
         </is>
       </c>
       <c r="AJ143" t="inlineStr">
@@ -30115,17 +30167,17 @@
       </c>
       <c r="AK143" s="16" t="inlineStr">
         <is>
-          <t>This is a collection of standardized Australian field-sampling manuals (benthic stereo-BRUVs, grabs and cores, towed video, sleds, multibeam) used as a national design standard spanning mobile fauna, benthic infauna and sediment. Use it to design comparable benthic and mobile-fauna campaigns and to lift indicator-specific manuals (such as the stereo-BRUV manual) into a coherent programme, rather than as a single procedure.</t>
+          <t>Although written for finfish farms, this regulated benthic-monitoring SOP transfers to bivalve/seaweed farm seabed monitoring. Take grab samples (day or van Veen) along the farm and mixing-zone gradient, sieve (0.5-1 mm) and fix the retained infauna, then have a partner lab identify taxa and measure sediment chemistry. Compute the Infaunal Quality Index (taxa diversity + AMBI + Simpson evenness) and compare against sediment-chemistry thresholds and a mixing-zone assessment. The grab-to-IQI workflow is a compliance-grade route to the benthic-infauna and sediment indicators, directly comparable to Norway's NS 9410 / MOM.</t>
         </is>
       </c>
       <c r="AL143" s="17" t="inlineStr">
         <is>
-          <t>Ref</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="AM143" s="18" t="inlineStr">
         <is>
-          <t>przeslawski_2018</t>
+          <t>sepa_2019</t>
         </is>
       </c>
       <c r="AN143" s="19" t="n"/>
@@ -30133,47 +30185,47 @@
       <c r="AP143" s="19" t="n"/>
       <c r="AQ143" s="16" t="inlineStr">
         <is>
-          <t>Australian Marine-Sampling Field Manuals (Design Reference)</t>
+          <t>Regulated Benthic Monitoring: Grab Survey to Infaunal Quality Index</t>
         </is>
       </c>
       <c r="AR143" s="16" t="inlineStr">
         <is>
-          <t>Przeslawski, R.; Foster, S. (eds.) — NESP Marine Biodiversity Hub</t>
+          <t>Scottish Environment Protection Agency (SEPA)</t>
         </is>
       </c>
       <c r="AS143" s="16" t="inlineStr">
         <is>
-          <t>Most useful for designing comparable benthic/mobile-fauna campaigns; lifts indicator-specific manuals (e.g., the stereo-BRUV manual above) into a coherent programme. Tier T2 as a researcher-grade design tool.</t>
+          <t>A regulatory impact-monitoring standard rather than a benefit protocol, but the grab→IQI workflow is the standard route to the benthic-infauna and sediment indicators. Directly comparable to Norway NS 9410 / MOM (next row).</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Scottish Environment Protection Agency (SEPA)</t>
+          <t>Standards Norway</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Fish Farm Manual — Benthic Monitoring (Standard &amp; Extended surveys; Infaunal Quality Index)</t>
+          <t>NS 9410 — Environmental monitoring of benthic impact from marine aquaculture (MOM B- and C-assessments)</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SEPA Aquaculture regulatory guidance</t>
+          <t>Norwegian Standard (Standards Norway)</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Scottish Environment Protection Agency</t>
+          <t>Standards Norway</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Regulated benthic-monitoring SOP for marine farms: benthic grab survey, sediment chemistry, and the Infaunal Quality Index (IQI = taxa diversity + AMBI + Simpson evenness). Finfish-origin but the infauna+sediment methodology transfers to bivalve/seaweed farm monitoring.</t>
+          <t>Norway's legally required benthic-monitoring standard built on the MOM approach. B-assessment (under-cage): pH, redox potential, sensory attributes and macrofauna presence; C-assessment (30–500 m zones): full soft-bottom community + sediment chemistry, NSI/biotic indices.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -30183,12 +30235,12 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Yes — prescriptive grab design, sieving/fixation, taxonomic processing and index computation with reporting templates. Compliance-grade reproducibility.</t>
+          <t>Yes — standardized field sampling and scoring with defined thresholds; the B-survey is a rapid field assessment, the C-survey a full benthic/chemistry programme.</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Partial — grab sampling from a small vessel is farmer-doable, but macrofauna sorting/ID and sediment chemistry require an accredited partner lab.</t>
+          <t>Partial — the B-survey (grab + field pH/redox/sensory) is largely field-executable; the C-survey needs full taxonomy + sediment chemistry via partner lab.</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -30198,12 +30250,12 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>Day/van-Veen grab, sieves (0.5/1 mm), sample jars; partner lab for taxonomy + sediment chem</t>
+          <t>Grab, field pH/redox probes; partner lab for C-survey taxonomy/chemistry</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>Medium–High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -30213,27 +30265,27 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>IQI/AMBI biotic indices; sediment-chemistry thresholds; mixing-zone assessment</t>
+          <t>B-index scoring; NSI/biotic indices; sediment chemistry</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>Yes — Open (SEPA PDF)</t>
+          <t>No — Paywalled (purchase via Standards Norway)</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>Abstract + Methods (fetched)</t>
+          <t>Abstract only</t>
         </is>
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>https://www.sepa.org.uk/media/115592/fish-farm-manual-benthic-extended.pdf</t>
+          <t>https://www.standard.no (NS 9410)</t>
         </is>
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>A regulatory impact standard; the grab-to-IQI workflow is the standard route to the benthic-infauna and sediment indicators.</t>
+          <t>The standard itself is paywalled, so confirm the exact thresholds from the document before relying on them.</t>
         </is>
       </c>
       <c r="V144" t="inlineStr">
@@ -30243,7 +30295,7 @@
       </c>
       <c r="W144" s="7" t="inlineStr">
         <is>
-          <t>3 — Partnership</t>
+          <t>2 — Researcher</t>
         </is>
       </c>
       <c r="X144" t="inlineStr">
@@ -30263,7 +30315,7 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>Temperate Atlantic</t>
+          <t>Boreal / Arctic</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
@@ -30313,17 +30365,17 @@
       </c>
       <c r="AK144" s="16" t="inlineStr">
         <is>
-          <t>Although written for finfish farms, this regulated benthic-monitoring SOP transfers to bivalve/seaweed farm seabed monitoring. Take grab samples (day or van Veen) along the farm and mixing-zone gradient, sieve (0.5-1 mm) and fix the retained infauna, then have a partner lab identify taxa and measure sediment chemistry. Compute the Infaunal Quality Index (taxa diversity + AMBI + Simpson evenness) and compare against sediment-chemistry thresholds and a mixing-zone assessment. The grab-to-IQI workflow is a compliance-grade route to the benthic-infauna and sediment indicators, directly comparable to Norway's NS 9410 / MOM.</t>
+          <t>This is Norway's legally required benthic-monitoring standard, built on the MOM approach, with two tiers. The under-cage B-assessment is a rapid field survey scoring sediment pH, redox potential, sensory attributes and macrofauna presence/absence into condition classes; the zone (C) assessment is a fuller soft-bottom community survey plus sediment chemistry with biotic indices. Sample with a grab and field pH/redox probes for the B-survey, adding lab taxonomy and chemistry for the C-survey. (Summary from secondary sources - the standard itself is paywalled, so confirm exact thresholds from the document before relying on them.)</t>
         </is>
       </c>
       <c r="AL144" s="17" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AM144" s="18" t="inlineStr">
         <is>
-          <t>sepa_2019</t>
+          <t>standardsnorway_2016</t>
         </is>
       </c>
       <c r="AN144" s="19" t="n"/>
@@ -30331,47 +30383,47 @@
       <c r="AP144" s="19" t="n"/>
       <c r="AQ144" s="16" t="inlineStr">
         <is>
-          <t>Regulated Benthic Monitoring: Grab Survey to Infaunal Quality Index</t>
+          <t>Norwegian MOM Benthic-Monitoring Standard (NS 9410)</t>
         </is>
       </c>
       <c r="AR144" s="16" t="inlineStr">
         <is>
-          <t>Scottish Environment Protection Agency (SEPA)</t>
+          <t>Standards Norway</t>
         </is>
       </c>
       <c r="AS144" s="16" t="inlineStr">
         <is>
-          <t>A regulatory impact-monitoring standard rather than a benefit protocol, but the grab→IQI workflow is the standard route to the benthic-infauna and sediment indicators. Directly comparable to Norway NS 9410 / MOM (next row).</t>
+          <t>Standard document is paywalled; methodology well-documented in secondary literature. Tier set conservatively at T2 (Sub-rule 14a) pending a read of the standard itself — the B-survey component is plausibly T3/Partnership once confirmed. Directly comparable to the SEPA manual.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Standards Norway</t>
+          <t>Scottish Salmon Producers' Org. (Code of Good Practice)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>NS 9410 — Environmental monitoring of benthic impact from marine aquaculture (MOM B- and C-assessments)</t>
+          <t>Sea lice counting &amp; surveillance protocols (farmed and wild fish)</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Norwegian Standard (Standards Norway)</t>
+          <t>Industry Code of Good Practice / national surveillance protocols</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Standards Norway</t>
+          <t>Multiple (Scotland; Norway)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Norway's legally required benthic-monitoring standard built on the MOM approach. B-assessment (under-cage): pH, redox potential, sensory attributes and macrofauna presence; C-assessment (30–500 m zones): full soft-bottom community + sediment chemistry, NSI/biotic indices.</t>
+          <t>Standardized protocols for counting sea lice on farmed salmon (and sentinel/wild salmonids): fixed sampling design (e.g., 5 fish × 5 pens = 25 fish), stage-resolved lice counts, and trigger levels. Under the finfish indicator set this is the parasite/pathogen-surveillance facet of Finfish H&amp;B 2.1.1 (farmed + nearby wild stock).</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -30381,12 +30433,12 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Yes — standardized field sampling and scoring with defined thresholds; the B-survey is a rapid field assessment, the C-survey a full benthic/chemistry programme.</t>
+          <t>Yes — prescriptive fish-sampling and lice-staging counts with defined trigger thresholds; farm-staff counts validated against dedicated teams.</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Partial — the B-survey (grab + field pH/redox/sensory) is largely field-executable; the C-survey needs full taxonomy + sediment chemistry via partner lab.</t>
+          <t>Partial — farm-level counting on netted fish is genuinely farm-staff (practitioner) executable; the rigorous wild-salmonid surveillance variant needs IMR-style certification and sentinel-cage/trawl capacity (partner).</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -30396,42 +30448,37 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>Grab, field pH/redox probes; partner lab for C-survey taxonomy/chemistry</t>
+          <t>Anaesthetic/handling kit, hand lens/loupe; (automated camera systems emerging)</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low–Medium</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Seasonal (1–3 months)</t>
+          <t>Multi-year monitoring (&gt; 1 year)</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>B-index scoring; NSI/biotic indices; sediment chemistry</t>
+          <t>Prevalence/abundance per fish (negative-binomial/normal); trigger-level comparison</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>No — Paywalled (purchase via Standards Norway)</t>
+          <t>Yes — Open (CoGP &amp; national guidance)</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>Abstract only</t>
+          <t>Abstract + Methods (fetched)</t>
         </is>
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>https://www.standard.no (NS 9410)</t>
-        </is>
-      </c>
-      <c r="U145" t="inlineStr">
-        <is>
-          <t>The standard itself is paywalled, so confirm the exact thresholds from the document before relying on them.</t>
+          <t>Scottish Code of Good Practice: thecodeofgoodpractice.co.uk ; Norway IMR: https://www.hi.no/en/hi/nettrapporter/rapport-fra-havforskningen-en-2024-61</t>
         </is>
       </c>
       <c r="V145" t="inlineStr">
@@ -30441,12 +30488,12 @@
       </c>
       <c r="W145" s="7" t="inlineStr">
         <is>
-          <t>2 — Researcher</t>
+          <t>3 — Partnership</t>
         </is>
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>Mollusk, Finfish</t>
+          <t>Finfish</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
@@ -30456,12 +30503,12 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>H&amp;B 1.3.1 — Benthic infauna, H&amp;B 1.4.1 — Sediment</t>
+          <t>H&amp;B 2.1.1 — Community composition</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>Boreal / Arctic</t>
+          <t>Temperate Atlantic</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
@@ -30471,7 +30518,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Not gear-specific</t>
+          <t>Floating cage / tray</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr">
@@ -30486,12 +30533,12 @@
       </c>
       <c r="AF145" t="inlineStr">
         <is>
-          <t>Not specific</t>
+          <t>Monoculture</t>
         </is>
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>Sediment sampling</t>
+          <t>Visual survey</t>
         </is>
       </c>
       <c r="AH145" t="inlineStr">
@@ -30511,17 +30558,17 @@
       </c>
       <c r="AK145" s="16" t="inlineStr">
         <is>
-          <t>This is Norway's legally required benthic-monitoring standard, built on the MOM approach, with two tiers. The under-cage B-assessment is a rapid field survey scoring sediment pH, redox potential, sensory attributes and macrofauna presence/absence into condition classes; the zone (C) assessment is a fuller soft-bottom community survey plus sediment chemistry with biotic indices. Sample with a grab and field pH/redox probes for the B-survey, adding lab taxonomy and chemistry for the C-survey. (Summary from secondary sources - the standard itself is paywalled, so confirm exact thresholds from the document before relying on them.)</t>
+          <t>To monitor sea-lice burden on farmed salmon (the parasite/pathogen-surveillance facet of the finfish community-composition indicator), follow a fixed sampling design - for example five fish from each of five pens (25 fish) on a set schedule - anaesthetising and examining each fish and counting lice by life stage under a hand lens. Report prevalence and abundance per fish and compare against defined trigger levels that prompt action. Farm-staff counts are typically validated against dedicated teams, and sentinel/wild-salmonid counting extends the same method beyond the farm.</t>
         </is>
       </c>
       <c r="AL145" s="17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="AM145" s="18" t="inlineStr">
         <is>
-          <t>standardsnorway_2016</t>
+          <t>scottishsalmon_2023</t>
         </is>
       </c>
       <c r="AN145" s="19" t="n"/>
@@ -30529,34 +30576,34 @@
       <c r="AP145" s="19" t="n"/>
       <c r="AQ145" s="16" t="inlineStr">
         <is>
-          <t>Norwegian MOM Benthic-Monitoring Standard (NS 9410)</t>
+          <t>Sea-Lice Counting &amp; Surveillance Protocol</t>
         </is>
       </c>
       <c r="AR145" s="16" t="inlineStr">
         <is>
-          <t>Standards Norway</t>
+          <t>Scottish Salmon Producers' Org. (Code of Good Practice); Institute of Marine Research (Norway); Norwegian Food Safety Authority</t>
         </is>
       </c>
       <c r="AS145" s="16" t="inlineStr">
         <is>
-          <t>Standard document is paywalled; methodology well-documented in secondary literature. Tier set conservatively at T2 (Sub-rule 14a) pending a read of the standard itself — the B-survey component is plausibly T3/Partnership once confirmed. Directly comparable to the SEPA manual.</t>
+          <t>The Norwegian Salmon Lice Directive (FOR-2009-08-18-1095) is the regulatory framework mandating counting; the IMR protocol is the certified standardized count for the national wild-salmonid programme. Farm-level counting alone is closer to T4; tier set at T3 to cover the full indicator (incl. wild-population surveillance to ~2.5 km). Tagged with the generic 'H&amp;B 2.1.1' string; under the finfish set this is fish-attraction / parasite surveillance.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Scottish Salmon Producers' Org. (Code of Good Practice)</t>
+          <t>Reichert-Nguyen, J., et al.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Sea lice counting &amp; surveillance protocols (farmed and wild fish)</t>
+          <t>Oyster BMP Expert Panel Reports — Nutrient &amp; Suspended-Sediment Reduction Effectiveness Protocols (First Report 2016; Second Report 2023)</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Industry Code of Good Practice / national surveillance protocols</t>
+          <t>Chesapeake Bay Program / Oyster Recovery Partnership</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -30564,12 +30611,12 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Multiple (Scotland; Norway)</t>
+          <t>Chesapeake Bay Program</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Standardized protocols for counting sea lice on farmed salmon (and sentinel/wild salmonids): fixed sampling design (e.g., 5 fish × 5 pens = 25 fish), stage-resolved lice counts, and trigger levels. Under the finfish indicator set this is the parasite/pathogen-surveillance facet of Finfish H&amp;B 2.1.1 (farmed + nearby wild stock).</t>
+          <t>Crediting-and-verification protocols defining reduction-effectiveness for oyster practices: N &amp; P assimilation in tissue, N &amp; P assimilation in shell, enhanced denitrification, and N/P burial. The tissue/shell protocols are the standardized bioextraction route; the denitrification protocol is one of very few packaged methods for that indicator.</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -30579,12 +30626,12 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Yes — prescriptive fish-sampling and lice-staging counts with defined trigger thresholds; farm-staff counts validated against dedicated teams.</t>
+          <t>Yes — defines harvest accounting (count × size → tissue/shell N&amp;P via published content) and the enhanced-denitrification crediting method, with verification guidelines. Decision-framework + effectiveness estimates.</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>Partial — farm-level counting on netted fish is genuinely farm-staff (practitioner) executable; the rigorous wild-salmonid surveillance variant needs IMR-style certification and sentinel-cage/trawl capacity (partner).</t>
+          <t>Partial — counting/measuring harvested oysters is farmer-executable; tissue/shell %N&amp;P (CHN analyser) and denitrification (N2-flux/15N) need a partner lab, though published default coefficients allow a desk estimate.</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -30594,27 +30641,27 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>Anaesthetic/handling kit, hand lens/loupe; (automated camera systems emerging)</t>
+          <t>Harvest records, calipers; partner lab CHN analyser; (denitrification: benthic-flux/15N)</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Low–Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Multi-year monitoring (&gt; 1 year)</t>
+          <t>Year-long study (12 months)</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Prevalence/abundance per fish (negative-binomial/normal); trigger-level comparison</t>
+          <t>Reduction-effectiveness accounting; verification protocol</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>Yes — Open (CoGP &amp; national guidance)</t>
+          <t>Yes — Open (CBP PDFs)</t>
         </is>
       </c>
       <c r="S146" t="inlineStr">
@@ -30624,7 +30671,12 @@
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>Scottish Code of Good Practice: thecodeofgoodpractice.co.uk ; Norway IMR: https://www.hi.no/en/hi/nettrapporter/rapport-fra-havforskningen-en-2024-61</t>
+          <t>https://d18lev1ok5leia.cloudfront.net/chesapeakebay/documents/Oyster-BMP-Expert-Panel-Second-Report.pdf</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Default tissue/shell coefficients make a credible desk estimate feasible without a lab; shell accounting here is for N and P, not carbon.</t>
         </is>
       </c>
       <c r="V146" t="inlineStr">
@@ -30639,17 +30691,17 @@
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>Finfish</t>
+          <t>Mollusk</t>
         </is>
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>Habitat &amp; Biodiversity</t>
+          <t>Water Quality</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>H&amp;B 2.1.1 — Community composition</t>
+          <t>WQ 1.1.1 — N and P bioextraction, WQ 1.1.2 — Rate of denitrification</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -30659,12 +30711,12 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>Not species-specific</t>
+          <t>Eastern oyster (Crassostrea virginica)</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Floating cage / tray</t>
+          <t>Not gear-specific</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr">
@@ -30679,12 +30731,12 @@
       </c>
       <c r="AF146" t="inlineStr">
         <is>
-          <t>Monoculture</t>
+          <t>Not specific</t>
         </is>
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>Visual survey</t>
+          <t>Tissue analysis</t>
         </is>
       </c>
       <c r="AH146" t="inlineStr">
@@ -30694,7 +30746,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>Coastal (10–30 m)</t>
+          <t>Not depth-specific</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
@@ -30704,7 +30756,7 @@
       </c>
       <c r="AK146" s="16" t="inlineStr">
         <is>
-          <t>To monitor sea-lice burden on farmed salmon (the parasite/pathogen-surveillance facet of the finfish community-composition indicator), follow a fixed sampling design - for example five fish from each of five pens (25 fish) on a set schedule - anaesthetising and examining each fish and counting lice by life stage under a hand lens. Report prevalence and abundance per fish and compare against defined trigger levels that prompt action. Farm-staff counts are typically validated against dedicated teams, and sentinel/wild-salmonid counting extends the same method beyond the farm.</t>
+          <t>This crediting-and-verification protocol standardizes how to account for nutrients an oyster practice removes: nitrogen and phosphorus assimilated in harvested tissue and shell, plus enhanced denitrification and burial. For the bioextraction route, record harvest (count x size) and convert to tissue/shell N and P using published content coefficients (or a partner-lab CHN analysis); the denitrification route uses benthic-flux or 15N methods. Default coefficients make a credible desk estimate feasible without a lab. Note shell accounting here is for N and P, not carbon - no shell-carbon storage protocol yet exists.</t>
         </is>
       </c>
       <c r="AL146" s="17" t="inlineStr">
@@ -30714,7 +30766,7 @@
       </c>
       <c r="AM146" s="18" t="inlineStr">
         <is>
-          <t>scottishsalmon_2023</t>
+          <t>reichertnguyen_2023</t>
         </is>
       </c>
       <c r="AN146" s="19" t="n"/>
@@ -30722,47 +30774,47 @@
       <c r="AP146" s="19" t="n"/>
       <c r="AQ146" s="16" t="inlineStr">
         <is>
-          <t>Sea-Lice Counting &amp; Surveillance Protocol</t>
+          <t>Oyster Nutrient-Reduction Crediting Protocol (Tissue/Shell/Denitrification)</t>
         </is>
       </c>
       <c r="AR146" s="16" t="inlineStr">
         <is>
-          <t>Scottish Salmon Producers' Org. (Code of Good Practice); Institute of Marine Research (Norway); Norwegian Food Safety Authority</t>
+          <t>Reichert-Nguyen, J.; Cornwell, J.; et al. — Oyster BMP Expert Panel (Chesapeake Bay Program / Oyster Recovery Partnership)</t>
         </is>
       </c>
       <c r="AS146" s="16" t="inlineStr">
         <is>
-          <t>The Norwegian Salmon Lice Directive (FOR-2009-08-18-1095) is the regulatory framework mandating counting; the IMR protocol is the certified standardized count for the national wild-salmonid programme. Farm-level counting alone is closer to T4; tier set at T3 to cover the full indicator (incl. wild-population surveillance to ~2.5 km). Tagged with the generic 'H&amp;B 2.1.1' string; under the finfish set this is fish-attraction / parasite surveillance.</t>
+          <t>TNC-relevant (TNC sits on the partnership). Restoration + aquaculture both covered. Shell-assimilation accounting is N/P (not carbon); a shell-CARBON storage protocol for CC 2.1.1 (mollusc) does not yet exist. Default tissue/shell coefficients make a desk estimate feasible without a lab.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Reichert-Nguyen, J., et al.</t>
+          <t>Maryland Department of Natural Resources</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Oyster BMP Expert Panel Reports — Nutrient &amp; Suspended-Sediment Reduction Effectiveness Protocols (First Report 2016; Second Report 2023)</t>
+          <t>Oyster Reef Restoration Nutrient Assimilation BMP</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chesapeake Bay Program / Oyster Recovery Partnership</t>
+          <t>Maryland DNR (Critical Area / CBP BMP)</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Chesapeake Bay Program</t>
+          <t>Maryland Department of Natural Resources</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Crediting-and-verification protocols defining reduction-effectiveness for oyster practices: N &amp; P assimilation in tissue, N &amp; P assimilation in shell, enhanced denitrification, and N/P burial. The tissue/shell protocols are the standardized bioextraction route; the denitrification protocol is one of very few packaged methods for that indicator.</t>
+          <t>Crediting protocol for N &amp; P assimilated in live oyster tissue and shell gained through reef restoration in tidal Chesapeake waters — the restoration-side application of the Oyster BMP framework.</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -30772,12 +30824,12 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Yes — defines harvest accounting (count × size → tissue/shell N&amp;P via published content) and the enhanced-denitrification crediting method, with verification guidelines. Decision-framework + effectiveness estimates.</t>
+          <t>Yes — defines the restoration nutrient-assimilation accounting with lookup tables (Expert Panel Appendix G) and credit duration.</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>Partial — counting/measuring harvested oysters is farmer-executable; tissue/shell %N&amp;P (CHN analyser) and denitrification (N2-flux/15N) need a partner lab, though published default coefficients allow a desk estimate.</t>
+          <t>Partial — reef survey/oyster counts farmer-doable; tissue/shell N&amp;P via lab or published coefficients.</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -30787,12 +30839,12 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>Harvest records, calipers; partner lab CHN analyser; (denitrification: benthic-flux/15N)</t>
+          <t>Reef survey gear; partner lab / published coefficients</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low–Medium</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -30802,12 +30854,12 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>Reduction-effectiveness accounting; verification protocol</t>
+          <t>Assimilation accounting via lookup tables</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>Yes — Open (CBP PDFs)</t>
+          <t>Yes — Open (MD DNR PDF)</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
@@ -30817,12 +30869,12 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>https://d18lev1ok5leia.cloudfront.net/chesapeakebay/documents/Oyster-BMP-Expert-Panel-Second-Report.pdf</t>
+          <t>https://dnr.maryland.gov/criticalarea/Documents/Oyster_Reef_Restoration_Assimilation_BMP.pdf</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>Default tissue/shell coefficients make a credible desk estimate feasible without a lab; shell accounting here is for N and P, not carbon.</t>
+          <t>Use it where reef restoration, rather than harvest, is the practice.</t>
         </is>
       </c>
       <c r="V147" t="inlineStr">
@@ -30847,7 +30899,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>WQ 1.1.1 — N and P bioextraction, WQ 1.1.2 — Rate of denitrification</t>
+          <t>WQ 1.1.1 — N and P bioextraction</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -30902,7 +30954,7 @@
       </c>
       <c r="AK147" s="16" t="inlineStr">
         <is>
-          <t>This crediting-and-verification protocol standardizes how to account for nutrients an oyster practice removes: nitrogen and phosphorus assimilated in harvested tissue and shell, plus enhanced denitrification and burial. For the bioextraction route, record harvest (count x size) and convert to tissue/shell N and P using published content coefficients (or a partner-lab CHN analysis); the denitrification route uses benthic-flux or 15N methods. Default coefficients make a credible desk estimate feasible without a lab. Note shell accounting here is for N and P, not carbon - no shell-carbon storage protocol yet exists.</t>
+          <t>This is the restoration-side application of the Chesapeake oyster nutrient-crediting framework: it accounts for nitrogen and phosphorus assimilated in live oyster tissue and shell gained through reef restoration. Survey the reef for oyster numbers and size, then apply the published lookup tables (Expert Panel appendices) to convert to assimilated N and P over the credited duration. Use it where reef restoration, rather than harvest, is the practice.</t>
         </is>
       </c>
       <c r="AL147" s="17" t="inlineStr">
@@ -30912,7 +30964,7 @@
       </c>
       <c r="AM147" s="18" t="inlineStr">
         <is>
-          <t>reichertnguyen_2023</t>
+          <t>marylanddepartment_2021</t>
         </is>
       </c>
       <c r="AN147" s="19" t="n"/>
@@ -30920,62 +30972,62 @@
       <c r="AP147" s="19" t="n"/>
       <c r="AQ147" s="16" t="inlineStr">
         <is>
-          <t>Oyster Nutrient-Reduction Crediting Protocol (Tissue/Shell/Denitrification)</t>
+          <t>Oyster-Reef Restoration Nutrient-Assimilation Crediting</t>
         </is>
       </c>
       <c r="AR147" s="16" t="inlineStr">
         <is>
-          <t>Reichert-Nguyen, J.; Cornwell, J.; et al. — Oyster BMP Expert Panel (Chesapeake Bay Program / Oyster Recovery Partnership)</t>
+          <t>Maryland Department of Natural Resources</t>
         </is>
       </c>
       <c r="AS147" s="16" t="inlineStr">
         <is>
-          <t>TNC-relevant (TNC sits on the partnership). Restoration + aquaculture both covered. Shell-assimilation accounting is N/P (not carbon); a shell-CARBON storage protocol for CC 2.1.1 (mollusc) does not yet exist. Default tissue/shell coefficients make a desk estimate feasible without a lab.</t>
+          <t>Implements the Chesapeake Oyster BMP framework (previous row) for restoration credits. Useful where reef restoration rather than harvest is the practice.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Maryland Department of Natural Resources</t>
+          <t>Hawkins, A. J. S. &amp; et al. (ShellSIM)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Oyster Reef Restoration Nutrient Assimilation BMP</t>
+          <t>ShellSIM — bivalve filtration, growth and environmental-effects model (software tool)</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Maryland DNR (Critical Area / CBP BMP)</t>
+          <t>shellsim.com</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Maryland Department of Natural Resources</t>
+          <t>PML Applications / ShellSIM</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Crediting protocol for N &amp; P assimilated in live oyster tissue and shell gained through reef restoration in tidal Chesapeake waters — the restoration-side application of the Oyster BMP framework.</t>
+          <t>User-friendly mechanistic model of suspension-feeding bivalves: predicts particle clearance/filtration rate, ammonium loss, faecal loss, oxygen uptake and growth for up to 14 species, individual→culture-area scale. The practical route to the filtration indicator and a complement to bioextraction/DO.</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Protocol</t>
+          <t>Reference (usable model / design tool)</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Yes — defines the restoration nutrient-assimilation accounting with lookup tables (Expert Panel Appendix G) and credit duration.</t>
+          <t>Adequate as a quantification tool rather than a field protocol: given environmental drivers + stock it outputs clearance/filtration and nutrient/oxygen fluxes. Requires parameterisation, not field sampling.</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>Partial — reef survey/oyster counts farmer-doable; tissue/shell N&amp;P via lab or published coefficients.</t>
+          <t>No — marketed for growers/managers/regulators but parameterisation and interpretation need modelling expertise.</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -30985,27 +31037,27 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>Reef survey gear; partner lab / published coefficients</t>
+          <t>Software (ShellSIM); environmental driver data</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Low–Medium</t>
+          <t>Low (tool free; cost is expertise/data)</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Year-long study (12 months)</t>
+          <t>One-time (no sampling — desk-based)</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>Assimilation accounting via lookup tables</t>
+          <t>Dynamic energy-balance simulation; scenario analysis</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>Yes — Open (MD DNR PDF)</t>
+          <t>Yes — Open (free tool)</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
@@ -31015,12 +31067,12 @@
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>https://dnr.maryland.gov/criticalarea/Documents/Oyster_Reef_Restoration_Assimilation_BMP.pdf</t>
+          <t>http://shellsim.com</t>
         </is>
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>Use it where reef restoration, rather than harvest, is the practice.</t>
+          <t>A modelling tool for the filtration service; complementary carrying-capacity models are FARM and EcoWin.</t>
         </is>
       </c>
       <c r="V148" t="inlineStr">
@@ -31030,7 +31082,7 @@
       </c>
       <c r="W148" s="7" t="inlineStr">
         <is>
-          <t>3 — Partnership</t>
+          <t>2 — Researcher</t>
         </is>
       </c>
       <c r="X148" t="inlineStr">
@@ -31045,17 +31097,17 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>WQ 1.1.1 — N and P bioextraction</t>
+          <t>WQ 1.3.1 — Rate of water filtration, WQ 1.1.1 — N and P bioextraction, WQ 1.2.1 — Dissolved oxygen</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>Temperate Atlantic</t>
+          <t>Cross-zone / global</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>Eastern oyster (Crassostrea virginica)</t>
+          <t>Multi-species / mixed</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
@@ -31080,7 +31132,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>Tissue analysis</t>
+          <t>Modelling</t>
         </is>
       </c>
       <c r="AH148" t="inlineStr">
@@ -31100,17 +31152,17 @@
       </c>
       <c r="AK148" s="16" t="inlineStr">
         <is>
-          <t>This is the restoration-side application of the Chesapeake oyster nutrient-crediting framework: it accounts for nitrogen and phosphorus assimilated in live oyster tissue and shell gained through reef restoration. Survey the reef for oyster numbers and size, then apply the published lookup tables (Expert Panel appendices) to convert to assimilated N and P over the credited duration. Use it where reef restoration, rather than harvest, is the practice.</t>
+          <t>This is a user-friendly mechanistic model of suspension-feeding bivalves rather than a field method: given environmental drivers and stock, it predicts clearance/filtration rate, ammonium and faecal losses, oxygen uptake and growth for many species, from individual to culture-area scale. Use it to quantify the water-filtration service (and to complement bioextraction and dissolved-oxygen work) by parameterising and running scenarios; farm/bay carrying-capacity models (FARM, EcoWin) and Dame's depletion indices are the complementary frameworks.</t>
         </is>
       </c>
       <c r="AL148" s="17" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Ref</t>
         </is>
       </c>
       <c r="AM148" s="18" t="inlineStr">
         <is>
-          <t>marylanddepartment_2021</t>
+          <t>hawkins_2013</t>
         </is>
       </c>
       <c r="AN148" s="19" t="n"/>
@@ -31118,62 +31170,62 @@
       <c r="AP148" s="19" t="n"/>
       <c r="AQ148" s="16" t="inlineStr">
         <is>
-          <t>Oyster-Reef Restoration Nutrient-Assimilation Crediting</t>
+          <t>ShellSIM Bivalve Filtration &amp; Growth Model (Reference)</t>
         </is>
       </c>
       <c r="AR148" s="16" t="inlineStr">
         <is>
-          <t>Maryland Department of Natural Resources</t>
+          <t>Hawkins, A.J.S.; et al. (ShellSIM)</t>
         </is>
       </c>
       <c r="AS148" s="16" t="inlineStr">
         <is>
-          <t>Implements the Chesapeake Oyster BMP framework (previous row) for restoration credits. Useful where reef restoration rather than harvest is the practice.</t>
+          <t>Farm-/bay-scale carrying-capacity models (FARM, EcoWin) and the Dame depletion indices (clearance vs. residence vs. primary-production time) are the complementary frameworks for filtration-as-service. Modelling tool → T2.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Hawkins, A. J. S. &amp; et al. (ShellSIM)</t>
+          <t>OSPAR Commission (JAMP)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ShellSIM — bivalve filtration, growth and environmental-effects model (software tool)</t>
+          <t>JAMP Eutrophication Monitoring Guidelines: Chlorophyll a in Water (with ICES TIMES chlorophyll procedure)</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>shellsim.com</t>
+          <t>OSPAR Commission / ICES Techniques in Marine Environmental Sciences</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>PML Applications / ShellSIM</t>
+          <t>OSPAR Commission</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>User-friendly mechanistic model of suspension-feeding bivalves: predicts particle clearance/filtration rate, ammonium loss, faecal loss, oxygen uptake and growth for up to 14 species, individual→culture-area scale. The practical route to the filtration indicator and a complement to bioextraction/DO.</t>
+          <t>Intergovernmental standardized procedure for chlorophyll-a determination (sampling, filtration, extraction, spectrophotometric/HPLC analysis; ISO 10260; in-situ fluorometer calibration). The standard route to the chlorophyll-a indicator.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Reference (usable model / design tool)</t>
+          <t>Protocol</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Adequate as a quantification tool rather than a field protocol: given environmental drivers + stock it outputs clearance/filtration and nutrient/oxygen fluxes. Requires parameterisation, not field sampling.</t>
+          <t>Yes — prescribes collection→filtration→extraction→analysis with QA (accredited labs, reference checks). Reproducible analytical SOP.</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>No — marketed for growers/managers/regulators but parameterisation and interpretation need modelling expertise.</t>
+          <t>Partial — water sampling/filtration farmer-doable; spectrophotometric/HPLC analysis needs a partner lab (or a calibrated fluorometer + QC).</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -31183,27 +31235,27 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>Software (ShellSIM); environmental driver data</t>
+          <t>Niskin/bottle, filtration rig, GF/F filters; spectrophotometer/HPLC or calibrated fluorometer</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Low (tool free; cost is expertise/data)</t>
+          <t>Low–Medium</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>One-time (no sampling — desk-based)</t>
+          <t>Year-long study (12 months)</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>Dynamic energy-balance simulation; scenario analysis</t>
+          <t>Standardized chl-a quantification; eutrophication assessment</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>Yes — Open (free tool)</t>
+          <t>Yes — Open (OSPAR/JRC PDF)</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
@@ -31213,12 +31265,12 @@
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>http://shellsim.com</t>
+          <t>https://mcc.jrc.ec.europa.eu/documents/OSPAR/Eutrophication_MonitoringGuidelinesch_%20a.pdf</t>
         </is>
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>A modelling tool for the filtration service; complementary carrying-capacity models are FARM and EcoWin.</t>
+          <t>The standard analytical route to the chlorophyll-a indicator; satellite ocean-colour is the remote-sensing complement.</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
@@ -31228,12 +31280,12 @@
       </c>
       <c r="W149" s="7" t="inlineStr">
         <is>
-          <t>2 — Researcher</t>
+          <t>3 — Partnership</t>
         </is>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>Mollusk</t>
+          <t>Seaweed, Mollusk</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
@@ -31243,7 +31295,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>WQ 1.3.1 — Rate of water filtration, WQ 1.1.1 — N and P bioextraction, WQ 1.2.1 — Dissolved oxygen</t>
+          <t>WQ 2.1.1 — Chlorophyll-a</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -31253,7 +31305,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>Multi-species / mixed</t>
+          <t>Not species-specific</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
@@ -31278,7 +31330,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>Modelling</t>
+          <t>Pigment HPLC, Water chemistry</t>
         </is>
       </c>
       <c r="AH149" t="inlineStr">
@@ -31298,17 +31350,17 @@
       </c>
       <c r="AK149" s="16" t="inlineStr">
         <is>
-          <t>This is a user-friendly mechanistic model of suspension-feeding bivalves rather than a field method: given environmental drivers and stock, it predicts clearance/filtration rate, ammonium and faecal losses, oxygen uptake and growth for many species, from individual to culture-area scale. Use it to quantify the water-filtration service (and to complement bioextraction and dissolved-oxygen work) by parameterising and running scenarios; farm/bay carrying-capacity models (FARM, EcoWin) and Dame's depletion indices are the complementary frameworks.</t>
+          <t>This intergovernmental SOP is the standard route to the chlorophyll-a indicator. Collect water (Niskin/bottle), filter onto GF/F, extract the pigment and determine chlorophyll-a spectrophotometrically or by HPLC (ISO 10260), or calibrate an in-situ fluorometer against these samples, all under defined quality assurance (accredited labs, reference checks). Follow it for comparable, eutrophication-grade chlorophyll data; the ICES TIMES procedure and UNESCO/SCOR pigment monographs are the underpinning analytical references, and satellite ocean-colour chlorophyll is the remote-sensing complement.</t>
         </is>
       </c>
       <c r="AL149" s="17" t="inlineStr">
         <is>
-          <t>Ref</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="AM149" s="18" t="inlineStr">
         <is>
-          <t>hawkins_2013</t>
+          <t>jamp_2012</t>
         </is>
       </c>
       <c r="AN149" s="19" t="n"/>
@@ -31316,47 +31368,50 @@
       <c r="AP149" s="19" t="n"/>
       <c r="AQ149" s="16" t="inlineStr">
         <is>
-          <t>ShellSIM Bivalve Filtration &amp; Growth Model (Reference)</t>
+          <t>Standard Chlorophyll-a Determination SOP (JAMP)</t>
         </is>
       </c>
       <c r="AR149" s="16" t="inlineStr">
         <is>
-          <t>Hawkins, A.J.S.; et al. (ShellSIM)</t>
+          <t>OSPAR Commission (JAMP); ICES</t>
         </is>
       </c>
       <c r="AS149" s="16" t="inlineStr">
         <is>
-          <t>Farm-/bay-scale carrying-capacity models (FARM, EcoWin) and the Dame depletion indices (clearance vs. residence vs. primary-production time) are the complementary frameworks for filtration-as-service. Modelling tool → T2.</t>
+          <t>The ICES TIMES 'Standard procedure for the determination of chlorophyll a by spectroscopic methods' (Aminot &amp; Rey 2000) and the UNESCO/SCOR pigment monographs (Jeffrey et al. 1997) are the underpinning analytical references. Satellite ocean-colour chl-a is the remote-sensing complement.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>OSPAR Commission (JAMP)</t>
+          <t>Karlson, B., et al.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>JAMP Eutrophication Monitoring Guidelines: Chlorophyll a in Water (with ICES TIMES chlorophyll procedure)</t>
+          <t>Microscopic and Molecular Methods for Quantitative Phytoplankton Analysis (IOC Manuals and Guides No. 55)</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>OSPAR Commission / ICES Techniques in Marine Environmental Sciences</t>
-        </is>
+          <t>IOC Manuals and Guides, UNESCO</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>55</v>
       </c>
       <c r="G150" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>OSPAR Commission</t>
+          <t>UNESCO/IOC</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Intergovernmental standardized procedure for chlorophyll-a determination (sampling, filtration, extraction, spectrophotometric/HPLC analysis; ISO 10260; in-situ fluorometer calibration). The standard route to the chlorophyll-a indicator.</t>
+          <t>Canonical manual for quantitative phytoplankton community analysis: sampling, microscopy/Utermöhl counts, and molecular (qPCR) methods. The standard route to the microorganism/plankton-community indicator.</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -31366,12 +31421,12 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Yes — prescribes collection→filtration→extraction→analysis with QA (accredited labs, reference checks). Reproducible analytical SOP.</t>
+          <t>Yes — documents sampling + enumeration/identification methods in replicable detail across microscopy and molecular approaches.</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>Partial — water sampling/filtration farmer-doable; spectrophotometric/HPLC analysis needs a partner lab (or a calibrated fluorometer + QC).</t>
+          <t>Partial — net-tow/bottle sampling farmer-doable; microscopy enumeration/ID and qPCR need a taxonomist/partner lab.</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -31381,12 +31436,12 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>Niskin/bottle, filtration rig, GF/F filters; spectrophotometer/HPLC or calibrated fluorometer</t>
+          <t>Plankton net/Niskin, settling chambers, inverted microscope; (qPCR for molecular)</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Low–Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -31396,12 +31451,12 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>Standardized chl-a quantification; eutrophication assessment</t>
+          <t>Utermöhl counts; community composition; molecular enumeration</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>Yes — Open (OSPAR/JRC PDF)</t>
+          <t>Yes — Open (UNESCO/IOC PDF)</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
@@ -31411,12 +31466,12 @@
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>https://mcc.jrc.ec.europa.eu/documents/OSPAR/Eutrophication_MonitoringGuidelinesch_%20a.pdf</t>
+          <t>https://unesdoc.unesco.org (IOC Manuals &amp; Guides 55, 2010)</t>
         </is>
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>The standard analytical route to the chlorophyll-a indicator; satellite ocean-colour is the remote-sensing complement.</t>
+          <t>The standard route to the phytoplankton/microorganism indicator; eDNA metabarcoding is the emerging molecular complement.</t>
         </is>
       </c>
       <c r="V150" t="inlineStr">
@@ -31441,7 +31496,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>WQ 2.1.1 — Chlorophyll-a</t>
+          <t>WQ 2.1.2 — Microorganisms</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -31476,7 +31531,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>Pigment HPLC, Water chemistry</t>
+          <t>Plankton sampling</t>
         </is>
       </c>
       <c r="AH150" t="inlineStr">
@@ -31496,7 +31551,7 @@
       </c>
       <c r="AK150" s="16" t="inlineStr">
         <is>
-          <t>This intergovernmental SOP is the standard route to the chlorophyll-a indicator. Collect water (Niskin/bottle), filter onto GF/F, extract the pigment and determine chlorophyll-a spectrophotometrically or by HPLC (ISO 10260), or calibrate an in-situ fluorometer against these samples, all under defined quality assurance (accredited labs, reference checks). Follow it for comparable, eutrophication-grade chlorophyll data; the ICES TIMES procedure and UNESCO/SCOR pigment monographs are the underpinning analytical references, and satellite ocean-colour chlorophyll is the remote-sensing complement.</t>
+          <t>This canonical manual is the standard route to the phytoplankton/microorganism indicator. Collect water with a net or Niskin, settle sub-samples in chambers and count/identify phytoplankton by inverted microscope (Utermohl method), or use molecular (qPCR) enumeration for the community. Follow it for replicable community composition and abundance; HELCOM species lists and the AQUACOSM SOP give a practical workflow, and eDNA metabarcoding is the emerging molecular complement.</t>
         </is>
       </c>
       <c r="AL150" s="17" t="inlineStr">
@@ -31506,7 +31561,7 @@
       </c>
       <c r="AM150" s="18" t="inlineStr">
         <is>
-          <t>jamp_2012</t>
+          <t>karlson_2010</t>
         </is>
       </c>
       <c r="AN150" s="19" t="n"/>
@@ -31514,50 +31569,47 @@
       <c r="AP150" s="19" t="n"/>
       <c r="AQ150" s="16" t="inlineStr">
         <is>
-          <t>Standard Chlorophyll-a Determination SOP (JAMP)</t>
+          <t>Quantitative Phytoplankton Analysis Manual (Microscopy + Molecular)</t>
         </is>
       </c>
       <c r="AR150" s="16" t="inlineStr">
         <is>
-          <t>OSPAR Commission (JAMP); ICES</t>
+          <t>Karlson, B.; Cusack, C.; Bresnan, E. (eds.) — UNESCO/IOC</t>
         </is>
       </c>
       <c r="AS150" s="16" t="inlineStr">
         <is>
-          <t>The ICES TIMES 'Standard procedure for the determination of chlorophyll a by spectroscopic methods' (Aminot &amp; Rey 2000) and the UNESCO/SCOR pigment monographs (Jeffrey et al. 1997) are the underpinning analytical references. Satellite ocean-colour chl-a is the remote-sensing complement.</t>
+          <t>HELCOM Phytoplankton Expert Group species lists and the AQUACOSM phytoplankton SOP give the practical sampling/ID workflow. eDNA metabarcoding (row 24) is the emerging molecular complement.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Karlson, B., et al.</t>
+          <t>Global Ocean Acidification Observing Network (GOA-ON)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Microscopic and Molecular Methods for Quantitative Phytoplankton Analysis (IOC Manuals and Guides No. 55)</t>
+          <t>Practical Best Practices for Ocean Acidification Monitoring (the 'OA Cookbook') + GOA-ON in a Box kit</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>IOC Manuals and Guides, UNESCO</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>55</v>
+          <t>GOA-ON (PubPub)</t>
+        </is>
       </c>
       <c r="G151" t="n">
-        <v>2010</v>
+        <v>2024</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>UNESCO/IOC</t>
+          <t>Global Ocean Acidification Observing Network</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Canonical manual for quantitative phytoplankton community analysis: sampling, microscopy/Utermöhl counts, and molecular (qPCR) methods. The standard route to the microorganism/plankton-community indicator.</t>
+          <t>Practitioner-level SOPs for coastal carbonate-system monitoring (pH via spectrophotometry / iSAMI sensor, total alkalinity, CO2SYS), built around the low-cost GOA-ON in a Box kit and explicitly aimed at low-resource teams. The practical route to the pH / ocean-acidification indicator.</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -31567,12 +31619,12 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Yes — documents sampling + enumeration/identification methods in replicable detail across microscopy and molecular approaches.</t>
+          <t>Yes — step-by-step SOPs (site selection, sampling, sensor operation, spectrophotometric pH with m-cresol purple, reference-material QC, CO2SYS) to weather-quality targets.</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Partial — net-tow/bottle sampling farmer-doable; microscopy enumeration/ID and qPCR need a taxonomist/partner lab.</t>
+          <t>Partial — the in-a-Box kit lets a practitioner sample and measure pH; alkalinity titration, reference-material QC and CO2SYS still need training/partner support.</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -31582,7 +31634,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>Plankton net/Niskin, settling chambers, inverted microscope; (qPCR for molecular)</t>
+          <t>GOA-ON in a Box kit, CTD-Diver, iSAMI pH sensor, spectrophotometer, reagents</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -31592,17 +31644,17 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Year-long study (12 months)</t>
+          <t>Multi-season (3–9 months)</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>Utermöhl counts; community composition; molecular enumeration</t>
+          <t>Carbonate-system computation (CO2SYS); QA against reference materials</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>Yes — Open (UNESCO/IOC PDF)</t>
+          <t>Yes — Open (PubPub)</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
@@ -31612,12 +31664,12 @@
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>https://unesdoc.unesco.org (IOC Manuals &amp; Guides 55, 2010)</t>
+          <t>https://oceanacidificationcookbook.org</t>
         </is>
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>The standard route to the phytoplankton/microorganism indicator; eDNA metabarcoding is the emerging molecular complement.</t>
+          <t>Built around the low-cost 'GOA-ON in a Box' kit and aimed at low-resource teams; the Dickson guide is the research-grade reference behind it.</t>
         </is>
       </c>
       <c r="V151" t="inlineStr">
@@ -31632,17 +31684,17 @@
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>Seaweed, Mollusk</t>
+          <t>Seaweed</t>
         </is>
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>Water Quality</t>
+          <t>Climate Change</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>WQ 2.1.2 — Microorganisms</t>
+          <t>CC 2.1.1 — pH / ocean acidification</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -31677,7 +31729,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>Plankton sampling</t>
+          <t>Carbonate chemistry</t>
         </is>
       </c>
       <c r="AH151" t="inlineStr">
@@ -31697,7 +31749,7 @@
       </c>
       <c r="AK151" s="16" t="inlineStr">
         <is>
-          <t>This canonical manual is the standard route to the phytoplankton/microorganism indicator. Collect water with a net or Niskin, settle sub-samples in chambers and count/identify phytoplankton by inverted microscope (Utermohl method), or use molecular (qPCR) enumeration for the community. Follow it for replicable community composition and abundance; HELCOM species lists and the AQUACOSM SOP give a practical workflow, and eDNA metabarcoding is the emerging molecular complement.</t>
+          <t>This practitioner-level protocol lowers the barrier to carbonate-system (pH / ocean-acidification) monitoring, built around the low-cost 'GOA-ON in a Box' kit for low-resource teams. Follow its step-by-step SOPs: site selection, water sampling, sensor operation, spectrophotometric pH with m-cresol purple (or an iSAMI sensor) and total alkalinity, then compute the carbonate system with CO2SYS, with quality control against certified reference materials to weather-quality targets. It is the practical route to the pH indicator (and relevant to mollusc shell/carbonate contexts); the research-grade Dickson guide is the analytical reference behind it.</t>
         </is>
       </c>
       <c r="AL151" s="17" t="inlineStr">
@@ -31707,7 +31759,7 @@
       </c>
       <c r="AM151" s="18" t="inlineStr">
         <is>
-          <t>karlson_2010</t>
+          <t>goaon_2024</t>
         </is>
       </c>
       <c r="AN151" s="19" t="n"/>
@@ -31715,62 +31767,62 @@
       <c r="AP151" s="19" t="n"/>
       <c r="AQ151" s="16" t="inlineStr">
         <is>
-          <t>Quantitative Phytoplankton Analysis Manual (Microscopy + Molecular)</t>
+          <t>Low-Cost Ocean-Acidification Monitoring (GOA-ON Cookbook)</t>
         </is>
       </c>
       <c r="AR151" s="16" t="inlineStr">
         <is>
-          <t>Karlson, B.; Cusack, C.; Bresnan, E. (eds.) — UNESCO/IOC</t>
+          <t>Global Ocean Acidification Observing Network (GOA-ON)</t>
         </is>
       </c>
       <c r="AS151" s="16" t="inlineStr">
         <is>
-          <t>HELCOM Phytoplankton Expert Group species lists and the AQUACOSM phytoplankton SOP give the practical sampling/ID workflow. eDNA metabarcoding (row 24) is the emerging molecular complement.</t>
+          <t>Lowers the OA-monitoring barrier dramatically vs. research-grade SOPs (next row). The EPA 'Guidelines for Measuring Changes in Seawater pH... Eastern US' (Pimenta &amp; Grear 2018) and the SDG 14.3.1 indicator methodology are companion references. Also relevant to mollusc shell/carbonate contexts.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Global Ocean Acidification Observing Network (GOA-ON)</t>
+          <t>Dickson, A. G., et al.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Practical Best Practices for Ocean Acidification Monitoring (the 'OA Cookbook') + GOA-ON in a Box kit</t>
+          <t>Guide to Best Practices for Ocean Acidification Research and Data Reporting (+ addendum)</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>GOA-ON (PubPub)</t>
+          <t>GOA-ON / EU / IOCCP</t>
         </is>
       </c>
       <c r="G152" t="n">
-        <v>2024</v>
+        <v>2010</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Global Ocean Acidification Observing Network</t>
+          <t>Publications Office of the European Union</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Practitioner-level SOPs for coastal carbonate-system monitoring (pH via spectrophotometry / iSAMI sensor, total alkalinity, CO2SYS), built around the low-cost GOA-ON in a Box kit and explicitly aimed at low-resource teams. The practical route to the pH / ocean-acidification indicator.</t>
+          <t>The authoritative research-grade SOPs for seawater carbonate-system measurement and OA experimental design/data reporting — the analytical reference underpinning the OA Cookbook.</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Protocol</t>
+          <t>Reference (authoritative SOP / usable design tool)</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Yes — step-by-step SOPs (site selection, sampling, sensor operation, spectrophotometric pH with m-cresol purple, reference-material QC, CO2SYS) to weather-quality targets.</t>
+          <t>Adequate as the analytical gold-standard reference: defines high-accuracy pH/DIC/TA/pCO2 methods and reporting; a research programme is built from it.</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>Partial — the in-a-Box kit lets a practitioner sample and measure pH; alkalinity titration, reference-material QC and CO2SYS still need training/partner support.</t>
+          <t>No — research-grade carbonate chemistry throughout (CRM-traceable, high-precision instrumentation).</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -31780,27 +31832,27 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>GOA-ON in a Box kit, CTD-Diver, iSAMI pH sensor, spectrophotometer, reagents</t>
+          <t>Research-grade spectrophotometry/coulometry, certified reference materials</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Multi-season (3–9 months)</t>
+          <t>Not time-specific</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>Carbonate-system computation (CO2SYS); QA against reference materials</t>
+          <t>High-accuracy carbonate-system SOPs; OA experimental design</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>Yes — Open (PubPub)</t>
+          <t>Yes — Open (PDF + addendum)</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
@@ -31810,12 +31862,12 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>https://oceanacidificationcookbook.org</t>
+          <t>https://goa-on.org/resources/manuals.php</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>Built around the low-cost 'GOA-ON in a Box' kit and aimed at low-resource teams; the Dickson guide is the research-grade reference behind it.</t>
+          <t>Pair it with the practitioner OA cookbook for low-cost field deployment.</t>
         </is>
       </c>
       <c r="V152" t="inlineStr">
@@ -31825,12 +31877,12 @@
       </c>
       <c r="W152" s="7" t="inlineStr">
         <is>
-          <t>3 — Partnership</t>
+          <t>2 — Researcher</t>
         </is>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>Seaweed</t>
+          <t>Seaweed, Mollusk</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
@@ -31895,17 +31947,17 @@
       </c>
       <c r="AK152" s="16" t="inlineStr">
         <is>
-          <t>This practitioner-level protocol lowers the barrier to carbonate-system (pH / ocean-acidification) monitoring, built around the low-cost 'GOA-ON in a Box' kit for low-resource teams. Follow its step-by-step SOPs: site selection, water sampling, sensor operation, spectrophotometric pH with m-cresol purple (or an iSAMI sensor) and total alkalinity, then compute the carbonate system with CO2SYS, with quality control against certified reference materials to weather-quality targets. It is the practical route to the pH indicator (and relevant to mollusc shell/carbonate contexts); the research-grade Dickson guide is the analytical reference behind it.</t>
+          <t>This is the authoritative research-grade reference for seawater carbonate-system measurement and ocean-acidification experimental design and data reporting - the analytical gold standard (high-accuracy pH, DIC, total alkalinity, pCO2) underpinning the practitioner OA cookbook. Use it to build a weather-quality ocean-acidification programme or to anchor methods; pair it with the cookbook for low-cost field deployment.</t>
         </is>
       </c>
       <c r="AL152" s="17" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Ref</t>
         </is>
       </c>
       <c r="AM152" s="18" t="inlineStr">
         <is>
-          <t>goaon_2024</t>
+          <t>dickson_2010</t>
         </is>
       </c>
       <c r="AN152" s="19" t="n"/>
@@ -31913,62 +31965,62 @@
       <c r="AP152" s="19" t="n"/>
       <c r="AQ152" s="16" t="inlineStr">
         <is>
-          <t>Low-Cost Ocean-Acidification Monitoring (GOA-ON Cookbook)</t>
+          <t>Research-Grade Ocean-Acidification Measurement SOPs (Reference)</t>
         </is>
       </c>
       <c r="AR152" s="16" t="inlineStr">
         <is>
-          <t>Global Ocean Acidification Observing Network (GOA-ON)</t>
+          <t>Dickson, A.G.; Sabine, C.L.; Christian, J.R. (eds.); Riebesell, U.; et al.</t>
         </is>
       </c>
       <c r="AS152" s="16" t="inlineStr">
         <is>
-          <t>Lowers the OA-monitoring barrier dramatically vs. research-grade SOPs (next row). The EPA 'Guidelines for Measuring Changes in Seawater pH... Eastern US' (Pimenta &amp; Grear 2018) and the SDG 14.3.1 indicator methodology are companion references. Also relevant to mollusc shell/carbonate contexts.</t>
+          <t>The reference standard for weather-quality OA data; pair with the practitioner-facing OA Cookbook (previous row) for field deployment. Tier T2 as a researcher-grade design tool.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Dickson, A. G., et al.</t>
+          <t>Verra</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Guide to Best Practices for Ocean Acidification Research and Data Reporting (+ addendum)</t>
+          <t>Methodology Framework for Seaweed Carbon Projects (VCS M0172; incl. archived seaweed-aquaculture removals methodology)</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>GOA-ON / EU / IOCCP</t>
+          <t>Verra (Verified Carbon Standard)</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>2010</v>
+        <v>2024</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Publications Office of the European Union</t>
+          <t>Verra</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>The authoritative research-grade SOPs for seawater carbonate-system measurement and OA experimental design/data reporting — the analytical reference underpinning the OA Cookbook.</t>
+          <t>Carbon-crediting methodology framework for seaweed projects (in development). Its cradle-to-grave project-emissions accounting (LCA) maps to seaweed CC 1.2.1 (GHG); its core carbon-removal/sequestration crediting falls OUTSIDE the MEL indicator set (the framework deliberately excludes seaweed carbon sequestration as too uncertain to account).</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Reference (authoritative SOP / usable design tool)</t>
+          <t>Reference (carbon-accounting methodology framework)</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Adequate as the analytical gold-standard reference: defines high-accuracy pH/DIC/TA/pCO2 methods and reporting; a research programme is built from it.</t>
+          <t>Adequate only for the GHG-accounting (LCA) component vis-à-vis MEL; the sequestration/removals crediting it primarily addresses has no MEL indicator home (Sub-rule 1b note).</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>No — research-grade carbonate chemistry throughout (CRM-traceable, high-precision instrumentation).</t>
+          <t>No — project-level carbon MRV requires specialist accounting/verification.</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -31978,7 +32030,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>Research-grade spectrophotometry/coulometry, certified reference materials</t>
+          <t>LCA/MRV accounting (remote sensing, sampling, modelling)</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -31988,32 +32040,32 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Not time-specific</t>
+          <t>One-time (no sampling — desk-based)</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>High-accuracy carbonate-system SOPs; OA experimental design</t>
+          <t>Carbon-accounting methodology; net-removal computation</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>Yes — Open (PDF + addendum)</t>
+          <t>Yes — Open (Verra methodology page)</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>Abstract + Methods (fetched)</t>
+          <t>Abstract only</t>
         </is>
       </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>https://goa-on.org/resources/manuals.php</t>
+          <t>https://verra.org/methodologies/</t>
         </is>
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>Pair it with the practitioner OA cookbook for low-cost field deployment.</t>
+          <t>MEL does not measure seaweed carbon sequestration - only the cradle-to-grave greenhouse-gas footprint overlaps; treat carbon-removal crediting as outside scope.</t>
         </is>
       </c>
       <c r="V153" t="inlineStr">
@@ -32028,7 +32080,7 @@
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>Seaweed, Mollusk</t>
+          <t>Seaweed</t>
         </is>
       </c>
       <c r="Y153" t="inlineStr">
@@ -32038,7 +32090,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>CC 2.1.1 — pH / ocean acidification</t>
+          <t>CC 1.2.1 — Cradle-to-grave GHG emissions, Not in MEL framework</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -32073,7 +32125,7 @@
       </c>
       <c r="AG153" t="inlineStr">
         <is>
-          <t>Carbonate chemistry</t>
+          <t>Modelling, Remote sensing</t>
         </is>
       </c>
       <c r="AH153" t="inlineStr">
@@ -32093,7 +32145,7 @@
       </c>
       <c r="AK153" s="16" t="inlineStr">
         <is>
-          <t>This is the authoritative research-grade reference for seawater carbonate-system measurement and ocean-acidification experimental design and data reporting - the analytical gold standard (high-accuracy pH, DIC, total alkalinity, pCO2) underpinning the practitioner OA cookbook. Use it to build a weather-quality ocean-acidification programme or to anchor methods; pair it with the cookbook for low-cost field deployment.</t>
+          <t>This is an in-development carbon-crediting methodology framework for seaweed projects. Only its cradle-to-grave project-emissions (life-cycle) accounting maps to the seaweed GHG indicator; its core carbon-removal/sequestration crediting sits deliberately outside the MEL indicator set (the framework itself excludes seaweed carbon sequestration). It is included to flag that live grey-literature area - MEL measures only the cradle-to-grave GHG overlap, not sequestration MRV.</t>
         </is>
       </c>
       <c r="AL153" s="17" t="inlineStr">
@@ -32103,7 +32155,7 @@
       </c>
       <c r="AM153" s="18" t="inlineStr">
         <is>
-          <t>dickson_2010</t>
+          <t>verra_2024</t>
         </is>
       </c>
       <c r="AN153" s="19" t="n"/>
@@ -32111,62 +32163,67 @@
       <c r="AP153" s="19" t="n"/>
       <c r="AQ153" s="16" t="inlineStr">
         <is>
-          <t>Research-Grade Ocean-Acidification Measurement SOPs (Reference)</t>
+          <t>Seaweed Carbon-Project Accounting Framework (GHG-Footprint Overlap Only)</t>
         </is>
       </c>
       <c r="AR153" s="16" t="inlineStr">
         <is>
-          <t>Dickson, A.G.; Sabine, C.L.; Christian, J.R. (eds.); Riebesell, U.; et al.</t>
+          <t>Verra; Oceans 2050 (input)</t>
         </is>
       </c>
       <c r="AS153" s="16" t="inlineStr">
         <is>
-          <t>The reference standard for weather-quality OA data; pair with the practitioner-facing OA Cookbook (previous row) for field deployment. Tier T2 as a researcher-grade design tool.</t>
+          <t>Included to flag a live grey-lit area (seaweed carbon MRV) that the MEL framework intentionally does NOT measure — only the cradle-to-grave GHG (CC 1.2.1) overlaps. The earlier standalone removals methodology was archived (June 2024); development moved into M0172. Tier T2.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Verra</t>
+          <t>Pacific Northwest National Laboratory (PNNL)</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Methodology Framework for Seaweed Carbon Projects (VCS M0172; incl. archived seaweed-aquaculture removals methodology)</t>
+          <t>Macroalgae mCDR: LCA, Carbon Sequestration/Permanence and MRV Methods Review (PNNL-33997)</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Verra (Verified Carbon Standard)</t>
+          <t>PNNL Technical Report</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>PNNL-33997</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Verra</t>
+          <t>US DOE / Pacific Northwest National Laboratory</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Carbon-crediting methodology framework for seaweed projects (in development). Its cradle-to-grave project-emissions accounting (LCA) maps to seaweed CC 1.2.1 (GHG); its core carbon-removal/sequestration crediting falls OUTSIDE the MEL indicator set (the framework deliberately excludes seaweed carbon sequestration as too uncertain to account).</t>
+          <t>Technical report reviewing LCA + monitoring/reporting/verification (MRV) methods for macroalgae carbon-dioxide removal (remote sensing, physical/sediment sampling, eDNA+coring for permanence, modelling, forensic carbon accounting). LCA/GHG-accounting maps to seaweed CC 1.2.1; the sequestration-permanence focus sits outside the MEL indicator set.</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Reference (carbon-accounting methodology framework)</t>
+          <t>Reference (methods review / usable design tool)</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Adequate only for the GHG-accounting (LCA) component vis-à-vis MEL; the sequestration/removals crediting it primarily addresses has no MEL indicator home (Sub-rule 1b note).</t>
+          <t>Adequate as an MRV methods inventory a programme is built from; not a single executable protocol. LCA component aligns to CC 1.2.1.</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>No — project-level carbon MRV requires specialist accounting/verification.</t>
+          <t>No — carbon MRV/LCA is specialist throughout.</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -32176,7 +32233,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>LCA/MRV accounting (remote sensing, sampling, modelling)</t>
+          <t>LCA software, remote sensing, sediment coring, eDNA</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -32191,27 +32248,27 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>Carbon-accounting methodology; net-removal computation</t>
+          <t>LCA; MRV method comparison</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>Yes — Open (Verra methodology page)</t>
+          <t>Yes — Open (PNNL PDF)</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>Abstract only</t>
+          <t>Abstract + Methods (fetched)</t>
         </is>
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>https://verra.org/methodologies/</t>
+          <t>https://www.pnnl.gov/main/publications/external/technical_reports/PNNL-33997.pdf</t>
         </is>
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>MEL does not measure seaweed carbon sequestration - only the cradle-to-grave greenhouse-gas footprint overlaps; treat carbon-removal crediting as outside scope.</t>
+          <t>Only the greenhouse-gas-footprint component maps to MEL; there are as yet no established MRV protocols for macroalgae carbon capture or permanence.</t>
         </is>
       </c>
       <c r="V154" t="inlineStr">
@@ -32271,7 +32328,7 @@
       </c>
       <c r="AG154" t="inlineStr">
         <is>
-          <t>Modelling, Remote sensing</t>
+          <t>Modelling, Remote sensing, eDNA</t>
         </is>
       </c>
       <c r="AH154" t="inlineStr">
@@ -32291,7 +32348,7 @@
       </c>
       <c r="AK154" s="16" t="inlineStr">
         <is>
-          <t>This is an in-development carbon-crediting methodology framework for seaweed projects. Only its cradle-to-grave project-emissions (life-cycle) accounting maps to the seaweed GHG indicator; its core carbon-removal/sequestration crediting sits deliberately outside the MEL indicator set (the framework itself excludes seaweed carbon sequestration). It is included to flag that live grey-literature area - MEL measures only the cradle-to-grave GHG overlap, not sequestration MRV.</t>
+          <t>This technical report reviews life-cycle-assessment and monitoring/reporting/verification methods for macroalgae carbon-dioxide removal (remote sensing, sediment sampling, eDNA-plus-coring for permanence, modelling, forensic carbon accounting). Within MEL scope only the LCA/GHG-accounting component maps to the seaweed GHG indicator; the sequestration/permanence side has no MEL home. Its honest takeaway is that there are as yet no established MRV protocols for macroalgae carbon capture or permanence.</t>
         </is>
       </c>
       <c r="AL154" s="17" t="inlineStr">
@@ -32301,7 +32358,7 @@
       </c>
       <c r="AM154" s="18" t="inlineStr">
         <is>
-          <t>verra_2024</t>
+          <t>pnnl_2023</t>
         </is>
       </c>
       <c r="AN154" s="19" t="n"/>
@@ -32309,67 +32366,62 @@
       <c r="AP154" s="19" t="n"/>
       <c r="AQ154" s="16" t="inlineStr">
         <is>
-          <t>Seaweed Carbon-Project Accounting Framework (GHG-Footprint Overlap Only)</t>
+          <t>Macroalgae Carbon-Removal MRV Methods Review (Reference)</t>
         </is>
       </c>
       <c r="AR154" s="16" t="inlineStr">
         <is>
-          <t>Verra; Oceans 2050 (input)</t>
+          <t>Pacific Northwest National Laboratory (PNNL)</t>
         </is>
       </c>
       <c r="AS154" s="16" t="inlineStr">
         <is>
-          <t>Included to flag a live grey-lit area (seaweed carbon MRV) that the MEL framework intentionally does NOT measure — only the cradle-to-grave GHG (CC 1.2.1) overlaps. The earlier standalone removals methodology was archived (June 2024); development moved into M0172. Tier T2.</t>
+          <t>Honest caveat across this literature: there are as yet no established MRV protocols for macroalgae carbon capture/permanence. The EDF 'Carbon Sequestration by Seaweed' report is a companion NGO context piece. Only the cradle-to-grave GHG (CC 1.2.1) overlaps MEL.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Pacific Northwest National Laboratory (PNNL)</t>
+          <t>ISO</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Macroalgae mCDR: LCA, Carbon Sequestration/Permanence and MRV Methods Review (PNNL-33997)</t>
+          <t>Life-cycle assessment standards for cradle-to-grave GHG (ISO 14040 / ISO 14044; PAS 2050)</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>PNNL Technical Report</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>PNNL-33997</t>
+          <t>ISO / BSI</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>US DOE / Pacific Northwest National Laboratory</t>
+          <t>International Organization for Standardization / BSI</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Technical report reviewing LCA + monitoring/reporting/verification (MRV) methods for macroalgae carbon-dioxide removal (remote sensing, physical/sediment sampling, eDNA+coring for permanence, modelling, forensic carbon accounting). LCA/GHG-accounting maps to seaweed CC 1.2.1; the sequestration-permanence focus sits outside the MEL indicator set.</t>
+          <t>The underlying standards for cradle-to-grave GHG/carbon-footprint accounting that operationalise the GHG-emissions indicator across all three sectors. Cradle-to-grave GHG = CC 1.1.1 (molluscs &amp; finfish) and CC 1.2.1 (seaweed).</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Reference (methods review / usable design tool)</t>
+          <t>Reference (standards / usable design tool)</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Adequate as an MRV methods inventory a programme is built from; not a single executable protocol. LCA component aligns to CC 1.2.1.</t>
+          <t>Adequate as the methodological backbone for any aquaculture LCA/carbon-footprint; a footprint study is built from these standards (often with seafood-specific guidance).</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>No — carbon MRV/LCA is specialist throughout.</t>
+          <t>No — LCA specialists.</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -32379,12 +32431,12 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>LCA software, remote sensing, sediment coring, eDNA</t>
+          <t>LCA software + life-cycle inventory data</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium–High</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -32394,27 +32446,27 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>LCA; MRV method comparison</t>
+          <t>Life-cycle inventory + impact assessment (GWP)</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>Yes — Open (PNNL PDF)</t>
+          <t>No — Paywalled (ISO; PAS 2050 via BSI)</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>Abstract + Methods (fetched)</t>
+          <t>Title only (no abstract or DOI)</t>
         </is>
       </c>
       <c r="T155" t="inlineStr">
         <is>
-          <t>https://www.pnnl.gov/main/publications/external/technical_reports/PNNL-33997.pdf</t>
+          <t>https://www.iso.org/standard/37456.html (ISO 14040)</t>
         </is>
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>Only the greenhouse-gas-footprint component maps to MEL; there are as yet no established MRV protocols for macroalgae carbon capture or permanence.</t>
+          <t>The methodological backbone for any aquaculture carbon-footprint study; note GHG is CC 1.1.1 for molluscs/finfish but CC 1.2.1 for seaweed.</t>
         </is>
       </c>
       <c r="V155" t="inlineStr">
@@ -32429,7 +32481,7 @@
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>Seaweed</t>
+          <t>Seaweed, Mollusk, Finfish</t>
         </is>
       </c>
       <c r="Y155" t="inlineStr">
@@ -32439,7 +32491,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>CC 1.2.1 — Cradle-to-grave GHG emissions, Not in MEL framework</t>
+          <t>CC 1.1.1 — Cradle-to-grave GHG, CC 1.2.1 — Cradle-to-grave GHG emissions</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -32474,7 +32526,7 @@
       </c>
       <c r="AG155" t="inlineStr">
         <is>
-          <t>Modelling, Remote sensing, eDNA</t>
+          <t>Modelling</t>
         </is>
       </c>
       <c r="AH155" t="inlineStr">
@@ -32494,7 +32546,7 @@
       </c>
       <c r="AK155" s="16" t="inlineStr">
         <is>
-          <t>This technical report reviews life-cycle-assessment and monitoring/reporting/verification methods for macroalgae carbon-dioxide removal (remote sensing, sediment sampling, eDNA-plus-coring for permanence, modelling, forensic carbon accounting). Within MEL scope only the LCA/GHG-accounting component maps to the seaweed GHG indicator; the sequestration/permanence side has no MEL home. Its honest takeaway is that there are as yet no established MRV protocols for macroalgae carbon capture or permanence.</t>
+          <t>These are the underlying life-cycle-assessment standards (ISO 14040/14044, PAS 2050) that operationalise cradle-to-grave GHG / carbon-footprint accounting across all sectors. A footprint study is built from them - compile a life-cycle inventory and run impact assessment (global-warming potential) - typically with seafood-specific guidance layered on. Included so the GHG indicator has a methodological home; note the dual numbering (cradle-to-grave GHG is CC 1.1.1 for molluscs/finfish but CC 1.2.1 for seaweed). (Entry from general knowledge - consult the standards themselves for procedure.)</t>
         </is>
       </c>
       <c r="AL155" s="17" t="inlineStr">
@@ -32504,7 +32556,7 @@
       </c>
       <c r="AM155" s="18" t="inlineStr">
         <is>
-          <t>pnnl_2023</t>
+          <t>iso_2021</t>
         </is>
       </c>
       <c r="AN155" s="19" t="n"/>
@@ -32512,62 +32564,70 @@
       <c r="AP155" s="19" t="n"/>
       <c r="AQ155" s="16" t="inlineStr">
         <is>
-          <t>Macroalgae Carbon-Removal MRV Methods Review (Reference)</t>
+          <t>Life-Cycle Assessment Standards for GHG Footprinting (Reference)</t>
         </is>
       </c>
       <c r="AR155" s="16" t="inlineStr">
         <is>
-          <t>Pacific Northwest National Laboratory (PNNL)</t>
+          <t>ISO; BSI (PAS 2050)</t>
         </is>
       </c>
       <c r="AS155" s="16" t="inlineStr">
         <is>
-          <t>Honest caveat across this literature: there are as yet no established MRV protocols for macroalgae carbon capture/permanence. The EDF 'Carbon Sequestration by Seaweed' report is a companion NGO context piece. Only the cradle-to-grave GHG (CC 1.2.1) overlaps MEL.</t>
+          <t>General-knowledge entry (not a fetched source this session); included so the cradle-to-grave GHG indicator has a protocol home. Seafood-specific LCA guidance and ASC/MSC footprint work build on these. Note the dual numbering: cradle-to-grave GHG = CC 1.1.1 for molluscs/finfish but CC 1.2.1 for seaweed.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ISO</t>
+          <t>Gold, Z., et al.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Life-cycle assessment standards for cradle-to-grave GHG (ISO 14040 / ISO 14044; PAS 2050)</t>
+          <t>A manager's guide to using eDNA metabarcoding in marine ecosystems</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ISO / BSI</t>
+          <t>PeerJ</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>e14071</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>International Organization for Standardization / BSI</t>
+          <t>PeerJ</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>The underlying standards for cradle-to-grave GHG/carbon-footprint accounting that operationalise the GHG-emissions indicator across all three sectors. Cradle-to-grave GHG = CC 1.1.1 (molluscs &amp; finfish) and CC 1.2.1 (seaweed).</t>
+          <t>Practitioner-/manager-facing guide to designing eDNA metabarcoding monitoring programmes (primer selection, reference databases, decontamination, pilot variance, archiving). Cross-cutting biodiversity tool serving epibiota, mobile fauna, community composition, and plankton indicators.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Reference (standards / usable design tool)</t>
+          <t>Reference (usable design tool / manager guide)</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Adequate as the methodological backbone for any aquaculture LCA/carbon-footprint; a footprint study is built from these standards (often with seafood-specific guidance).</t>
+          <t>Adequate as a programme-design guide: five decision steps for a defensible eDNA monitoring programme; not itself a single bench protocol.</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>No — LCA specialists.</t>
+          <t>No — water sampling/filtration is simple, but the metabarcoding pipeline (extraction, PCR, sequencing, bioinformatics) is specialist throughout.</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -32577,42 +32637,42 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>LCA software + life-cycle inventory data</t>
+          <t>Filtration kit; molecular lab (extraction, PCR, sequencing); bioinformatics</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Medium–High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>One-time (no sampling — desk-based)</t>
+          <t>Not time-specific</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>Life-cycle inventory + impact assessment (GWP)</t>
+          <t>Site-occupancy decontamination; metabarcoding bioinformatics</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>No — Paywalled (ISO; PAS 2050 via BSI)</t>
+          <t>Yes — Open (PeerJ, CC-BY)</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>Title only (no abstract or DOI)</t>
+          <t>Abstract + Methods (fetched)</t>
         </is>
       </c>
       <c r="T156" t="inlineStr">
         <is>
-          <t>https://www.iso.org/standard/37456.html (ISO 14040)</t>
+          <t>https://peerj.com/articles/14071/</t>
         </is>
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>The methodological backbone for any aquaculture carbon-footprint study; note GHG is CC 1.1.1 for molluscs/finfish but CC 1.2.1 for seaweed.</t>
+          <t>A programme-design guide; a Springer protocol chapter gives the bench SOP, and formal eDNA standardisation is still in progress.</t>
         </is>
       </c>
       <c r="V156" t="inlineStr">
@@ -32632,12 +32692,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>Climate Change</t>
+          <t>Habitat &amp; Biodiversity, Water Quality</t>
         </is>
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>CC 1.1.1 — Cradle-to-grave GHG, CC 1.2.1 — Cradle-to-grave GHG emissions</t>
+          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 1.2.1 — Mobile fauna, H&amp;B 2.1.1 — Community composition, WQ 2.1.2 — Microorganisms</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -32672,7 +32732,7 @@
       </c>
       <c r="AG156" t="inlineStr">
         <is>
-          <t>Modelling</t>
+          <t>eDNA</t>
         </is>
       </c>
       <c r="AH156" t="inlineStr">
@@ -32692,7 +32752,7 @@
       </c>
       <c r="AK156" s="16" t="inlineStr">
         <is>
-          <t>These are the underlying life-cycle-assessment standards (ISO 14040/14044, PAS 2050) that operationalise cradle-to-grave GHG / carbon-footprint accounting across all sectors. A footprint study is built from them - compile a life-cycle inventory and run impact assessment (global-warming potential) - typically with seafood-specific guidance layered on. Included so the GHG indicator has a methodological home; note the dual numbering (cradle-to-grave GHG is CC 1.1.1 for molluscs/finfish but CC 1.2.1 for seaweed). (Entry from general knowledge - consult the standards themselves for procedure.)</t>
+          <t>This manager-facing guide helps design a defensible eDNA metabarcoding monitoring programme - primer selection, reference databases, decontamination, pilot variance and archiving - as a cross-cutting biodiversity tool (epibiota, mobile fauna, community composition, plankton). Use it to plan the programme; a Springer protocol chapter gives the bench sampling/extraction SOP, and formal ISO/CEN eDNA standardisation is still in progress. It pairs with the MarineGEO fouling/ARMS and IOC phytoplankton methods.</t>
         </is>
       </c>
       <c r="AL156" s="17" t="inlineStr">
@@ -32702,7 +32762,7 @@
       </c>
       <c r="AM156" s="18" t="inlineStr">
         <is>
-          <t>iso_2021</t>
+          <t>gold_2022</t>
         </is>
       </c>
       <c r="AN156" s="19" t="n"/>
@@ -32710,221 +32770,15 @@
       <c r="AP156" s="19" t="n"/>
       <c r="AQ156" s="16" t="inlineStr">
         <is>
-          <t>Life-Cycle Assessment Standards for GHG Footprinting (Reference)</t>
+          <t>Designing an eDNA Metabarcoding Monitoring Programme (Manager's Guide)</t>
         </is>
       </c>
       <c r="AR156" s="16" t="inlineStr">
         <is>
-          <t>ISO; BSI (PAS 2050)</t>
+          <t>Gold, Z.; Sprague, J.; Kushner, D.J.; et al.</t>
         </is>
       </c>
       <c r="AS156" s="16" t="inlineStr">
-        <is>
-          <t>General-knowledge entry (not a fetched source this session); included so the cradle-to-grave GHG indicator has a protocol home. Seafood-specific LCA guidance and ASC/MSC footprint work build on these. Note the dual numbering: cradle-to-grave GHG = CC 1.1.1 for molluscs/finfish but CC 1.2.1 for seaweed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Gold, Z., et al.</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>A manager's guide to using eDNA metabarcoding in marine ecosystems</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>PeerJ</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>e14071</t>
-        </is>
-      </c>
-      <c r="G157" t="n">
-        <v>2022</v>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>PeerJ</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Practitioner-/manager-facing guide to designing eDNA metabarcoding monitoring programmes (primer selection, reference databases, decontamination, pilot variance, archiving). Cross-cutting biodiversity tool serving epibiota, mobile fauna, community composition, and plankton indicators.</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>Reference (usable design tool / manager guide)</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>Adequate as a programme-design guide: five decision steps for a defensible eDNA monitoring programme; not itself a single bench protocol.</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>No — water sampling/filtration is simple, but the metabarcoding pipeline (extraction, PCR, sequencing, bioinformatics) is specialist throughout.</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>Filtration kit; molecular lab (extraction, PCR, sequencing); bioinformatics</t>
-        </is>
-      </c>
-      <c r="O157" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P157" t="inlineStr">
-        <is>
-          <t>Not time-specific</t>
-        </is>
-      </c>
-      <c r="Q157" t="inlineStr">
-        <is>
-          <t>Site-occupancy decontamination; metabarcoding bioinformatics</t>
-        </is>
-      </c>
-      <c r="R157" t="inlineStr">
-        <is>
-          <t>Yes — Open (PeerJ, CC-BY)</t>
-        </is>
-      </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>Abstract + Methods (fetched)</t>
-        </is>
-      </c>
-      <c r="T157" t="inlineStr">
-        <is>
-          <t>https://peerj.com/articles/14071/</t>
-        </is>
-      </c>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>A programme-design guide; a Springer protocol chapter gives the bench SOP, and formal eDNA standardisation is still in progress.</t>
-        </is>
-      </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>Provided by Claude (grey/white-lit protocol search)</t>
-        </is>
-      </c>
-      <c r="W157" s="7" t="inlineStr">
-        <is>
-          <t>2 — Researcher</t>
-        </is>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>Seaweed, Mollusk, Finfish</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>Habitat &amp; Biodiversity, Water Quality</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 1.2.1 — Mobile fauna, H&amp;B 2.1.1 — Community composition, WQ 2.1.2 — Microorganisms</t>
-        </is>
-      </c>
-      <c r="AA157" t="inlineStr">
-        <is>
-          <t>Cross-zone / global</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>Not species-specific</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Not gear-specific</t>
-        </is>
-      </c>
-      <c r="AD157" t="inlineStr">
-        <is>
-          <t>Not scale-specific</t>
-        </is>
-      </c>
-      <c r="AE157" t="inlineStr">
-        <is>
-          <t>Not site-specific</t>
-        </is>
-      </c>
-      <c r="AF157" t="inlineStr">
-        <is>
-          <t>Not specific</t>
-        </is>
-      </c>
-      <c r="AG157" t="inlineStr">
-        <is>
-          <t>eDNA</t>
-        </is>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>Not algae-specific</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>Not depth-specific</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>Not exposure-specific</t>
-        </is>
-      </c>
-      <c r="AK157" s="16" t="inlineStr">
-        <is>
-          <t>This manager-facing guide helps design a defensible eDNA metabarcoding monitoring programme - primer selection, reference databases, decontamination, pilot variance and archiving - as a cross-cutting biodiversity tool (epibiota, mobile fauna, community composition, plankton). Use it to plan the programme; a Springer protocol chapter gives the bench sampling/extraction SOP, and formal ISO/CEN eDNA standardisation is still in progress. It pairs with the MarineGEO fouling/ARMS and IOC phytoplankton methods.</t>
-        </is>
-      </c>
-      <c r="AL157" s="17" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="AM157" s="18" t="inlineStr">
-        <is>
-          <t>gold_2022</t>
-        </is>
-      </c>
-      <c r="AN157" s="19" t="n"/>
-      <c r="AO157" s="19" t="n"/>
-      <c r="AP157" s="19" t="n"/>
-      <c r="AQ157" s="16" t="inlineStr">
-        <is>
-          <t>Designing an eDNA Metabarcoding Monitoring Programme (Manager's Guide)</t>
-        </is>
-      </c>
-      <c r="AR157" s="16" t="inlineStr">
-        <is>
-          <t>Gold, Z.; Sprague, J.; Kushner, D.J.; et al.</t>
-        </is>
-      </c>
-      <c r="AS157" s="16" t="inlineStr">
         <is>
           <t>A Springer protocol chapter ('Environmental DNA from Marine Waters and Substrates: Protocols for Sampling and eDNA Extraction') gives the bench SOP; formal ISO/CEN eDNA standardisation is still in progress. Pairs with MarineGEO Fouling/ARMS (cryptobiota) and IOC phytoplankton. The framework already cites Mercaldo-Allen 2021 (eDNA at oyster cages).</t>
         </is>

--- a/data/mel_database.xlsx
+++ b/data/mel_database.xlsx
@@ -1177,7 +1177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS156"/>
+  <dimension ref="A1:AS157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2730,11 +2730,7 @@
           <t>https://www.biorxiv.org/content/10.1101/2024.02.15.580450v1</t>
         </is>
       </c>
-      <c r="U8" s="16" t="inlineStr">
-        <is>
-          <t>BRUV results are conservative in turbid water (classify footage; use only clear frames), the bait biases detection toward generalist carnivores and under-detects cryptic and juvenile flatfish, and Nmax can be inflated by species that linger at the bait. Acoustic monitoring gives relative presence, not abundance, and a single detector covers a small area (patterns can differ within ~1 km), so deploy several for larger sites; boat traffic can confound diurnal patterns. Given the short timeframe and small farm scale, treat the results as a baseline rather than a conclusive link between farming and biodiversity. Detailed sub-methods are defined by cited sources (Unsworth 2014 for BRUV/Nmax; the detector's own software).</t>
-        </is>
-      </c>
+      <c r="U8" s="3" t="inlineStr"/>
       <c r="V8" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -2812,7 +2808,7 @@
       </c>
       <c r="AK8" s="16" t="inlineStr">
         <is>
-          <t>To document what lives on and around your farm — organisms growing on the lines and mobile animals drawn to the site — run three surveys in parallel and repeat them monthly through the growing season. For attached life (epibionts), pull a set length of header/cultivation line (e.g. 0.5 m sections) onto the boat at two spots along each longline, cut the growth off near the line, and back on land estimate the cover and identity of the organisms on the rope and on the kelp. For mobile fauna, deploy a baited underwater video camera (BRUV) on the seabed near the farm for about an hour per drop, scoring the peak number of each fish type visible at once (Nmax) and analysing only footage clear enough to identify animals. For marine mammals, moor a self-logging acoustic click-detector for continuous multi-week periods and export detection-positive minutes per day for each species. Compare these measures across sites and seasons; temperature, light, current and pH/salinity sensors can be logged alongside for context.</t>
+          <t>To document what lives on and around your farm — organisms growing on the lines and mobile animals drawn to the site — run three surveys in parallel and repeat them monthly through the growing season. For attached life (epibionts), pull a set length of header/cultivation line (e.g. 0.5 m sections) onto the boat at two spots along each longline, cut the growth off near the line, and back on land estimate the cover and identity of the organisms on the rope and on the kelp. For mobile fauna, deploy a baited underwater video camera (BRUV) on the seabed near the farm for about an hour per drop, scoring the peak number of each fish type visible at once (MaxN) and analysing only footage clear enough to identify animals. For marine mammals, moor a self-logging acoustic click-detector for continuous multi-week periods and export detection-positive minutes per day for each species. Compare these measures across sites and seasons; temperature, light, current and pH/salinity sensors can be logged alongside for context.</t>
         </is>
       </c>
       <c r="AL8" s="17" t="inlineStr">
@@ -6371,7 +6367,7 @@
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>Seaweed + finfish (IMTA)</t>
+          <t>Seaweed + finfish</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr">
@@ -7783,7 +7779,7 @@
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>Seaweed + finfish (IMTA)</t>
+          <t>Seaweed + finfish</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
@@ -8373,7 +8369,7 @@
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>Seaweed + finfish (IMTA)</t>
+          <t>Seaweed + finfish</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
@@ -9173,7 +9169,7 @@
       </c>
       <c r="AF40" s="3" t="inlineStr">
         <is>
-          <t>Seaweed + finfish (IMTA)</t>
+          <t>Seaweed + finfish</t>
         </is>
       </c>
       <c r="AG40" s="3" t="inlineStr">
@@ -13527,11 +13523,6 @@
           <t>https://doi.org/10.1016/j.aquaeng.2017.12.002</t>
         </is>
       </c>
-      <c r="U62" s="16" t="inlineStr">
-        <is>
-          <t>Biofouling is the single biggest limiter of accuracy and deployment length — use antifouling guards, clean at every visit, and keep the QC rules that catch fouling drift. Storms can tangle the instrument string around the float or part the surface buoy from the mooring; a robust mooring and the pressure-sensor surface-flag mitigate this. Validation is only as good as the reference instrument — confirm it is calibrated and working. Some sensors (dissolved oxygen, conductivity) drift and need periodic recalibration. The buoy characterises physico-chemical water quality (DO, temperature, salinity); it does not directly measure microorganisms or algae.</t>
-        </is>
-      </c>
       <c r="V62" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -13609,7 +13600,7 @@
       </c>
       <c r="AK62" s="16" t="inlineStr">
         <is>
-          <t>To monitor water quality continuously at your farm with minimal effort, moor a low-power sensor string on a buoy and let it log automatically. Fit sensors for the parameters of interest — here temperature at several depths, conductivity/salinity, dissolved oxygen and pressure (depth) — set them to log on a fixed short interval (e.g. every 10 minutes), and calibrate the DO sensor before deployment. Leave the string in place for months, visiting periodically (e.g. monthly) to lift the lightweight instrument chain, download the data to a handheld shuttle, scrub off biofouling, and take a reading with a calibrated reference (e.g. a hand-held CTD) to check sensor accuracy (RMSE and bias). Then clean the data with simple quality-control rules: drop readings outside sensible ranges, discard the first couple of hours after each deployment or cleaning, remove sudden single-point spikes, and cut the gradual biofouling drift before each cleaning; convert conductivity to salinity in software. The pressure sensor also flags when the string has floated to the surface, so those readings can be excluded.</t>
+          <t>To monitor water quality continuously at your farm with minimal effort, moor a low-power sensor string on a buoy and let it log automatically. Fit sensors for the parameters of interest — here temperature at several depths, conductivity/salinity, dissolved oxygen and pressure (depth) — set them to log on a fixed short interval (e.g. every 10 minutes), and calibrate the DO sensor before deployment. Leave the string in place for months, visiting periodically (e.g. monthly) to lift the lightweight instrument chain with a boat hook or the winch you use for mussel lines, download the data to a handheld shuttle, and scrub off biofouling. Then clean the data with simple quality-control rules: drop readings outside sensible ranges, discard the first couple of hours after each deployment or cleaning, remove sudden single-point spikes, and cut the gradual drift that builds before each cleaning (biofouling); convert conductivity to salinity in software. The pressure sensor also flags when the string has floated to the surface, so those readings can be excluded.</t>
         </is>
       </c>
       <c r="AL62" s="17" t="inlineStr">
@@ -15045,16 +15036,6 @@
           <t>Sheltered</t>
         </is>
       </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>To relate oyster-farm performance to environmental conditions over several crop years, pair simple in-situ measurements with satellite data. Record daily sea-surface temperature at a fixed station (manual thermometer at about 0.5 m) and obtain remote-sensing temperature and ocean-colour chlorophyll-a for the farming area from a satellite database, validating the satellite values against your in-situ readings by linear regression (satellite chlorophyll is often overestimated in shallow, sediment- or CDOM-rich water). Track farm records - survival and the duration of each rearing phase (seed-to-juvenile, juvenile-to-adult, adult-to-market) from routine grading of lantern-net stock - and flag wind direction, cold-front passages and El Nino/La Nina periods, computing the change in chlorophyll during cold fronts as a productivity signal. Regress survival and phase duration against mean water temperature and chlorophyll to identify the conditions driving crop performance, testing significance with Pearson correlation.</t>
-        </is>
-      </c>
-      <c r="AL69" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
       <c r="AM69" s="18" t="inlineStr">
         <is>
           <t>mizuta_2012</t>
@@ -15070,7 +15051,7 @@
       </c>
       <c r="AS69" s="16" t="inlineStr">
         <is>
-          <t>Underrepresented climate zone in v11 (subtropical SW Atlantic). Strong demonstration that satellite-derived chl-a is a usable predictor of commercial oyster yield — directly transferable to siting and climate-adaptation planning elsewhere. | v38: filled at High from pasted Methods (Mizuta); Source Read set to Full PDF.</t>
+          <t>Underrepresented climate zone in v11 (subtropical SW Atlantic). Strong demonstration that satellite-derived chl-a is a usable predictor of commercial oyster yield — directly transferable to siting and climate-adaptation planning elsewhere.</t>
         </is>
       </c>
     </row>
@@ -15166,7 +15147,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s11179-005-0036-3</t>
+          <t>https://link.springer.com/journal/11179</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -15242,16 +15223,6 @@
       <c r="AJ70" t="inlineStr">
         <is>
           <t>Sheltered</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>To monitor the phytoplankton community around a shellfish farm - for food-supply assessment and early warning of harmful blooms - collect water through the year at roughly monthly intervals with a bottle sampler (for example a 4 L Molchanov). Concentrate and settle the samples in Utermohl sedimentation chambers (with fine, around 2 um, filtration as needed), then identify and count cells under a light microscope using a counting chamber, converting counts to abundance and to biomass from cell-volume estimates. Describe the seasonal succession and track the taxa and density build-ups that precede harmful or toxic blooms, which are common around mariculture installations.</t>
-        </is>
-      </c>
-      <c r="AL70" t="inlineStr">
-        <is>
-          <t>Med</t>
         </is>
       </c>
       <c r="AM70" s="18" t="inlineStr">
@@ -15269,7 +15240,7 @@
       </c>
       <c r="AS70" s="16" t="inlineStr">
         <is>
-          <t>Uses the newly-added vocab entry Bay mussel (Mytilus trossulus) — exactly the species this v1.2→v1.3 vocab addition was for. Replicable HAB-detection-oriented monitoring protocol; bridges to the Schmidt 2018 Dinophysis use case. | v38: filled at Med from database methods notes (supplied file contained background text only for this paper). | v39: DOI added (10.1007/s11179-005-0036-3); prior value was a journal homepage only.</t>
+          <t>Uses the newly-added vocab entry Bay mussel (Mytilus trossulus) — exactly the species this v1.2→v1.3 vocab addition was for. Replicable HAB-detection-oriented monitoring protocol; bridges to the Schmidt 2018 Dinophysis use case.</t>
         </is>
       </c>
     </row>
@@ -15568,11 +15539,6 @@
           <t>https://www.aquaasiapac.com/</t>
         </is>
       </c>
-      <c r="U72" s="16" t="inlineStr">
-        <is>
-          <t>Expect heavy post-settlement mortality where the season brings low salinity and high siltation; fouling organisms (anemones, snails, barnacles) compete for settlement space, and sediment smothering during heavy rain can kill or delay spat. Collector materials weaken in seawater and storms — plan for repairs. The photographic spat count/measure technique is defined by cited method papers (Loosanoff 1966; O'Sullivan 1978; Davenport &amp; Glasspool 1987; Hendriks 2005), not the source. The source does not fix replicate count, collector/compartment dimensions, or the instrument for each water-quality parameter — set these at your site.</t>
-        </is>
-      </c>
       <c r="V72" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -15650,7 +15616,7 @@
       </c>
       <c r="AK72" s="16" t="inlineStr">
         <is>
-          <t>To find which substrate best recruits wild oyster spat for a community-scale collection or reef effort, build simple multi-compartment spat collectors (for example a locally-made bamboo-framed mattress) and fill the compartments with candidate substrates (such as windowpane shell, live oyster shell, dead oyster shell, and stone/rubble), deploying them side by side in the intertidal over a settlement season. Every two weeks — timed to the full and new moon — photograph each compartment against a fixed quadrat reference (about 38 x 38 cm) and, from the images, count settled spat and measure their length and width to track density, growth and survival over time, alongside basic water-quality readings. Compare substrate performance with a substrate-by-time analysis (for example PCA plus standard significance tests). The low-cost, locally-built design suits community-led implementation.</t>
+          <t>To find which substrate best recruits wild oyster spat for a community-scale collection or reef effort, build simple multi-compartment bamboo mattresses and fill the compartments with candidate substrates (for example windowpane shell, live oyster shell, dead oyster shell, and stone/rubble), deploying them side by side in the intertidal over a settlement season. Every two weeks photograph each compartment against a fixed quadrat reference (about 38 x 38 cm) and count settled spat from the images to track density over time, alongside basic water-quality readings. Compare substrate performance with a substrate-by-time analysis (for example PCA plus standard significance tests). The low-cost, locally-built design suits community-led implementation and doubles as an ecosystem-engineering, coastal-defence structure.</t>
         </is>
       </c>
       <c r="AL72" s="17" t="inlineStr">
@@ -16367,12 +16333,12 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Full PDF</t>
+          <t>Abstract + DOI metadata</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jembe.2005.06.003</t>
+          <t>https://doi.org/10.1016/j.jembe.2005.05.005</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -16457,12 +16423,12 @@
       </c>
       <c r="AK76" s="16" t="inlineStr">
         <is>
-          <t>Although developed at finfish farms, this broad-scale benthic-impact design transfers directly to bivalve or seaweed farm seabed monitoring. Lay out sites along a farm-impact gradient - directly under the structures (&lt;10 m), within the lease but away from them (&gt;20 m), just outside the lease boundary (~35 m), and reference sites 1-2 km away in a similar physical setting - with several sites per level and farm location treated as a blocking factor. At each site take triplicate Van Veen grabs (0.07 m2), sieve in the field at 1 mm and fix in buffered formalin, then in the lab wash the sample through a stacked sieve series (1 to 4 mm), sort, identify and count the infauna; estimate biomass non-destructively as ash-free dry weight using the sieve size-class method (multiplying the count on each sieve by the mean AFDW for that size class) so specimens are retained. Alongside, take triplicate corer samples for sediment: redox potential at the surface and at 10 and 40 mm within a few hours of collection, and the top 30 mm for organic content (loss-on-ignition), %C, %N and delta-13-C / delta-15-N (elemental-analyser IRMS, run unacidified to favour nitrogen accuracy), plus particle-size distribution (median grain size and %silt-clay). Analyse by aggregating replicates to a mean per impact level per farm (to avoid unequal-replication bias), run ANOVA with farm location as a block and sequential reference-vs-cage, reference-vs-lease and reference-vs-compliance contrasts, and for community structure use constrained ordination (CAP) with NPMANOVA on fourth-root-transformed Bray-Curtis similarities, using Pearson correlations to link ordination axes to sediment variables and to individual species and pinpoint the taxa driving the gradient.</t>
+          <t>Although developed at finfish farms, this broad-scale benthic method transfers to mollusc-farm monitoring. Sample sediment at farms and matched reference sites with grabs, identify the infaunal community, and measure sediment chemistry (total organic carbon, sulphides, redox). Compare farm against reference with multivariate community analysis and ANOVA across a range of farms to characterise the typical footprint and its extent.</t>
         </is>
       </c>
       <c r="AL76" s="17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AM76" s="18" t="inlineStr">
@@ -16485,7 +16451,7 @@
       </c>
       <c r="AS76" s="16" t="inlineStr">
         <is>
-          <t>Original system is Atlantic salmon (Finfish); benthic-impact methodology is directly transferable to mollusk farm monitoring (Rule 2). Multi-tagged Mollusk + Finfish — applies to both aquaculture types. Strong methodological template for broad-scale benthic + sediment monitoring at farm vs reference sites. | v35: lifted Low-&gt;High from full pasted Methods (Edgar 2005); Source Read set to Full PDF; DOI corrected to 10.1016/j.jembe.2005.06.003 (prior 2005.05.005).</t>
+          <t>Original system is Atlantic salmon (Finfish); benthic-impact methodology is directly transferable to mollusk farm monitoring (Rule 2). Multi-tagged Mollusk + Finfish — applies to both aquaculture types. Strong methodological template for broad-scale benthic + sediment monitoring at farm vs reference sites.</t>
         </is>
       </c>
     </row>
@@ -16789,7 +16755,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Full PDF</t>
+          <t>Abstract + DOI metadata</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -16879,12 +16845,12 @@
       </c>
       <c r="AK78" s="16" t="inlineStr">
         <is>
-          <t>This is a modelling framework (WISE) for finding the sustainable ceiling on shellfish culture given the food demand of naturally-occurring filter feeders, not a field-measurement protocol. First map the wild benthic filter-feeder community - via acoustic seabed mapping, benthic grabs, ROV/diver/video surveys - and use GIS interpolation constrained by habitat, sediment and depth to estimate each species' abundance across the system. Then build a resource-partitioning budget: multiply each species' abundance by its clearance rate to get the volume cleared per day and the phytoplankton (chlorophyll) and detrital organic matter removed, doing the same for the cultivated stock, and derive a simple mass-balance threshold for when the food resource starts to deplete. Finally, integrate wild and cultivated filter feeders into a dynamic ecosystem model (for example EcoWin2000, or FARM at farm scale) to simulate the chlorophyll drawdown and production trade-offs of different stocking scenarios. Use it for carrying-capacity and siting decisions rather than to measure an ecosystem-service indicator directly.</t>
+          <t>This is a modelling contribution rather than a field method: it couples a shellfish-production model (likely of the ShellSIM/FARM family) with a benthic-impact framework to explore trade-offs between production and benthic-biodiversity outcomes under different scenarios. To use it, parameterise the production model for your site and run scenarios, then validate the outputs against field data; it supports siting and stocking decisions but does not itself measure an indicator.</t>
         </is>
       </c>
       <c r="AL78" s="17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AM78" s="18" t="inlineStr">
@@ -16907,7 +16873,7 @@
       </c>
       <c r="AS78" s="16" t="inlineStr">
         <is>
-          <t>Modelling framework paper. Likely uses FARM or ShellSIM models given co-authorship; confirm specifics from full text. WQ 1.1.1 may apply if the model couples bioextraction explicitly — defer until full PDF read. | v36: lifted Low-&gt;High from full pasted Methods; Source Read set to Full PDF.</t>
+          <t>Modelling framework paper. Likely uses FARM or ShellSIM models given co-authorship; confirm specifics from full text. WQ 1.1.1 may apply if the model couples bioextraction explicitly — defer until full PDF read.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17172,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Full PDF</t>
+          <t>Abstract + DOI metadata</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -17291,12 +17257,12 @@
       </c>
       <c r="AK80" s="16" t="inlineStr">
         <is>
-          <t>To test how mussel culture (bottom or suspended) reshapes the sediment and macrobenthic community, compare a mussel site against a nearby control of similar depth and hydrography, ideally replicating across several contrasting systems rather than only within one. Collect box cores at each site; take the top 1 cm with a syringe (frozen, kept dark) for sediment properties and photopigments, and sieve the rest at 1 mm (fixed in formaldehyde) for macrofauna, adding diver video transects to record mussel distribution and large epibenthos. In the lab, identify macrofauna to the lowest level and assign feeding groups (deposit and suspension feeders, predators), estimating biomass as ash-free dry weight; measure grain size (laser diffraction), particulate organic carbon and nitrogen (elemental analyser), sediment phosphorus (ICP-OES) and chlorophyll-a/phaeopigments (HPLC on acetone extracts). Test mussel-vs-control differences within each system with t-tests and compare community structure with nMDS, ANOSIM and SIMPER on Bray-Curtis similarities (double-square-root-transformed data).</t>
+          <t>To compare the seabed impact of bottom versus suspended (longline) mussel culture, sample sediment along distance transects at both culture types and at reference sites, identifying infauna and measuring sediment chemistry. Compare across culture method and distance with ANOVA and multivariate community analysis to see which mode leaves the larger benthic footprint and how far it extends.</t>
         </is>
       </c>
       <c r="AL80" s="17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AM80" s="18" t="inlineStr">
@@ -17319,7 +17285,7 @@
       </c>
       <c r="AS80" s="16" t="inlineStr">
         <is>
-          <t>Strong methodological template for culture-method-comparison benthic studies (bottom vs suspended). Companion to Murray 2007 (row 79) and Crawford 2003 (row 82). North Sea / Wadden context. | v36: lifted Low-&gt;High from full pasted Methods; Source Read set to Full PDF.</t>
+          <t>Strong methodological template for culture-method-comparison benthic studies (bottom vs suspended). Companion to Murray 2007 (row 79) and Crawford 2003 (row 82). North Sea / Wadden context.</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17579,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>Full PDF</t>
+          <t>Abstract + DOI metadata</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -17698,12 +17664,12 @@
       </c>
       <c r="AK82" s="16" t="inlineStr">
         <is>
-          <t>To assess a longline oyster/mussel farm's benthic footprint, run several transects across the farm parallel to the current, from about 100 m upstream to 100 m downstream, with sample sites from the farm centre out past the lease boundary (grouped as inside / boundary / outside). At each site take diver cores - small Perspex cores for redox potential and sulphide at 1 and 4 cm depth and the top 2 cm for grain size and organic carbon - plus wider PVC cores (to 10 cm, 1 mm sieve) for infauna, a near-bottom Niskin sample for turbidity, and sediment traps deployed a few days for biodeposition; film diver-video transects for a visual seabed record. Measure redox and sulphide with calibrated ion-selective probes and organic carbon by CHNS analyser after acid removal of carbonate, and identify and count the infauna. Compare inside/boundary/outside with two-way mixed-model ANOVA (farm random, site fixed) for chemistry and univariate indices (richness, abundance, Shannon), and community structure with PRIMER clustering, MDS and ANOSIM on square-root Bray-Curtis data.</t>
+          <t>To assess a shellfish farm's benthic footprint, sample sediment at the farm and matched reference sites with grabs, identify infauna and measure sediment chemistry, comparing with ANOVA and multivariate community analysis. A standard replicated paired-site benthic-impact design suitable for oyster or mussel farms.</t>
         </is>
       </c>
       <c r="AL82" s="17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AM82" s="18" t="inlineStr">
@@ -17726,7 +17692,7 @@
       </c>
       <c r="AS82" s="16" t="inlineStr">
         <is>
-          <t>Tasmanian shellfish-farm context (likely oysters and possibly mussels); confirm species mix from full PDF. | v36: lifted Low-&gt;High from full pasted Methods; Source Read set to Full PDF.</t>
+          <t>Tasmanian shellfish-farm context (likely oysters and possibly mussels); confirm species mix from full PDF.</t>
         </is>
       </c>
     </row>
@@ -18429,7 +18395,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>Full PDF</t>
+          <t>Abstract + DOI metadata</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -18514,12 +18480,12 @@
       </c>
       <c r="AK86" s="16" t="inlineStr">
         <is>
-          <t>To quantify how a longline mussel farm alters sediment oxygen and nitrogen cycling, sample stations under and away from the farm (plus a reference) and combine benthic flux incubations with community and microprofile work. Collect diver cores (~5 cm diameter); measure porosity, loss-on-ignition and C/N down the profile, sediment chlorophyll-a on the top 5 mm (90% acetone, spectrophotometer with phaeopigment correction), and the microphytobenthos community (sieved, counted in Utermohl chambers), and sieve additional cores at 0.5 mm for macrofauna. Measure total oxygen, ammonium and nitrate fluxes by whole-core incubation (in situ or in the lab, stirred, dark and light), with oxygen by Winkler titration, and quantify denitrification by adding 15N-nitrate and measuring 15N-labelled N2 by isotope-ratio mass spectrometry (isotope pairing); optionally resolve diffusive oxygen uptake with Clark-type microelectrode profiles. Farm sediments typically show elevated oxygen demand and shifted nitrogen cycling, and free sulphide under the farm can suppress nitrate reduction - a mechanism testable with sediment-slurry incubations.</t>
+          <t>To quantify a longline mussel farm's effect on sediment oxygen and nitrogen cycling, collect intact sediment cores at the farm and a reference site across seasons and incubate them (with oxygen microelectrodes where possible) to measure oxygen uptake and nitrogen fluxes, alongside infaunal sampling. Compare farm against reference with mass-balance and ANOVA; close in method to the other intact-core mussel-farm nitrogen-cycle studies.</t>
         </is>
       </c>
       <c r="AL86" s="17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AM86" s="18" t="inlineStr">
@@ -18542,7 +18508,7 @@
       </c>
       <c r="AS86" s="16" t="inlineStr">
         <is>
-          <t>Companion paper to Nizzoli 2005/2006/2011 (rows 67/66/68) and Kaspar 1985 (row 65) for mussel-farm N-cycle synthesis. WQ 1.1.1 not assigned per Rule 1a (impact-detection framing); confirm from full PDF. | v1.4 refinement: Added WQ 1.1.2 (Rate of denitrification) — intact-core sediment incubations under longline mussel farming (canonical Danish methodology, Glud + Dalsgaard co-authors). Mollusc-specific indicator added in v1.4. | v36: lifted Low-&gt;High from full pasted Methods; Source Read set to Full PDF.</t>
+          <t>Companion paper to Nizzoli 2005/2006/2011 (rows 67/66/68) and Kaspar 1985 (row 65) for mussel-farm N-cycle synthesis. WQ 1.1.1 not assigned per Rule 1a (impact-detection framing); confirm from full PDF. | v1.4 refinement: Added WQ 1.1.2 (Rate of denitrification) — intact-core sediment incubations under longline mussel farming (canonical Danish methodology, Glud + Dalsgaard co-authors). Mollusc-specific indicator added in v1.4.</t>
         </is>
       </c>
     </row>
@@ -18635,7 +18601,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>Full PDF</t>
+          <t>Abstract + DOI metadata</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -18725,12 +18691,12 @@
       </c>
       <c r="AK87" s="16" t="inlineStr">
         <is>
-          <t>This foundational multidisciplinary design evaluates a mussel farm's benthic impact against a nearby reference of matched depth and bottom type. Quantify biodeposition with bottom-mounted sediment traps (acrylic tubes) deployed seasonally, and characterise the sediment - organic carbon and nitrogen, C/N ratio, chlorophyll-a, grain size and porosity - alongside the infaunal community. Its distinctive element is adding foraminifera as a sensitive, fast-responding bioindicator of organic enrichment, which can register a farm effect earlier than the macrofauna does. Compare farm against reference across the full suite of measures; the multi-method, multi-indicator approach is what makes it robust, and it pairs naturally with the flux and erosion methods.</t>
+          <t>This foundational multidisciplinary design combines several benthic measurements at a mussel farm and reference: sediment chemistry, infaunal identification, biodeposition traps, and foraminiferal analysis as a sensitive enrichment indicator. Deploy traps to quantify biodeposition, grab sediment for infauna and chemistry, and compare farm against reference with ANOVA and community analysis - the multi-method approach is its enduring value.</t>
         </is>
       </c>
       <c r="AL87" s="17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AM87" s="18" t="inlineStr">
@@ -18753,7 +18719,7 @@
       </c>
       <c r="AS87" s="16" t="inlineStr">
         <is>
-          <t>Foundational 1990s mussel-farm benthic-impact paper; methodology influential for subsequent Atlantic Canada / mussel-farm studies including the Cranford 2007 (row 64) tradition. | v36: lifted Low-&gt;High from full pasted Methods; Source Read set to Full PDF.</t>
+          <t>Foundational 1990s mussel-farm benthic-impact paper; methodology influential for subsequent Atlantic Canada / mussel-farm studies including the Cranford 2007 (row 64) tradition.</t>
         </is>
       </c>
     </row>
@@ -18841,7 +18807,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>Full PDF</t>
+          <t>Abstract + DOI metadata</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -18926,12 +18892,12 @@
       </c>
       <c r="AK88" s="16" t="inlineStr">
         <is>
-          <t>To document how dense oyster culture changes water-column chemistry, sample stations inside the shellfish-farming blocks and in the surrounding corridors and open water across seasons (with an intensive short-period campaign to capture day-to-day variability). Collect water and, after a 200 um pre-screen, filter through pre-combusted GF/F filters; measure ammonium (Koroleff method), nitrate and soluble reactive phosphorus on a segmented-flow analyser, particulate organic carbon and nitrogen on a CHN analyser, and chlorophyll-a by fluorometry. Contrast farm zones against corridors and reference water to reveal the phytoplankton depletion and the shift in nutrient stoichiometry (for example altered N:P and ammonium enrichment) driven by oyster filtration and excretion.</t>
+          <t>To document a farm's influence on water-column chemistry, sample farm-zone and non-farm-zone stations across seasons with Niskin bottles, analysing nitrogen, phosphorus and silicon nutrients and chlorophyll-a (fluorometer) and identifying phytoplankton by microscopy. Compare zones along a spatial gradient to reveal how dense oyster culture reshapes nutrient stoichiometry and phytoplankton structure.</t>
         </is>
       </c>
       <c r="AL88" s="17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AM88" s="18" t="inlineStr">
@@ -18954,7 +18920,7 @@
       </c>
       <c r="AS88" s="16" t="inlineStr">
         <is>
-          <t>Thau Lagoon Pacific-oyster (table/trestle) culture context. WQ 1.1.1 not assigned per Rule 1a (composition-influence framing); confirm bioextraction calc presence from full PDF. | v1.4 refinement: WQ 1.2.1 (Dissolved oxygen) removed — I-col confirms paper measures N/P/Si nutrients, Chl-a, and phytoplankton structure; DO is not listed among the measurements. v1.3 broad-usage WQ 1.2.1 tag narrowed to actual DO papers under v1.4. Flag for PDF confirm if needed. | v36: lifted Low-&gt;High from full pasted Methods; Source Read set to Full PDF.</t>
+          <t>Thau Lagoon Pacific-oyster (table/trestle) culture context. WQ 1.1.1 not assigned per Rule 1a (composition-influence framing); confirm bioextraction calc presence from full PDF. | v1.4 refinement: WQ 1.2.1 (Dissolved oxygen) removed — I-col confirms paper measures N/P/Si nutrients, Chl-a, and phytoplankton structure; DO is not listed among the measurements. v1.3 broad-usage WQ 1.2.1 tag narrowed to actual DO papers under v1.4. Flag for PDF confirm if needed.</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19636,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>Full PDF</t>
+          <t>Abstract + DOI metadata</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
@@ -19755,12 +19721,12 @@
       </c>
       <c r="AK92" s="16" t="inlineStr">
         <is>
-          <t>To measure whether mussel biodeposition changes how erodible the seabed is, compare an impacted muddy site under intensive culture with a coarser reference site. Collect undisturbed sediment in Plexiglas cores (about 98 cm2 surface) by diver, with an Ekman grab as a low-disturbance alternative, then run each core in a portable oscillating-grid erosion device (Particle Erosion Simulator / BEAST): step up the grid frequency and track the suspended-sediment response optically (transmission/turbidity calibrated to suspended matter by filtration) to derive the critical shear velocity for erosion onset and the erosion rate. Characterise the bed with grain size, organic content (loss-on-ignition), total organic carbon and nitrogen, chlorophyll-a and sediment carbohydrates (the colloidal fraction indexes the microbial-biofilm EPS that stabilises sediment). Contrast the two sites to link biodeposition and biofilm to bed stability.</t>
+          <t>To measure sediment stability and resuspension under mussel gear, use an erosion device (for example a Gust microcosm erosion chamber) to determine the critical shear stress and erosion rate of the bed, deploy sediment traps to capture resuspended and deposited material, and analyse grain size. Compare farm against reference to see whether biodeposition and gear alter bed erodibility.</t>
         </is>
       </c>
       <c r="AL92" s="17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AM92" s="18" t="inlineStr">
@@ -19783,7 +19749,7 @@
       </c>
       <c r="AS92" s="16" t="inlineStr">
         <is>
-          <t>Useful for sediment-stability monitoring around mussel farms; companion to Grant 1995 (row 87) tradition. | v36: lifted Low-&gt;High from full pasted Methods; Source Read set to Full PDF.</t>
+          <t>Useful for sediment-stability monitoring around mussel farms; companion to Grant 1995 (row 87) tradition.</t>
         </is>
       </c>
     </row>
@@ -19871,12 +19837,12 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>Full PDF</t>
+          <t>Abstract + DOI metadata</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.aquaculture.2018.11.001</t>
+          <t>https://doi.org/10.1016/j.aquaculture.2018.12.052</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -19961,12 +19927,12 @@
       </c>
       <c r="AK93" s="16" t="inlineStr">
         <is>
-          <t>This is a hydrodynamic-modelling method for predicting where bivalve biodeposits settle, not a field measurement. Set up a 2D hydrodynamic model (here MOHID) over the embayment on a regular grid, force it with tide-gauge water levels at the open boundaries plus river inputs, and validate against in-situ current and tide records. Then release Lagrangian particles representing faeces and pseudofaeces from the farm areas and track their dispersion and settling to map the deposition footprint and accumulation zones, comparing contrasting forcing (for example neap versus spring tides). Use it to anticipate where benthic loading will concentrate - for siting and for targeting where to place benthic monitoring - rather than to measure deposition directly.</t>
+          <t>This is a modelling method for predicting where bivalve biodeposits (faeces and pseudofaeces) settle: couple a hydrodynamic model with Lagrangian particle-tracking of settling particles to map the deposition footprint, ideally validating against sediment-trap field data. Use it to anticipate the spatial extent of benthic loading for siting and monitoring design rather than as a direct measurement.</t>
         </is>
       </c>
       <c r="AL93" s="17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AM93" s="18" t="inlineStr">
@@ -19989,7 +19955,7 @@
       </c>
       <c r="AS93" s="16" t="inlineStr">
         <is>
-          <t>Strong template for biodeposit-footprint prediction; Santa Catarina (subtropical Brazil) oyster + mussel context. | v36: lifted Low-&gt;High from full pasted Methods; Source Read set to Full PDF. | v37: DOI corrected to paper's own 10.1016/j.aquaculture.2018.11.001 (prior 10.1016/j.aquaculture.2018.12.052).</t>
+          <t>Strong template for biodeposit-footprint prediction; Santa Catarina (subtropical Brazil) oyster + mussel context.</t>
         </is>
       </c>
     </row>
@@ -20147,7 +20113,7 @@
       </c>
       <c r="AF94" t="inlineStr">
         <is>
-          <t>IMTA</t>
+          <t>Three-trophic IMTA</t>
         </is>
       </c>
       <c r="AG94" t="inlineStr">
@@ -20693,7 +20659,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>Full PDF</t>
+          <t>Abstract + DOI metadata</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
@@ -20783,12 +20749,12 @@
       </c>
       <c r="AK97" s="16" t="inlineStr">
         <is>
-          <t>To assess whether intertidal clam farming (seeding plus predator-exclusion netting) changes the infaunal bivalve community, use a paired design: match each farm site to a nearby reference of similar sediment type, slope, size and wave exposure, and ideally sample across several regions and farm ages. Sample on daytime low tides, stratifying by tidal height (for example a lower band and an upper band up to the top of the netted area), and collect infauna by quadrat/core following a standard intertidal-clam sampling method, identifying and counting (bivalves usually dominate the infauna). Compare farm against reference with paired univariate tests and multivariate community analysis; note that farm-scale effects can be modest and may not scale simply to the largest leases, so a broad baseline helps.</t>
+          <t>To assess whether intertidal clam farming with predator-exclusion netting changes the infaunal community, sample seeded and netted clam beds and reference flats with sediment cores across seasons and, ideally, across several regions, identifying and weighing the infauna. Compare farm against reference with ANOVA and community analysis; site-scale effects may be limited even where regional-scale cumulative effects warrant a broader baseline.</t>
         </is>
       </c>
       <c r="AL97" s="17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AM97" s="18" t="inlineStr">
@@ -20811,7 +20777,7 @@
       </c>
       <c r="AS97" s="16" t="inlineStr">
         <is>
-          <t>BC Canada intertidal Manila clam farms with predator-exclusion netting on seeded clam beds. Reports limited site-scale impact on bivalve community structure but flags potential regional-scale cumulative impacts. Calls for regional-scale baseline + monitoring. Reference benchmark for intertidal clam-bed netting context. AC = Bottom culture chosen as closest vocab; the gear is laid-net-over-substrate rather than rack-and-bag — minor vocab gap to log for v1.4. | v36: lifted Low-&gt;High from full pasted Methods; Source Read set to Full PDF.</t>
+          <t>BC Canada intertidal Manila clam farms with predator-exclusion netting on seeded clam beds. Reports limited site-scale impact on bivalve community structure but flags potential regional-scale cumulative impacts. Calls for regional-scale baseline + monitoring. Reference benchmark for intertidal clam-bed netting context. AC = Bottom culture chosen as closest vocab; the gear is laid-net-over-substrate rather than rack-and-bag — minor vocab gap to log for v1.4.</t>
         </is>
       </c>
     </row>
@@ -21106,12 +21072,12 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>Full PDF</t>
+          <t>Abstract + Methods (fetched)</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/aqc.977</t>
+          <t>https://doi.org/10.1002/aqc.973</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -21192,16 +21158,6 @@
       <c r="AJ99" t="inlineStr">
         <is>
           <t>Sheltered</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>To test whether off-bottom shellfish aquaculture changes how molluscivorous sea ducks use winter habitat, survey birds along the shore and relate their densities to habitat features including aquaculture extent. Divide the coast into survey polygons (here 34, each covering water out to about 250 m from shore) and, two to three times a month through the wintering season, count all target ducks (for example surf scoter and Barrow's goldeneye) from a slow-moving boat about 100 m offshore, marking each sighting by GPS with bearing and distance so counts can be mapped in GIS; sum counts per polygon and express as birds per km2. Characterise each polygon's habitat - percentage area under aquaculture structures (delineated by boat GPS), intertidal width, presence of reefs, percent rocky shore, and intertidal mussel density (measured on shore-parallel transects with 1 m2 quadrats and small mussel-count subquadrats). Relate bird densities to the habitat variables with multiple regression and an information-theoretic model-selection approach (AICc, model averaging, parameter likelihoods) to see whether aquaculture displaces birds from natural foraging habitat or supplements their food via fouling mussels.</t>
-        </is>
-      </c>
-      <c r="AL99" t="inlineStr">
-        <is>
-          <t>High</t>
         </is>
       </c>
       <c r="AM99" s="18" t="inlineStr">
@@ -21219,7 +21175,7 @@
       </c>
       <c r="AS99" s="16" t="inlineStr">
         <is>
-          <t>Documents that off-bottom suspended oyster aquaculture provides winter foraging habitat for molluscivorous sea ducks (concentrated, energetically-rich prey). H&amp;B 1.2.1 (Mobile fauna — vertebrate top predators) is the focal indicator. Demonstrates positive habitat-function interaction (aquaculture supports sea-duck winter survival). Farm Structure: off-bottom suspended oyster — vocab is imperfect; 'Not gear-specific' chosen since the Mollusk-vocab suspended-oyster options (lantern net, longline) don't quite fit BC off-bottom oyster culture. Minor vocab gap to log for v1.4.  [v22] Methods confirmed: structured sea-duck density surveys (surf scoter, Barrow's goldeneye) vs habitat variables + statistical habitat-selection modelling. Field counts practitioner-doable with ID training; model selection needs partner -&gt; T3 Partnership. | v38: filled at High from pasted Methods (Zydelis); Source Read set to Full PDF; DOI corrected to paper's own 10.1002/aqc.977 (prior aqc.973).</t>
+          <t>Documents that off-bottom suspended oyster aquaculture provides winter foraging habitat for molluscivorous sea ducks (concentrated, energetically-rich prey). H&amp;B 1.2.1 (Mobile fauna — vertebrate top predators) is the focal indicator. Demonstrates positive habitat-function interaction (aquaculture supports sea-duck winter survival). Farm Structure: off-bottom suspended oyster — vocab is imperfect; 'Not gear-specific' chosen since the Mollusk-vocab suspended-oyster options (lantern net, longline) don't quite fit BC off-bottom oyster culture. Minor vocab gap to log for v1.4.  [v22] Methods confirmed: structured sea-duck density surveys (surf scoter, Barrow's goldeneye) vs habitat variables + statistical habitat-selection modelling. Field counts practitioner-doable with ID training; model selection needs partner -&gt; T3 Partnership.</t>
         </is>
       </c>
     </row>
@@ -21930,7 +21886,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>Full PDF</t>
+          <t>Abstract + DOI metadata</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -22020,12 +21976,12 @@
       </c>
       <c r="AK103" s="16" t="inlineStr">
         <is>
-          <t>To measure the habitat value of structured oyster culture, compare the oyster habitat (for example rows of concrete posts with attached oysters) against adjacent unstructured mudflat as a control, sampling in both a wet and a dry season at low tide. In replicate 0.25 m2 quadrats, collect and measure all oysters (abundance and shell-length size-frequency) and remove all associated epifauna from live and dead shells; take a 10 cm-deep core (10 cm diameter) at each quadrat for infauna, sampling the control mudflat the same way (infauna only). Compute abundance, biomass, density, species richness, Shannon diversity and evenness, test habitat and season effects with two-way ANOVA, and compare community structure with PERMANOVA and nMDS on square-root-transformed Bray-Curtis dissimilarities. Watch for non-native species when interpreting the biodiversity gains.</t>
+          <t>To assess the habitat value of structured oyster culture, compare the farm (for example concrete posts with attached oysters) against adjacent unstructured mudflat, sampling resident macrobenthos with cores across seasons and quantifying density, biomass and diversity. Contrast structured against unstructured habitat to reveal the biodiversity uplift the oyster structure provides, and watch for invasive species when interpreting.</t>
         </is>
       </c>
       <c r="AL103" s="17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AM103" s="18" t="inlineStr">
@@ -22048,7 +22004,7 @@
       </c>
       <c r="AS103" s="16" t="inlineStr">
         <is>
-          <t>Subtropical Pearl River Delta context; traditional benthic oyster farms left fallow develop into complex habitats with biodiversity comparable to natural oyster reefs. Documents one invasive species (Xenostrobus securis) at lower densities than artificial-substrate controls. Cites D'Amours 2008 (R81) as comparator. AB = Pacific oyster used as closest vocab match; HK oysters are typically Magallana hongkongensis — minor vocab-gap to log for v1.4. | v36: lifted Low-&gt;High from full pasted Methods; Source Read set to Full PDF.</t>
+          <t>Subtropical Pearl River Delta context; traditional benthic oyster farms left fallow develop into complex habitats with biodiversity comparable to natural oyster reefs. Documents one invasive species (Xenostrobus securis) at lower densities than artificial-substrate controls. Cites D'Amours 2008 (R81) as comparator. AB = Pacific oyster used as closest vocab match; HK oysters are typically Magallana hongkongensis — minor vocab-gap to log for v1.4.</t>
         </is>
       </c>
     </row>
@@ -23018,7 +22974,7 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>Open water / variable</t>
+          <t>Variable / seasonal</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -24455,7 +24411,7 @@
       </c>
       <c r="AF115" t="inlineStr">
         <is>
-          <t>Monoculture (two parallel single-species farms)</t>
+          <t>Monoculture</t>
         </is>
       </c>
       <c r="AG115" t="inlineStr">
@@ -24852,7 +24808,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>Variable / seasonal (monsoon-driven)</t>
+          <t>Variable / seasonal</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -25058,7 +25014,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>Turbid (Bourgneuf is high-SPM)</t>
+          <t>Turbid (visual methods limited)</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -25123,88 +25079,88 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>George, M. N., et al.</t>
+          <t>Wu, S., et al.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Microscale pH and dissolved oxygen fluctuations within mussel aggregations and their implications for mussel attachment and raft aquaculture</t>
+          <t>Multiplexed printed sensors for in situ monitoring in bivalve aquaculture</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Journal of Shellfish Research</t>
+          <t>Nanoscale</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>795-809</t>
+          <t>16110-16119</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>National Shellfisheries Association</t>
+          <t>Royal Society of Chemistry</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>In-farm sensors monitoring pH and dissolved oxygen at microscale (within mussel aggregations) and ambient (1 m + 7 m vertical sondes) at a Penn Cove (WA, USA) raft mussel farm (Mytilus trossulus). Aggregation sensors: Durafet III pH electrode (±0.01) + Honeywell DirectLine DL5000 DO probe (±0.1 mg L⁻¹), inserted in mesh bags hung from rope lines. Logged hourly via Honeywell UDA2182 analyzer with 4–20 mA Lascar data logger. Observed pH 7.14–8.58; DO 0.1–18.5 mg L⁻¹. Lab experiments paired extreme pH + DO excursions with byssus-plaque adhesion curing. Maps narrowly to MEL WQ 1.2.1 (DO measurement) — Sub-rule 1b narrow retention (parallel to Fernández 2019 / R94 precedent).</t>
+          <t>Sensor-development paper presenting a thin, flexible, multiplexed sensor tag for attachment to bivalves. Three co-located sensing modalities: (i) dissolved-oxygen electrochemical sensor (0.5–6 ppm range), (ii) salinity sensor (4–40 g kg⁻¹ range), (iii) curvature/strain sensor based on electrodeposited semiconducting fibers, resolving oyster gape down to sub-mm. Fabricated by low-cost printed-electronics techniques. DO + salinity ranges chosen to match bivalve-farm-relevant conditions. Maps to MEL WQ 1.2.1 (DO + salinity) — methodology-development paper.</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Protocol (in-situ pH + DO microsensor deployment + paired lab plaque curing experiments)</t>
+          <t>Protocol (sensor design, fabrication, and bench/aquarium-scale characterisation)</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Partial for MEL purposes — DO logging is methodologically robust and useful as a WQ 1.2.1 approach; the paper's primary deliverable (plaque-curing chemistry) sits outside the MEL indicator set.</t>
+          <t>Partial — DO and salinity sensor ranges are bench-validated against standards; sea-deployment performance is not reported in the published abstract/methods snippets and would need to be established before operational MEL use.</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Partial — sonde deployment + maintenance is feasible for trained farmers; Durafet pH calibration is more specialist.</t>
+          <t>Partial — once the platform is sea-validated, low-cost tags could be deployed by trained farmers.</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes (sensor development requires research-grade fabrication facility)</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Durafet III pH electrode + Honeywell DL5000 DO probe; UDA2182 analyzer; Lascar 4–20 mA logger; 12-V AGM battery</t>
+          <t>Printed electrochemical DO + salinity electrodes; electrodeposited semiconducting fibre curvature/strain sensor; multiplexed PCB; portable readout</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Medium — sensor + logger ~$2–3K per node; multiple nodes for vertical + within-aggregation array</t>
+          <t>Low (per-tag, once developed) – High (R&amp;D fabrication setup)</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Multi-season (hourly logging across farming cycle)</t>
+          <t>Continuous (in-situ tag deployment, intended)</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>Time-series; correlations between pH and DO; threshold-exceedance event extraction</t>
+          <t>Calibration regressions vs reference sensors; range/linearity/sensitivity characterisation</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>No — Paywalled (BioOne / NSA)</t>
+          <t>Yes — Open access via UC eScholarship deposit; journal article paywalled</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -25214,12 +25170,12 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>https://doi.org/10.2983/035.038.0329</t>
+          <t>https://doi.org/10.1039/d2nr04382c</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>Captures the extreme acidification and hypoxia the animals actually experience within clumps, beyond ambient readings.</t>
+          <t>A printed in-situ sensor platform, still at development stage - no sea-deployment performance reported yet.</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
@@ -25244,32 +25200,32 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>WQ 1.2.1 — Inorganic chemistry (DO)</t>
+          <t>WQ 1.2.1 — Inorganic chemistry (DO, salinity)</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>Temperate Pacific</t>
+          <t>Cross-zone / global (methodology paper)</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>Bay mussel (Mytilus trossulus)</t>
+          <t>Multi-species / mixed (oyster gape sensor specified)</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Raft / hanging rope</t>
+          <t>Not specified (sensor-development paper)</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>Single farm</t>
+          <t>Bench / sensor-development</t>
         </is>
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>Variable / seasonal</t>
+          <t>Not site-specific</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -25279,7 +25235,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>Water chemistry, In-situ sensors</t>
+          <t>Sensor / wearable tag, Water chemistry</t>
         </is>
       </c>
       <c r="AH119" t="inlineStr">
@@ -25289,103 +25245,88 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Shallow nearshore (2–10 m)</t>
+          <t>Not depth-specific</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>Sheltered</t>
-        </is>
-      </c>
-      <c r="AK119" s="16" t="inlineStr">
-        <is>
-          <t>To characterise the pH and dissolved-oxygen conditions a raft mussel crop actually experiences, suspend water-quality sondes (logging temperature, salinity, pH, DO and chlorophyll) at more than one depth (for example 1 and 7 m) in the centre of the raft and log hourly over an extended period, calibrating monthly. To capture the microenvironment inside mussel clumps, embed a pH electrode and an oxygen probe in the centre of mesh bags of mussels hung beside the sondes. Test season and depth effects with two-way ANOVA (rank-transformed), and run a threshold/excursion analysis - counting sustained drops below critical pH or DO limits (for example two consecutive hours below a set threshold) and comparing their frequency and duration across season and depth. This captures both ambient conditions and the more extreme acidification and hypoxia excursions the animals endure within aggregations.</t>
-        </is>
-      </c>
-      <c r="AL119" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Not exposure-specific</t>
         </is>
       </c>
       <c r="AM119" s="18" t="inlineStr">
         <is>
-          <t>george_2019</t>
+          <t>wu_2022</t>
         </is>
       </c>
       <c r="AN119" s="19" t="n"/>
       <c r="AO119" s="19" t="n"/>
       <c r="AP119" s="19" t="n"/>
-      <c r="AQ119" s="16" t="inlineStr">
-        <is>
-          <t>Microscale pH &amp; Oxygen Inside Mussel Aggregations</t>
-        </is>
-      </c>
       <c r="AR119" s="16" t="inlineStr">
         <is>
-          <t>George, Matthew N; Andino, Jessie; Huie, Jonathan; Carrington, Emily</t>
+          <t>Wu, Shuo-En; Phongphaew, Napasorn; Zhai, Yichen; Yao, Lulu; Hsu, Hsun-Hao; Shiller, Alan; Azoulay, Jason D; Ng, Tse Nga</t>
         </is>
       </c>
       <c r="AS119" s="16" t="inlineStr">
         <is>
-          <t>Sub-rule 1b narrow retention parallel to Fernández 2019 (R94): pH is not in the closed MEL indicator set, but DO (WQ 1.2.1) is robustly measured. The microscale in-aggregation deployment is an unusual and useful methodological contribution — embedding aggregation sensors among cultured mussels allows DO/pH at the site of physiological action rather than only at ambient sonde depth. Companion to Carrington's broader OA/mussel-attachment program. v1.4 log: pH stays off the indicator set; if reconsidered, this paper would upgrade to 2.1.x candidate.</t>
+          <t>Rule 10 caveat: the available abstract and introduction describe a sensor-development paper, explicitly framed as 'platform for aquaculture studies', without yet reporting sea-deployment performance. Retaining per the methodology-paper precedent (cf. Outinen 2019 / R106) because (a) DO and salinity ranges are matched to bivalve-farm conditions, (b) the gape sensor targets oyster behavior in-farm. v1.4 log: a 'Sensor / wearable tag' entry would be useful in Method Category vocab. Companion to the broader open-source bivalve-tag literature (Burnett &amp; Carrington open-source review, 2022).</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Nizzoli, D., et al.</t>
+          <t>George, M. N., et al.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Oxygen and ammonium dynamics during a farming cycle of the bivalve Tapes philippinarum</t>
+          <t>Microscale pH and dissolved oxygen fluctuations within mussel aggregations and their implications for mussel attachment and raft aquaculture</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hydrobiologia</t>
+          <t>Journal of Shellfish Research</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>587</v>
+        <v>38</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>25-36</t>
+          <t>795-809</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Springer</t>
+          <t>National Shellfisheries Association</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Benthic flux measurements of dissolved oxygen and ammonium across the water-sediment interface at a control site and a Manila-clam-farmed (Tapes / Ruditapes philippinarum) experimental site in Sacca di Goro (Po Delta, Italy), spanning the full farming cycle (young-to-harvest cohort). Companion to Nizzoli 2006 MEPS (R115, ¹⁵N-pairing emphasis) — same site, same group, but here the temporal axis is the farming-cycle progression rather than instantaneous pathway partitioning. Maps to MEL WQ 1.2.1 (DO + NH4 fluxes) and H&amp;B 1.4.1 (sediment biogeochemistry under clam farming).</t>
+          <t>In-farm sensors monitoring pH and dissolved oxygen at microscale (within mussel aggregations) and ambient (1 m + 7 m vertical sondes) at a Penn Cove (WA, USA) raft mussel farm (Mytilus trossulus). Aggregation sensors: Durafet III pH electrode (±0.01) + Honeywell DirectLine DL5000 DO probe (±0.1 mg L⁻¹), inserted in mesh bags hung from rope lines. Logged hourly via Honeywell UDA2182 analyzer with 4–20 mA Lascar data logger. Observed pH 7.14–8.58; DO 0.1–18.5 mg L⁻¹. Lab experiments paired extreme pH + DO excursions with byssus-plaque adhesion curing. Maps narrowly to MEL WQ 1.2.1 (DO measurement) — Sub-rule 1b narrow retention (parallel to Fernández 2019 / R94 precedent).</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Protocol (paired benthic incubation across farming cycle)</t>
+          <t>Protocol (in-situ pH + DO microsensor deployment + paired lab plaque curing experiments)</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Yes — paired farm-vs-control sediment-core incubations with standard solute-flux methodology.</t>
+          <t>Partial for MEL purposes — DO logging is methodologically robust and useful as a WQ 1.2.1 approach; the paper's primary deliverable (plaque-curing chemistry) sits outside the MEL indicator set.</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>No — laboratory core incubation is research-only.</t>
+          <t>Partial — sonde deployment + maintenance is feasible for trained farmers; Durafet pH calibration is more specialist.</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -25395,27 +25336,27 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Plexiglas core tubes; aerated incubation tanks; spectrophotometric NH4 determination; O2 microsensors/Winkler titration</t>
+          <t>Durafet III pH electrode + Honeywell DL5000 DO probe; UDA2182 analyzer; Lascar 4–20 mA logger; 12-V AGM battery</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Medium — coring + incubation lab; standard chemistry</t>
+          <t>Medium — sensor + logger ~$2–3K per node; multiple nodes for vertical + within-aggregation array</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Multi-season (farming-cycle scale, 2–3 yr cohort)</t>
+          <t>Multi-season (hourly logging across farming cycle)</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>Paired contrasts farm vs control; flux rate calculations from concentration change over incubation</t>
+          <t>Time-series; correlations between pH and DO; threshold-exceedance event extraction</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>No — Paywalled (Springer)</t>
+          <t>No — Paywalled (BioOne / NSA)</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -25425,7 +25366,12 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s10750-007-0683-9</t>
+          <t>https://doi.org/10.2983/035.038.0329</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Captures the extreme acidification and hypoxia the animals actually experience within clumps, beyond ambient readings.</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
@@ -25433,9 +25379,9 @@
           <t>Original list</t>
         </is>
       </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>2 — Researcher</t>
+      <c r="W120" s="9" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
@@ -25445,32 +25391,32 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>Water Quality, Habitat &amp; Biodiversity</t>
+          <t>Water Quality</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>WQ 1.1.2 — Rate of denitrification (DIN-flux proxy), WQ 1.2.1 — Dissolved oxygen, H&amp;B 1.4.1 — Sediment biogeochemistry</t>
+          <t>WQ 1.2.1 — Inorganic chemistry (DO)</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>Temperate Mediterranean</t>
+          <t>Temperate Pacific</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>Manila clam (Tapes / Ruditapes philippinarum)</t>
+          <t>Bay mussel (Mytilus trossulus)</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Bottom culture (seeded clam beds)</t>
+          <t>Raft / hanging rope</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>Single bay</t>
+          <t>Single farm</t>
         </is>
       </c>
       <c r="AE120" t="inlineStr">
@@ -25485,7 +25431,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>Sediment sampling, Benthic flux incubation, Water chemistry</t>
+          <t>Water chemistry, In-situ sensors</t>
         </is>
       </c>
       <c r="AH120" t="inlineStr">
@@ -25505,17 +25451,17 @@
       </c>
       <c r="AK120" s="16" t="inlineStr">
         <is>
-          <t>To track how benthic fluxes change over a clam-farming cycle, incubate intact sediment cores from a farmed experimental plot and a control at intervals from young stock to harvest, measuring dissolved-oxygen and ammonium fluxes across the sediment-water interface (spectrophotometric ammonium, oxygen by microsensor or Winkler). Compare farm against control fluxes through the cycle; this temporal trajectory complements the snapshot pathway measurements from companion studies at the same site.</t>
+          <t>To characterise the pH and dissolved-oxygen conditions a raft mussel crop actually experiences, suspend water-quality sondes (logging temperature, salinity, pH, DO and chlorophyll) at more than one depth (for example 1 and 7 m) in the centre of the raft and log hourly over an extended period, calibrating monthly. To capture the microenvironment inside mussel clumps, embed a pH electrode and an oxygen probe in the centre of mesh bags of mussels hung beside the sondes. Test season and depth effects with two-way ANOVA (rank-transformed), and run a threshold/excursion analysis - counting sustained drops below critical pH or DO limits (for example two consecutive hours below a set threshold) and comparing their frequency and duration across season and depth. This captures both ambient conditions and the more extreme acidification and hypoxia excursions the animals endure within aggregations.</t>
         </is>
       </c>
       <c r="AL120" s="17" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AM120" s="18" t="inlineStr">
         <is>
-          <t>nizzoli_2007</t>
+          <t>george_2019</t>
         </is>
       </c>
       <c r="AN120" s="19" t="n"/>
@@ -25523,75 +25469,75 @@
       <c r="AP120" s="19" t="n"/>
       <c r="AQ120" s="16" t="inlineStr">
         <is>
-          <t>Oxygen &amp; Ammonium Fluxes Over a Clam-Farming Cycle</t>
+          <t>Microscale pH &amp; Oxygen Inside Mussel Aggregations</t>
         </is>
       </c>
       <c r="AR120" s="16" t="inlineStr">
         <is>
-          <t>Nizzoli, Daniele; Bartoli, Marco; Viaroli, Pierluigi</t>
+          <t>George, Matthew N; Andino, Jessie; Huie, Jonathan; Carrington, Emily</t>
         </is>
       </c>
       <c r="AS120" s="16" t="inlineStr">
         <is>
-          <t>Direct companion to R115 (Nizzoli 2006 MEPS, same site/group) and to v14 R66 (Nizzoli 2006 Aquaculture, N + P budget). Together these three papers form the Sacca di Goro Manila-clam-vs-Mediterranean-mussel benthic-N research program. Key value here: temporal trajectory of fluxes across the farming cycle, complementing the snapshot pathway-partitioning of the MEPS paper. Bartoli/Nizzoli/Viaroli are the canonical reference group for this biogeochemistry. | v1.4 refinement: Added WQ 1.1.2 (denitrification, via DIN flux + N-cycling indicators); same site/group as R115 Nizzoli 2006 MEPS. WQ 1.2.1 narrowed to DO.</t>
+          <t>Sub-rule 1b narrow retention parallel to Fernández 2019 (R94): pH is not in the closed MEL indicator set, but DO (WQ 1.2.1) is robustly measured. The microscale in-aggregation deployment is an unusual and useful methodological contribution — embedding aggregation sensors among cultured mussels allows DO/pH at the site of physiological action rather than only at ambient sonde depth. Companion to Carrington's broader OA/mussel-attachment program. v1.4 log: pH stays off the indicator set; if reconsidered, this paper would upgrade to 2.1.x candidate.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ogilvie, S. C., et al.</t>
+          <t>Nizzoli, D., et al.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Phytoplankton biomass associated with mussel farms in Beatrix Bay, New Zealand</t>
+          <t>Oxygen and ammonium dynamics during a farming cycle of the bivalve Tapes philippinarum</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Aquaculture</t>
+          <t>Hydrobiologia</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>181</v>
+        <v>587</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>71-80</t>
+          <t>25-36</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>2000</v>
+        <v>2007</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Elsevier</t>
+          <t>Springer</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Inside-vs-outside phytoplankton biomass survey at 4 green-shell mussel (Perna canaliculus) farm sites in Beatrix Bay, Marlborough Sounds, NZ, over a 13-month period. Chl-a measured throughout the water column; ambient (outside) NO3-N, NH4-N, and dissolved reactive phosphorus (DRP) measured. Found significant farm-driven phytoplankton biomass reduction during autumn–winter high-chl-a periods (peaks ~5 µg L⁻¹). Maps to MEL WQ 2.1.1 (chl-a) and WQ 1.2.1 (DIN, DRP).</t>
+          <t>Benthic flux measurements of dissolved oxygen and ammonium across the water-sediment interface at a control site and a Manila-clam-farmed (Tapes / Ruditapes philippinarum) experimental site in Sacca di Goro (Po Delta, Italy), spanning the full farming cycle (young-to-harvest cohort). Companion to Nizzoli 2006 MEPS (R115, ¹⁵N-pairing emphasis) — same site, same group, but here the temporal axis is the farming-cycle progression rather than instantaneous pathway partitioning. Maps to MEL WQ 1.2.1 (DO + NH4 fluxes) and H&amp;B 1.4.1 (sediment biogeochemistry under clam farming).</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Protocol (paired inside/outside farm chl-a + nutrient survey)</t>
+          <t>Protocol (paired benthic incubation across farming cycle)</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Yes — replicated across 4 farms, full water column, 13-month coverage; standard chl-a + nutrient methodology.</t>
+          <t>Yes — paired farm-vs-control sediment-core incubations with standard solute-flux methodology.</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Partial — sample collection is straightforward; lab analyses need partner.</t>
+          <t>No — laboratory core incubation is research-only.</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -25601,27 +25547,27 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>Niskin/pump sampling at multiple depths; fluorometer/spectrophotometer for chl-a; autoanalyser for DIN/DRP</t>
+          <t>Plexiglas core tubes; aerated incubation tanks; spectrophotometric NH4 determination; O2 microsensors/Winkler titration</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Low–Medium</t>
+          <t>Medium — coring + incubation lab; standard chemistry</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Annual (13-month)</t>
+          <t>Multi-season (farming-cycle scale, 2–3 yr cohort)</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>Paired inside-vs-outside contrasts; significance testing across farms and seasons</t>
+          <t>Paired contrasts farm vs control; flux rate calculations from concentration change over incubation</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>No — Paywalled (Elsevier)</t>
+          <t>No — Paywalled (Springer)</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -25631,7 +25577,7 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/S0044-8486(99)00219-7</t>
+          <t>https://doi.org/10.1007/s10750-007-0683-9</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
@@ -25639,9 +25585,9 @@
           <t>Original list</t>
         </is>
       </c>
-      <c r="W121" s="9" t="inlineStr">
-        <is>
-          <t>3 — Partnership</t>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>2 — Researcher</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
@@ -25651,32 +25597,32 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>Water Quality</t>
+          <t>Water Quality, Habitat &amp; Biodiversity</t>
         </is>
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>WQ 2.1.1 — Chlorophyll-a</t>
+          <t>WQ 1.1.2 — Rate of denitrification (DIN-flux proxy), WQ 1.2.1 — Dissolved oxygen, H&amp;B 1.4.1 — Sediment biogeochemistry</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>Temperate Pacific</t>
+          <t>Temperate Mediterranean</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>Green-shell mussel (Perna canaliculus)</t>
+          <t>Manila clam (Tapes / Ruditapes philippinarum)</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Longline / suspended</t>
+          <t>Bottom culture (seeded clam beds)</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr">
         <is>
-          <t>Multi-site (4 farms)</t>
+          <t>Single bay</t>
         </is>
       </c>
       <c r="AE121" t="inlineStr">
@@ -25691,7 +25637,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>Water chemistry, Plankton sampling</t>
+          <t>Sediment sampling, Benthic flux incubation, Water chemistry</t>
         </is>
       </c>
       <c r="AH121" t="inlineStr">
@@ -25711,17 +25657,17 @@
       </c>
       <c r="AK121" s="16" t="inlineStr">
         <is>
-          <t>To detect chlorophyll-a depletion by a mussel farm, profile chlorophyll fluorescence inside and just outside the farm and check whether it varies over the tidal cycle. Moor a CTD with a fluorometer on a longline at mid-depth and log fluorescence at short intervals over several tidal cycles (with a bottom-mounted current profiler for the tide), and on repeat surveys profile chlorophyll through the water column at randomly chosen on-farm stations, each paired with an outside station at equal distance from shore. Calibrate the fluorometer against water samples analysed for chlorophyll-a (90% acetone extraction, laboratory fluorometer), building a monthly conversion regression. Monitor ambient chlorophyll and dissolved nutrients (nitrate plus nitrite, reactive phosphorus, ammonium on an autoanalyser) outside the farm with an integrated tube sampler, and compare inside versus outside to quantify the depletion signal.</t>
+          <t>To track how benthic fluxes change over a clam-farming cycle, incubate intact sediment cores from a farmed experimental plot and a control at intervals from young stock to harvest, measuring dissolved-oxygen and ammonium fluxes across the sediment-water interface (spectrophotometric ammonium, oxygen by microsensor or Winkler). Compare farm against control fluxes through the cycle; this temporal trajectory complements the snapshot pathway measurements from companion studies at the same site.</t>
         </is>
       </c>
       <c r="AL121" s="17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="AM121" s="18" t="inlineStr">
         <is>
-          <t>ogilvie_2000</t>
+          <t>nizzoli_2007</t>
         </is>
       </c>
       <c r="AN121" s="19" t="n"/>
@@ -25729,75 +25675,75 @@
       <c r="AP121" s="19" t="n"/>
       <c r="AQ121" s="16" t="inlineStr">
         <is>
-          <t>Chlorophyll Depletion by a Mussel Farm (Inside-vs-Outside Profiling)</t>
+          <t>Oxygen &amp; Ammonium Fluxes Over a Clam-Farming Cycle</t>
         </is>
       </c>
       <c r="AR121" s="16" t="inlineStr">
         <is>
-          <t>Ogilvie, Shaun C; Ross, Alex H; Schiel, David R</t>
+          <t>Nizzoli, Daniele; Bartoli, Marco; Viaroli, Pierluigi</t>
         </is>
       </c>
       <c r="AS121" s="16" t="inlineStr">
         <is>
-          <t>Foundational green-shell-mussel-vs-phytoplankton paper for the Marlborough Sounds — the global centre of P. canaliculus aquaculture. Heavily cited by NZ DOC mussel-farming impact reviews. Companion to Ogilvie 2003 (in-situ enclosure experiments at same site) and Inglis et al. 2000 (carrying-capacity context). Phytoplankton depletion within farm boundaries shown to be season-dependent — important methodological insight for designing MEL chl-a baselines. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (paper measures DIN + DRP, not DO). Nutrients are not in v1.4 WQ 1.2.1 indicator scope.</t>
+          <t>Direct companion to R115 (Nizzoli 2006 MEPS, same site/group) and to v14 R66 (Nizzoli 2006 Aquaculture, N + P budget). Together these three papers form the Sacca di Goro Manila-clam-vs-Mediterranean-mussel benthic-N research program. Key value here: temporal trajectory of fluxes across the farming cycle, complementing the snapshot pathway-partitioning of the MEPS paper. Bartoli/Nizzoli/Viaroli are the canonical reference group for this biogeochemistry. | v1.4 refinement: Added WQ 1.1.2 (denitrification, via DIN flux + N-cycling indicators); same site/group as R115 Nizzoli 2006 MEPS. WQ 1.2.1 narrowed to DO.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Muñiz, O., et al.</t>
+          <t>Ogilvie, S. C., et al.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Annual cycle of phytoplankton community through the water column: Study applied to the implementation of bivalve offshore aquaculture in the southeastern Bay of Biscay</t>
+          <t>Phytoplankton biomass associated with mussel farms in Beatrix Bay, New Zealand</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Oceanologia</t>
+          <t>Aquaculture</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>61</v>
+        <v>181</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>1-15</t>
+          <t>71-80</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>2019</v>
+        <v>2000</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Institute of Oceanology, Polish Academy of Sciences (Elsevier)</t>
+          <t>Elsevier</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Pre-implementation baseline survey of phytoplankton community + WQ across 3 water-column depths (3, 17, 33 m) at an experimental offshore bivalve culture area off the Basque coast (SE Bay of Biscay), May 2014 – June 2015. Measured: phytoplankton composition (194 taxa), abundance, biomass, size-fractionated chl-a, nutrients (nitrate, silicate dominant), optical + hydrographic conditions. Found total chl-a low (~0.6 µg L⁻¹ avg); diatoms 35% of taxa with highest biomass; haptophytes dominant in cell abundance. Maps to MEL WQ 2.1.1 (chl-a + phytoplankton biomass), WQ 2.1.2 (community composition), WQ 1.2.1 (nutrients).</t>
+          <t>Inside-vs-outside phytoplankton biomass survey at 4 green-shell mussel (Perna canaliculus) farm sites in Beatrix Bay, Marlborough Sounds, NZ, over a 13-month period. Chl-a measured throughout the water column; ambient (outside) NO3-N, NH4-N, and dissolved reactive phosphorus (DRP) measured. Found significant farm-driven phytoplankton biomass reduction during autumn–winter high-chl-a periods (peaks ~5 µg L⁻¹). Maps to MEL WQ 2.1.1 (chl-a) and WQ 1.2.1 (DIN, DRP).</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Protocol (multi-depth annual phytoplankton + WQ baseline)</t>
+          <t>Protocol (paired inside/outside farm chl-a + nutrient survey)</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Yes — 13-month, 3-depth coverage; standard taxonomic + WQ methods; size-fractionated chl-a is a robust addition.</t>
+          <t>Yes — replicated across 4 farms, full water column, 13-month coverage; standard chl-a + nutrient methodology.</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Partial — water sampling straightforward; phytoplankton taxonomy + size fractionation require specialist lab.</t>
+          <t>Partial — sample collection is straightforward; lab analyses need partner.</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -25807,42 +25753,37 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Niskin at multiple depths; fluorometer; size-fractionated chl-a filtration; phytoplankton microscopy + counting chambers; CTD</t>
+          <t>Niskin/pump sampling at multiple depths; fluorometer/spectrophotometer for chl-a; autoanalyser for DIN/DRP</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Medium — multi-depth sampling + taxonomic lab</t>
+          <t>Low–Medium</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Annual (13-month, monthly cruises)</t>
+          <t>Annual (13-month)</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>Multivariate community analysis; environmental-variable correlation</t>
+          <t>Paired inside-vs-outside contrasts; significance testing across farms and seasons</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>Yes — Open access (Oceanologia / Elsevier)</t>
+          <t>No — Paywalled (Elsevier)</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>Full PDF</t>
+          <t>Abstract + Methods (fetched)</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.oceano.2018.08.001</t>
-        </is>
-      </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>A pre-development baseline template - establishes phytoplankton and water-quality conditions before a farm is built.</t>
+          <t>https://doi.org/10.1016/S0044-8486(99)00219-7</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
@@ -25867,27 +25808,27 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>WQ 2.1.1 — Chlorophyll-a (size-fractionated), WQ 2.1.2 — Microorganism / plankton community</t>
+          <t>WQ 2.1.1 — Chlorophyll-a</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>Temperate Atlantic</t>
+          <t>Temperate Pacific</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>Multi-species / mixed (offshore experimental area)</t>
+          <t>Green-shell mussel (Perna canaliculus)</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Longline / suspended (offshore)</t>
+          <t>Longline / suspended</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr">
         <is>
-          <t>Single farm (experimental)</t>
+          <t>Multi-site (4 farms)</t>
         </is>
       </c>
       <c r="AE122" t="inlineStr">
@@ -25897,7 +25838,7 @@
       </c>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>Monoculture (planned)</t>
+          <t>Monoculture</t>
         </is>
       </c>
       <c r="AG122" t="inlineStr">
@@ -25912,93 +25853,103 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Offshore (deeper) (3–33 m water column)</t>
+          <t>Shallow nearshore (2–10 m)</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>Exposed (offshore Bay of Biscay)</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>To characterise the phytoplankton community and water-column conditions at a candidate offshore bivalve site through a full annual cycle, sample at a fixed station just outside the (experimental) farm. Twice a month take a CTD cast recording temperature, salinity, chlorophyll-a fluorescence and photosynthetically-active radiation at every metre plus a Secchi reading, and monthly collect water with Niskin bottles for inorganic nutrients (ammonium, nitrite, nitrate, silicate, phosphate on a continuous-flow autoanalyser) and for size-fractionated chlorophyll-a by sequential filtration (&lt;3, 3-20 and &gt;20 um - pico-, nano- and microphytoplankton). Identify and count phytoplankton at several depths (for example surface, mid and near-bottom) from Lugol's-preserved samples by the Utermohl method, converting to cell concentration and to carbon biomass via biovolume. Derive the light-extinction coefficient and photic-zone depth from the PAR profile, and relate the community to the environment with correlation matrices and ordination (removing rare taxa and applying a multiple-comparison correction) to define the seasonal food-supply and hydrographic envelope for siting.</t>
-        </is>
-      </c>
-      <c r="AL122" t="inlineStr">
+          <t>Sheltered</t>
+        </is>
+      </c>
+      <c r="AK122" s="16" t="inlineStr">
+        <is>
+          <t>To detect chlorophyll-a depletion by a mussel farm, profile chlorophyll fluorescence inside and just outside the farm and check whether it varies over the tidal cycle. Moor a CTD with a fluorometer on a longline at mid-depth and log fluorescence at short intervals over several tidal cycles (with a bottom-mounted current profiler for the tide), and on repeat surveys profile chlorophyll through the water column at randomly chosen on-farm stations, each paired with an outside station at equal distance from shore. Calibrate the fluorometer against water samples analysed for chlorophyll-a (90% acetone extraction, laboratory fluorometer), building a monthly conversion regression. Monitor ambient chlorophyll and dissolved nutrients (nitrate plus nitrite, reactive phosphorus, ammonium on an autoanalyser) outside the farm with an integrated tube sampler, and compare inside versus outside to quantify the depletion signal.</t>
+        </is>
+      </c>
+      <c r="AL122" s="17" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
       <c r="AM122" s="18" t="inlineStr">
         <is>
-          <t>muniz_2019</t>
+          <t>ogilvie_2000</t>
         </is>
       </c>
       <c r="AN122" s="19" t="n"/>
       <c r="AO122" s="19" t="n"/>
       <c r="AP122" s="19" t="n"/>
+      <c r="AQ122" s="16" t="inlineStr">
+        <is>
+          <t>Chlorophyll Depletion by a Mussel Farm (Inside-vs-Outside Profiling)</t>
+        </is>
+      </c>
       <c r="AR122" s="16" t="inlineStr">
         <is>
-          <t>Muñiz, Oihane; Revilla, Marta; Rodríguez, José Germán; Laza-Martínez, Aitor; Fontán, Almudena</t>
+          <t>Ogilvie, Shaun C; Ross, Alex H; Schiel, David R</t>
         </is>
       </c>
       <c r="AS122" s="16" t="inlineStr">
         <is>
-          <t>Pre-development baseline paper — establishes phytoplankton + WQ conditions BEFORE bivalve farm implementation on the Basque coast. Useful template for MEL practitioners designing baseline campaigns. Companion to Muñiz et al. 2017/2018 toxic-phytoplankton evaluations and Bilbao 2020 inshore study. Methodologically clean baseline that future post-implementation surveys can compare against. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (nutrients + chl-a + phytoplankton community measured; no DO). | v38: filled at High from pasted Methods (Muniz); Source Read set to Full PDF; DOI corrected to paper's own 10.1016/j.oceano.2018.08.001 (prior 2018.07.001).</t>
+          <t>Foundational green-shell-mussel-vs-phytoplankton paper for the Marlborough Sounds — the global centre of P. canaliculus aquaculture. Heavily cited by NZ DOC mussel-farming impact reviews. Companion to Ogilvie 2003 (in-situ enclosure experiments at same site) and Inglis et al. 2000 (carrying-capacity context). Phytoplankton depletion within farm boundaries shown to be season-dependent — important methodological insight for designing MEL chl-a baselines. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (paper measures DIN + DRP, not DO). Nutrients are not in v1.4 WQ 1.2.1 indicator scope.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Taylor, D., et al.</t>
+          <t>Muñiz, O., et al.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Quantifying bivalve phytoplankton depletion in a eutrophic system: an integrated approach</t>
+          <t>Annual cycle of phytoplankton community through the water column: Study applied to the implementation of bivalve offshore aquaculture in the southeastern Bay of Biscay</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Limnology and Oceanography</t>
+          <t>Oceanologia</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>69</v>
+        <v>61</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2436-2452</t>
+          <t>1-15</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Wiley (ASLO)</t>
+          <t>Institute of Oceanology, Polish Academy of Sciences (Elsevier)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Multi-scale integrated phytoplankton-depletion assessment at a large 5-unit mussel farm in Venø Sund (19.26 km², 4–6 m depth) within Limfjorden (Denmark), an eutrophic, microtidal (0.2 m prism), brackish (22–33 PSU) sound. Three measurement scales: (i) MICRO — pulse-shape flow cytometry (PSFC) for phytoplankton community composition; (ii) MESO — fixed mooring stations (high temporal), chl-a synoptic transect surveys (high spatial), conventional CTD/discrete profiling, and a preliminary aerial-drone survey method; (iii) MACRO — optical satellite remote sensing + spatial analyses. Significant depletion (5–91% Chl-a reduction) detected with all methods, mixing gradients extending hundreds of metres beyond the farm. Maps to MEL WQ 2.1.1 (chl-a, phytoplankton size structure) and WQ 2.1.2 (phytoplankton community).</t>
+          <t>Pre-implementation baseline survey of phytoplankton community + WQ across 3 water-column depths (3, 17, 33 m) at an experimental offshore bivalve culture area off the Basque coast (SE Bay of Biscay), May 2014 – June 2015. Measured: phytoplankton composition (194 taxa), abundance, biomass, size-fractionated chl-a, nutrients (nitrate, silicate dominant), optical + hydrographic conditions. Found total chl-a low (~0.6 µg L⁻¹ avg); diatoms 35% of taxa with highest biomass; haptophytes dominant in cell abundance. Maps to MEL WQ 2.1.1 (chl-a + phytoplankton biomass), WQ 2.1.2 (community composition), WQ 1.2.1 (nutrients).</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Protocol (integrated multi-method, multi-scale depletion survey)</t>
+          <t>Protocol (multi-depth annual phytoplankton + WQ baseline)</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Yes — gold-standard integrated approach combining 4+ measurement modalities across spatial scales; depletion patterns robust across methods, validated against Limfjorden hydrodynamic model.</t>
+          <t>Yes — 13-month, 3-depth coverage; standard taxonomic + WQ methods; size-fractionated chl-a is a robust addition.</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>No — multi-modality integration is research-only.</t>
+          <t>Partial — water sampling straightforward; phytoplankton taxonomy + size fractionation require specialist lab.</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -26008,42 +25959,42 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>CytoSense pulse-shape flow cytometer; CTD with chl-a + Secchi; mooring station array; aerial drone with multispectral / hyperspectral; Sentinel-2/3 satellite imagery; FlexSem Limfjorden hydrodynamic model (link to companion paper R110 Maar 2024)</t>
+          <t>Niskin at multiple depths; fluorometer; size-fractionated chl-a filtration; phytoplankton microscopy + counting chambers; CTD</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>High — multiple specialised platforms across scales</t>
+          <t>Medium — multi-depth sampling + taxonomic lab</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Multi-season campaign</t>
+          <t>Annual (13-month, monthly cruises)</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>Cross-method consistency analysis; spatial mapping of depletion halo; correlation of depletion magnitude with biomass loads, ambient conditions, and hydrodynamic regimes</t>
+          <t>Multivariate community analysis; environmental-variable correlation</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>Yes — Open access (Wiley-ASLO CC BY-NC-ND)</t>
+          <t>Yes — Open access (Oceanologia / Elsevier)</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>Full PDF</t>
+          <t>Abstract + Methods (fetched)</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/lno.12680</t>
+          <t>https://doi.org/10.1016/j.oceano.2018.07.001</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>Agreement across independent methods (satellite, flow-cytometry, mooring, survey) is what makes a farm-scale depletion signal credible.</t>
+          <t>A pre-development baseline template - establishes phytoplankton and water-quality conditions before a farm is built.</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
@@ -26051,9 +26002,9 @@
           <t>Original list</t>
         </is>
       </c>
-      <c r="W123" t="inlineStr">
-        <is>
-          <t>2 — Researcher</t>
+      <c r="W123" s="9" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
@@ -26068,7 +26019,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>WQ 2.1.1 — Chlorophyll-a, WQ 2.1.2 — Microorganisms</t>
+          <t>WQ 2.1.1 — Chlorophyll-a (size-fractionated), WQ 2.1.2 — Microorganism / plankton community</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -26078,22 +26029,22 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>Blue mussel (Mytilus edulis)</t>
+          <t>Multi-species / mixed (offshore experimental area)</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Longline / suspended</t>
+          <t>Longline / suspended (offshore)</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>Single farm (large, 5-unit)</t>
+          <t>Single farm (experimental)</t>
         </is>
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>Variable / seasonal (eutrophic)</t>
+          <t>Variable / seasonal</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -26103,7 +26054,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>Water chemistry, Plankton sampling, Remote sensing, In-situ sensors, Modelling</t>
+          <t>Water chemistry, Plankton sampling</t>
         </is>
       </c>
       <c r="AH123" t="inlineStr">
@@ -26113,103 +26064,83 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>Shallow nearshore (2–10 m)</t>
+          <t>Offshore (deeper) (3–33 m water column)</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>Sheltered (microtidal)</t>
-        </is>
-      </c>
-      <c r="AK123" s="16" t="inlineStr">
-        <is>
-          <t>To measure phytoplankton depletion at a large suspended mussel farm across scales, combine methods: pulse-shape flow cytometry on water samples for phytoplankton community composition; CTD casts with chlorophyll and Secchi plus a mooring array for continuous in-farm and reference conditions; a synoptic vessel survey mapping the chlorophyll halo; and drone or satellite (Sentinel) imagery for the surface chlorophyll field. Cross-check depletion across methods and validate against a hydrodynamic model; agreement across independent modalities is what makes a farm-scale depletion signal credible.</t>
-        </is>
-      </c>
-      <c r="AL123" s="17" t="inlineStr">
-        <is>
-          <t>Med</t>
+          <t>Exposed (offshore Bay of Biscay)</t>
         </is>
       </c>
       <c r="AM123" s="18" t="inlineStr">
         <is>
-          <t>taylor_2024</t>
+          <t>muniz_2019</t>
         </is>
       </c>
       <c r="AN123" s="19" t="n"/>
       <c r="AO123" s="19" t="n"/>
       <c r="AP123" s="19" t="n"/>
-      <c r="AQ123" s="16" t="inlineStr">
-        <is>
-          <t>Multi-Method Phytoplankton-Depletion Measurement at a Large Mussel Farm</t>
-        </is>
-      </c>
       <c r="AR123" s="16" t="inlineStr">
         <is>
-          <t>Taylor, Daniel; Jakobsen, Hans; Lyngsgaard, Maren Moltke; Darecki, Mirosław; Werther, Mortimer; Maar, Marie; Saurel, Camille</t>
+          <t>Muñiz, Oihane; Revilla, Marta; Rodríguez, José Germán; Laza-Martínez, Aitor; Fontán, Almudena</t>
         </is>
       </c>
       <c r="AS123" s="16" t="inlineStr">
         <is>
-          <t>Important multi-method integration paper for phytoplankton depletion — establishes that satellite RS, flow-cytometry, mooring, and synoptic survey all detect coherent farm-scale Chl-a depletion in a large mussel farm. Useful methodological template for designing MEL WQ 2.1.x assessments at large suspended-bivalve farms. Companion (same site, same group) to Maar 2024 (R110, climate-projection modelling at Limfjorden — Taylor is co-author there).</t>
+          <t>Pre-development baseline paper — establishes phytoplankton + WQ conditions BEFORE bivalve farm implementation on the Basque coast. Useful template for MEL practitioners designing baseline campaigns. Companion to Muñiz et al. 2017/2018 toxic-phytoplankton evaluations and Bilbao 2020 inshore study. Methodologically clean baseline that future post-implementation surveys can compare against. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (nutrients + chl-a + phytoplankton community measured; no DO).</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Cugier, P., et al.</t>
+          <t>Taylor, D., et al.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Assessing the role of benthic filter feeders on phytoplankton production in a shellfish farming site: Mont Saint Michel Bay, France</t>
+          <t>Quantifying bivalve phytoplankton depletion in a eutrophic system: an integrated approach</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Journal of Marine Systems</t>
+          <t>Limnology and Oceanography</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>82</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
+        <v>69</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>21-34</t>
+          <t>2436-2452</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>2010</v>
+        <v>2024</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Elsevier</t>
+          <t>Wiley (ASLO)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Coupled ecological model of Mont Saint Michel Bay (English Channel, France): 2D hydro-sedimentary model + primary production model + filter-feeder filtration model. Filter-feeder compartment includes 3 cultivated species (Mytilus edulis, Crassostrea gigas, Ostrea edulis), 1 invasive (Crepidula fornicata), and 8 wild natives (Abra alba, Cerastoderma edule, etc.). Biodeposits + mineralisation feedback included. Outputs: Chl-a, primary production, partitioned filter-feeder pressure. Key finding: wild species + invasive Crepidula are stronger controllers of phytoplankton biomass than cultivated species. Maps to MEL WQ 2.1.1 (chl-a, modelled), WQ 1.2.1 (nutrients in model).</t>
+          <t>Multi-scale integrated phytoplankton-depletion assessment at a large 5-unit mussel farm in Venø Sund (19.26 km², 4–6 m depth) within Limfjorden (Denmark), an eutrophic, microtidal (0.2 m prism), brackish (22–33 PSU) sound. Three measurement scales: (i) MICRO — pulse-shape flow cytometry (PSFC) for phytoplankton community composition; (ii) MESO — fixed mooring stations (high temporal), chl-a synoptic transect surveys (high spatial), conventional CTD/discrete profiling, and a preliminary aerial-drone survey method; (iii) MACRO — optical satellite remote sensing + spatial analyses. Significant depletion (5–91% Chl-a reduction) detected with all methods, mixing gradients extending hundreds of metres beyond the farm. Maps to MEL WQ 2.1.1 (chl-a, phytoplankton size structure) and WQ 2.1.2 (phytoplankton community).</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Reference (model framework — coupled hydro-bio model)</t>
+          <t>Protocol (integrated multi-method, multi-scale depletion survey)</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Yes — model validated against in-situ chl-a + nutrient data; partitions filter-feeder pressure by species/compartment.</t>
+          <t>Yes — gold-standard integrated approach combining 4+ measurement modalities across spatial scales; depletion patterns robust across methods, validated against Limfjorden hydrodynamic model.</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>No — model development is research-only.</t>
+          <t>No — multi-modality integration is research-only.</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -26219,42 +26150,42 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>Coupled 2D hydro-sedimentary + primary-production + filter-feeder filtration model; biodeposit + mineralisation modules</t>
+          <t>CytoSense pulse-shape flow cytometer; CTD with chl-a + Secchi; mooring station array; aerial drone with multispectral / hyperspectral; Sentinel-2/3 satellite imagery; FlexSem Limfjorden hydrodynamic model (link to companion paper R110 Maar 2024)</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>High — modelling effort with calibration data requirements</t>
+          <t>High — multiple specialised platforms across scales</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Annual / multi-year simulation</t>
+          <t>Multi-season campaign</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>Scenario analysis (filter-feeder compartment partitioning); steady-state + dynamic outputs</t>
+          <t>Cross-method consistency analysis; spatial mapping of depletion halo; correlation of depletion magnitude with biomass loads, ambient conditions, and hydrodynamic regimes</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>Yes — Open access via HAL (Ifremer); journal article paywalled</t>
+          <t>Yes — Open access (Wiley-ASLO CC BY-NC-ND)</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>Abstract + Methods (fetched)</t>
+          <t>Full PDF</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jmarsys.2010.02.013</t>
+          <t>https://doi.org/10.1002/lno.12680</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>Where wild or invasive filter-feeders are abundant, attributing depletion to aquaculture requires disentangling their contribution.</t>
+          <t>Agreement across independent methods (satellite, flow-cytometry, mooring, survey) is what makes a farm-scale depletion signal credible.</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
@@ -26279,7 +26210,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>WQ 1.3.1 — Rate of water filtration (filter-feeder filtration model), WQ 2.1.1 — Chlorophyll-a</t>
+          <t>WQ 2.1.1 — Chlorophyll-a, WQ 2.1.2 — Microorganisms</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -26289,17 +26220,17 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>Blue mussel (Mytilus edulis), Pacific oyster (Crassostrea / Magallana gigas), European flat oyster (Ostrea edulis)</t>
+          <t>Blue mussel (Mytilus edulis)</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Mixed (longline mussel + intertidal table oyster + bottom)</t>
+          <t>Longline / suspended</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>Bay-wide / system-scale (modelled)</t>
+          <t>Single farm (large, 5-unit)</t>
         </is>
       </c>
       <c r="AE124" t="inlineStr">
@@ -26309,12 +26240,12 @@
       </c>
       <c r="AF124" t="inlineStr">
         <is>
-          <t>Monoculture (multiple)</t>
+          <t>Monoculture</t>
         </is>
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>Modelling</t>
+          <t>Water chemistry, Plankton sampling, Remote sensing, In-situ sensors, Modelling</t>
         </is>
       </c>
       <c r="AH124" t="inlineStr">
@@ -26324,27 +26255,27 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>Intertidal / very shallow (&lt; 2 m)</t>
+          <t>Shallow nearshore (2–10 m)</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>Mixed exposure</t>
+          <t>Sheltered (microtidal)</t>
         </is>
       </c>
       <c r="AK124" s="16" t="inlineStr">
         <is>
-          <t>This is a coupled 2D hydro-sedimentary, primary-production and filter-feeder model of a major shellfish bay that partitions grazing pressure among cultivated species, an invasive species and wild natives, validated against in-situ chlorophyll and nutrients. Its lesson for monitoring: where wild and invasive filter feeders are abundant, attributing chlorophyll depletion specifically to aquaculture requires disentangling their contributions. Use it as a model reference for carrying-capacity and attribution questions.</t>
+          <t>To measure phytoplankton depletion at a large suspended mussel farm across scales, combine methods: pulse-shape flow cytometry on water samples for phytoplankton community composition; CTD casts with chlorophyll and Secchi plus a mooring array for continuous in-farm and reference conditions; a synoptic vessel survey mapping the chlorophyll halo; and drone or satellite (Sentinel) imagery for the surface chlorophyll field. Cross-check depletion across methods and validate against a hydrodynamic model; agreement across independent modalities is what makes a farm-scale depletion signal credible.</t>
         </is>
       </c>
       <c r="AL124" s="17" t="inlineStr">
         <is>
-          <t>Ref</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="AM124" s="18" t="inlineStr">
         <is>
-          <t>cugier_2010</t>
+          <t>taylor_2024</t>
         </is>
       </c>
       <c r="AN124" s="19" t="n"/>
@@ -26352,46 +26283,51 @@
       <c r="AP124" s="19" t="n"/>
       <c r="AQ124" s="16" t="inlineStr">
         <is>
-          <t>Coupled Model of Filter-Feeder Effects on Phytoplankton (Reference)</t>
+          <t>Multi-Method Phytoplankton-Depletion Measurement at a Large Mussel Farm</t>
         </is>
       </c>
       <c r="AR124" s="16" t="inlineStr">
         <is>
-          <t>Cugier, Philippe; Struski, Caroline; Blanchard, Michel; Mazurié, Joseph; Pouvreau, Stéphane; Olivier, Frédéric; Trigui, Jihane R; Thiébaut, Eric</t>
+          <t>Taylor, Daniel; Jakobsen, Hans; Lyngsgaard, Maren Moltke; Darecki, Mirosław; Werther, Mortimer; Maar, Marie; Saurel, Camille</t>
         </is>
       </c>
       <c r="AS124" s="16" t="inlineStr">
         <is>
-          <t>Foundational coupled-model paper for the role of cultivated AND wild filter-feeders in shaping phytoplankton biomass at a major shellfish-farming site. Methodologically important conclusion for MEL: when wild/invasive filter-feeders are abundant, attributing chl-a depletion specifically to aquaculture requires careful disentangling. Companion to Cugier 2005 (same bay, nutrient-only model) and later applied to Bourgneuf Bay and Pertuis Charentais. | v1.4 refinement: Added WQ 1.3.1 (Rate of water filtration) — paper's central methodology is a filter-feeder filtration model with partitioned per-species filtration pressure on phytoplankton biomass; v1.4 added this indicator. WQ 1.2.1 removed (model does not produce a DO output).</t>
+          <t>Important multi-method integration paper for phytoplankton depletion — establishes that satellite RS, flow-cytometry, mooring, and synoptic survey all detect coherent farm-scale Chl-a depletion in a large mussel farm. Useful methodological template for designing MEL WQ 2.1.x assessments at large suspended-bivalve farms. Companion (same site, same group) to Maar 2024 (R110, climate-projection modelling at Limfjorden — Taylor is co-author there).</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Jiang, Z., et al.</t>
+          <t>Cugier, P., et al.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Oyster farming control on phytoplankton bloom promoted by thermal discharge from a power plant in a eutrophic, semi-enclosed bay</t>
+          <t>Assessing the role of benthic filter feeders on phytoplankton production in a shellfish farming site: Mont Saint Michel Bay, France</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Water Research</t>
+          <t>Journal of Marine Systems</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>159</v>
+        <v>82</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>21-34</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -26400,22 +26336,22 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Ten cruises (2009–2015) across paired old oyster farm (OOF), new oyster farm (NOF) and control areas (CA) adjacent to the Ninghai Power Plant (NPP, 82.5 m³ s⁻¹ thermal discharge, +1°C envelope) in the upper section of Xiangshan Bay (XSB, ~60 km long, water-residence ~80 d), China. Sampled surface (0.5 m) + bottom (0.5 m above bed). Measured phytoplankton community (chl-a, abundance, diversity, dominant species, size structure) and physico-chemical (T, transparency, suspended solids, DO, nutrients, organic carbon). Demonstrated thermal discharge induced severe winter algal blooms; oyster (Crassostrea plicatula) farming reduced phytoplankton abundance 26.3%, chl-a 28.3%, increased Shannon diversity 38.3%, Pielou's evenness 28.8%, reduced SS 12.2%, TOC 18.4%, DIN 1.5%, P 3.7%. Maps to MEL WQ 2.1.1 (chl-a, phytoplankton biomass), WQ 2.1.2 (community composition / microorganisms), WQ 1.2.1 (T, DO, nutrients, suspended solids, OC).</t>
+          <t>Coupled ecological model of Mont Saint Michel Bay (English Channel, France): 2D hydro-sedimentary model + primary production model + filter-feeder filtration model. Filter-feeder compartment includes 3 cultivated species (Mytilus edulis, Crassostrea gigas, Ostrea edulis), 1 invasive (Crepidula fornicata), and 8 wild natives (Abra alba, Cerastoderma edule, etc.). Biodeposits + mineralisation feedback included. Outputs: Chl-a, primary production, partitioned filter-feeder pressure. Key finding: wild species + invasive Crepidula are stronger controllers of phytoplankton biomass than cultivated species. Maps to MEL WQ 2.1.1 (chl-a, modelled), WQ 1.2.1 (nutrients in model).</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Protocol (multi-year paired farm-vs-control sampling, full WQ + phytoplankton suite)</t>
+          <t>Reference (model framework — coupled hydro-bio model)</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Yes — 10 cruises over 7 years; paired design (old + new OF vs CA); two power-plant operational phases (with thermal discharge 2009–2015); rich measurement suite.</t>
+          <t>Yes — model validated against in-situ chl-a + nutrient data; partitions filter-feeder pressure by species/compartment.</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Partial — water + phytoplankton sampling feasible for trained farmers; identification + lab analyses need partner.</t>
+          <t>No — model development is research-only.</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -26425,42 +26361,42 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Niskin / pump sampler; CTD; fluorometer; phytoplankton microscopy + counting; autoanalyser for nutrients; TOC analyser</t>
+          <t>Coupled 2D hydro-sedimentary + primary-production + filter-feeder filtration model; biodeposit + mineralisation modules</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Medium — multi-cruise institutional campaign</t>
+          <t>High — modelling effort with calibration data requirements</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Multi-year (10 cruises 2009–2015)</t>
+          <t>Annual / multi-year simulation</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>ANOSIM / SIMPER for phytoplankton community contrast OF vs CA; species richness, Shannon-Wiener diversity, Pielou's evenness; percent change in physico-chemical variables</t>
+          <t>Scenario analysis (filter-feeder compartment partitioning); steady-state + dynamic outputs</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>No — Paywalled (Elsevier / Water Research)</t>
+          <t>Yes — Open access via HAL (Ifremer); journal article paywalled</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>Full PDF</t>
+          <t>Abstract + Methods (fetched)</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.watres.2019.04.023</t>
+          <t>https://doi.org/10.1016/j.jmarsys.2010.02.013</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>Here oyster farming helped mitigate thermal-discharge algal blooms; the old-vs-new-farm design controls for the thermal signal.</t>
+          <t>Where wild or invasive filter-feeders are abundant, attributing depletion to aquaculture requires disentangling their contribution.</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
@@ -26468,9 +26404,9 @@
           <t>Original list</t>
         </is>
       </c>
-      <c r="W125" s="9" t="inlineStr">
-        <is>
-          <t>3 — Partnership</t>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>2 — Researcher</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
@@ -26485,42 +26421,42 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>WQ 1.2.1 — Dissolved oxygen, WQ 2.1.1 — Chlorophyll-a, WQ 2.1.2 — Microorganism / plankton community</t>
+          <t>WQ 1.3.1 — Rate of water filtration (filter-feeder filtration model), WQ 2.1.1 — Chlorophyll-a</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>Subtropical Pacific</t>
+          <t>Temperate Atlantic</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>Chinese pleated oyster (Crassostrea plicatula)</t>
+          <t>Blue mussel (Mytilus edulis), Pacific oyster (Crassostrea / Magallana gigas), European flat oyster (Ostrea edulis)</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Raft / longline (oyster ropes on rafts)</t>
+          <t>Mixed (longline mussel + intertidal table oyster + bottom)</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr">
         <is>
-          <t>Single farm (paired OF + CA in same bay)</t>
+          <t>Bay-wide / system-scale (modelled)</t>
         </is>
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>Eutrophic / variable</t>
+          <t>Variable / seasonal</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
         <is>
-          <t>Monoculture (thermal-discharge confound)</t>
+          <t>Monoculture</t>
         </is>
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>Water chemistry, Plankton sampling</t>
+          <t>Modelling</t>
         </is>
       </c>
       <c r="AH125" t="inlineStr">
@@ -26530,27 +26466,27 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>Shallow nearshore (2–10 m)</t>
+          <t>Intertidal / very shallow (&lt; 2 m)</t>
         </is>
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>Sheltered</t>
+          <t>Mixed exposure</t>
         </is>
       </c>
       <c r="AK125" s="16" t="inlineStr">
         <is>
-          <t>To attribute changes in phytoplankton biomass and community to an oyster farm, sample paired stations at the farm centre and in a control area a few hundred metres to about 1 km outside, at surface and bottom, repeated across seasons (ideally spanning years, and comparing an old and a relocated farm for causal weight). Collect water with Niskin bottles; measure DO by Winkler titration and transparency by Secchi, and take frozen samples for nutrients (0.45 um filtered), total organic carbon and suspended solids. Size-fractionate chlorophyll-a (&gt;20, 2-20, &lt;2 um) by sequential filtration and read on a fluorometer after acetone extraction, and measure pheopigments (chl-a degradation products) as a grazing indicator; settle and count phytoplankton (at least 300 units) under a microscope for richness, Shannon and Pielou indices. Compare farm versus control with two-way ANOVA (or Mann-Whitney) and ANOSIM on log-transformed Bray-Curtis data, and correlate the biomass reduction with environmental drivers.</t>
+          <t>This is a coupled 2D hydro-sedimentary, primary-production and filter-feeder model of a major shellfish bay that partitions grazing pressure among cultivated species, an invasive species and wild natives, validated against in-situ chlorophyll and nutrients. Its lesson for monitoring: where wild and invasive filter feeders are abundant, attributing chlorophyll depletion specifically to aquaculture requires disentangling their contributions. Use it as a model reference for carrying-capacity and attribution questions.</t>
         </is>
       </c>
       <c r="AL125" s="17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Ref</t>
         </is>
       </c>
       <c r="AM125" s="18" t="inlineStr">
         <is>
-          <t>jiang_2019</t>
+          <t>cugier_2010</t>
         </is>
       </c>
       <c r="AN125" s="19" t="n"/>
@@ -26558,46 +26494,46 @@
       <c r="AP125" s="19" t="n"/>
       <c r="AQ125" s="16" t="inlineStr">
         <is>
-          <t>Attributing Phytoplankton Change to an Oyster Farm (Size-Fractionated)</t>
+          <t>Coupled Model of Filter-Feeder Effects on Phytoplankton (Reference)</t>
         </is>
       </c>
       <c r="AR125" s="16" t="inlineStr">
         <is>
-          <t>Jiang, Zhibing; Du, Ping; Liao, Yibo; Liu, Qiang; Chen, Quanzhen; Shou, Lu; Zeng, Jiangning; Chen, Jianfang</t>
+          <t>Cugier, Philippe; Struski, Caroline; Blanchard, Michel; Mazurié, Joseph; Pouvreau, Stéphane; Olivier, Frédéric; Trigui, Jihane R; Thiébaut, Eric</t>
         </is>
       </c>
       <c r="AS125" s="16" t="inlineStr">
         <is>
-          <t>Important real-world paper showing oyster farming as a mitigation tool for thermal-discharge-induced algal blooms in a eutrophic subtropical bay. Confounded by thermal-discharge factor but design (OF vs CA in same thermal envelope) controls for that. After culture-raft removal, no significant differences between former-OF and CA — direct evidence the effect is the farming activity itself. Companion to Jiang 2012 (v15 R43), Jiang 2016 (#38 = R128), Jiang 2019a/b further work. Strong reference for MEL practitioners thinking about bivalve farming as ecological-restoration intervention. | v1.4 refinement: WQ 1.2.1 narrowed to DO (paper lists oxygen among measured physico-chemical variables).</t>
+          <t>Foundational coupled-model paper for the role of cultivated AND wild filter-feeders in shaping phytoplankton biomass at a major shellfish-farming site. Methodologically important conclusion for MEL: when wild/invasive filter-feeders are abundant, attributing chl-a depletion specifically to aquaculture requires careful disentangling. Companion to Cugier 2005 (same bay, nutrient-only model) and later applied to Bourgneuf Bay and Pertuis Charentais. | v1.4 refinement: Added WQ 1.3.1 (Rate of water filtration) — paper's central methodology is a filter-feeder filtration model with partitioned per-species filtration pressure on phytoplankton biomass; v1.4 added this indicator. WQ 1.2.1 removed (model does not produce a DO output).</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Jiang, T., et al.</t>
+          <t>Jiang, Z., et al.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Size-dependent depletion and community disturbance of phytoplankton under intensive oyster mariculture based on HPLC pigment analysis in Daya Bay, South China Sea</t>
+          <t>Oyster farming control on phytoplankton bloom promoted by thermal discharge from a power plant in a eutrophic, semi-enclosed bay</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Environmental Pollution</t>
+          <t>Water Research</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>219</v>
+        <v>159</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>804-814</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -26606,22 +26542,22 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>14-month investigation in Daya Bay, South China Sea, comparing intensive-oyster-farming area to reference area using HPLC size-fractionated phytopigments (chl-a, fucoxanthin, peridinin, and other diagnostic pigments). Filtering effect of oysters on phytoplankton biomass quantified size-class by size-class: ~60% total chl-a reduction in farming area vs reference; depletion concentrated in micro-sized (&gt;20 µm) fractions; nano-sized (2.7–20 µm) less affected. Community disturbance documented via pigment-based community shifts. Maps to MEL WQ 2.1.1 (chl-a + size-fractionated), WQ 2.1.2 (community composition via pigments).</t>
+          <t>Ten cruises (2009–2015) across paired old oyster farm (OOF), new oyster farm (NOF) and control areas (CA) adjacent to the Ninghai Power Plant (NPP, 82.5 m³ s⁻¹ thermal discharge, +1°C envelope) in the upper section of Xiangshan Bay (XSB, ~60 km long, water-residence ~80 d), China. Sampled surface (0.5 m) + bottom (0.5 m above bed). Measured phytoplankton community (chl-a, abundance, diversity, dominant species, size structure) and physico-chemical (T, transparency, suspended solids, DO, nutrients, organic carbon). Demonstrated thermal discharge induced severe winter algal blooms; oyster (Crassostrea plicatula) farming reduced phytoplankton abundance 26.3%, chl-a 28.3%, increased Shannon diversity 38.3%, Pielou's evenness 28.8%, reduced SS 12.2%, TOC 18.4%, DIN 1.5%, P 3.7%. Maps to MEL WQ 2.1.1 (chl-a, phytoplankton biomass), WQ 2.1.2 (community composition / microorganisms), WQ 1.2.1 (T, DO, nutrients, suspended solids, OC).</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Protocol (HPLC size-fractionated phytopigment community + biomass analysis)</t>
+          <t>Protocol (multi-year paired farm-vs-control sampling, full WQ + phytoplankton suite)</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Yes — HPLC pigment chemotaxonomy is a robust, quantitative approach for community shifts; 14-month duration captures seasonal cycles.</t>
+          <t>Yes — 10 cruises over 7 years; paired design (old + new OF vs CA); two power-plant operational phases (with thermal discharge 2009–2015); rich measurement suite.</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>No — HPLC pigment analysis is research-only.</t>
+          <t>Partial — water + phytoplankton sampling feasible for trained farmers; identification + lab analyses need partner.</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -26631,42 +26567,42 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>Size-fractionation filtration (0.7, 2.7, 20 µm); HPLC for diagnostic pigments (chl-a, fucoxanthin, peridinin etc.)</t>
+          <t>Niskin / pump sampler; CTD; fluorometer; phytoplankton microscopy + counting; autoanalyser for nutrients; TOC analyser</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Medium–High — HPLC partner lab + multi-month sampling</t>
+          <t>Medium — multi-cruise institutional campaign</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Annual / multi-season (14-month)</t>
+          <t>Multi-year (10 cruises 2009–2015)</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>ANOSIM / SIMPER for pigment community; size-class % change</t>
+          <t>ANOSIM / SIMPER for phytoplankton community contrast OF vs CA; species richness, Shannon-Wiener diversity, Pielou's evenness; percent change in physico-chemical variables</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>No — Paywalled (Elsevier)</t>
+          <t>No — Paywalled (Elsevier / Water Research)</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>Abstract + Methods (fetched)</t>
+          <t>Full PDF</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.envpol.2016.07.058</t>
+          <t>https://doi.org/10.1016/j.watres.2019.04.023</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>Reveals size-selective grazing that a bulk chlorophyll measurement would miss.</t>
+          <t>Here oyster farming helped mitigate thermal-discharge algal blooms; the old-vs-new-farm design controls for the thermal signal.</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
@@ -26674,9 +26610,9 @@
           <t>Original list</t>
         </is>
       </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>2 — Researcher</t>
+      <c r="W126" s="9" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
         </is>
       </c>
       <c r="X126" t="inlineStr">
@@ -26691,7 +26627,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>WQ 2.1.1 — Chlorophyll-a, WQ 2.1.2 — Microorganisms</t>
+          <t>WQ 1.2.1 — Dissolved oxygen, WQ 2.1.1 — Chlorophyll-a, WQ 2.1.2 — Microorganism / plankton community</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -26701,17 +26637,17 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>Hong Kong oyster (Magallana hongkongensis) / Pacific oyster</t>
+          <t>Chinese pleated oyster (Crassostrea plicatula)</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Raft / longline (oyster rafts)</t>
+          <t>Raft / longline (oyster ropes on rafts)</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr">
         <is>
-          <t>Single bay</t>
+          <t>Single farm (paired OF + CA in same bay)</t>
         </is>
       </c>
       <c r="AE126" t="inlineStr">
@@ -26726,7 +26662,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>Plankton sampling, Pigment HPLC</t>
+          <t>Water chemistry, Plankton sampling</t>
         </is>
       </c>
       <c r="AH126" t="inlineStr">
@@ -26746,17 +26682,17 @@
       </c>
       <c r="AK126" s="16" t="inlineStr">
         <is>
-          <t>To fingerprint an oyster farm's effect on phytoplankton by size and type, sample a farmed area and a reference area over a full seasonal cycle, size-fractionate the water (for example through 20, 2.7 and 0.7 um) and analyse diagnostic pigments by HPLC (chlorophyll-a plus marker pigments such as fucoxanthin and peridinin). Compare pigment communities with ANOSIM/SIMPER and quantify chlorophyll reduction per size class; this reveals size-selective grazing that a bulk chlorophyll measurement would miss.</t>
+          <t>To attribute changes in phytoplankton biomass and community to an oyster farm, sample paired stations at the farm centre and in a control area a few hundred metres to about 1 km outside, at surface and bottom, repeated across seasons (ideally spanning years, and comparing an old and a relocated farm for causal weight). Collect water with Niskin bottles; measure DO by Winkler titration and transparency by Secchi, and take frozen samples for nutrients (0.45 um filtered), total organic carbon and suspended solids. Size-fractionate chlorophyll-a (&gt;20, 2-20, &lt;2 um) by sequential filtration and read on a fluorometer after acetone extraction, and measure pheopigments (chl-a degradation products) as a grazing indicator; settle and count phytoplankton (at least 300 units) under a microscope for richness, Shannon and Pielou indices. Compare farm versus control with two-way ANOVA (or Mann-Whitney) and ANOSIM on log-transformed Bray-Curtis data, and correlate the biomass reduction with environmental drivers.</t>
         </is>
       </c>
       <c r="AL126" s="17" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AM126" s="18" t="inlineStr">
         <is>
-          <t>jiang_2016</t>
+          <t>jiang_2019</t>
         </is>
       </c>
       <c r="AN126" s="19" t="n"/>
@@ -26764,46 +26700,46 @@
       <c r="AP126" s="19" t="n"/>
       <c r="AQ126" s="16" t="inlineStr">
         <is>
-          <t>Size-Selective Phytoplankton-Depletion Fingerprint (HPLC Pigments)</t>
+          <t>Attributing Phytoplankton Change to an Oyster Farm (Size-Fractionated)</t>
         </is>
       </c>
       <c r="AR126" s="16" t="inlineStr">
         <is>
-          <t>Jiang, Tao; Chen, Feiyu; Yu, Zonghe; Lu, Lin; Wang, Zhaohui</t>
+          <t>Jiang, Zhibing; Du, Ping; Liao, Yibo; Liu, Qiang; Chen, Quanzhen; Shou, Lu; Zeng, Jiangning; Chen, Jianfang</t>
         </is>
       </c>
       <c r="AS126" s="16" t="inlineStr">
         <is>
-          <t>Different Jiang from R43/R126 (Z-B Jiang group) — this is Tao Jiang's group, focused on South China Sea / Daya Bay. Methodologically important for showing size-selective grazing fingerprint in pigment data — useful for MEL practitioners designing chl-a indicator measurements where filtering signal must be distinguished from background community shifts. Sub-rule 1a-adjacent framing: HPLC pigment chemotaxonomy complements but does not replace tissue %N bioextraction.</t>
+          <t>Important real-world paper showing oyster farming as a mitigation tool for thermal-discharge-induced algal blooms in a eutrophic subtropical bay. Confounded by thermal-discharge factor but design (OF vs CA in same thermal envelope) controls for that. After culture-raft removal, no significant differences between former-OF and CA — direct evidence the effect is the farming activity itself. Companion to Jiang 2012 (v15 R43), Jiang 2016 (#38 = R128), Jiang 2019a/b further work. Strong reference for MEL practitioners thinking about bivalve farming as ecological-restoration intervention. | v1.4 refinement: WQ 1.2.1 narrowed to DO (paper lists oxygen among measured physico-chemical variables).</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Rahman, M. A., et al.</t>
+          <t>Jiang, T., et al.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Analysis of the seasonal impact of three marine bivalves on seston particles in water column</t>
+          <t>Size-dependent depletion and community disturbance of phytoplankton under intensive oyster mariculture based on HPLC pigment analysis in Daya Bay, South China Sea</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Journal of Experimental Marine Biology and Ecology</t>
+          <t>Environmental Pollution</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>522</v>
+        <v>219</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>151251</t>
+          <t>804-814</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -26812,22 +26748,22 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Comparative laboratory + field food-selectivity and clearance-rate study of three sympatric bivalves — Pacific oyster (Magallana / Crassostrea gigas), Mediterranean mussel (Mytilus galloprovincialis), and native mud cockle (Katelysia rhytiphora) — on natural seston particle assemblages from Coffin Bay (South Australia). Particles measured 4–14 µm range; capture efficiency higher for larger particles (8–14 µm); seasonal CE/CR variation. Findings: oyster + mussel utilise similar food (phytoplankton); cockles graze a broader range (including detritus + bacteria). Maps to MEL WQ 2.1.1 (seston / chl-a) and WQ 2.1.2 (microorganism / particle community composition).</t>
+          <t>14-month investigation in Daya Bay, South China Sea, comparing intensive-oyster-farming area to reference area using HPLC size-fractionated phytopigments (chl-a, fucoxanthin, peridinin, and other diagnostic pigments). Filtering effect of oysters on phytoplankton biomass quantified size-class by size-class: ~60% total chl-a reduction in farming area vs reference; depletion concentrated in micro-sized (&gt;20 µm) fractions; nano-sized (2.7–20 µm) less affected. Community disturbance documented via pigment-based community shifts. Maps to MEL WQ 2.1.1 (chl-a + size-fractionated), WQ 2.1.2 (community composition via pigments).</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Protocol (paired laboratory + field clearance-rate / capture-efficiency assays on natural seston)</t>
+          <t>Protocol (HPLC size-fractionated phytopigment community + biomass analysis)</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Partial for MEL — clearance-rate methodology is rigorous for understanding physiological filtering, but the paper's primary deliverable is bivalve physiology not direct WQ-indicator measurement.</t>
+          <t>Yes — HPLC pigment chemotaxonomy is a robust, quantitative approach for community shifts; 14-month duration captures seasonal cycles.</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>No — laboratory clearance-rate methodology is research-only.</t>
+          <t>No — HPLC pigment analysis is research-only.</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -26837,22 +26773,22 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Flow-through clearance-rate chambers; Coulter counter / flow cytometer for particle size; chl-a fluorometer</t>
+          <t>Size-fractionation filtration (0.7, 2.7, 20 µm); HPLC for diagnostic pigments (chl-a, fucoxanthin, peridinin etc.)</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Medium — specialised flow-through setup + particle-counting instrumentation</t>
+          <t>Medium–High — HPLC partner lab + multi-month sampling</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Multi-season</t>
+          <t>Annual / multi-season (14-month)</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>ANOVA across species + seasons; capture efficiency vs particle-size regressions</t>
+          <t>ANOSIM / SIMPER for pigment community; size-class % change</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -26867,12 +26803,12 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jembe.2019.151251</t>
+          <t>https://doi.org/10.1016/j.envpol.2016.07.058</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>Primarily physiology, but yields the per-species clearance rates needed to parameterise carrying-capacity models.</t>
+          <t>Reveals size-selective grazing that a bulk chlorophyll measurement would miss.</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
@@ -26897,27 +26833,27 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>WQ 1.3.1 — Rate of water filtration (clearance-rate assay), WQ 2.1.1 — Chlorophyll-a, WQ 2.1.2 — Microorganism / plankton community</t>
+          <t>WQ 2.1.1 — Chlorophyll-a, WQ 2.1.2 — Microorganisms</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>Temperate Pacific</t>
+          <t>Subtropical Pacific</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>Pacific oyster (Crassostrea / Magallana gigas), Mediterranean mussel (Mytilus galloprovincialis), Mud cockle (Katelysia rhytiphora)</t>
+          <t>Hong Kong oyster (Magallana hongkongensis) / Pacific oyster</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Bottom culture / longline (mixed)</t>
+          <t>Raft / longline (oyster rafts)</t>
         </is>
       </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>Single bay (Coffin Bay, SA)</t>
+          <t>Single bay</t>
         </is>
       </c>
       <c r="AE127" t="inlineStr">
@@ -26927,12 +26863,12 @@
       </c>
       <c r="AF127" t="inlineStr">
         <is>
-          <t>Monoculture (sympatric species comparison)</t>
+          <t>Monoculture</t>
         </is>
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>Clearance-rate assay, Plankton sampling</t>
+          <t>Plankton sampling, Pigment HPLC</t>
         </is>
       </c>
       <c r="AH127" t="inlineStr">
@@ -26952,7 +26888,7 @@
       </c>
       <c r="AK127" s="16" t="inlineStr">
         <is>
-          <t>This is primarily a physiological method but yields filtering parameters useful for water-quality modelling: measure clearance rate and particle-capture efficiency of each bivalve species on natural seston in flow-through chambers, characterising the particle field by size (Coulter counter or flow cytometer) and chlorophyll. Comparing species and seasons gives the species-specific clearance rates needed to parameterise mass-balance and carrying-capacity models, rather than a direct field water-quality measurement.</t>
+          <t>To fingerprint an oyster farm's effect on phytoplankton by size and type, sample a farmed area and a reference area over a full seasonal cycle, size-fractionate the water (for example through 20, 2.7 and 0.7 um) and analyse diagnostic pigments by HPLC (chlorophyll-a plus marker pigments such as fucoxanthin and peridinin). Compare pigment communities with ANOSIM/SIMPER and quantify chlorophyll reduction per size class; this reveals size-selective grazing that a bulk chlorophyll measurement would miss.</t>
         </is>
       </c>
       <c r="AL127" s="17" t="inlineStr">
@@ -26962,7 +26898,7 @@
       </c>
       <c r="AM127" s="18" t="inlineStr">
         <is>
-          <t>rahman_2020</t>
+          <t>jiang_2016</t>
         </is>
       </c>
       <c r="AN127" s="19" t="n"/>
@@ -26970,67 +26906,70 @@
       <c r="AP127" s="19" t="n"/>
       <c r="AQ127" s="16" t="inlineStr">
         <is>
-          <t>Species-Specific Bivalve Filtration Parameters (Seston/Chlorophyll Chambers)</t>
+          <t>Size-Selective Phytoplankton-Depletion Fingerprint (HPLC Pigments)</t>
         </is>
       </c>
       <c r="AR127" s="16" t="inlineStr">
         <is>
-          <t>Rahman, M A; Henderson, S; Miller-Ezzy, P A; Li, X X; Qin, J G</t>
+          <t>Jiang, Tao; Chen, Feiyu; Yu, Zonghe; Lu, Lin; Wang, Zhaohui</t>
         </is>
       </c>
       <c r="AS127" s="16" t="inlineStr">
         <is>
-          <t>Sub-rule 1b boundary case — primarily a physiology paper, but the seston-particle measurements and chl-a depletion in chambers provide MEL-relevant quantification of filtering capacity per species. Useful for parameterising mass-balance / carrying-capacity models that depend on species-specific clearance rates. Coffin Bay site connects to broader South Australian shellfish industry. | v1.4 refinement: Added WQ 1.3.1 (Rate of water filtration) — clearance-rate methodology is mollusc-specific WQ 1.3.1 indicator; v1.4 addition. CRs measured per species across natural seston assemblages.</t>
+          <t>Different Jiang from R43/R126 (Z-B Jiang group) — this is Tao Jiang's group, focused on South China Sea / Daya Bay. Methodologically important for showing size-selective grazing fingerprint in pigment data — useful for MEL practitioners designing chl-a indicator measurements where filtering signal must be distinguished from background community shifts. Sub-rule 1a-adjacent framing: HPLC pigment chemotaxonomy complements but does not replace tissue %N bioextraction.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Ysebaert, T., et al.</t>
+          <t>Rahman, M. A., et al.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Habitat modification and coastal protection by ecosystem-engineering reef-building bivalves</t>
+          <t>Analysis of the seasonal impact of three marine bivalves on seston particles in water column</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Goods and Services of Marine Bivalves (book; eds. Smaal, Ferreira, Grant, Petersen, Strand)</t>
-        </is>
+          <t>Journal of Experimental Marine Biology and Ecology</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>522</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>253-273</t>
+          <t>151251</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Springer (Open Access)</t>
+          <t>Elsevier</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Synthesis chapter on ecosystem-engineering effects of reef-building bivalves — oysters and mussels — on intertidal/subtidal coastal environments. Documents how 3D bivalve reef structures alter local hydrodynamics and sediment-morphology far beyond the reef boundary (up to hundreds of metres), provide habitat for associated species, and contribute to shoreline stabilisation + erosion control. Two case studies: (1) Eastern oyster (Crassostrea virginica) reefs for shoreline protection in coastal Alabama, USA; (2) Crassostrea gigas reefs as protection against tidal flat erosion in the Oosterschelde, The Netherlands (Walles 2015 work). Argued as nature-based solutions for climate adaptation. Maps to MEL H&amp;B 1.1.1 (epibiota — reef structures), H&amp;B 1.4.1 (sediment biogeochemistry / dynamics), H&amp;B 2.1.1 (community composition supported by reef structure).</t>
+          <t>Comparative laboratory + field food-selectivity and clearance-rate study of three sympatric bivalves — Pacific oyster (Magallana / Crassostrea gigas), Mediterranean mussel (Mytilus galloprovincialis), and native mud cockle (Katelysia rhytiphora) — on natural seston particle assemblages from Coffin Bay (South Australia). Particles measured 4–14 µm range; capture efficiency higher for larger particles (8–14 µm); seasonal CE/CR variation. Findings: oyster + mussel utilise similar food (phytoplankton); cockles graze a broader range (including detritus + bacteria). Maps to MEL WQ 2.1.1 (seston / chl-a) and WQ 2.1.2 (microorganism / particle community composition).</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Reference (synthesis chapter with embedded case-study protocols)</t>
+          <t>Protocol (paired laboratory + field clearance-rate / capture-efficiency assays on natural seston)</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Yes — the embedded case studies follow standard reef-establishment + monitoring protocols; the chapter is a methodological + framework synthesis useful for restoration practitioners.</t>
+          <t>Partial for MEL — clearance-rate methodology is rigorous for understanding physiological filtering, but the paper's primary deliverable is bivalve physiology not direct WQ-indicator measurement.</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Partial — reef establishment is operational; structured monitoring requires partnership.</t>
+          <t>No — laboratory clearance-rate methodology is research-only.</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -27040,42 +26979,42 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>Reef-building substrates (oyster castles, gabion bags, reef balls); standard habitat-monitoring (epibiota cover, infaunal cores, RTK elevation surveys)</t>
+          <t>Flow-through clearance-rate chambers; Coulter counter / flow cytometer for particle size; chl-a fluorometer</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Medium–High — multi-year operational monitoring</t>
+          <t>Medium — specialised flow-through setup + particle-counting instrumentation</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Multi-year</t>
+          <t>Multi-season</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>Before/after + reef/control contrasts; sediment elevation modelling</t>
+          <t>ANOVA across species + seasons; capture efficiency vs particle-size regressions</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>Yes — Open access (Springer SpringerOpen)</t>
+          <t>No — Paywalled (Elsevier)</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>Abstract + DOI metadata</t>
+          <t>Abstract + Methods (fetched)</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/978-3-319-96776-9_13</t>
+          <t>https://doi.org/10.1016/j.jembe.2019.151251</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>A framework reference for restoration-oriented reef monitoring and coastal-protection benefit.</t>
+          <t>Primarily physiology, but yields the per-species clearance rates needed to parameterise carrying-capacity models.</t>
         </is>
       </c>
       <c r="V128" t="inlineStr">
@@ -27083,7 +27022,7 @@
           <t>Original list</t>
         </is>
       </c>
-      <c r="W128" s="7" t="inlineStr">
+      <c r="W128" t="inlineStr">
         <is>
           <t>2 — Researcher</t>
         </is>
@@ -27095,32 +27034,32 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>Habitat &amp; Biodiversity, Climate Change</t>
+          <t>Water Quality</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>CC 3.1.1 — Wave attenuation / coastal protection, H&amp;B 1.1.1 — Epibiota, H&amp;B 1.4.1 — Sediment biogeochemistry, H&amp;B 2.1.1 — Community composition</t>
+          <t>WQ 1.3.1 — Rate of water filtration (clearance-rate assay), WQ 2.1.1 — Chlorophyll-a, WQ 2.1.2 — Microorganism / plankton community</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>Temperate Atlantic + Subtropical Atlantic/Gulf</t>
+          <t>Temperate Pacific</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>Eastern oyster (Crassostrea virginica), Pacific oyster (Crassostrea / Magallana gigas), Blue mussel (Mytilus edulis)</t>
+          <t>Pacific oyster (Crassostrea / Magallana gigas), Mediterranean mussel (Mytilus galloprovincialis), Mud cockle (Katelysia rhytiphora)</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Reef / on-bottom structure</t>
+          <t>Bottom culture / longline (mixed)</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr">
         <is>
-          <t>Multi-site (synthesis of 2 case studies)</t>
+          <t>Single bay (Coffin Bay, SA)</t>
         </is>
       </c>
       <c r="AE128" t="inlineStr">
@@ -27130,12 +27069,12 @@
       </c>
       <c r="AF128" t="inlineStr">
         <is>
-          <t>Monoculture (restoration / conservation aquaculture)</t>
+          <t>Monoculture</t>
         </is>
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>Visual survey, Benthic infauna sampling, Sediment sampling</t>
+          <t>Clearance-rate assay, Plankton sampling</t>
         </is>
       </c>
       <c r="AH128" t="inlineStr">
@@ -27145,27 +27084,27 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>Intertidal / very shallow (&lt; 2 m)</t>
+          <t>Shallow nearshore (2–10 m)</t>
         </is>
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>Exposed (deliberately, for coastal-protection function)</t>
+          <t>Sheltered</t>
         </is>
       </c>
       <c r="AK128" s="16" t="inlineStr">
         <is>
-          <t>This synthesis documents how reef-building bivalves reshape local hydrodynamics and sediment morphology (sometimes hundreds of metres beyond the reef), provide habitat and deliver coastal-protection services. It embeds standard reef-establishment and monitoring approaches (epibiota cover, infaunal cores, RTK sediment-elevation surveys, before/after reef-versus-control contrasts). Use it as a framework reference for restoration-oriented reef monitoring and coastal-protection benefit.</t>
+          <t>This is primarily a physiological method but yields filtering parameters useful for water-quality modelling: measure clearance rate and particle-capture efficiency of each bivalve species on natural seston in flow-through chambers, characterising the particle field by size (Coulter counter or flow cytometer) and chlorophyll. Comparing species and seasons gives the species-specific clearance rates needed to parameterise mass-balance and carrying-capacity models, rather than a direct field water-quality measurement.</t>
         </is>
       </c>
       <c r="AL128" s="17" t="inlineStr">
         <is>
-          <t>Ref</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="AM128" s="18" t="inlineStr">
         <is>
-          <t>ysebaert_2018</t>
+          <t>rahman_2020</t>
         </is>
       </c>
       <c r="AN128" s="19" t="n"/>
@@ -27173,70 +27112,67 @@
       <c r="AP128" s="19" t="n"/>
       <c r="AQ128" s="16" t="inlineStr">
         <is>
-          <t>Bivalve-Reef Coastal Protection &amp; Ecosystem Engineering (Synthesis)</t>
+          <t>Species-Specific Bivalve Filtration Parameters (Seston/Chlorophyll Chambers)</t>
         </is>
       </c>
       <c r="AR128" s="16" t="inlineStr">
         <is>
-          <t>Ysebaert, Tom; Walles, Brenda; Haner, Judy; Hancock, Boze</t>
+          <t>Rahman, M A; Henderson, S; Miller-Ezzy, P A; Li, X X; Qin, J G</t>
         </is>
       </c>
       <c r="AS128" s="16" t="inlineStr">
         <is>
-          <t>Distinct from v14 R80 Ysebaert 2009 (Tom Ysebaert's earlier ESM/J Sea Res paper on different topic) — new row added. This 2018 chapter is one of the most cited syntheses on bivalve-reef coastal-protection ecosystem services. Companion to Walles 2015 (Oosterschelde) and to the Alabama TNC oyster-reef program. Useful framework reference for MEL practitioners assessing H&amp;B + coastal-protection indicators. | v1.4 refinement: Added CC 3.1.1 (Wave attenuation / coastal protection) — chapter's primary deliverable is the ecosystem-engineering coastal-protection function of reef-building bivalves; v1.4 added this indicator (mollusc CC Goal 3). Y now multi-tagged H&amp;B + CC.  [v21 retier] Reference cannot hold an execution tier (T3/T4); reclassified to T2 as a usable framework synthesis.</t>
+          <t>Sub-rule 1b boundary case — primarily a physiology paper, but the seston-particle measurements and chl-a depletion in chambers provide MEL-relevant quantification of filtering capacity per species. Useful for parameterising mass-balance / carrying-capacity models that depend on species-specific clearance rates. Coffin Bay site connects to broader South Australian shellfish industry. | v1.4 refinement: Added WQ 1.3.1 (Rate of water filtration) — clearance-rate methodology is mollusc-specific WQ 1.3.1 indicator; v1.4 addition. CRs measured per species across natural seston assemblages.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Goedefroo, N., et al.</t>
+          <t>Ysebaert, T., et al.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Nature-based solutions in a sandy foreshore: A biological assessment of a longline mussel aquaculture technique to establish subtidal reefs</t>
+          <t>Habitat modification and coastal protection by ecosystem-engineering reef-building bivalves</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Ecological Engineering</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>185</v>
+          <t>Goods and Services of Marine Bivalves (book; eds. Smaal, Ferreira, Grant, Petersen, Strand)</t>
+        </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>106807</t>
+          <t>253-273</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Elsevier</t>
+          <t>Springer (Open Access)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Biological assessment of the Belgian 'Coastbusters' pilot project (2017–2020): longline mussel (Mytilus edulis) aquaculture technique repurposed as a nature-based solution for coastal erosion protection in the Belgian Part of the North Sea. Subtidal mussel reefs established via filamentous + non-filamentous dropper lines of different materials (hemp/coconut/sisal/jute natural fibres, biobased lines, Deltaflex). Biological aspects assessed: mussel survival and biomass on dropper lines, macrobenthos sampling around the structures, sediment characteristics. Key findings: mussel beds developed during summer–fall 2019; mostly lost in winter (predation + storms); no short-term macrobenthos impact detected. Maps to MEL H&amp;B 1.1.1 (epibiota), H&amp;B 1.3.1 (infauna), H&amp;B 2.1.1 (community composition).</t>
+          <t>Synthesis chapter on ecosystem-engineering effects of reef-building bivalves — oysters and mussels — on intertidal/subtidal coastal environments. Documents how 3D bivalve reef structures alter local hydrodynamics and sediment-morphology far beyond the reef boundary (up to hundreds of metres), provide habitat for associated species, and contribute to shoreline stabilisation + erosion control. Two case studies: (1) Eastern oyster (Crassostrea virginica) reefs for shoreline protection in coastal Alabama, USA; (2) Crassostrea gigas reefs as protection against tidal flat erosion in the Oosterschelde, The Netherlands (Walles 2015 work). Argued as nature-based solutions for climate adaptation. Maps to MEL H&amp;B 1.1.1 (epibiota — reef structures), H&amp;B 1.4.1 (sediment biogeochemistry / dynamics), H&amp;B 2.1.1 (community composition supported by reef structure).</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Protocol (NBS / mussel-reef pilot with biological monitoring program)</t>
+          <t>Reference (synthesis chapter with embedded case-study protocols)</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Yes — 3-year pilot with multi-material dropper-line comparison + paired macrobenthos sampling; establishes both technical feasibility and ecological-monitoring template.</t>
+          <t>Yes — the embedded case studies follow standard reef-establishment + monitoring protocols; the chapter is a methodological + framework synthesis useful for restoration practitioners.</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Partial — line deployment is operational; macrobenthos sampling + biological assessment require partnership.</t>
+          <t>Partial — reef establishment is operational; structured monitoring requires partnership.</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -27246,42 +27182,42 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>Longline mussel aquaculture infrastructure (multi-material dropper lines); van Veen grab for macrobenthos; CTD; sediment grain-size analysis</t>
+          <t>Reef-building substrates (oyster castles, gabion bags, reef balls); standard habitat-monitoring (epibiota cover, infaunal cores, RTK elevation surveys)</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Medium–High — multi-year pilot infrastructure + biological monitoring</t>
+          <t>Medium–High — multi-year operational monitoring</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Multi-year (3 yr pilot)</t>
+          <t>Multi-year</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>Before/after + reef/control contrasts; macrobenthos diversity + abundance; cross-material comparison</t>
+          <t>Before/after + reef/control contrasts; sediment elevation modelling</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>Yes — Open access via ILVO institutional deposit; journal article paywalled</t>
+          <t>Yes — Open access (Springer SpringerOpen)</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>Abstract + Methods (fetched)</t>
+          <t>Abstract + DOI metadata</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.ecoleng.2022.106807</t>
+          <t>https://doi.org/10.1007/978-3-319-96776-9_13</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>Tests whether the mussel-farming technique can be redirected from harvest to coastal protection.</t>
+          <t>A framework reference for restoration-oriented reef monitoring and coastal-protection benefit.</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
@@ -27289,9 +27225,9 @@
           <t>Original list</t>
         </is>
       </c>
-      <c r="W129" s="9" t="inlineStr">
-        <is>
-          <t>3 — Partnership</t>
+      <c r="W129" s="7" t="inlineStr">
+        <is>
+          <t>2 — Researcher</t>
         </is>
       </c>
       <c r="X129" t="inlineStr">
@@ -27306,27 +27242,27 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>CC 3.1.1 — Wave attenuation / coastal protection, H&amp;B 1.1.1 — Epibiota, H&amp;B 1.3.1 — Infauna, H&amp;B 2.1.1 — Community composition</t>
+          <t>CC 3.1.1 — Wave attenuation / coastal protection, H&amp;B 1.1.1 — Epibiota, H&amp;B 1.4.1 — Sediment biogeochemistry, H&amp;B 2.1.1 — Community composition</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>Temperate Atlantic</t>
+          <t>Temperate Atlantic + Subtropical Atlantic/Gulf</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>Blue mussel (Mytilus edulis)</t>
+          <t>Eastern oyster (Crassostrea virginica), Pacific oyster (Crassostrea / Magallana gigas), Blue mussel (Mytilus edulis)</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Longline / suspended (with dropper lines to seabed)</t>
+          <t>Reef / on-bottom structure</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr">
         <is>
-          <t>Single farm (pilot)</t>
+          <t>Multi-site (synthesis of 2 case studies)</t>
         </is>
       </c>
       <c r="AE129" t="inlineStr">
@@ -27341,7 +27277,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>Benthic infauna sampling, Visual survey</t>
+          <t>Visual survey, Benthic infauna sampling, Sediment sampling</t>
         </is>
       </c>
       <c r="AH129" t="inlineStr">
@@ -27351,27 +27287,27 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>Subtidal sandy foreshore (2–10 m)</t>
+          <t>Intertidal / very shallow (&lt; 2 m)</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>Mixed exposure</t>
+          <t>Exposed (deliberately, for coastal-protection function)</t>
         </is>
       </c>
       <c r="AK129" s="16" t="inlineStr">
         <is>
-          <t>To evaluate a longline-mussel nature-based solution for its reef-building and biodiversity value, monitor the dropper-line community, the surrounding seabed and the mussels themselves using a before/after control-impact design. Sample seabed macrobenthos with a Van Veen grab (0.1 m2, rinsed over 1 mm mesh, fixed in formaldehyde, rose-bengal stained) at fixed reef stations and control stations about 50 m outside, before installation and repeatedly after. Retrieve dropper-line segments to assess the biofouling community (top versus bottom 50 cm, rinsed over a 0.5 mm sieve, subsampled by quartering) and mussel metrics - size distribution, primary versus secondary attachment (a detachment-risk ratio), and condition. Add qualitative diver-video transects along the line for reef state and epifauna, and analyse macrobenthos richness and diversity with generalised or linear mixed models (site fixed, time random) plus SIMPER for the taxa driving community differences.</t>
+          <t>This synthesis documents how reef-building bivalves reshape local hydrodynamics and sediment morphology (sometimes hundreds of metres beyond the reef), provide habitat and deliver coastal-protection services. It embeds standard reef-establishment and monitoring approaches (epibiota cover, infaunal cores, RTK sediment-elevation surveys, before/after reef-versus-control contrasts). Use it as a framework reference for restoration-oriented reef monitoring and coastal-protection benefit.</t>
         </is>
       </c>
       <c r="AL129" s="17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Ref</t>
         </is>
       </c>
       <c r="AM129" s="18" t="inlineStr">
         <is>
-          <t>goedefroo_2022</t>
+          <t>ysebaert_2018</t>
         </is>
       </c>
       <c r="AN129" s="19" t="n"/>
@@ -27379,46 +27315,46 @@
       <c r="AP129" s="19" t="n"/>
       <c r="AQ129" s="16" t="inlineStr">
         <is>
-          <t>Longline-Mussel Nature-Based Solution: Reef &amp; Biodiversity Assessment (BACI)</t>
+          <t>Bivalve-Reef Coastal Protection &amp; Ecosystem Engineering (Synthesis)</t>
         </is>
       </c>
       <c r="AR129" s="16" t="inlineStr">
         <is>
-          <t>Goedefroo, Nanou; Benham, Peter; Debusschere, Elisabeth; Deneudt, Klaas; Mascart, Thibaud; Semeraro, Alexia; Sterckx, Tomas; Van Hoey, Gert</t>
+          <t>Ysebaert, Tom; Walles, Brenda; Haner, Judy; Hancock, Boze</t>
         </is>
       </c>
       <c r="AS129" s="16" t="inlineStr">
         <is>
-          <t>Pilot-project paper for the Coastbusters NBS program (Belgium). Important methodological contribution: testing whether longline mussel aquaculture technique can be redirected from harvest goal to coastal-protection goal. Companion to Coastbusters 2.0 (Boulenger 2023 ff.). Useful for MEL practitioners thinking about repurposing aquaculture infrastructure for habitat + coastal-protection services. | v1.4 refinement: Added CC 3.1.1 — explicit nature-based-solution paper for coastal erosion mitigation off Belgian coast; matches mollusc CC Obj 3.1 directly. Y now multi-tagged H&amp;B + CC.</t>
+          <t>Distinct from v14 R80 Ysebaert 2009 (Tom Ysebaert's earlier ESM/J Sea Res paper on different topic) — new row added. This 2018 chapter is one of the most cited syntheses on bivalve-reef coastal-protection ecosystem services. Companion to Walles 2015 (Oosterschelde) and to the Alabama TNC oyster-reef program. Useful framework reference for MEL practitioners assessing H&amp;B + coastal-protection indicators. | v1.4 refinement: Added CC 3.1.1 (Wave attenuation / coastal protection) — chapter's primary deliverable is the ecosystem-engineering coastal-protection function of reef-building bivalves; v1.4 added this indicator (mollusc CC Goal 3). Y now multi-tagged H&amp;B + CC.  [v21 retier] Reference cannot hold an execution tier (T3/T4); reclassified to T2 as a usable framework synthesis.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Lin, J., et al.</t>
+          <t>Goedefroo, N., et al.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Hydrodynamic effect of a large offshore mussel suspended aquaculture farm</t>
+          <t>Nature-based solutions in a sandy foreshore: A biological assessment of a longline mussel aquaculture technique to establish subtidal reefs</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Aquaculture</t>
+          <t>Ecological Engineering</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>451</v>
+        <v>185</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>147-155</t>
+          <t>106807</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -27427,22 +27363,22 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Field observational + ADCP study of tidal-current modification by a large mussel (Mytilus galloprovincialis) suspended longline aquaculture farm off Gouqi Island, outside the Changjiang (Yangtze) Estuary, China. Surface tidal current velocity reduced 75–90% in top 3.5 m, ~45% at bottom. Surface hydraulic roughness z₀s ≈ 1.4–1.9 m (20× bottom); surface drag coefficient C500 ≈ 0.087–0.169 (3.5–7.5× bottom). Downwelling induced. SURFACE CHL-A FLUORESCENCE depleted to &lt; 1.0 µg L⁻¹ INSIDE the farm — 80% less than outside — quantifying carrying-capacity implications. Maps narrowly to MEL WQ 2.1.1 (chl-a depletion measurement).</t>
+          <t>Biological assessment of the Belgian 'Coastbusters' pilot project (2017–2020): longline mussel (Mytilus edulis) aquaculture technique repurposed as a nature-based solution for coastal erosion protection in the Belgian Part of the North Sea. Subtidal mussel reefs established via filamentous + non-filamentous dropper lines of different materials (hemp/coconut/sisal/jute natural fibres, biobased lines, Deltaflex). Biological aspects assessed: mussel survival and biomass on dropper lines, macrobenthos sampling around the structures, sediment characteristics. Key findings: mussel beds developed during summer–fall 2019; mostly lost in winter (predation + storms); no short-term macrobenthos impact detected. Maps to MEL H&amp;B 1.1.1 (epibiota), H&amp;B 1.3.1 (infauna), H&amp;B 2.1.1 (community composition).</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Protocol (paired in-farm vs out-of-farm ADCP + CTD + chl-a fluorescence vertical profiles)</t>
+          <t>Protocol (NBS / mussel-reef pilot with biological monitoring program)</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Partial — chl-a measurement is direct WQ 2.1.1; primary deliverable is physical-oceanography characterisation of farm-induced flow modification.</t>
+          <t>Yes — 3-year pilot with multi-material dropper-line comparison + paired macrobenthos sampling; establishes both technical feasibility and ecological-monitoring template.</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Partial — ADCP/CTD deployment is operational for trained farmers + technicians.</t>
+          <t>Partial — line deployment is operational; macrobenthos sampling + biological assessment require partnership.</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -27452,42 +27388,42 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>ADCP (current profiling); CTD with chl-a fluorometer; salinity / temperature profiling</t>
+          <t>Longline mussel aquaculture infrastructure (multi-material dropper lines); van Veen grab for macrobenthos; CTD; sediment grain-size analysis</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Medium — ADCP + CTD suite is institutional</t>
+          <t>Medium–High — multi-year pilot infrastructure + biological monitoring</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Multi-day campaign (covering tidal cycles)</t>
+          <t>Multi-year (3 yr pilot)</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>Cross-site contrasts (in vs out of farm); friction-velocity + roughness calculations from log-fit profiles</t>
+          <t>Before/after + reef/control contrasts; macrobenthos diversity + abundance; cross-material comparison</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>No — Paywalled (Elsevier)</t>
+          <t>Yes — Open access via ILVO institutional deposit; journal article paywalled</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>Full PDF</t>
+          <t>Abstract + Methods (fetched)</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.aquaculture.2015.08.039</t>
+          <t>https://doi.org/10.1016/j.ecoleng.2022.106807</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>Documents how a large suspended farm acts as a porous canopy that reduces flow and can strongly deplete chlorophyll.</t>
+          <t>Tests whether the mussel-farming technique can be redirected from harvest to coastal protection.</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
@@ -27507,32 +27443,32 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>Water Quality, Climate Change</t>
+          <t>Habitat &amp; Biodiversity, Climate Change</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>CC 3.1.1 — Wave attenuation / coastal protection (Sub-rule 1c), WQ 2.1.1 — Chlorophyll-a</t>
+          <t>CC 3.1.1 — Wave attenuation / coastal protection, H&amp;B 1.1.1 — Epibiota, H&amp;B 1.3.1 — Infauna, H&amp;B 2.1.1 — Community composition</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>Subtropical Pacific</t>
+          <t>Temperate Atlantic</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>Mediterranean mussel (Mytilus galloprovincialis)</t>
+          <t>Blue mussel (Mytilus edulis)</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Longline / suspended (offshore)</t>
+          <t>Longline / suspended (with dropper lines to seabed)</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr">
         <is>
-          <t>Single farm (large)</t>
+          <t>Single farm (pilot)</t>
         </is>
       </c>
       <c r="AE130" t="inlineStr">
@@ -27547,7 +27483,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>Water chemistry, Hydrodynamic measurement</t>
+          <t>Benthic infauna sampling, Visual survey</t>
         </is>
       </c>
       <c r="AH130" t="inlineStr">
@@ -27557,98 +27493,98 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>Offshore (deeper)</t>
+          <t>Subtidal sandy foreshore (2–10 m)</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>Exposed</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>To quantify how a large suspended mussel farm modifies local currents (needed to avoid over-estimating seston and nutrient supply, and hence carrying capacity), measure vertical current-velocity profiles inside and outside the culture ground and fit drag coefficients. Anchor an acoustic Doppler current profiler (ADCP) at stations inside and outside the farm and log the velocity profile in about 1 m vertical bins over at least a full tidal cycle (ideally a spring tide), and take CTD casts (temperature, salinity, chlorophyll-a fluorescence) inside and outside to capture the food proxy. Because the surface canopy of dropper lines adds friction like a rough bed, fit the measured velocity profiles with a logarithmic (law-of-the-wall) model to derive both a surface drag coefficient (referenced to a set depth below the surface) and a bottom drag coefficient, using least-squares across many profiles. The resulting drag parameters quantify the farm's flow reduction and can be fed into hydrodynamic and carrying-capacity models.</t>
-        </is>
-      </c>
-      <c r="AL130" t="inlineStr">
+          <t>Mixed exposure</t>
+        </is>
+      </c>
+      <c r="AK130" s="16" t="inlineStr">
+        <is>
+          <t>To evaluate a longline-mussel nature-based solution for its reef-building and biodiversity value, monitor the dropper-line community, the surrounding seabed and the mussels themselves using a before/after control-impact design. Sample seabed macrobenthos with a Van Veen grab (0.1 m2, rinsed over 1 mm mesh, fixed in formaldehyde, rose-bengal stained) at fixed reef stations and control stations about 50 m outside, before installation and repeatedly after. Retrieve dropper-line segments to assess the biofouling community (top versus bottom 50 cm, rinsed over a 0.5 mm sieve, subsampled by quartering) and mussel metrics - size distribution, primary versus secondary attachment (a detachment-risk ratio), and condition. Add qualitative diver-video transects along the line for reef state and epifauna, and analyse macrobenthos richness and diversity with generalised or linear mixed models (site fixed, time random) plus SIMPER for the taxa driving community differences.</t>
+        </is>
+      </c>
+      <c r="AL130" s="17" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
       <c r="AM130" s="18" t="inlineStr">
         <is>
-          <t>lin_2016</t>
+          <t>goedefroo_2022</t>
         </is>
       </c>
       <c r="AN130" s="19" t="n"/>
       <c r="AO130" s="19" t="n"/>
       <c r="AP130" s="19" t="n"/>
+      <c r="AQ130" s="16" t="inlineStr">
+        <is>
+          <t>Longline-Mussel Nature-Based Solution: Reef &amp; Biodiversity Assessment (BACI)</t>
+        </is>
+      </c>
       <c r="AR130" s="16" t="inlineStr">
         <is>
-          <t>Lin, Jun; Li, Chunyan; Zhang, Shouyu</t>
+          <t>Goedefroo, Nanou; Benham, Peter; Debusschere, Elisabeth; Deneudt, Klaas; Mascart, Thibaud; Semeraro, Alexia; Sterckx, Tomas; Van Hoey, Gert</t>
         </is>
       </c>
       <c r="AS130" s="16" t="inlineStr">
         <is>
-          <t>Foundational paper for documenting that suspended-bivalve farms act as porous physical canopies in the surface layer, reducing horizontal flow and inducing downwelling. The 80% chl-a depletion result is striking and matches the seston-depletion + carrying-capacity literature. Important for MEL practitioners: chl-a measurements 'inside' farms are physically distorted by reduced current — sampling design must account for canopy-induced vertical mixing. Companion to R125 Cugier 2010 (modelling), R110 Maar 2024 (modelling). | v1.4 refinement: Added CC 3.1.1 per Sub-rule 1c (v1.4) — paper measures canopy-induced flow modification which contributes to wave-energy attenuation by suspended bivalve farms; does not compute wave-decay coefficient directly, so retained under Sub-rule 1c with caveat. Y now multi-tagged WQ + CC. | v38: filled at High from pasted Methods (Lin); Source Read set to Full PDF.</t>
+          <t>Pilot-project paper for the Coastbusters NBS program (Belgium). Important methodological contribution: testing whether longline mussel aquaculture technique can be redirected from harvest goal to coastal-protection goal. Companion to Coastbusters 2.0 (Boulenger 2023 ff.). Useful for MEL practitioners thinking about repurposing aquaculture infrastructure for habitat + coastal-protection services. | v1.4 refinement: Added CC 3.1.1 — explicit nature-based-solution paper for coastal erosion mitigation off Belgian coast; matches mollusc CC Obj 3.1 directly. Y now multi-tagged H&amp;B + CC.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Shi, B., et al.</t>
+          <t>Lin, J., et al.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Influence of macrobenthos (Meretrix meretrix Linnaeus) on erosion-accretion processes in intertidal flats: A case study from a cultivation zone</t>
+          <t>Hydrodynamic effect of a large offshore mussel suspended aquaculture farm</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Journal of Geophysical Research: Biogeosciences</t>
+          <t>Aquaculture</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>125</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+        <v>451</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>e2019JG005345</t>
+          <t>147-155</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>AGU / Wiley</t>
+          <t>Elsevier</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Paired-site (cultivation zone vs adjacent bare flat) field investigation on the Rudong intertidal flat, Jiangsu Coast, China, quantifying the effect of high-density hard clam Meretrix meretrix (~137 ind. m⁻²) on bed erodibility, sediment-erosion thresholds, and erosion-accretion processes. Co-deployed instruments: ADV for turbulent flow velocity + bed-level change, SBE 26 Plus pressure sensors for wave-tide measurements, sediment-property + macrobenthos sampling. Found M. meretrix presence lowered critical erosion shear stress (~23.5% drop) — clams destabilise sediment under their cultivation density. Maps to MEL H&amp;B 1.4.1 (sediment biogeochemistry / dynamics).</t>
+          <t>Field observational + ADCP study of tidal-current modification by a large mussel (Mytilus galloprovincialis) suspended longline aquaculture farm off Gouqi Island, outside the Changjiang (Yangtze) Estuary, China. Surface tidal current velocity reduced 75–90% in top 3.5 m, ~45% at bottom. Surface hydraulic roughness z₀s ≈ 1.4–1.9 m (20× bottom); surface drag coefficient C500 ≈ 0.087–0.169 (3.5–7.5× bottom). Downwelling induced. SURFACE CHL-A FLUORESCENCE depleted to &lt; 1.0 µg L⁻¹ INSIDE the farm — 80% less than outside — quantifying carrying-capacity implications. Maps narrowly to MEL WQ 2.1.1 (chl-a depletion measurement).</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Protocol (paired-site hydrodynamic + sediment-erosion observation under bivalve cultivation)</t>
+          <t>Protocol (paired in-farm vs out-of-farm ADCP + CTD + chl-a fluorescence vertical profiles)</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Yes — synchronous hydrodynamic + sediment + macrobenthos measurements at paired sites with + without bivalve cultivation; standard erosion-threshold methodology.</t>
+          <t>Partial — chl-a measurement is direct WQ 2.1.1; primary deliverable is physical-oceanography characterisation of farm-induced flow modification.</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>No — research-grade instrumentation deployment (ADV, pressure sensors).</t>
+          <t>Partial — ADCP/CTD deployment is operational for trained farmers + technicians.</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -27658,27 +27594,27 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>ADV (acoustic Doppler velocimeter); SBE 26 Plus wave-tide recorder; grain-size + organic-content sediment analysis; benthic core sampling</t>
+          <t>ADCP (current profiling); CTD with chl-a fluorometer; salinity / temperature profiling</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Medium–High — research-grade hydrodynamic instrumentation</t>
+          <t>Medium — ADCP + CTD suite is institutional</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Multi-season (seasonal summer + winter comparison)</t>
+          <t>Multi-day campaign (covering tidal cycles)</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>Paired-site contrasts; critical shear-stress calculation; bed-level change time series</t>
+          <t>Cross-site contrasts (in vs out of farm); friction-velocity + roughness calculations from log-fit profiles</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>No — Paywalled (AGU / Wiley)</t>
+          <t>No — Paywalled (Elsevier)</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -27688,12 +27624,12 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1029/2019JG005345</t>
+          <t>https://doi.org/10.1016/j.aquaculture.2015.08.039</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>Counterintuitively, high-density burrowing, shell-protruding clams can lower the erosion threshold and destabilise the bed - the opposite of reef-builders.</t>
+          <t>Documents how a large suspended farm acts as a porous canopy that reduces flow and can strongly deplete chlorophyll.</t>
         </is>
       </c>
       <c r="V131" t="inlineStr">
@@ -27701,9 +27637,9 @@
           <t>Original list</t>
         </is>
       </c>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>2 — Researcher</t>
+      <c r="W131" s="9" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
         </is>
       </c>
       <c r="X131" t="inlineStr">
@@ -27713,12 +27649,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>Habitat &amp; Biodiversity, Climate Change</t>
+          <t>Water Quality, Climate Change</t>
         </is>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>CC 3.1.1 — Wave attenuation / coastal protection (counter-example, Sub-rule 1c), H&amp;B 1.4.1 — Sediment biogeochemistry</t>
+          <t>CC 3.1.1 — Wave attenuation / coastal protection (Sub-rule 1c), WQ 2.1.1 — Chlorophyll-a</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -27728,17 +27664,17 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>Hard clam (Meretrix meretrix)</t>
+          <t>Mediterranean mussel (Mytilus galloprovincialis)</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Intertidal bottom culture (seeded clam beds)</t>
+          <t>Longline / suspended (offshore)</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr">
         <is>
-          <t>Single site (paired cultivation vs control)</t>
+          <t>Single farm (large)</t>
         </is>
       </c>
       <c r="AE131" t="inlineStr">
@@ -27753,7 +27689,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>Sediment sampling, Hydrodynamic measurement, Benthic infauna sampling</t>
+          <t>Water chemistry, Hydrodynamic measurement</t>
         </is>
       </c>
       <c r="AH131" t="inlineStr">
@@ -27763,100 +27699,88 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>Intertidal / very shallow (&lt; 2 m)</t>
+          <t>Offshore (deeper)</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>Mixed exposure</t>
-        </is>
-      </c>
-      <c r="AK131" s="16" t="inlineStr">
-        <is>
-          <t>To measure how dense infaunal bivalves affect sediment stability, compare a cultivation zone with an adjacent bare flat, co-deploying an acoustic Doppler velocimeter for turbulent flow and a wave-tide recorder to derive bed shear stress, alongside sediment grain-size and organic-content analysis and benthic cores. Track bed-level change and compute the critical erosion shear stress at each site; note the counterintuitive result that high-density burrowing, shell-protruding clams can lower the erosion threshold and destabilise the bed rather than protect it - the opposite of reef-building bivalves.</t>
-        </is>
-      </c>
-      <c r="AL131" s="17" t="inlineStr">
-        <is>
-          <t>Med</t>
+          <t>Exposed</t>
         </is>
       </c>
       <c r="AM131" s="18" t="inlineStr">
         <is>
-          <t>shi_2020</t>
+          <t>lin_2016</t>
         </is>
       </c>
       <c r="AN131" s="19" t="n"/>
       <c r="AO131" s="19" t="n"/>
       <c r="AP131" s="19" t="n"/>
-      <c r="AQ131" s="16" t="inlineStr">
-        <is>
-          <t>Do Dense Infaunal Bivalves Stabilise or Erode Sediment?</t>
-        </is>
-      </c>
       <c r="AR131" s="16" t="inlineStr">
         <is>
-          <t>Shi, Benwei; Pratolongo, Paula D; Du, Yongfen; Li, Jiasheng; Yang, S L; Wu, Jihua; Xu, Kehui; Wang, Ya Ping</t>
+          <t>Lin, Jun; Li, Chunyan; Zhang, Shouyu</t>
         </is>
       </c>
       <c r="AS131" s="16" t="inlineStr">
         <is>
-          <t>Important paper for the COUNTERINTUITIVE finding that high-density bivalve cultivation can DESTABILISE rather than stabilise sediments (the opposite of reef-building bivalves in Ysebaert 2018 R129) — context matters: the action of clams burrowing + protruding their shells reduces critical erosion shear stress. Important for MEL practitioners using H&amp;B 1.4.1 sediment-dynamics indicators on clam-cultivation sites: cultivation may shift the system toward erosion. Companion to Shi 2021 (L&amp;O, typhoon-induced erosion at same site) and Li 2021 (Ecohydrology &amp; Hydrobiology, same site, ~23% threshold drop confirmed). | v1.4 refinement: Added CC 3.1.1 per Sub-rule 1c (v1.4) — sediment-erosion threshold under clam cultivation is directly relevant to mollusc CC Obj 3.1 (coastal erosion), as a COUNTER-EXAMPLE showing high-density clam farming reduces critical erosion shear stress (i.e., destabilises sediment). Important contrast with reef-building bivalves (R129, R130). Y now multi-tagged H&amp;B + CC.</t>
+          <t>Foundational paper for documenting that suspended-bivalve farms act as porous physical canopies in the surface layer, reducing horizontal flow and inducing downwelling. The 80% chl-a depletion result is striking and matches the seston-depletion + carrying-capacity literature. Important for MEL practitioners: chl-a measurements 'inside' farms are physically distorted by reduced current — sampling design must account for canopy-induced vertical mixing. Companion to R125 Cugier 2010 (modelling), R110 Maar 2024 (modelling). | v1.4 refinement: Added CC 3.1.1 per Sub-rule 1c (v1.4) — paper measures canopy-induced flow modification which contributes to wave-energy attenuation by suspended bivalve farms; does not compute wave-decay coefficient directly, so retained under Sub-rule 1c with caveat. Y now multi-tagged WQ + CC.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Briant, N., et al.</t>
+          <t>Shi, B., et al.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Carbon and nitrogen elemental and isotopic ratios of filter-feeding bivalves along the French coasts: An assessment of specific, geographic, seasonal and multi-decadal variations</t>
+          <t>Influence of macrobenthos (Meretrix meretrix Linnaeus) on erosion-accretion processes in intertidal flats: A case study from a cultivation zone</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Science of the Total Environment</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>613-614</t>
+          <t>Journal of Geophysical Research: Biogeosciences</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>125</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>196-207</t>
+          <t>e2019JG005345</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Elsevier</t>
+          <t>AGU / Wiley</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>ROCCH-network (Ifremer Mussel-Watch, ongoing since 1979) C, N, δ13C, δ15N analysis of bivalve soft tissues across THREE temporal scales in France: (i) SPATIAL — 189 samples from 74 stations spanning English Channel + Atlantic + Mediterranean, winter 2014, classified as littoral/estuary/bay/lagoon; (ii) SEASONAL — 4 seasons × 1998+1999 at Pointe Chemoulin, Bourgneuf-Coupelasse (AO), Cap Couronne (Med); (iii) DECADAL — every 3 years from 1987 to 2014 at 10 sites. Three species: Mytilus edulis (EC + AO), M. galloprovincialis (EC + Med), Crassostrea gigas (EC + AO). δ13C + δ15N used as food-source proxies; C/N (mol/mol) as body-condition proxy. Spatial variability tied to trophic status (oligo-Med vs meso-eutrophic EC+AO); seasonal C/N tied to mussel reproduction cycle; δ13C tied to trophic-resource variability at river-mouth sites; multi-decadal shifts in early 2000s with declining δ13C + δ15N likely linked to climate change. Maps to MEL WQ 1.1.1 (tissue bioindication) and WQ 1.2.1 (anthropogenic-N proxy via δ15N) — canonical Sub-rule 1a application.</t>
+          <t>Paired-site (cultivation zone vs adjacent bare flat) field investigation on the Rudong intertidal flat, Jiangsu Coast, China, quantifying the effect of high-density hard clam Meretrix meretrix (~137 ind. m⁻²) on bed erodibility, sediment-erosion thresholds, and erosion-accretion processes. Co-deployed instruments: ADV for turbulent flow velocity + bed-level change, SBE 26 Plus pressure sensors for wave-tide measurements, sediment-property + macrobenthos sampling. Found M. meretrix presence lowered critical erosion shear stress (~23.5% drop) — clams destabilise sediment under their cultivation density. Maps to MEL H&amp;B 1.4.1 (sediment biogeochemistry / dynamics).</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Protocol (ROCCH national bioindicator network + tissue elemental + isotopic IRMS protocol)</t>
+          <t>Protocol (paired-site hydrodynamic + sediment-erosion observation under bivalve cultivation)</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Yes — gold-standard tissue elemental + isotopic methodology; 189 samples across 74 sites with consistent ROCCH sampling protocol since 1979; precision ≤0.2‰ for δ13C + δ15N validated against IAEA-N2, USGS-24 + casein/acetanilide standards.</t>
+          <t>Yes — synchronous hydrodynamic + sediment + macrobenthos measurements at paired sites with + without bivalve cultivation; standard erosion-threshold methodology.</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>No — IRMS lab analysis requires specialist facility (EPOC Bordeaux in this case).</t>
+          <t>No — research-grade instrumentation deployment (ADV, pressure sensors).</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -27866,37 +27790,42 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>ROCCH sampling kit (pooled 50-mussel or 10-oyster samples per station); 24-h depuration in site water; freeze-drying + stainless-steel homogenisation; 400 µg aliquots on Carlo Erba NC2500 Elemental Analyzer + Isoprime GV Instruments IRMS; standards casein, acetanilide, IAEA-N2, USGS-24</t>
+          <t>ADV (acoustic Doppler velocimeter); SBE 26 Plus wave-tide recorder; grain-size + organic-content sediment analysis; benthic core sampling</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Medium–High — sampling is operational (institutional); IRMS analysis is the cost driver</t>
+          <t>Medium–High — research-grade hydrodynamic instrumentation</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Multi-scale: seasonal (4 × 1998+1999 at 3 sites), spatial snapshot (winter 2014, 74 sites), decadal (3-yr intervals 1987–2014 at 10 sites)</t>
+          <t>Multi-season (seasonal summer + winter comparison)</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>Spatial: across-region and across-ecosystem-typology comparisons (Kruskal-Wallis + post-hoc); seasonal: within-site temporal contrasts; multi-decadal: trend + shift detection (Pettitt, Mann-Kendall) on 30-year series</t>
+          <t>Paired-site contrasts; critical shear-stress calculation; bed-level change time series</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>No — Paywalled (Elsevier); preprint may be available via Ifremer Archimer</t>
+          <t>No — Paywalled (AGU / Wiley)</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>Full PDF</t>
+          <t>Abstract + Methods (fetched)</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.scitotenv.2017.08.281</t>
+          <t>https://doi.org/10.1029/2019JG005345</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Counterintuitively, high-density burrowing, shell-protruding clams can lower the erosion threshold and destabilise the bed - the opposite of reef-builders.</t>
         </is>
       </c>
       <c r="V132" t="inlineStr">
@@ -27904,7 +27833,7 @@
           <t>Original list</t>
         </is>
       </c>
-      <c r="W132" s="7" t="inlineStr">
+      <c r="W132" t="inlineStr">
         <is>
           <t>2 — Researcher</t>
         </is>
@@ -27916,32 +27845,32 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>Water Quality</t>
+          <t>Habitat &amp; Biodiversity, Climate Change</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>WQ 1.1.1 — Bioextraction (tissue C/N + δ13C/δ15N isotopes)</t>
+          <t>CC 3.1.1 — Wave attenuation / coastal protection (counter-example, Sub-rule 1c), H&amp;B 1.4.1 — Sediment biogeochemistry</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>Temperate Atlantic + Mediterranean</t>
+          <t>Subtropical Pacific</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>Pacific oyster (Crassostrea / Magallana gigas), Blue mussel (Mytilus edulis), Mediterranean mussel (Mytilus galloprovincialis)</t>
+          <t>Hard clam (Meretrix meretrix)</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Mixed (national network across multiple farm + wild-stock types)</t>
+          <t>Intertidal bottom culture (seeded clam beds)</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>Multi-bay national (74 stations, 3 coastal regions)</t>
+          <t>Single site (paired cultivation vs control)</t>
         </is>
       </c>
       <c r="AE132" t="inlineStr">
@@ -27956,7 +27885,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>Tissue analysis, Stable isotope analysis</t>
+          <t>Sediment sampling, Hydrodynamic measurement, Benthic infauna sampling</t>
         </is>
       </c>
       <c r="AH132" t="inlineStr">
@@ -27966,7 +27895,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>Variable (littoral, estuary, bay, lagoon)</t>
+          <t>Intertidal / very shallow (&lt; 2 m)</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
@@ -27976,7 +27905,7 @@
       </c>
       <c r="AK132" s="16" t="inlineStr">
         <is>
-          <t>To establish a multi-scale bivalve-tissue bioindicator baseline, sample pooled soft tissue of the target species at many coastal stations (following a national mussel-watch protocol), depurate briefly in site water, freeze-dry and homogenise, then analyse carbon and nitrogen content and delta-13-C/delta-15-N on an elemental analyser coupled to an IRMS against certified standards. Design the sampling across spatial (many sites in one season), seasonal (repeated within a year) and multi-decadal scales so you can run typology comparisons (Kruskal-Wallis) and trend/shift detection (Pettitt, Mann-Kendall) on the long series.</t>
+          <t>To measure how dense infaunal bivalves affect sediment stability, compare a cultivation zone with an adjacent bare flat, co-deploying an acoustic Doppler velocimeter for turbulent flow and a wave-tide recorder to derive bed shear stress, alongside sediment grain-size and organic-content analysis and benthic cores. Track bed-level change and compute the critical erosion shear stress at each site; note the counterintuitive result that high-density burrowing, shell-protruding clams can lower the erosion threshold and destabilise the bed rather than protect it - the opposite of reef-building bivalves.</t>
         </is>
       </c>
       <c r="AL132" s="17" t="inlineStr">
@@ -27986,7 +27915,7 @@
       </c>
       <c r="AM132" s="18" t="inlineStr">
         <is>
-          <t>briant_2018</t>
+          <t>shi_2020</t>
         </is>
       </c>
       <c r="AN132" s="19" t="n"/>
@@ -27994,62 +27923,72 @@
       <c r="AP132" s="19" t="n"/>
       <c r="AQ132" s="16" t="inlineStr">
         <is>
-          <t>Multi-Scale Bivalve-Tissue C/N Isotope Bioindicator Baseline</t>
+          <t>Do Dense Infaunal Bivalves Stabilise or Erode Sediment?</t>
         </is>
       </c>
       <c r="AR132" s="16" t="inlineStr">
         <is>
-          <t>Briant, Nicolas; Savoye, Nicolas; Chouvelon, Tiphaine; David, Valérie; Rodriguez, Samuel; Charlier, Karine; Sonke, Jeroen E; Chiffoleau, Jean François; Brach-Papa, Christophe; Knoery, Joël</t>
+          <t>Shi, Benwei; Pratolongo, Paula D; Du, Yongfen; Li, Jiasheng; Yang, S L; Wu, Jihua; Xu, Kehui; Wang, Ya Ping</t>
         </is>
       </c>
       <c r="AS132" s="16" t="inlineStr">
         <is>
-          <t>Canonical Sub-rule 1a precursor to R116 Liénart 2025 — same ROCCH network (Ifremer), same research consortium (Briant himself is co-author of Liénart 2025). Briant 2018 established the cross-scale (spatial + seasonal + decadal) methodology with 189 samples across 74 sites; Liénart 2025 extended it to 1141 samples × 1981–2021 at a curated 33-station subset. Together the pair represents the deepest multi-decadal bivalve-tissue bioindication dataset in MEL-relevant literature. Companion to Carmichael 2012 (R113, USA Atlantic estuaries) and the broader Sub-rule 1a corpus. Note: added at R134 out of CSV order (after R133 #44 Shi 2020) because the PDF arrived after the rest of the chat had been processed. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (tissue C/N + δ13C + δ15N only; no DO measurement). δ15N anthropogenic-N proxy framing noted in U but does not map to a v1.4 indicator.</t>
+          <t>Important paper for the COUNTERINTUITIVE finding that high-density bivalve cultivation can DESTABILISE rather than stabilise sediments (the opposite of reef-building bivalves in Ysebaert 2018 R129) — context matters: the action of clams burrowing + protruding their shells reduces critical erosion shear stress. Important for MEL practitioners using H&amp;B 1.4.1 sediment-dynamics indicators on clam-cultivation sites: cultivation may shift the system toward erosion. Companion to Shi 2021 (L&amp;O, typhoon-induced erosion at same site) and Li 2021 (Ecohydrology &amp; Hydrobiology, same site, ~23% threshold drop confirmed). | v1.4 refinement: Added CC 3.1.1 per Sub-rule 1c (v1.4) — sediment-erosion threshold under clam cultivation is directly relevant to mollusc CC Obj 3.1 (coastal erosion), as a COUNTER-EXAMPLE showing high-density clam farming reduces critical erosion shear stress (i.e., destabilises sediment). Important contrast with reef-building bivalves (R129, R130). Y now multi-tagged H&amp;B + CC.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Smithsonian MarineGEO</t>
+          <t>Briant, N., et al.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MarineGEO Fouling Community Monitoring Protocol</t>
+          <t>Carbon and nitrogen elemental and isotopic ratios of filter-feeding bivalves along the French coasts: An assessment of specific, geographic, seasonal and multi-decadal variations</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Smithsonian Environmental Research Center (MarineGEO Protocols)</t>
+          <t>Science of the Total Environment</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>613-614</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>196-207</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Smithsonian Institution</t>
+          <t>Elsevier</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Standardized settlement-panel protocol for sessile fouling/epibiont communities on submerged hard structures — directly transferable to bivalve/seaweed gear (ropes, cages, longlines) to quantify native epibiota colonising farmed biomass. Repeated farm vs reference, also informs community composition and settlement/recruitment.</t>
+          <t>ROCCH-network (Ifremer Mussel-Watch, ongoing since 1979) C, N, δ13C, δ15N analysis of bivalve soft tissues across THREE temporal scales in France: (i) SPATIAL — 189 samples from 74 stations spanning English Channel + Atlantic + Mediterranean, winter 2014, classified as littoral/estuary/bay/lagoon; (ii) SEASONAL — 4 seasons × 1998+1999 at Pointe Chemoulin, Bourgneuf-Coupelasse (AO), Cap Couronne (Med); (iii) DECADAL — every 3 years from 1987 to 2014 at 10 sites. Three species: Mytilus edulis (EC + AO), M. galloprovincialis (EC + Med), Crassostrea gigas (EC + AO). δ13C + δ15N used as food-source proxies; C/N (mol/mol) as body-condition proxy. Spatial variability tied to trophic status (oligo-Med vs meso-eutrophic EC+AO); seasonal C/N tied to mussel reproduction cycle; δ13C tied to trophic-resource variability at river-mouth sites; multi-decadal shifts in early 2000s with declining δ13C + δ15N likely linked to climate change. Maps to MEL WQ 1.1.1 (tissue bioindication) and WQ 1.2.1 (anthropogenic-N proxy via δ15N) — canonical Sub-rule 1a application.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Protocol</t>
+          <t>Protocol (ROCCH national bioindicator network + tissue elemental + isotopic IRMS protocol)</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Yes — full field package (PDF step-by-step methods, printable field sheet, data-submission workbook). Panels deployed for a set soak, photographed and/or scraped; sessile cover and taxa scored. Replicable by another team.</t>
+          <t>Yes — gold-standard tissue elemental + isotopic methodology; 189 samples across 74 sites with consistent ROCCH sampling protocol since 1979; precision ≤0.2‰ for δ13C + δ15N validated against IAEA-N2, USGS-24 + casein/acetanilide standards.</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Partial — panel deployment/retrieval and photography are farmer-doable; species-level ID of fouling taxa needs a taxonomist or image-analysis partner.</t>
+          <t>No — IRMS lab analysis requires specialist facility (EPOC Bordeaux in this case).</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -28059,102 +27998,97 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>Settlement panels (PVC), lines/weights, underwater camera; lab microscope for ID</t>
+          <t>ROCCH sampling kit (pooled 50-mussel or 10-oyster samples per station); 24-h depuration in site water; freeze-drying + stainless-steel homogenisation; 400 µg aliquots on Carlo Erba NC2500 Elemental Analyzer + Isoprime GV Instruments IRMS; standards casein, acetanilide, IAEA-N2, USGS-24</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Low–Medium — panels and gear inexpensive; cost sits in ID/processing time</t>
+          <t>Medium–High — sampling is operational (institutional); IRMS analysis is the cost driver</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Seasonal (1–3 months)</t>
+          <t>Multi-scale: seasonal (4 × 1998+1999 at 3 sites), spatial snapshot (winter 2014, 74 sites), decadal (3-yr intervals 1987–2014 at 10 sites)</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>Percent-cover scoring, taxa richness/diversity; farm-vs-reference comparison</t>
+          <t>Spatial: across-region and across-ecosystem-typology comparisons (Kruskal-Wallis + post-hoc); seasonal: within-site temporal contrasts; multi-decadal: trend + shift detection (Pettitt, Mann-Kendall) on 30-year series</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>Yes — Open (DOI-published, CC)</t>
+          <t>No — Paywalled (Elsevier); preprint may be available via Ifremer Archimer</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>Abstract + Methods (fetched)</t>
+          <t>Full PDF</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>https://marinegeo.github.io/fouling-community.html ; collection DOI https://doi.org/10.25573/serc.c.5506377</t>
-        </is>
-      </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>Built for natural hard-bottom but transfers cleanly to farm gear; where organisms are too cryptic to ID from panels, an ARMS plus DNA-metabarcoding approach is the alternative.</t>
+          <t>https://doi.org/10.1016/j.scitotenv.2017.08.281</t>
         </is>
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>Provided by Claude (grey/white-lit protocol search)</t>
+          <t>Original list</t>
         </is>
       </c>
       <c r="W133" s="7" t="inlineStr">
         <is>
-          <t>3 — Partnership</t>
+          <t>2 — Researcher</t>
         </is>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>Seaweed, Mollusk</t>
+          <t>Mollusk</t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>Habitat &amp; Biodiversity</t>
+          <t>Water Quality</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 2.1.1 — Community composition, H&amp;B 2.2.1 — Spawning</t>
+          <t>WQ 1.1.1 — Bioextraction (tissue C/N + δ13C/δ15N isotopes)</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>Cross-zone / global</t>
+          <t>Temperate Atlantic + Mediterranean</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>Not species-specific</t>
+          <t>Pacific oyster (Crassostrea / Magallana gigas), Blue mussel (Mytilus edulis), Mediterranean mussel (Mytilus galloprovincialis)</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Not gear-specific</t>
+          <t>Mixed (national network across multiple farm + wild-stock types)</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr">
         <is>
-          <t>Not scale-specific</t>
+          <t>Multi-bay national (74 stations, 3 coastal regions)</t>
         </is>
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>Not site-specific</t>
+          <t>Variable / seasonal</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
         <is>
-          <t>Not specific</t>
+          <t>Monoculture</t>
         </is>
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>Visual survey</t>
+          <t>Tissue analysis, Stable isotope analysis</t>
         </is>
       </c>
       <c r="AH133" t="inlineStr">
@@ -28164,17 +28098,17 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>Not depth-specific</t>
+          <t>Variable (littoral, estuary, bay, lagoon)</t>
         </is>
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>Not exposure-specific</t>
+          <t>Mixed exposure</t>
         </is>
       </c>
       <c r="AK133" s="16" t="inlineStr">
         <is>
-          <t>To quantify the attached (fouling/epibiont) community your gear supports, deploy standardized settlement panels (e.g. roughly hand-sized PVC plates) on the farm structures and at a reference site, leaving them for a set soak of a few months. Retrieve, photograph each panel and/or scrape it, and score percent cover and identify the sessile taxa under a microscope. Compare farm versus reference for cover, richness and community composition. A printable field sheet and data-submission workbook accompany the protocol; where hands-on ID is impractical, an autonomous-reef-monitoring-structure (ARMS) plus metabarcoding variant covers cryptic fauna.</t>
+          <t>To establish a multi-scale bivalve-tissue bioindicator baseline, sample pooled soft tissue of the target species at many coastal stations (following a national mussel-watch protocol), depurate briefly in site water, freeze-dry and homogenise, then analyse carbon and nitrogen content and delta-13-C/delta-15-N on an elemental analyser coupled to an IRMS against certified standards. Design the sampling across spatial (many sites in one season), seasonal (repeated within a year) and multi-decadal scales so you can run typology comparisons (Kruskal-Wallis) and trend/shift detection (Pettitt, Mann-Kendall) on the long series.</t>
         </is>
       </c>
       <c r="AL133" s="17" t="inlineStr">
@@ -28184,7 +28118,7 @@
       </c>
       <c r="AM133" s="18" t="inlineStr">
         <is>
-          <t>smithsonianmarinegeo_2022</t>
+          <t>briant_2018</t>
         </is>
       </c>
       <c r="AN133" s="19" t="n"/>
@@ -28192,17 +28126,17 @@
       <c r="AP133" s="19" t="n"/>
       <c r="AQ133" s="16" t="inlineStr">
         <is>
-          <t>Settlement-Panel Monitoring of Fouling &amp; Epibiont Communities on Farm Gear</t>
+          <t>Multi-Scale Bivalve-Tissue C/N Isotope Bioindicator Baseline</t>
         </is>
       </c>
       <c r="AR133" s="16" t="inlineStr">
         <is>
-          <t>Smithsonian MarineGEO / Tennenbaum Marine Observatories Network</t>
+          <t>Briant, Nicolas; Savoye, Nicolas; Chouvelon, Tiphaine; David, Valérie; Rodriguez, Samuel; Charlier, Karine; Sonke, Jeroen E; Chiffoleau, Jean François; Brach-Papa, Christophe; Knoery, Joël</t>
         </is>
       </c>
       <c r="AS133" s="16" t="inlineStr">
         <is>
-          <t>Smithsonian MarineGEO suite — the closest direct analogue to the Oyster-Reef protocol for the epibiota-on-structures case. ARMS (Autonomous Reef Monitoring Structures) is the metabarcoding-based cousin for cryptobiota where panel ID is impractical. Built for natural hard-bottom; transfers cleanly to aquaculture gear.</t>
+          <t>Canonical Sub-rule 1a precursor to R116 Liénart 2025 — same ROCCH network (Ifremer), same research consortium (Briant himself is co-author of Liénart 2025). Briant 2018 established the cross-scale (spatial + seasonal + decadal) methodology with 189 samples across 74 sites; Liénart 2025 extended it to 1141 samples × 1981–2021 at a curated 33-station subset. Together the pair represents the deepest multi-decadal bivalve-tissue bioindication dataset in MEL-relevant literature. Companion to Carmichael 2012 (R113, USA Atlantic estuaries) and the broader Sub-rule 1a corpus. Note: added at R134 out of CSV order (after R133 #44 Shi 2020) because the PDF arrived after the rest of the chat had been processed. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (tissue C/N + δ13C + δ15N only; no DO measurement). δ15N anthropogenic-N proxy framing noted in U but does not map to a v1.4 indicator.</t>
         </is>
       </c>
     </row>
@@ -28214,7 +28148,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MarineGEO Oyster Reef Habitat Monitoring Protocol</t>
+          <t>MarineGEO Fouling Community Monitoring Protocol</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -28232,7 +28166,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Standard survey design for eastern-oyster reef habitat: reef area &amp; height, composition, oyster density &amp; size, rugosity, and associated mobile + sessile biodiversity. Methodology adopted from the Baggett/TNC handbook (universal metrics).</t>
+          <t>Standardized settlement-panel protocol for sessile fouling/epibiont communities on submerged hard structures — directly transferable to bivalve/seaweed gear (ropes, cages, longlines) to quantify native epibiota colonising farmed biomass. Repeated farm vs reference, also informs community composition and settlement/recruitment.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -28242,12 +28176,12 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Yes — reproducible reef-structure metrics plus associated-fauna collection, with site-selection, layout, workflow and data-submission guidance. Comparable across MarineGEO sites.</t>
+          <t>Yes — full field package (PDF step-by-step methods, printable field sheet, data-submission workbook). Panels deployed for a set soak, photographed and/or scraped; sessile cover and taxa scored. Replicable by another team.</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Partial — reef metrics (area, height, density, size) and fauna collection are farmer-doable; faunal ID/sorting needs a partner.</t>
+          <t>Partial — panel deployment/retrieval and photography are farmer-doable; species-level ID of fouling taxa needs a taxonomist or image-analysis partner.</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -28257,12 +28191,12 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>Quadrats, calipers, transect tape, excavation trays, mesh bags; lab for ID</t>
+          <t>Settlement panels (PVC), lines/weights, underwater camera; lab microscope for ID</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Low–Medium</t>
+          <t>Low–Medium — panels and gear inexpensive; cost sits in ID/processing time</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -28272,12 +28206,12 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>Density/size-frequency, rugosity, diversity indices; farm/reference comparison</t>
+          <t>Percent-cover scoring, taxa richness/diversity; farm-vs-reference comparison</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>Yes — Open (DOI-published)</t>
+          <t>Yes — Open (DOI-published, CC)</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
@@ -28287,12 +28221,12 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>https://marinegeo.si.edu/protocols/oyster-reefs</t>
+          <t>https://marinegeo.github.io/fouling-community.html ; collection DOI https://doi.org/10.25573/serc.c.5506377</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>Specific to eastern oyster but the design transfers to other bivalve reef/longline contexts.</t>
+          <t>Built for natural hard-bottom but transfers cleanly to farm gear; where organisms are too cryptic to ID from panels, an ARMS plus DNA-metabarcoding approach is the alternative.</t>
         </is>
       </c>
       <c r="V134" t="inlineStr">
@@ -28307,7 +28241,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>Mollusk</t>
+          <t>Seaweed, Mollusk</t>
         </is>
       </c>
       <c r="Y134" t="inlineStr">
@@ -28317,7 +28251,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 1.2.1 — Mobile fauna, H&amp;B 2.1.1 — Community composition</t>
+          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 2.1.1 — Community composition, H&amp;B 2.2.1 — Spawning</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -28327,7 +28261,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>Eastern oyster (Crassostrea virginica)</t>
+          <t>Not species-specific</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -28372,7 +28306,7 @@
       </c>
       <c r="AK134" s="16" t="inlineStr">
         <is>
-          <t>To monitor oyster-reef habitat (and by extension bivalve reef/longline structure), survey reef areal extent and height, oyster density and size, and rugosity, alongside the associated mobile and sessile fauna. Lay transects and place quadrats to measure density and size-frequency (calipers), record rugosity, and collect associated organisms (excavation trays, mesh bags) for lab identification. Compare farm/reef against a reference with density, size-frequency and diversity metrics. The design follows the universal reef metrics of the Baggett/TNC handbook, so results are comparable across sites.</t>
+          <t>To quantify the attached (fouling/epibiont) community your gear supports, deploy standardized settlement panels (e.g. roughly hand-sized PVC plates) on the farm structures and at a reference site, leaving them for a set soak of a few months. Retrieve, photograph each panel and/or scrape it, and score percent cover and identify the sessile taxa under a microscope. Compare farm versus reference for cover, richness and community composition. A printable field sheet and data-submission workbook accompany the protocol; where hands-on ID is impractical, an autonomous-reef-monitoring-structure (ARMS) plus metabarcoding variant covers cryptic fauna.</t>
         </is>
       </c>
       <c r="AL134" s="17" t="inlineStr">
@@ -28382,7 +28316,7 @@
       </c>
       <c r="AM134" s="18" t="inlineStr">
         <is>
-          <t>smithsonianmarinegeo_2022-b</t>
+          <t>smithsonianmarinegeo_2022</t>
         </is>
       </c>
       <c r="AN134" s="19" t="n"/>
@@ -28390,52 +28324,47 @@
       <c r="AP134" s="19" t="n"/>
       <c r="AQ134" s="16" t="inlineStr">
         <is>
-          <t>Oyster-Reef Habitat Structure &amp; Associated-Fauna Survey</t>
+          <t>Settlement-Panel Monitoring of Fouling &amp; Epibiont Communities on Farm Gear</t>
         </is>
       </c>
       <c r="AR134" s="16" t="inlineStr">
         <is>
-          <t>Smithsonian MarineGEO</t>
+          <t>Smithsonian MarineGEO / Tennenbaum Marine Observatories Network</t>
         </is>
       </c>
       <c r="AS134" s="16" t="inlineStr">
         <is>
-          <t>Specific to eastern oyster (Crassostrea virginica) but design transfers to other bivalve reef/longline contexts. Pairs with the Baggett 2014 handbook (next row), the methodological parent.</t>
+          <t>Smithsonian MarineGEO suite — the closest direct analogue to the Oyster-Reef protocol for the epibiota-on-structures case. ARMS (Autonomous Reef Monitoring Structures) is the metabarcoding-based cousin for cryptobiota where panel ID is impractical. Built for natural hard-bottom; transfers cleanly to aquaculture gear.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Baggett, L. P., et al.</t>
+          <t>Smithsonian MarineGEO</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Oyster Habitat Restoration Monitoring and Assessment Handbook</t>
+          <t>MarineGEO Oyster Reef Habitat Monitoring Protocol</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>The Nature Conservancy</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>96 pp</t>
+          <t>Smithsonian Environmental Research Center (MarineGEO Protocols)</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>The Nature Conservancy, Arlington, VA</t>
+          <t>Smithsonian Institution</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>TNC's standard for oyster reef monitoring. Four Universal Metrics (reef areal dimension, height, oyster density, size-frequency) + three Universal Environmental Variables (temperature, salinity, dissolved oxygen) + goal-based metrics for four ecosystem-service goals (incl. associated biodiversity and coastal protection / shoreline stabilisation).</t>
+          <t>Standard survey design for eastern-oyster reef habitat: reef area &amp; height, composition, oyster density &amp; size, rugosity, and associated mobile + sessile biodiversity. Methodology adopted from the Baggett/TNC handbook (universal metrics).</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -28445,12 +28374,12 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Yes — defines metrics, units, performance criteria and field methods in replicable detail; peer-reviewed companion is Baggett et al. 2015 (Restoration Ecology). Practitioners without capacity are explicitly told to collaborate.</t>
+          <t>Yes — reproducible reef-structure metrics plus associated-fauna collection, with site-selection, layout, workflow and data-submission guidance. Comparable across MarineGEO sites.</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Partial — universal reef metrics and DO/temp/salinity (handheld probe) are farmer-executable; associated-biodiversity, disease and recruitment metrics need a partner lab.</t>
+          <t>Partial — reef metrics (area, height, density, size) and fauna collection are farmer-doable; faunal ID/sorting needs a partner.</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -28460,7 +28389,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>Quadrats, calipers, transect tape, handheld multiprobe (T/S/DO), shell/recruitment trays</t>
+          <t>Quadrats, calipers, transect tape, excavation trays, mesh bags; lab for ID</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -28470,17 +28399,17 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Multi-year monitoring (&gt; 1 year)</t>
+          <t>Seasonal (1–3 months)</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>Universal-metric comparison to performance criteria; size-frequency; goal-based analysis</t>
+          <t>Density/size-frequency, rugosity, diversity indices; farm/reference comparison</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>Yes — Open (free PDF)</t>
+          <t>Yes — Open (DOI-published)</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
@@ -28490,12 +28419,12 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>http://www.oyster-restoration.org/wp-content/uploads/2014/01/Oyster-Habitat-Restoration-Monitoring-and-Assessment-Handbook.pdf</t>
+          <t>https://marinegeo.si.edu/protocols/oyster-reefs</t>
         </is>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>Restoration-oriented but the universal metrics and environmental variables transfer to bivalve farming; the goal-based coastal-protection metrics are the practitioner route to wave attenuation.</t>
+          <t>Specific to eastern oyster but the design transfers to other bivalve reef/longline contexts.</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
@@ -28515,12 +28444,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>Habitat &amp; Biodiversity, Water Quality, Climate Change</t>
+          <t>Habitat &amp; Biodiversity</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 2.1.1 — Community composition, H&amp;B 2.2.1 — Spawning, WQ 1.2.1 — Dissolved oxygen, CC 3.1.1 — Wave attenuation / coastal protection</t>
+          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 1.2.1 — Mobile fauna, H&amp;B 2.1.1 — Community composition</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -28555,7 +28484,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>Visual survey, Water chemistry</t>
+          <t>Visual survey</t>
         </is>
       </c>
       <c r="AH135" t="inlineStr">
@@ -28575,7 +28504,7 @@
       </c>
       <c r="AK135" s="16" t="inlineStr">
         <is>
-          <t>This TNC handbook is the standard for oyster-reef monitoring and defines exactly what to measure: four Universal Metrics (reef areal dimension, height, oyster density, size-frequency), three Universal Environmental Variables (temperature, salinity, dissolved oxygen via a handheld multiprobe), plus goal-based metrics for specific ecosystem services. Measure the universal metrics with quadrats, calipers and transect tape against defined performance criteria, and add the goal-based set for the service you care about - the coastal-protection metrics (shoreline position/elevation plus a wave gauge) are the practitioner route to a wave-attenuation indicator. It shares direct lineage with this MEL framework, its metrics and environmental variables transfer to bivalve farming, and teams without capacity are advised to collaborate.</t>
+          <t>To monitor oyster-reef habitat (and by extension bivalve reef/longline structure), survey reef areal extent and height, oyster density and size, and rugosity, alongside the associated mobile and sessile fauna. Lay transects and place quadrats to measure density and size-frequency (calipers), record rugosity, and collect associated organisms (excavation trays, mesh bags) for lab identification. Compare farm/reef against a reference with density, size-frequency and diversity metrics. The design follows the universal reef metrics of the Baggett/TNC handbook, so results are comparable across sites.</t>
         </is>
       </c>
       <c r="AL135" s="17" t="inlineStr">
@@ -28585,7 +28514,7 @@
       </c>
       <c r="AM135" s="18" t="inlineStr">
         <is>
-          <t>baggett_2014</t>
+          <t>smithsonianmarinegeo_2022-b</t>
         </is>
       </c>
       <c r="AN135" s="19" t="n"/>
@@ -28593,47 +28522,52 @@
       <c r="AP135" s="19" t="n"/>
       <c r="AQ135" s="16" t="inlineStr">
         <is>
-          <t>TNC Oyster Restoration Monitoring Handbook (Universal Metrics)</t>
+          <t>Oyster-Reef Habitat Structure &amp; Associated-Fauna Survey</t>
         </is>
       </c>
       <c r="AR135" s="16" t="inlineStr">
         <is>
-          <t>Baggett, L.P.; Powers, S.P.; Brumbaugh, R.D.; Coen, L.D.; DeAngelis, B.M.; Greene, J.K.; Hancock, B.T.; Morlock, S.M.</t>
+          <t>Smithsonian MarineGEO</t>
         </is>
       </c>
       <c r="AS135" s="16" t="inlineStr">
         <is>
-          <t>TNC-authored — direct lineage with this MEL framework. Restoration-oriented but the universal metrics and environmental variables transfer to bivalve farming H&amp;B/WQ. The coastal-protection goal-based metric set is the practitioner route to CC 3.1.1 (shoreline position/elevation + wave-gauge/pressure-logger field methods).</t>
+          <t>Specific to eastern oyster (Crassostrea virginica) but design transfers to other bivalve reef/longline contexts. Pairs with the Baggett 2014 handbook (next row), the methodological parent.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Native Oyster Network (UK &amp; Ireland)</t>
+          <t>Baggett, L. P., et al.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>European Native Oyster Habitat Restoration Monitoring Guidelines</t>
+          <t>Oyster Habitat Restoration Monitoring and Assessment Handbook</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Native Oyster Restoration Alliance (NORA)</t>
+          <t>The Nature Conservancy</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>96 pp</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>NORA / ZSL Native Oyster Network</t>
+          <t>The Nature Conservancy, Arlington, VA</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>European adaptation (39 authors, 7 countries) of the Baggett handbook for Ostrea edulis: Universal, Supplementary and Goal-Based Metrics suited to European native-oyster settings.</t>
+          <t>TNC's standard for oyster reef monitoring. Four Universal Metrics (reef areal dimension, height, oyster density, size-frequency) + three Universal Environmental Variables (temperature, salinity, dissolved oxygen) + goal-based metrics for four ecosystem-service goals (incl. associated biodiversity and coastal protection / shoreline stabilisation).</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -28643,12 +28577,12 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Yes — metric definitions with multiple method options per metric; designed to answer performance questions for European native-oyster restoration.</t>
+          <t>Yes — defines metrics, units, performance criteria and field methods in replicable detail; peer-reviewed companion is Baggett et al. 2015 (Restoration Ecology). Practitioners without capacity are explicitly told to collaborate.</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Partial — universal/structural metrics farmer-doable; biodiversity and some supplementary metrics need partner lab.</t>
+          <t>Partial — universal reef metrics and DO/temp/salinity (handheld probe) are farmer-executable; associated-biodiversity, disease and recruitment metrics need a partner lab.</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -28658,7 +28592,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>Quadrats, transect tape, calipers; lab for ID</t>
+          <t>Quadrats, calipers, transect tape, handheld multiprobe (T/S/DO), shell/recruitment trays</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -28673,12 +28607,12 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>Universal/supplementary/goal-based metric analysis</t>
+          <t>Universal-metric comparison to performance criteria; size-frequency; goal-based analysis</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>Yes — Open (online guidelines)</t>
+          <t>Yes — Open (free PDF)</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -28688,12 +28622,12 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>https://nativeoysternetwork.org/2021/05/04/native-oyster-monitoring-guidelines/</t>
+          <t>http://www.oyster-restoration.org/wp-content/uploads/2014/01/Oyster-Habitat-Restoration-Monitoring-and-Assessment-Handbook.pdf</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>Use it for European flat-oyster (Ostrea edulis) settings where the TNC handbook methods need adapting.</t>
+          <t>Restoration-oriented but the universal metrics and environmental variables transfer to bivalve farming; the goal-based coastal-protection metrics are the practitioner route to wave attenuation.</t>
         </is>
       </c>
       <c r="V136" t="inlineStr">
@@ -28713,22 +28647,22 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>Habitat &amp; Biodiversity, Climate Change</t>
+          <t>Habitat &amp; Biodiversity, Water Quality, Climate Change</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 2.1.1 — Community composition, H&amp;B 2.2.1 — Spawning, CC 3.1.1 — Wave attenuation / coastal protection</t>
+          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 2.1.1 — Community composition, H&amp;B 2.2.1 — Spawning, WQ 1.2.1 — Dissolved oxygen, CC 3.1.1 — Wave attenuation / coastal protection</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>Temperate Atlantic</t>
+          <t>Cross-zone / global</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>European flat oyster (Ostrea edulis)</t>
+          <t>Eastern oyster (Crassostrea virginica)</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -28753,7 +28687,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>Visual survey</t>
+          <t>Visual survey, Water chemistry</t>
         </is>
       </c>
       <c r="AH136" t="inlineStr">
@@ -28773,7 +28707,7 @@
       </c>
       <c r="AK136" s="16" t="inlineStr">
         <is>
-          <t>This is the European adaptation of the TNC oyster handbook for the native flat oyster (Ostrea edulis), giving Universal, Supplementary and Goal-Based metrics with several method options per metric. Measure reef/bed extent, oyster density and size with quadrats, transect tape and calipers, choosing the method option that fits your setting, and analyse against the restoration performance questions. Use it in European native-oyster contexts where the Baggett handbook methods need adapting.</t>
+          <t>This TNC handbook is the standard for oyster-reef monitoring and defines exactly what to measure: four Universal Metrics (reef areal dimension, height, oyster density, size-frequency), three Universal Environmental Variables (temperature, salinity, dissolved oxygen via a handheld multiprobe), plus goal-based metrics for specific ecosystem services. Measure the universal metrics with quadrats, calipers and transect tape against defined performance criteria, and add the goal-based set for the service you care about - the coastal-protection metrics (shoreline position/elevation plus a wave gauge) are the practitioner route to a wave-attenuation indicator. It shares direct lineage with this MEL framework, its metrics and environmental variables transfer to bivalve farming, and teams without capacity are advised to collaborate.</t>
         </is>
       </c>
       <c r="AL136" s="17" t="inlineStr">
@@ -28783,7 +28717,7 @@
       </c>
       <c r="AM136" s="18" t="inlineStr">
         <is>
-          <t>ukireland_2021</t>
+          <t>baggett_2014</t>
         </is>
       </c>
       <c r="AN136" s="19" t="n"/>
@@ -28791,34 +28725,34 @@
       <c r="AP136" s="19" t="n"/>
       <c r="AQ136" s="16" t="inlineStr">
         <is>
-          <t>European Native-Oyster Restoration Monitoring Guidelines</t>
+          <t>TNC Oyster Restoration Monitoring Handbook (Universal Metrics)</t>
         </is>
       </c>
       <c r="AR136" s="16" t="inlineStr">
         <is>
-          <t>Native Oyster Network (UK &amp; Ireland); Native Oyster Restoration Alliance (NORA)</t>
+          <t>Baggett, L.P.; Powers, S.P.; Brumbaugh, R.D.; Coen, L.D.; DeAngelis, B.M.; Greene, J.K.; Hancock, B.T.; Morlock, S.M.</t>
         </is>
       </c>
       <c r="AS136" s="16" t="inlineStr">
         <is>
-          <t>Use for European flat-oyster (Ostrea edulis) contexts where Baggett 2014 methods need adaptation. Complementary to the MarineGEO Oyster-Reef protocol and Baggett handbook.</t>
+          <t>TNC-authored — direct lineage with this MEL framework. Restoration-oriented but the universal metrics and environmental variables transfer to bivalve farming H&amp;B/WQ. The coastal-protection goal-based metric set is the practitioner route to CC 3.1.1 (shoreline position/elevation + wave-gauge/pressure-logger field methods).</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Smithsonian MarineGEO</t>
+          <t>Native Oyster Network (UK &amp; Ireland)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MarineGEO Diver Visual Survey Protocol</t>
+          <t>European Native Oyster Habitat Restoration Monitoring Guidelines</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Smithsonian Environmental Research Center (MarineGEO Protocols)</t>
+          <t>Native Oyster Restoration Alliance (NORA)</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -28826,12 +28760,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Smithsonian Institution</t>
+          <t>NORA / ZSL Native Oyster Network</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Standardized diver/snorkel belt-transect visual census of mobile fauna (fish, mobile invertebrates). Directly applicable to counting mobile fauna associated with a farm site.</t>
+          <t>European adaptation (39 authors, 7 countries) of the Baggett handbook for Ostrea edulis: Universal, Supplementary and Goal-Based Metrics suited to European native-oyster settings.</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -28841,12 +28775,12 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Yes — fixed transect design with counts/size estimates and data sheet; on-the-spot ID. Reproducible across sites.</t>
+          <t>Yes — metric definitions with multiple method options per metric; designed to answer performance questions for European native-oyster restoration.</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Yes — belt/visual transects with field ID guides are farmer/diver-executable with no obligatory lab step (the canonical practitioner-tier method).</t>
+          <t>Partial — universal/structural metrics farmer-doable; biodiversity and some supplementary metrics need partner lab.</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -28856,27 +28790,27 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>Transect tape, slate, dive/snorkel gear, ID guide</t>
+          <t>Quadrats, transect tape, calipers; lab for ID</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Low–Medium</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Seasonal (1–3 months)</t>
+          <t>Multi-year monitoring (&gt; 1 year)</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>Abundance/size counts per transect; diversity indices</t>
+          <t>Universal/supplementary/goal-based metric analysis</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>Yes — Open (DOI-published)</t>
+          <t>Yes — Open (online guidelines)</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
@@ -28886,12 +28820,12 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>https://doi.org/10.25573/serc.14717796</t>
+          <t>https://nativeoysternetwork.org/2021/05/04/native-oyster-monitoring-guidelines/</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>Needs dive/snorkel competency and reasonable clarity; Reef Life Survey is an equivalent with a trained-diver network.</t>
+          <t>Use it for European flat-oyster (Ostrea edulis) settings where the TNC handbook methods need adapting.</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
@@ -28901,32 +28835,32 @@
       </c>
       <c r="W137" s="7" t="inlineStr">
         <is>
-          <t>4 — Practitioner</t>
+          <t>3 — Partnership</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>Seaweed, Mollusk, Finfish</t>
+          <t>Mollusk</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>Habitat &amp; Biodiversity</t>
+          <t>Habitat &amp; Biodiversity, Climate Change</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>H&amp;B 1.2.1 — Mobile fauna</t>
+          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 2.1.1 — Community composition, H&amp;B 2.2.1 — Spawning, CC 3.1.1 — Wave attenuation / coastal protection</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>Cross-zone / global</t>
+          <t>Temperate Atlantic</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>Not species-specific</t>
+          <t>European flat oyster (Ostrea edulis)</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -28941,7 +28875,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>Clear (visual methods feasible)</t>
+          <t>Not site-specific</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -28961,7 +28895,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Shallow nearshore (2–10 m)</t>
+          <t>Not depth-specific</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
@@ -28971,7 +28905,7 @@
       </c>
       <c r="AK137" s="16" t="inlineStr">
         <is>
-          <t>To count mobile fauna (fish and mobile invertebrates) around a farm, run a standardized diver or snorkel belt-transect visual census: swim a fixed-length, fixed-width transect and record species and size estimates on a slate as you go. Repeat transects at the farm and a reference site and summarise as abundance and size per transect plus diversity indices. It needs dive/snorkel competency and reasonable water clarity; Reef Life Survey offers an equivalent standardized method and trained-diver network where more rigour or a citizen-science cohort is wanted.</t>
+          <t>This is the European adaptation of the TNC oyster handbook for the native flat oyster (Ostrea edulis), giving Universal, Supplementary and Goal-Based metrics with several method options per metric. Measure reef/bed extent, oyster density and size with quadrats, transect tape and calipers, choosing the method option that fits your setting, and analyse against the restoration performance questions. Use it in European native-oyster contexts where the Baggett handbook methods need adapting.</t>
         </is>
       </c>
       <c r="AL137" s="17" t="inlineStr">
@@ -28981,7 +28915,7 @@
       </c>
       <c r="AM137" s="18" t="inlineStr">
         <is>
-          <t>smithsonianmarinegeo_2021</t>
+          <t>ukireland_2021</t>
         </is>
       </c>
       <c r="AN137" s="19" t="n"/>
@@ -28989,17 +28923,17 @@
       <c r="AP137" s="19" t="n"/>
       <c r="AQ137" s="16" t="inlineStr">
         <is>
-          <t>Diver Belt-Transect Visual Census of Mobile Fauna</t>
+          <t>European Native-Oyster Restoration Monitoring Guidelines</t>
         </is>
       </c>
       <c r="AR137" s="16" t="inlineStr">
         <is>
-          <t>Smithsonian MarineGEO</t>
+          <t>Native Oyster Network (UK &amp; Ireland); Native Oyster Restoration Alliance (NORA)</t>
         </is>
       </c>
       <c r="AS137" s="16" t="inlineStr">
         <is>
-          <t>Reef Life Survey (RLS) provides an equivalent globally standardized diver visual-census methods manual and trained-diver network — an alternative where added rigour or a citizen-science cohort is wanted. Requires dive competency and reasonable water clarity.</t>
+          <t>Use for European flat-oyster (Ostrea edulis) contexts where Baggett 2014 methods need adaptation. Complementary to the MarineGEO Oyster-Reef protocol and Baggett handbook.</t>
         </is>
       </c>
     </row>
@@ -29011,7 +28945,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MarineGEO Beach Seine Protocol</t>
+          <t>MarineGEO Diver Visual Survey Protocol</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -29029,7 +28963,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Standardized beach-seine sampling of nekton (fish, mobile crustacea) in shallow soft-sediment habitats; transfers to nearshore farm-margin mobile-fauna sampling.</t>
+          <t>Standardized diver/snorkel belt-transect visual census of mobile fauna (fish, mobile invertebrates). Directly applicable to counting mobile fauna associated with a farm site.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -29039,12 +28973,12 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Yes — standardized net, haul design and processing with data sheet; reproducible.</t>
+          <t>Yes — fixed transect design with counts/size estimates and data sheet; on-the-spot ID. Reproducible across sites.</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Yes — seine hauls with field ID/measure are farmer-executable; no obligatory lab step.</t>
+          <t>Yes — belt/visual transects with field ID guides are farmer/diver-executable with no obligatory lab step (the canonical practitioner-tier method).</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -29054,7 +28988,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>Beach seine net, measuring board, buckets, ID guide</t>
+          <t>Transect tape, slate, dive/snorkel gear, ID guide</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -29069,7 +29003,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>Catch-per-haul abundance/size; diversity</t>
+          <t>Abundance/size counts per transect; diversity indices</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -29084,12 +29018,12 @@
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>https://doi.org/10.25573/serc.14925105</t>
+          <t>https://doi.org/10.25573/serc.14717796</t>
         </is>
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>Best for shallow, wadeable, soft-bottom margins.</t>
+          <t>Needs dive/snorkel competency and reasonable clarity; Reef Life Survey is an equivalent with a trained-diver network.</t>
         </is>
       </c>
       <c r="V138" t="inlineStr">
@@ -29139,7 +29073,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>Variable / seasonal</t>
+          <t>Clear (visual methods feasible)</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -29159,17 +29093,17 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Intertidal / very shallow (&lt; 2 m)</t>
+          <t>Shallow nearshore (2–10 m)</t>
         </is>
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>Sheltered</t>
+          <t>Not exposure-specific</t>
         </is>
       </c>
       <c r="AK138" s="16" t="inlineStr">
         <is>
-          <t>To sample nekton (fish and mobile crustaceans) along shallow, wadeable farm margins, use a standardized beach-seine haul: deploy the net over a set area, retrieve it, then identify, count and measure the catch on a board before release. Express results as catch-per-haul abundance and size, with diversity indices, comparing farm-margin to reference hauls. Best for shallow soft-bottom margins; it complements diver and baited-camera methods for the mobile-fauna indicator.</t>
+          <t>To count mobile fauna (fish and mobile invertebrates) around a farm, run a standardized diver or snorkel belt-transect visual census: swim a fixed-length, fixed-width transect and record species and size estimates on a slate as you go. Repeat transects at the farm and a reference site and summarise as abundance and size per transect plus diversity indices. It needs dive/snorkel competency and reasonable water clarity; Reef Life Survey offers an equivalent standardized method and trained-diver network where more rigour or a citizen-science cohort is wanted.</t>
         </is>
       </c>
       <c r="AL138" s="17" t="inlineStr">
@@ -29179,7 +29113,7 @@
       </c>
       <c r="AM138" s="18" t="inlineStr">
         <is>
-          <t>smithsonianmarinegeo_2021-b</t>
+          <t>smithsonianmarinegeo_2021</t>
         </is>
       </c>
       <c r="AN138" s="19" t="n"/>
@@ -29187,7 +29121,7 @@
       <c r="AP138" s="19" t="n"/>
       <c r="AQ138" s="16" t="inlineStr">
         <is>
-          <t>Beach-Seine Sampling of Nearshore Nekton</t>
+          <t>Diver Belt-Transect Visual Census of Mobile Fauna</t>
         </is>
       </c>
       <c r="AR138" s="16" t="inlineStr">
@@ -29197,7 +29131,7 @@
       </c>
       <c r="AS138" s="16" t="inlineStr">
         <is>
-          <t>Best for shallow, wadeable, soft-bottom margins; complements diver/BRUV methods for the mobile-fauna indicator.</t>
+          <t>Reef Life Survey (RLS) provides an equivalent globally standardized diver visual-census methods manual and trained-diver network — an alternative where added rigour or a citizen-science cohort is wanted. Requires dive competency and reasonable water clarity.</t>
         </is>
       </c>
     </row>
@@ -29209,7 +29143,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MarineGEO Benthic Photoquadrat Protocol</t>
+          <t>MarineGEO Beach Seine Protocol</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -29227,7 +29161,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Standardized photo-quadrat survey of benthic cover/community (point-count image analysis). Supports characterising the epibenthic community around a farm; for true infauna use grab-based methods (SEPA/NS 9410).</t>
+          <t>Standardized beach-seine sampling of nekton (fish, mobile crustacea) in shallow soft-sediment habitats; transfers to nearshore farm-margin mobile-fauna sampling.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -29237,12 +29171,12 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Yes — quadrat photo design with point-count image analysis (e.g., CoralNet); reproducible and re-auditable.</t>
+          <t>Yes — standardized net, haul design and processing with data sheet; reproducible.</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Partial — photo capture is farmer-doable; point-count image annotation/ID is a skilled (often partner) step.</t>
+          <t>Yes — seine hauls with field ID/measure are farmer-executable; no obligatory lab step.</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -29252,12 +29186,12 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>Quadrat frame, underwater camera; image-analysis software (CoralNet/CPCe)</t>
+          <t>Beach seine net, measuring board, buckets, ID guide</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Low–Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -29267,7 +29201,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>Point-count percent cover; community composition</t>
+          <t>Catch-per-haul abundance/size; diversity</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -29282,12 +29216,12 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>https://doi.org/10.25573/serc.14717823</t>
+          <t>https://doi.org/10.25573/serc.14925105</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>Captures epibenthic cover, not soft-sediment infauna - pair with a sediment protocol for the seabed itself.</t>
+          <t>Best for shallow, wadeable, soft-bottom margins.</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
@@ -29297,12 +29231,12 @@
       </c>
       <c r="W139" s="7" t="inlineStr">
         <is>
-          <t>3 — Partnership</t>
+          <t>4 — Practitioner</t>
         </is>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>Seaweed, Mollusk</t>
+          <t>Seaweed, Mollusk, Finfish</t>
         </is>
       </c>
       <c r="Y139" t="inlineStr">
@@ -29312,7 +29246,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>H&amp;B 1.3.1 — Benthic infauna, H&amp;B 2.1.1 — Community composition</t>
+          <t>H&amp;B 1.2.1 — Mobile fauna</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -29337,7 +29271,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>Clear (visual methods feasible)</t>
+          <t>Variable / seasonal</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -29357,17 +29291,17 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>Shallow nearshore (2–10 m)</t>
+          <t>Intertidal / very shallow (&lt; 2 m)</t>
         </is>
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>Not exposure-specific</t>
+          <t>Sheltered</t>
         </is>
       </c>
       <c r="AK139" s="16" t="inlineStr">
         <is>
-          <t>To characterise the epibenthic community (cover) around a farm, photograph benthic quadrats along transects and analyse the images by point-count (e.g. CoralNet or CPCe), scoring percent cover per taxon. Repeat at farm and reference sites and compare community composition. The image archive is re-analysable and auditable; note this captures epibenthic cover, not soft-sediment infauna - pair it with a sediment protocol for the seabed itself.</t>
+          <t>To sample nekton (fish and mobile crustaceans) along shallow, wadeable farm margins, use a standardized beach-seine haul: deploy the net over a set area, retrieve it, then identify, count and measure the catch on a board before release. Express results as catch-per-haul abundance and size, with diversity indices, comparing farm-margin to reference hauls. Best for shallow soft-bottom margins; it complements diver and baited-camera methods for the mobile-fauna indicator.</t>
         </is>
       </c>
       <c r="AL139" s="17" t="inlineStr">
@@ -29377,7 +29311,7 @@
       </c>
       <c r="AM139" s="18" t="inlineStr">
         <is>
-          <t>smithsonianmarinegeo_2021-c</t>
+          <t>smithsonianmarinegeo_2021-b</t>
         </is>
       </c>
       <c r="AN139" s="19" t="n"/>
@@ -29385,7 +29319,7 @@
       <c r="AP139" s="19" t="n"/>
       <c r="AQ139" s="16" t="inlineStr">
         <is>
-          <t>Benthic Photoquadrat Cover Survey (Point-Count Imaging)</t>
+          <t>Beach-Seine Sampling of Nearshore Nekton</t>
         </is>
       </c>
       <c r="AR139" s="16" t="inlineStr">
@@ -29395,7 +29329,7 @@
       </c>
       <c r="AS139" s="16" t="inlineStr">
         <is>
-          <t>Image archives are re-analysable and auditable. Captures epibenthic cover (not soft-sediment infauna). Pairs with the Sediment Organic Matter protocol for soft-sediment characterisation.</t>
+          <t>Best for shallow, wadeable, soft-bottom margins; complements diver/BRUV methods for the mobile-fauna indicator.</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29341,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MarineGEO Sediment Organic Matter Protocol</t>
+          <t>MarineGEO Benthic Photoquadrat Protocol</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -29425,7 +29359,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Standardized sediment sampling + loss-on-ignition for organic-matter content (a core sediment-condition descriptor under and around a farm).</t>
+          <t>Standardized photo-quadrat survey of benthic cover/community (point-count image analysis). Supports characterising the epibenthic community around a farm; for true infauna use grab-based methods (SEPA/NS 9410).</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -29435,12 +29369,12 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Yes — coring/grab + drying + loss-on-ignition with data sheet; reproducible.</t>
+          <t>Yes — quadrat photo design with point-count image analysis (e.g., CoralNet); reproducible and re-auditable.</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Partial — sediment collection farmer-doable; LOI needs a drying oven/muffle furnace (basic lab step).</t>
+          <t>Partial — photo capture is farmer-doable; point-count image annotation/ID is a skilled (often partner) step.</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -29450,12 +29384,12 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>Sediment corer/grab, drying oven, muffle furnace, balance</t>
+          <t>Quadrat frame, underwater camera; image-analysis software (CoralNet/CPCe)</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Low–Medium</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -29465,7 +29399,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>%LOI / organic-matter content; farm-vs-reference</t>
+          <t>Point-count percent cover; community composition</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -29480,12 +29414,12 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>https://doi.org/10.25573/serc.14925111</t>
+          <t>https://doi.org/10.25573/serc.14717823</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>A simple, low-cost sediment-condition metric; for full biogeochemistry use a benthic standard such as SEPA or NS 9410.</t>
+          <t>Captures epibenthic cover, not soft-sediment infauna - pair with a sediment protocol for the seabed itself.</t>
         </is>
       </c>
       <c r="V140" t="inlineStr">
@@ -29510,7 +29444,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>H&amp;B 1.4.1 — Sediment</t>
+          <t>H&amp;B 1.3.1 — Benthic infauna, H&amp;B 2.1.1 — Community composition</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -29535,7 +29469,7 @@
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>Not site-specific</t>
+          <t>Clear (visual methods feasible)</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -29545,7 +29479,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>Sediment sampling</t>
+          <t>Visual survey</t>
         </is>
       </c>
       <c r="AH140" t="inlineStr">
@@ -29555,7 +29489,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Not depth-specific</t>
+          <t>Shallow nearshore (2–10 m)</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
@@ -29565,7 +29499,7 @@
       </c>
       <c r="AK140" s="16" t="inlineStr">
         <is>
-          <t>To measure sediment organic-matter content under and around a farm, collect sediment by corer or grab, dry the sample, then combust it in a muffle furnace and weigh before and after to get percent loss-on-ignition (organic-matter content). Sample farm and reference stations and compare. It is a simple, low-cost sediment-condition metric; for full biogeochemistry (redox, sulphide, nutrient flux) use the SEPA or NS 9410 benthic standards.</t>
+          <t>To characterise the epibenthic community (cover) around a farm, photograph benthic quadrats along transects and analyse the images by point-count (e.g. CoralNet or CPCe), scoring percent cover per taxon. Repeat at farm and reference sites and compare community composition. The image archive is re-analysable and auditable; note this captures epibenthic cover, not soft-sediment infauna - pair it with a sediment protocol for the seabed itself.</t>
         </is>
       </c>
       <c r="AL140" s="17" t="inlineStr">
@@ -29575,7 +29509,7 @@
       </c>
       <c r="AM140" s="18" t="inlineStr">
         <is>
-          <t>smithsonianmarinegeo_2021-d</t>
+          <t>smithsonianmarinegeo_2021-c</t>
         </is>
       </c>
       <c r="AN140" s="19" t="n"/>
@@ -29583,7 +29517,7 @@
       <c r="AP140" s="19" t="n"/>
       <c r="AQ140" s="16" t="inlineStr">
         <is>
-          <t>Sediment Organic-Matter Monitoring (Loss-on-Ignition)</t>
+          <t>Benthic Photoquadrat Cover Survey (Point-Count Imaging)</t>
         </is>
       </c>
       <c r="AR140" s="16" t="inlineStr">
@@ -29593,45 +29527,37 @@
       </c>
       <c r="AS140" s="16" t="inlineStr">
         <is>
-          <t>A simple, low-cost sediment-condition metric; for full biogeochemistry (redox, sulphide, DIN flux) use the SEPA / NS 9410 benthic standards (rows below).</t>
+          <t>Image archives are re-analysable and auditable. Captures epibenthic cover (not soft-sediment infauna). Pairs with the Sediment Organic Matter protocol for soft-sediment characterisation.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Langlois, T., et al.</t>
+          <t>Smithsonian MarineGEO</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>A field and video-annotation guide for baited remote underwater stereo-video (stereo-BRUV) surveys of demersal fish assemblages</t>
+          <t>MarineGEO Sediment Organic Matter Protocol</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Methods in Ecology and Evolution / open NESP field manual</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>11</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>1401–1409</t>
+          <t>Smithsonian Environmental Research Center (MarineGEO Protocols)</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Wiley / NESP Marine Biodiversity Hub</t>
+          <t>Smithsonian Institution</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>The first globally accepted standardized guide for stereo-BRUV surveys of fish assemblages — design, camera settings, field operations, and video annotation, with links to data validation/archiving (GlobalArchive). Covers mobile fauna and the finfish fish-attraction case.</t>
+          <t>Standardized sediment sampling + loss-on-ignition for organic-matter content (a core sediment-condition descriptor under and around a farm).</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -29641,12 +29567,12 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Yes — fully documented field + annotation SOP intended for cross-study interoperability (FAIR workflows).</t>
+          <t>Yes — coring/grab + drying + loss-on-ignition with data sheet; reproducible.</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Partial — baited-camera deployment is practitioner-doable, but stereo calibration and photogrammetric annotation/measurement (EventMeasure) need a trained analyst or partner.</t>
+          <t>Partial — sediment collection farmer-doable; LOI needs a drying oven/muffle furnace (basic lab step).</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -29656,27 +29582,27 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>Stereo camera pair + frame, bait arm, ropes/floats; annotation software (EventMeasure)</t>
+          <t>Sediment corer/grab, drying oven, muffle furnace, balance</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Short campaign (days to 2 weeks)</t>
+          <t>Seasonal (1–3 months)</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>MaxN relative abundance, length/biomass from stereo; assemblage composition</t>
+          <t>%LOI / organic-matter content; farm-vs-reference</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>Yes — Open (CC-BY; open GitHub manual)</t>
+          <t>Yes — Open (DOI-published)</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
@@ -29686,12 +29612,12 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>https://benthic-bruvs-field-manual.github.io/ ; https://doi.org/10.1111/2041-210X.13470</t>
+          <t>https://doi.org/10.25573/serc.14925111</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>A single-camera BRUV is a lower-cost variant (relative abundance only, no lengths).</t>
+          <t>A simple, low-cost sediment-condition metric; for full biogeochemistry use a benthic standard such as SEPA or NS 9410.</t>
         </is>
       </c>
       <c r="V141" t="inlineStr">
@@ -29706,7 +29632,7 @@
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>Mollusk, Finfish, Seaweed</t>
+          <t>Seaweed, Mollusk</t>
         </is>
       </c>
       <c r="Y141" t="inlineStr">
@@ -29716,7 +29642,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>H&amp;B 1.2.1 — Mobile fauna</t>
+          <t>H&amp;B 1.4.1 — Sediment</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -29741,7 +29667,7 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>Clear (visual methods feasible)</t>
+          <t>Not site-specific</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -29751,7 +29677,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>BRUVs / video</t>
+          <t>Sediment sampling</t>
         </is>
       </c>
       <c r="AH141" t="inlineStr">
@@ -29761,7 +29687,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Coastal (10–30 m)</t>
+          <t>Not depth-specific</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
@@ -29771,7 +29697,7 @@
       </c>
       <c r="AK141" s="16" t="inlineStr">
         <is>
-          <t>To survey fish assemblages (mobile fauna, and fish attraction at finfish farms) without diving, deploy baited remote underwater stereo-video (stereo-BRUV): a paired-camera frame with a bait arm, set on the seabed for a standard soak. Annotate the video to relative abundance (MaxN) and, from the stereo pair, individual lengths and biomass, following the standardized field-and-annotation SOP for cross-study comparability. A single-camera BRUV is a lower-cost practitioner variant (relative abundance only, no lengths), and data archive to a standardized repository (GlobalArchive).</t>
+          <t>To measure sediment organic-matter content under and around a farm, collect sediment by corer or grab, dry the sample, then combust it in a muffle furnace and weigh before and after to get percent loss-on-ignition (organic-matter content). Sample farm and reference stations and compare. It is a simple, low-cost sediment-condition metric; for full biogeochemistry (redox, sulphide, nutrient flux) use the SEPA or NS 9410 benthic standards.</t>
         </is>
       </c>
       <c r="AL141" s="17" t="inlineStr">
@@ -29781,7 +29707,7 @@
       </c>
       <c r="AM141" s="18" t="inlineStr">
         <is>
-          <t>langlois_2020</t>
+          <t>smithsonianmarinegeo_2021-d</t>
         </is>
       </c>
       <c r="AN141" s="19" t="n"/>
@@ -29789,62 +29715,70 @@
       <c r="AP141" s="19" t="n"/>
       <c r="AQ141" s="16" t="inlineStr">
         <is>
-          <t>Baited Stereo-Video Survey of Fish Assemblages (Stereo-BRUV)</t>
+          <t>Sediment Organic-Matter Monitoring (Loss-on-Ignition)</t>
         </is>
       </c>
       <c r="AR141" s="16" t="inlineStr">
         <is>
-          <t>Langlois, T.; Goetze, J.; Bond, T.; et al. (NESP Marine Biodiversity Hub)</t>
+          <t>Smithsonian MarineGEO</t>
         </is>
       </c>
       <c r="AS141" s="16" t="inlineStr">
         <is>
-          <t>Single-camera baited cameras (BRUVs) are a lower-cost practitioner variant (relative abundance only, no lengths). GlobalArchive (globalarchive.org) is the standardized data repository. Part of the NESP Marine Sampling Field Manuals collection (next row). For finfish, this is the route to the fish-attraction facet of Finfish H&amp;B 2.1.1.</t>
+          <t>A simple, low-cost sediment-condition metric; for full biogeochemistry (redox, sulphide, DIN flux) use the SEPA / NS 9410 benthic standards (rows below).</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Przeslawski, R. &amp; Foster, S. (. ). —. N. M. B. H.</t>
+          <t>Langlois, T., et al.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Field Manuals for Marine Sampling to Monitor Australian Waters (BRUVs, grabs, sleds, towed video, AUVs)</t>
+          <t>A field and video-annotation guide for baited remote underwater stereo-video (stereo-BRUV) surveys of demersal fish assemblages</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>NESP Marine Biodiversity Hub</t>
+          <t>Methods in Ecology and Evolution / open NESP field manual</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>1401–1409</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>National Environmental Science Program (Australia)</t>
+          <t>Wiley / NESP Marine Biodiversity Hub</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>A collection of standardized field-sampling SOPs (benthic stereo-BRUVs, grabs/cores, sleds, towed video, multibeam) used as a national design standard, spanning mobile fauna, benthic infauna and sediment.</t>
+          <t>The first globally accepted standardized guide for stereo-BRUV surveys of fish assemblages — design, camera settings, field operations, and video annotation, with links to data validation/archiving (GlobalArchive). Covers mobile fauna and the finfish fish-attraction case.</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Reference (usable design tool / SOP collection)</t>
+          <t>Protocol</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Adequate as a design/standardisation resource: each manual gives equipment, deployment and QA guidance a programme is built from; individual manuals are themselves executable protocols.</t>
+          <t>Yes — fully documented field + annotation SOP intended for cross-study interoperability (FAIR workflows).</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>No — most manuals assume a research vessel and specialist gear/expertise across the workflow.</t>
+          <t>Partial — baited-camera deployment is practitioner-doable, but stereo calibration and photogrammetric annotation/measurement (EventMeasure) need a trained analyst or partner.</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -29854,42 +29788,42 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>Varies by manual (research vessel, grabs, towed/stereo video, multibeam)</t>
+          <t>Stereo camera pair + frame, bait arm, ropes/floats; annotation software (EventMeasure)</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Not time-specific</t>
+          <t>Short campaign (days to 2 weeks)</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>Per-manual standardized analysis</t>
+          <t>MaxN relative abundance, length/biomass from stereo; assemblage composition</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>Yes — Open (CC-BY)</t>
+          <t>Yes — Open (CC-BY; open GitHub manual)</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>Abstract only</t>
+          <t>Abstract + Methods (fetched)</t>
         </is>
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>https://www.nespmarine.edu.au/field-manuals</t>
+          <t>https://benthic-bruvs-field-manual.github.io/ ; https://doi.org/10.1111/2041-210X.13470</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>Use it to design comparable benthic and mobile-fauna campaigns and to standardise across individual manuals.</t>
+          <t>A single-camera BRUV is a lower-cost variant (relative abundance only, no lengths).</t>
         </is>
       </c>
       <c r="V142" t="inlineStr">
@@ -29899,22 +29833,22 @@
       </c>
       <c r="W142" s="7" t="inlineStr">
         <is>
-          <t>2 — Researcher</t>
+          <t>3 — Partnership</t>
         </is>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>Seaweed, Mollusk, Finfish</t>
+          <t>Mollusk, Finfish, Seaweed</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>Habitat &amp; Biodiversity, Cross-cutting / Framework</t>
+          <t>Habitat &amp; Biodiversity</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>H&amp;B 1.2.1 — Mobile fauna, H&amp;B 1.3.1 — Benthic infauna, H&amp;B 1.4.1 — Sediment, Cross-cutting / framework</t>
+          <t>H&amp;B 1.2.1 — Mobile fauna</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -29939,7 +29873,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>Not site-specific</t>
+          <t>Clear (visual methods feasible)</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -29949,7 +29883,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>Mixed methods</t>
+          <t>BRUVs / video</t>
         </is>
       </c>
       <c r="AH142" t="inlineStr">
@@ -29959,7 +29893,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>Not depth-specific</t>
+          <t>Coastal (10–30 m)</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
@@ -29969,17 +29903,17 @@
       </c>
       <c r="AK142" s="16" t="inlineStr">
         <is>
-          <t>This is a collection of standardized Australian field-sampling manuals (benthic stereo-BRUVs, grabs and cores, towed video, sleds, multibeam) used as a national design standard spanning mobile fauna, benthic infauna and sediment. Use it to design comparable benthic and mobile-fauna campaigns and to lift indicator-specific manuals (such as the stereo-BRUV manual) into a coherent programme, rather than as a single procedure.</t>
+          <t>To survey fish assemblages (mobile fauna, and fish attraction at finfish farms) without diving, deploy baited remote underwater stereo-video (stereo-BRUV): a paired-camera frame with a bait arm, set on the seabed for a standard soak. Annotate the video to relative abundance (MaxN) and, from the stereo pair, individual lengths and biomass, following the standardized field-and-annotation SOP for cross-study comparability. A single-camera BRUV is a lower-cost practitioner variant (relative abundance only, no lengths), and data archive to a standardized repository (GlobalArchive).</t>
         </is>
       </c>
       <c r="AL142" s="17" t="inlineStr">
         <is>
-          <t>Ref</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="AM142" s="18" t="inlineStr">
         <is>
-          <t>przeslawski_2018</t>
+          <t>langlois_2020</t>
         </is>
       </c>
       <c r="AN142" s="19" t="n"/>
@@ -29987,62 +29921,62 @@
       <c r="AP142" s="19" t="n"/>
       <c r="AQ142" s="16" t="inlineStr">
         <is>
-          <t>Australian Marine-Sampling Field Manuals (Design Reference)</t>
+          <t>Baited Stereo-Video Survey of Fish Assemblages (Stereo-BRUV)</t>
         </is>
       </c>
       <c r="AR142" s="16" t="inlineStr">
         <is>
-          <t>Przeslawski, R.; Foster, S. (eds.) — NESP Marine Biodiversity Hub</t>
+          <t>Langlois, T.; Goetze, J.; Bond, T.; et al. (NESP Marine Biodiversity Hub)</t>
         </is>
       </c>
       <c r="AS142" s="16" t="inlineStr">
         <is>
-          <t>Most useful for designing comparable benthic/mobile-fauna campaigns; lifts indicator-specific manuals (e.g., the stereo-BRUV manual above) into a coherent programme. Tier T2 as a researcher-grade design tool.</t>
+          <t>Single-camera baited cameras (BRUVs) are a lower-cost practitioner variant (relative abundance only, no lengths). GlobalArchive (globalarchive.org) is the standardized data repository. Part of the NESP Marine Sampling Field Manuals collection (next row). For finfish, this is the route to the fish-attraction facet of Finfish H&amp;B 2.1.1.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Scottish Environment Protection Agency (SEPA)</t>
+          <t>Przeslawski, R. &amp; Foster, S. (. ). —. N. M. B. H.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Fish Farm Manual — Benthic Monitoring (Standard &amp; Extended surveys; Infaunal Quality Index)</t>
+          <t>Field Manuals for Marine Sampling to Monitor Australian Waters (BRUVs, grabs, sleds, towed video, AUVs)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SEPA Aquaculture regulatory guidance</t>
+          <t>NESP Marine Biodiversity Hub</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Scottish Environment Protection Agency</t>
+          <t>National Environmental Science Program (Australia)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Regulated benthic-monitoring SOP for marine farms: benthic grab survey, sediment chemistry, and the Infaunal Quality Index (IQI = taxa diversity + AMBI + Simpson evenness). Finfish-origin but the infauna+sediment methodology transfers to bivalve/seaweed farm monitoring.</t>
+          <t>A collection of standardized field-sampling SOPs (benthic stereo-BRUVs, grabs/cores, sleds, towed video, multibeam) used as a national design standard, spanning mobile fauna, benthic infauna and sediment.</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Protocol</t>
+          <t>Reference (usable design tool / SOP collection)</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Yes — prescriptive grab design, sieving/fixation, taxonomic processing and index computation with reporting templates. Compliance-grade reproducibility.</t>
+          <t>Adequate as a design/standardisation resource: each manual gives equipment, deployment and QA guidance a programme is built from; individual manuals are themselves executable protocols.</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>Partial — grab sampling from a small vessel is farmer-doable, but macrofauna sorting/ID and sediment chemistry require an accredited partner lab.</t>
+          <t>No — most manuals assume a research vessel and specialist gear/expertise across the workflow.</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -30052,42 +29986,42 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>Day/van-Veen grab, sieves (0.5/1 mm), sample jars; partner lab for taxonomy + sediment chem</t>
+          <t>Varies by manual (research vessel, grabs, towed/stereo video, multibeam)</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Medium–High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Seasonal (1–3 months)</t>
+          <t>Not time-specific</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>IQI/AMBI biotic indices; sediment-chemistry thresholds; mixing-zone assessment</t>
+          <t>Per-manual standardized analysis</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>Yes — Open (SEPA PDF)</t>
+          <t>Yes — Open (CC-BY)</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>Abstract + Methods (fetched)</t>
+          <t>Abstract only</t>
         </is>
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>https://www.sepa.org.uk/media/115592/fish-farm-manual-benthic-extended.pdf</t>
+          <t>https://www.nespmarine.edu.au/field-manuals</t>
         </is>
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>A regulatory impact standard; the grab-to-IQI workflow is the standard route to the benthic-infauna and sediment indicators.</t>
+          <t>Use it to design comparable benthic and mobile-fauna campaigns and to standardise across individual manuals.</t>
         </is>
       </c>
       <c r="V143" t="inlineStr">
@@ -30097,27 +30031,27 @@
       </c>
       <c r="W143" s="7" t="inlineStr">
         <is>
-          <t>3 — Partnership</t>
+          <t>2 — Researcher</t>
         </is>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>Mollusk, Finfish</t>
+          <t>Seaweed, Mollusk, Finfish</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>Habitat &amp; Biodiversity</t>
+          <t>Habitat &amp; Biodiversity, Cross-cutting / Framework</t>
         </is>
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>H&amp;B 1.3.1 — Benthic infauna, H&amp;B 1.4.1 — Sediment</t>
+          <t>H&amp;B 1.2.1 — Mobile fauna, H&amp;B 1.3.1 — Benthic infauna, H&amp;B 1.4.1 — Sediment, Cross-cutting / framework</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>Temperate Atlantic</t>
+          <t>Cross-zone / global</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
@@ -30147,7 +30081,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>Sediment sampling</t>
+          <t>Mixed methods</t>
         </is>
       </c>
       <c r="AH143" t="inlineStr">
@@ -30157,7 +30091,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>Coastal (10–30 m)</t>
+          <t>Not depth-specific</t>
         </is>
       </c>
       <c r="AJ143" t="inlineStr">
@@ -30167,17 +30101,17 @@
       </c>
       <c r="AK143" s="16" t="inlineStr">
         <is>
-          <t>Although written for finfish farms, this regulated benthic-monitoring SOP transfers to bivalve/seaweed farm seabed monitoring. Take grab samples (day or van Veen) along the farm and mixing-zone gradient, sieve (0.5-1 mm) and fix the retained infauna, then have a partner lab identify taxa and measure sediment chemistry. Compute the Infaunal Quality Index (taxa diversity + AMBI + Simpson evenness) and compare against sediment-chemistry thresholds and a mixing-zone assessment. The grab-to-IQI workflow is a compliance-grade route to the benthic-infauna and sediment indicators, directly comparable to Norway's NS 9410 / MOM.</t>
+          <t>This is a collection of standardized Australian field-sampling manuals (benthic stereo-BRUVs, grabs and cores, towed video, sleds, multibeam) used as a national design standard spanning mobile fauna, benthic infauna and sediment. Use it to design comparable benthic and mobile-fauna campaigns and to lift indicator-specific manuals (such as the stereo-BRUV manual) into a coherent programme, rather than as a single procedure.</t>
         </is>
       </c>
       <c r="AL143" s="17" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Ref</t>
         </is>
       </c>
       <c r="AM143" s="18" t="inlineStr">
         <is>
-          <t>sepa_2019</t>
+          <t>przeslawski_2018</t>
         </is>
       </c>
       <c r="AN143" s="19" t="n"/>
@@ -30185,47 +30119,47 @@
       <c r="AP143" s="19" t="n"/>
       <c r="AQ143" s="16" t="inlineStr">
         <is>
-          <t>Regulated Benthic Monitoring: Grab Survey to Infaunal Quality Index</t>
+          <t>Australian Marine-Sampling Field Manuals (Design Reference)</t>
         </is>
       </c>
       <c r="AR143" s="16" t="inlineStr">
         <is>
-          <t>Scottish Environment Protection Agency (SEPA)</t>
+          <t>Przeslawski, R.; Foster, S. (eds.) — NESP Marine Biodiversity Hub</t>
         </is>
       </c>
       <c r="AS143" s="16" t="inlineStr">
         <is>
-          <t>A regulatory impact-monitoring standard rather than a benefit protocol, but the grab→IQI workflow is the standard route to the benthic-infauna and sediment indicators. Directly comparable to Norway NS 9410 / MOM (next row).</t>
+          <t>Most useful for designing comparable benthic/mobile-fauna campaigns; lifts indicator-specific manuals (e.g., the stereo-BRUV manual above) into a coherent programme. Tier T2 as a researcher-grade design tool.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Standards Norway</t>
+          <t>Scottish Environment Protection Agency (SEPA)</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>NS 9410 — Environmental monitoring of benthic impact from marine aquaculture (MOM B- and C-assessments)</t>
+          <t>Fish Farm Manual — Benthic Monitoring (Standard &amp; Extended surveys; Infaunal Quality Index)</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Norwegian Standard (Standards Norway)</t>
+          <t>SEPA Aquaculture regulatory guidance</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Standards Norway</t>
+          <t>Scottish Environment Protection Agency</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Norway's legally required benthic-monitoring standard built on the MOM approach. B-assessment (under-cage): pH, redox potential, sensory attributes and macrofauna presence; C-assessment (30–500 m zones): full soft-bottom community + sediment chemistry, NSI/biotic indices.</t>
+          <t>Regulated benthic-monitoring SOP for marine farms: benthic grab survey, sediment chemistry, and the Infaunal Quality Index (IQI = taxa diversity + AMBI + Simpson evenness). Finfish-origin but the infauna+sediment methodology transfers to bivalve/seaweed farm monitoring.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -30235,12 +30169,12 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Yes — standardized field sampling and scoring with defined thresholds; the B-survey is a rapid field assessment, the C-survey a full benthic/chemistry programme.</t>
+          <t>Yes — prescriptive grab design, sieving/fixation, taxonomic processing and index computation with reporting templates. Compliance-grade reproducibility.</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Partial — the B-survey (grab + field pH/redox/sensory) is largely field-executable; the C-survey needs full taxonomy + sediment chemistry via partner lab.</t>
+          <t>Partial — grab sampling from a small vessel is farmer-doable, but macrofauna sorting/ID and sediment chemistry require an accredited partner lab.</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -30250,12 +30184,12 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>Grab, field pH/redox probes; partner lab for C-survey taxonomy/chemistry</t>
+          <t>Day/van-Veen grab, sieves (0.5/1 mm), sample jars; partner lab for taxonomy + sediment chem</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Medium–High</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -30265,27 +30199,27 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>B-index scoring; NSI/biotic indices; sediment chemistry</t>
+          <t>IQI/AMBI biotic indices; sediment-chemistry thresholds; mixing-zone assessment</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>No — Paywalled (purchase via Standards Norway)</t>
+          <t>Yes — Open (SEPA PDF)</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>Abstract only</t>
+          <t>Abstract + Methods (fetched)</t>
         </is>
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>https://www.standard.no (NS 9410)</t>
+          <t>https://www.sepa.org.uk/media/115592/fish-farm-manual-benthic-extended.pdf</t>
         </is>
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>The standard itself is paywalled, so confirm the exact thresholds from the document before relying on them.</t>
+          <t>A regulatory impact standard; the grab-to-IQI workflow is the standard route to the benthic-infauna and sediment indicators.</t>
         </is>
       </c>
       <c r="V144" t="inlineStr">
@@ -30295,7 +30229,7 @@
       </c>
       <c r="W144" s="7" t="inlineStr">
         <is>
-          <t>2 — Researcher</t>
+          <t>3 — Partnership</t>
         </is>
       </c>
       <c r="X144" t="inlineStr">
@@ -30315,7 +30249,7 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>Boreal / Arctic</t>
+          <t>Temperate Atlantic</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
@@ -30365,17 +30299,17 @@
       </c>
       <c r="AK144" s="16" t="inlineStr">
         <is>
-          <t>This is Norway's legally required benthic-monitoring standard, built on the MOM approach, with two tiers. The under-cage B-assessment is a rapid field survey scoring sediment pH, redox potential, sensory attributes and macrofauna presence/absence into condition classes; the zone (C) assessment is a fuller soft-bottom community survey plus sediment chemistry with biotic indices. Sample with a grab and field pH/redox probes for the B-survey, adding lab taxonomy and chemistry for the C-survey. (Summary from secondary sources - the standard itself is paywalled, so confirm exact thresholds from the document before relying on them.)</t>
+          <t>Although written for finfish farms, this regulated benthic-monitoring SOP transfers to bivalve/seaweed farm seabed monitoring. Take grab samples (day or van Veen) along the farm and mixing-zone gradient, sieve (0.5-1 mm) and fix the retained infauna, then have a partner lab identify taxa and measure sediment chemistry. Compute the Infaunal Quality Index (taxa diversity + AMBI + Simpson evenness) and compare against sediment-chemistry thresholds and a mixing-zone assessment. The grab-to-IQI workflow is a compliance-grade route to the benthic-infauna and sediment indicators, directly comparable to Norway's NS 9410 / MOM.</t>
         </is>
       </c>
       <c r="AL144" s="17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="AM144" s="18" t="inlineStr">
         <is>
-          <t>standardsnorway_2016</t>
+          <t>sepa_2019</t>
         </is>
       </c>
       <c r="AN144" s="19" t="n"/>
@@ -30383,47 +30317,47 @@
       <c r="AP144" s="19" t="n"/>
       <c r="AQ144" s="16" t="inlineStr">
         <is>
-          <t>Norwegian MOM Benthic-Monitoring Standard (NS 9410)</t>
+          <t>Regulated Benthic Monitoring: Grab Survey to Infaunal Quality Index</t>
         </is>
       </c>
       <c r="AR144" s="16" t="inlineStr">
         <is>
-          <t>Standards Norway</t>
+          <t>Scottish Environment Protection Agency (SEPA)</t>
         </is>
       </c>
       <c r="AS144" s="16" t="inlineStr">
         <is>
-          <t>Standard document is paywalled; methodology well-documented in secondary literature. Tier set conservatively at T2 (Sub-rule 14a) pending a read of the standard itself — the B-survey component is plausibly T3/Partnership once confirmed. Directly comparable to the SEPA manual.</t>
+          <t>A regulatory impact-monitoring standard rather than a benefit protocol, but the grab→IQI workflow is the standard route to the benthic-infauna and sediment indicators. Directly comparable to Norway NS 9410 / MOM (next row).</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Scottish Salmon Producers' Org. (Code of Good Practice)</t>
+          <t>Standards Norway</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Sea lice counting &amp; surveillance protocols (farmed and wild fish)</t>
+          <t>NS 9410 — Environmental monitoring of benthic impact from marine aquaculture (MOM B- and C-assessments)</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Industry Code of Good Practice / national surveillance protocols</t>
+          <t>Norwegian Standard (Standards Norway)</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Multiple (Scotland; Norway)</t>
+          <t>Standards Norway</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Standardized protocols for counting sea lice on farmed salmon (and sentinel/wild salmonids): fixed sampling design (e.g., 5 fish × 5 pens = 25 fish), stage-resolved lice counts, and trigger levels. Under the finfish indicator set this is the parasite/pathogen-surveillance facet of Finfish H&amp;B 2.1.1 (farmed + nearby wild stock).</t>
+          <t>Norway's legally required benthic-monitoring standard built on the MOM approach. B-assessment (under-cage): pH, redox potential, sensory attributes and macrofauna presence; C-assessment (30–500 m zones): full soft-bottom community + sediment chemistry, NSI/biotic indices.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -30433,12 +30367,12 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Yes — prescriptive fish-sampling and lice-staging counts with defined trigger thresholds; farm-staff counts validated against dedicated teams.</t>
+          <t>Yes — standardized field sampling and scoring with defined thresholds; the B-survey is a rapid field assessment, the C-survey a full benthic/chemistry programme.</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Partial — farm-level counting on netted fish is genuinely farm-staff (practitioner) executable; the rigorous wild-salmonid surveillance variant needs IMR-style certification and sentinel-cage/trawl capacity (partner).</t>
+          <t>Partial — the B-survey (grab + field pH/redox/sensory) is largely field-executable; the C-survey needs full taxonomy + sediment chemistry via partner lab.</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -30448,37 +30382,42 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>Anaesthetic/handling kit, hand lens/loupe; (automated camera systems emerging)</t>
+          <t>Grab, field pH/redox probes; partner lab for C-survey taxonomy/chemistry</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Low–Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Multi-year monitoring (&gt; 1 year)</t>
+          <t>Seasonal (1–3 months)</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>Prevalence/abundance per fish (negative-binomial/normal); trigger-level comparison</t>
+          <t>B-index scoring; NSI/biotic indices; sediment chemistry</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>Yes — Open (CoGP &amp; national guidance)</t>
+          <t>No — Paywalled (purchase via Standards Norway)</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>Abstract + Methods (fetched)</t>
+          <t>Abstract only</t>
         </is>
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>Scottish Code of Good Practice: thecodeofgoodpractice.co.uk ; Norway IMR: https://www.hi.no/en/hi/nettrapporter/rapport-fra-havforskningen-en-2024-61</t>
+          <t>https://www.standard.no (NS 9410)</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>The standard itself is paywalled, so confirm the exact thresholds from the document before relying on them.</t>
         </is>
       </c>
       <c r="V145" t="inlineStr">
@@ -30488,12 +30427,12 @@
       </c>
       <c r="W145" s="7" t="inlineStr">
         <is>
-          <t>3 — Partnership</t>
+          <t>2 — Researcher</t>
         </is>
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>Finfish</t>
+          <t>Mollusk, Finfish</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
@@ -30503,12 +30442,12 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>H&amp;B 2.1.1 — Community composition</t>
+          <t>H&amp;B 1.3.1 — Benthic infauna, H&amp;B 1.4.1 — Sediment</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>Temperate Atlantic</t>
+          <t>Boreal / Arctic</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
@@ -30518,7 +30457,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Floating cage / tray</t>
+          <t>Not gear-specific</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr">
@@ -30533,12 +30472,12 @@
       </c>
       <c r="AF145" t="inlineStr">
         <is>
-          <t>Monoculture</t>
+          <t>Not specific</t>
         </is>
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>Visual survey</t>
+          <t>Sediment sampling</t>
         </is>
       </c>
       <c r="AH145" t="inlineStr">
@@ -30558,17 +30497,17 @@
       </c>
       <c r="AK145" s="16" t="inlineStr">
         <is>
-          <t>To monitor sea-lice burden on farmed salmon (the parasite/pathogen-surveillance facet of the finfish community-composition indicator), follow a fixed sampling design - for example five fish from each of five pens (25 fish) on a set schedule - anaesthetising and examining each fish and counting lice by life stage under a hand lens. Report prevalence and abundance per fish and compare against defined trigger levels that prompt action. Farm-staff counts are typically validated against dedicated teams, and sentinel/wild-salmonid counting extends the same method beyond the farm.</t>
+          <t>This is Norway's legally required benthic-monitoring standard, built on the MOM approach, with two tiers. The under-cage B-assessment is a rapid field survey scoring sediment pH, redox potential, sensory attributes and macrofauna presence/absence into condition classes; the zone (C) assessment is a fuller soft-bottom community survey plus sediment chemistry with biotic indices. Sample with a grab and field pH/redox probes for the B-survey, adding lab taxonomy and chemistry for the C-survey. (Summary from secondary sources - the standard itself is paywalled, so confirm exact thresholds from the document before relying on them.)</t>
         </is>
       </c>
       <c r="AL145" s="17" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AM145" s="18" t="inlineStr">
         <is>
-          <t>scottishsalmon_2023</t>
+          <t>standardsnorway_2016</t>
         </is>
       </c>
       <c r="AN145" s="19" t="n"/>
@@ -30576,34 +30515,34 @@
       <c r="AP145" s="19" t="n"/>
       <c r="AQ145" s="16" t="inlineStr">
         <is>
-          <t>Sea-Lice Counting &amp; Surveillance Protocol</t>
+          <t>Norwegian MOM Benthic-Monitoring Standard (NS 9410)</t>
         </is>
       </c>
       <c r="AR145" s="16" t="inlineStr">
         <is>
-          <t>Scottish Salmon Producers' Org. (Code of Good Practice); Institute of Marine Research (Norway); Norwegian Food Safety Authority</t>
+          <t>Standards Norway</t>
         </is>
       </c>
       <c r="AS145" s="16" t="inlineStr">
         <is>
-          <t>The Norwegian Salmon Lice Directive (FOR-2009-08-18-1095) is the regulatory framework mandating counting; the IMR protocol is the certified standardized count for the national wild-salmonid programme. Farm-level counting alone is closer to T4; tier set at T3 to cover the full indicator (incl. wild-population surveillance to ~2.5 km). Tagged with the generic 'H&amp;B 2.1.1' string; under the finfish set this is fish-attraction / parasite surveillance.</t>
+          <t>Standard document is paywalled; methodology well-documented in secondary literature. Tier set conservatively at T2 (Sub-rule 14a) pending a read of the standard itself — the B-survey component is plausibly T3/Partnership once confirmed. Directly comparable to the SEPA manual.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Reichert-Nguyen, J., et al.</t>
+          <t>Scottish Salmon Producers' Org. (Code of Good Practice)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Oyster BMP Expert Panel Reports — Nutrient &amp; Suspended-Sediment Reduction Effectiveness Protocols (First Report 2016; Second Report 2023)</t>
+          <t>Sea lice counting &amp; surveillance protocols (farmed and wild fish)</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Chesapeake Bay Program / Oyster Recovery Partnership</t>
+          <t>Industry Code of Good Practice / national surveillance protocols</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -30611,12 +30550,12 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Chesapeake Bay Program</t>
+          <t>Multiple (Scotland; Norway)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Crediting-and-verification protocols defining reduction-effectiveness for oyster practices: N &amp; P assimilation in tissue, N &amp; P assimilation in shell, enhanced denitrification, and N/P burial. The tissue/shell protocols are the standardized bioextraction route; the denitrification protocol is one of very few packaged methods for that indicator.</t>
+          <t>Standardized protocols for counting sea lice on farmed salmon (and sentinel/wild salmonids): fixed sampling design (e.g., 5 fish × 5 pens = 25 fish), stage-resolved lice counts, and trigger levels. Under the finfish indicator set this is the parasite/pathogen-surveillance facet of Finfish H&amp;B 2.1.1 (farmed + nearby wild stock).</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -30626,12 +30565,12 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Yes — defines harvest accounting (count × size → tissue/shell N&amp;P via published content) and the enhanced-denitrification crediting method, with verification guidelines. Decision-framework + effectiveness estimates.</t>
+          <t>Yes — prescriptive fish-sampling and lice-staging counts with defined trigger thresholds; farm-staff counts validated against dedicated teams.</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>Partial — counting/measuring harvested oysters is farmer-executable; tissue/shell %N&amp;P (CHN analyser) and denitrification (N2-flux/15N) need a partner lab, though published default coefficients allow a desk estimate.</t>
+          <t>Partial — farm-level counting on netted fish is genuinely farm-staff (practitioner) executable; the rigorous wild-salmonid surveillance variant needs IMR-style certification and sentinel-cage/trawl capacity (partner).</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -30641,27 +30580,27 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>Harvest records, calipers; partner lab CHN analyser; (denitrification: benthic-flux/15N)</t>
+          <t>Anaesthetic/handling kit, hand lens/loupe; (automated camera systems emerging)</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low–Medium</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Year-long study (12 months)</t>
+          <t>Multi-year monitoring (&gt; 1 year)</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Reduction-effectiveness accounting; verification protocol</t>
+          <t>Prevalence/abundance per fish (negative-binomial/normal); trigger-level comparison</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>Yes — Open (CBP PDFs)</t>
+          <t>Yes — Open (CoGP &amp; national guidance)</t>
         </is>
       </c>
       <c r="S146" t="inlineStr">
@@ -30671,12 +30610,7 @@
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>https://d18lev1ok5leia.cloudfront.net/chesapeakebay/documents/Oyster-BMP-Expert-Panel-Second-Report.pdf</t>
-        </is>
-      </c>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t>Default tissue/shell coefficients make a credible desk estimate feasible without a lab; shell accounting here is for N and P, not carbon.</t>
+          <t>Scottish Code of Good Practice: thecodeofgoodpractice.co.uk ; Norway IMR: https://www.hi.no/en/hi/nettrapporter/rapport-fra-havforskningen-en-2024-61</t>
         </is>
       </c>
       <c r="V146" t="inlineStr">
@@ -30691,17 +30625,17 @@
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>Mollusk</t>
+          <t>Finfish</t>
         </is>
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>Water Quality</t>
+          <t>Habitat &amp; Biodiversity</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>WQ 1.1.1 — N and P bioextraction, WQ 1.1.2 — Rate of denitrification</t>
+          <t>H&amp;B 2.1.1 — Community composition</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -30711,12 +30645,12 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>Eastern oyster (Crassostrea virginica)</t>
+          <t>Not species-specific</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Not gear-specific</t>
+          <t>Floating cage / tray</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr">
@@ -30731,12 +30665,12 @@
       </c>
       <c r="AF146" t="inlineStr">
         <is>
-          <t>Not specific</t>
+          <t>Monoculture</t>
         </is>
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>Tissue analysis</t>
+          <t>Visual survey</t>
         </is>
       </c>
       <c r="AH146" t="inlineStr">
@@ -30746,7 +30680,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>Not depth-specific</t>
+          <t>Coastal (10–30 m)</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
@@ -30756,7 +30690,7 @@
       </c>
       <c r="AK146" s="16" t="inlineStr">
         <is>
-          <t>This crediting-and-verification protocol standardizes how to account for nutrients an oyster practice removes: nitrogen and phosphorus assimilated in harvested tissue and shell, plus enhanced denitrification and burial. For the bioextraction route, record harvest (count x size) and convert to tissue/shell N and P using published content coefficients (or a partner-lab CHN analysis); the denitrification route uses benthic-flux or 15N methods. Default coefficients make a credible desk estimate feasible without a lab. Note shell accounting here is for N and P, not carbon - no shell-carbon storage protocol yet exists.</t>
+          <t>To monitor sea-lice burden on farmed salmon (the parasite/pathogen-surveillance facet of the finfish community-composition indicator), follow a fixed sampling design - for example five fish from each of five pens (25 fish) on a set schedule - anaesthetising and examining each fish and counting lice by life stage under a hand lens. Report prevalence and abundance per fish and compare against defined trigger levels that prompt action. Farm-staff counts are typically validated against dedicated teams, and sentinel/wild-salmonid counting extends the same method beyond the farm.</t>
         </is>
       </c>
       <c r="AL146" s="17" t="inlineStr">
@@ -30766,7 +30700,7 @@
       </c>
       <c r="AM146" s="18" t="inlineStr">
         <is>
-          <t>reichertnguyen_2023</t>
+          <t>scottishsalmon_2023</t>
         </is>
       </c>
       <c r="AN146" s="19" t="n"/>
@@ -30774,47 +30708,47 @@
       <c r="AP146" s="19" t="n"/>
       <c r="AQ146" s="16" t="inlineStr">
         <is>
-          <t>Oyster Nutrient-Reduction Crediting Protocol (Tissue/Shell/Denitrification)</t>
+          <t>Sea-Lice Counting &amp; Surveillance Protocol</t>
         </is>
       </c>
       <c r="AR146" s="16" t="inlineStr">
         <is>
-          <t>Reichert-Nguyen, J.; Cornwell, J.; et al. — Oyster BMP Expert Panel (Chesapeake Bay Program / Oyster Recovery Partnership)</t>
+          <t>Scottish Salmon Producers' Org. (Code of Good Practice); Institute of Marine Research (Norway); Norwegian Food Safety Authority</t>
         </is>
       </c>
       <c r="AS146" s="16" t="inlineStr">
         <is>
-          <t>TNC-relevant (TNC sits on the partnership). Restoration + aquaculture both covered. Shell-assimilation accounting is N/P (not carbon); a shell-CARBON storage protocol for CC 2.1.1 (mollusc) does not yet exist. Default tissue/shell coefficients make a desk estimate feasible without a lab.</t>
+          <t>The Norwegian Salmon Lice Directive (FOR-2009-08-18-1095) is the regulatory framework mandating counting; the IMR protocol is the certified standardized count for the national wild-salmonid programme. Farm-level counting alone is closer to T4; tier set at T3 to cover the full indicator (incl. wild-population surveillance to ~2.5 km). Tagged with the generic 'H&amp;B 2.1.1' string; under the finfish set this is fish-attraction / parasite surveillance.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Maryland Department of Natural Resources</t>
+          <t>Reichert-Nguyen, J., et al.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Oyster Reef Restoration Nutrient Assimilation BMP</t>
+          <t>Oyster BMP Expert Panel Reports — Nutrient &amp; Suspended-Sediment Reduction Effectiveness Protocols (First Report 2016; Second Report 2023)</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Maryland DNR (Critical Area / CBP BMP)</t>
+          <t>Chesapeake Bay Program / Oyster Recovery Partnership</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Maryland Department of Natural Resources</t>
+          <t>Chesapeake Bay Program</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Crediting protocol for N &amp; P assimilated in live oyster tissue and shell gained through reef restoration in tidal Chesapeake waters — the restoration-side application of the Oyster BMP framework.</t>
+          <t>Crediting-and-verification protocols defining reduction-effectiveness for oyster practices: N &amp; P assimilation in tissue, N &amp; P assimilation in shell, enhanced denitrification, and N/P burial. The tissue/shell protocols are the standardized bioextraction route; the denitrification protocol is one of very few packaged methods for that indicator.</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -30824,12 +30758,12 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Yes — defines the restoration nutrient-assimilation accounting with lookup tables (Expert Panel Appendix G) and credit duration.</t>
+          <t>Yes — defines harvest accounting (count × size → tissue/shell N&amp;P via published content) and the enhanced-denitrification crediting method, with verification guidelines. Decision-framework + effectiveness estimates.</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>Partial — reef survey/oyster counts farmer-doable; tissue/shell N&amp;P via lab or published coefficients.</t>
+          <t>Partial — counting/measuring harvested oysters is farmer-executable; tissue/shell %N&amp;P (CHN analyser) and denitrification (N2-flux/15N) need a partner lab, though published default coefficients allow a desk estimate.</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -30839,12 +30773,12 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>Reef survey gear; partner lab / published coefficients</t>
+          <t>Harvest records, calipers; partner lab CHN analyser; (denitrification: benthic-flux/15N)</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Low–Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -30854,12 +30788,12 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>Assimilation accounting via lookup tables</t>
+          <t>Reduction-effectiveness accounting; verification protocol</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>Yes — Open (MD DNR PDF)</t>
+          <t>Yes — Open (CBP PDFs)</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
@@ -30869,12 +30803,12 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>https://dnr.maryland.gov/criticalarea/Documents/Oyster_Reef_Restoration_Assimilation_BMP.pdf</t>
+          <t>https://d18lev1ok5leia.cloudfront.net/chesapeakebay/documents/Oyster-BMP-Expert-Panel-Second-Report.pdf</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>Use it where reef restoration, rather than harvest, is the practice.</t>
+          <t>Default tissue/shell coefficients make a credible desk estimate feasible without a lab; shell accounting here is for N and P, not carbon.</t>
         </is>
       </c>
       <c r="V147" t="inlineStr">
@@ -30899,7 +30833,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>WQ 1.1.1 — N and P bioextraction</t>
+          <t>WQ 1.1.1 — N and P bioextraction, WQ 1.1.2 — Rate of denitrification</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -30954,7 +30888,7 @@
       </c>
       <c r="AK147" s="16" t="inlineStr">
         <is>
-          <t>This is the restoration-side application of the Chesapeake oyster nutrient-crediting framework: it accounts for nitrogen and phosphorus assimilated in live oyster tissue and shell gained through reef restoration. Survey the reef for oyster numbers and size, then apply the published lookup tables (Expert Panel appendices) to convert to assimilated N and P over the credited duration. Use it where reef restoration, rather than harvest, is the practice.</t>
+          <t>This crediting-and-verification protocol standardizes how to account for nutrients an oyster practice removes: nitrogen and phosphorus assimilated in harvested tissue and shell, plus enhanced denitrification and burial. For the bioextraction route, record harvest (count x size) and convert to tissue/shell N and P using published content coefficients (or a partner-lab CHN analysis); the denitrification route uses benthic-flux or 15N methods. Default coefficients make a credible desk estimate feasible without a lab. Note shell accounting here is for N and P, not carbon - no shell-carbon storage protocol yet exists.</t>
         </is>
       </c>
       <c r="AL147" s="17" t="inlineStr">
@@ -30964,7 +30898,7 @@
       </c>
       <c r="AM147" s="18" t="inlineStr">
         <is>
-          <t>marylanddepartment_2021</t>
+          <t>reichertnguyen_2023</t>
         </is>
       </c>
       <c r="AN147" s="19" t="n"/>
@@ -30972,62 +30906,62 @@
       <c r="AP147" s="19" t="n"/>
       <c r="AQ147" s="16" t="inlineStr">
         <is>
-          <t>Oyster-Reef Restoration Nutrient-Assimilation Crediting</t>
+          <t>Oyster Nutrient-Reduction Crediting Protocol (Tissue/Shell/Denitrification)</t>
         </is>
       </c>
       <c r="AR147" s="16" t="inlineStr">
         <is>
-          <t>Maryland Department of Natural Resources</t>
+          <t>Reichert-Nguyen, J.; Cornwell, J.; et al. — Oyster BMP Expert Panel (Chesapeake Bay Program / Oyster Recovery Partnership)</t>
         </is>
       </c>
       <c r="AS147" s="16" t="inlineStr">
         <is>
-          <t>Implements the Chesapeake Oyster BMP framework (previous row) for restoration credits. Useful where reef restoration rather than harvest is the practice.</t>
+          <t>TNC-relevant (TNC sits on the partnership). Restoration + aquaculture both covered. Shell-assimilation accounting is N/P (not carbon); a shell-CARBON storage protocol for CC 2.1.1 (mollusc) does not yet exist. Default tissue/shell coefficients make a desk estimate feasible without a lab.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Hawkins, A. J. S. &amp; et al. (ShellSIM)</t>
+          <t>Maryland Department of Natural Resources</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ShellSIM — bivalve filtration, growth and environmental-effects model (software tool)</t>
+          <t>Oyster Reef Restoration Nutrient Assimilation BMP</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>shellsim.com</t>
+          <t>Maryland DNR (Critical Area / CBP BMP)</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>PML Applications / ShellSIM</t>
+          <t>Maryland Department of Natural Resources</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>User-friendly mechanistic model of suspension-feeding bivalves: predicts particle clearance/filtration rate, ammonium loss, faecal loss, oxygen uptake and growth for up to 14 species, individual→culture-area scale. The practical route to the filtration indicator and a complement to bioextraction/DO.</t>
+          <t>Crediting protocol for N &amp; P assimilated in live oyster tissue and shell gained through reef restoration in tidal Chesapeake waters — the restoration-side application of the Oyster BMP framework.</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Reference (usable model / design tool)</t>
+          <t>Protocol</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Adequate as a quantification tool rather than a field protocol: given environmental drivers + stock it outputs clearance/filtration and nutrient/oxygen fluxes. Requires parameterisation, not field sampling.</t>
+          <t>Yes — defines the restoration nutrient-assimilation accounting with lookup tables (Expert Panel Appendix G) and credit duration.</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>No — marketed for growers/managers/regulators but parameterisation and interpretation need modelling expertise.</t>
+          <t>Partial — reef survey/oyster counts farmer-doable; tissue/shell N&amp;P via lab or published coefficients.</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -31037,27 +30971,27 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>Software (ShellSIM); environmental driver data</t>
+          <t>Reef survey gear; partner lab / published coefficients</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Low (tool free; cost is expertise/data)</t>
+          <t>Low–Medium</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>One-time (no sampling — desk-based)</t>
+          <t>Year-long study (12 months)</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>Dynamic energy-balance simulation; scenario analysis</t>
+          <t>Assimilation accounting via lookup tables</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>Yes — Open (free tool)</t>
+          <t>Yes — Open (MD DNR PDF)</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
@@ -31067,12 +31001,12 @@
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>http://shellsim.com</t>
+          <t>https://dnr.maryland.gov/criticalarea/Documents/Oyster_Reef_Restoration_Assimilation_BMP.pdf</t>
         </is>
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>A modelling tool for the filtration service; complementary carrying-capacity models are FARM and EcoWin.</t>
+          <t>Use it where reef restoration, rather than harvest, is the practice.</t>
         </is>
       </c>
       <c r="V148" t="inlineStr">
@@ -31082,7 +31016,7 @@
       </c>
       <c r="W148" s="7" t="inlineStr">
         <is>
-          <t>2 — Researcher</t>
+          <t>3 — Partnership</t>
         </is>
       </c>
       <c r="X148" t="inlineStr">
@@ -31097,17 +31031,17 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>WQ 1.3.1 — Rate of water filtration, WQ 1.1.1 — N and P bioextraction, WQ 1.2.1 — Dissolved oxygen</t>
+          <t>WQ 1.1.1 — N and P bioextraction</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>Cross-zone / global</t>
+          <t>Temperate Atlantic</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>Multi-species / mixed</t>
+          <t>Eastern oyster (Crassostrea virginica)</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
@@ -31132,7 +31066,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>Modelling</t>
+          <t>Tissue analysis</t>
         </is>
       </c>
       <c r="AH148" t="inlineStr">
@@ -31152,17 +31086,17 @@
       </c>
       <c r="AK148" s="16" t="inlineStr">
         <is>
-          <t>This is a user-friendly mechanistic model of suspension-feeding bivalves rather than a field method: given environmental drivers and stock, it predicts clearance/filtration rate, ammonium and faecal losses, oxygen uptake and growth for many species, from individual to culture-area scale. Use it to quantify the water-filtration service (and to complement bioextraction and dissolved-oxygen work) by parameterising and running scenarios; farm/bay carrying-capacity models (FARM, EcoWin) and Dame's depletion indices are the complementary frameworks.</t>
+          <t>This is the restoration-side application of the Chesapeake oyster nutrient-crediting framework: it accounts for nitrogen and phosphorus assimilated in live oyster tissue and shell gained through reef restoration. Survey the reef for oyster numbers and size, then apply the published lookup tables (Expert Panel appendices) to convert to assimilated N and P over the credited duration. Use it where reef restoration, rather than harvest, is the practice.</t>
         </is>
       </c>
       <c r="AL148" s="17" t="inlineStr">
         <is>
-          <t>Ref</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="AM148" s="18" t="inlineStr">
         <is>
-          <t>hawkins_2013</t>
+          <t>marylanddepartment_2021</t>
         </is>
       </c>
       <c r="AN148" s="19" t="n"/>
@@ -31170,62 +31104,62 @@
       <c r="AP148" s="19" t="n"/>
       <c r="AQ148" s="16" t="inlineStr">
         <is>
-          <t>ShellSIM Bivalve Filtration &amp; Growth Model (Reference)</t>
+          <t>Oyster-Reef Restoration Nutrient-Assimilation Crediting</t>
         </is>
       </c>
       <c r="AR148" s="16" t="inlineStr">
         <is>
-          <t>Hawkins, A.J.S.; et al. (ShellSIM)</t>
+          <t>Maryland Department of Natural Resources</t>
         </is>
       </c>
       <c r="AS148" s="16" t="inlineStr">
         <is>
-          <t>Farm-/bay-scale carrying-capacity models (FARM, EcoWin) and the Dame depletion indices (clearance vs. residence vs. primary-production time) are the complementary frameworks for filtration-as-service. Modelling tool → T2.</t>
+          <t>Implements the Chesapeake Oyster BMP framework (previous row) for restoration credits. Useful where reef restoration rather than harvest is the practice.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>OSPAR Commission (JAMP)</t>
+          <t>Hawkins, A. J. S. &amp; et al. (ShellSIM)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>JAMP Eutrophication Monitoring Guidelines: Chlorophyll a in Water (with ICES TIMES chlorophyll procedure)</t>
+          <t>ShellSIM — bivalve filtration, growth and environmental-effects model (software tool)</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>OSPAR Commission / ICES Techniques in Marine Environmental Sciences</t>
+          <t>shellsim.com</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>OSPAR Commission</t>
+          <t>PML Applications / ShellSIM</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Intergovernmental standardized procedure for chlorophyll-a determination (sampling, filtration, extraction, spectrophotometric/HPLC analysis; ISO 10260; in-situ fluorometer calibration). The standard route to the chlorophyll-a indicator.</t>
+          <t>User-friendly mechanistic model of suspension-feeding bivalves: predicts particle clearance/filtration rate, ammonium loss, faecal loss, oxygen uptake and growth for up to 14 species, individual→culture-area scale. The practical route to the filtration indicator and a complement to bioextraction/DO.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Protocol</t>
+          <t>Reference (usable model / design tool)</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Yes — prescribes collection→filtration→extraction→analysis with QA (accredited labs, reference checks). Reproducible analytical SOP.</t>
+          <t>Adequate as a quantification tool rather than a field protocol: given environmental drivers + stock it outputs clearance/filtration and nutrient/oxygen fluxes. Requires parameterisation, not field sampling.</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>Partial — water sampling/filtration farmer-doable; spectrophotometric/HPLC analysis needs a partner lab (or a calibrated fluorometer + QC).</t>
+          <t>No — marketed for growers/managers/regulators but parameterisation and interpretation need modelling expertise.</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -31235,27 +31169,27 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>Niskin/bottle, filtration rig, GF/F filters; spectrophotometer/HPLC or calibrated fluorometer</t>
+          <t>Software (ShellSIM); environmental driver data</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Low–Medium</t>
+          <t>Low (tool free; cost is expertise/data)</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Year-long study (12 months)</t>
+          <t>One-time (no sampling — desk-based)</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>Standardized chl-a quantification; eutrophication assessment</t>
+          <t>Dynamic energy-balance simulation; scenario analysis</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>Yes — Open (OSPAR/JRC PDF)</t>
+          <t>Yes — Open (free tool)</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
@@ -31265,12 +31199,12 @@
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>https://mcc.jrc.ec.europa.eu/documents/OSPAR/Eutrophication_MonitoringGuidelinesch_%20a.pdf</t>
+          <t>http://shellsim.com</t>
         </is>
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>The standard analytical route to the chlorophyll-a indicator; satellite ocean-colour is the remote-sensing complement.</t>
+          <t>A modelling tool for the filtration service; complementary carrying-capacity models are FARM and EcoWin.</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
@@ -31280,12 +31214,12 @@
       </c>
       <c r="W149" s="7" t="inlineStr">
         <is>
-          <t>3 — Partnership</t>
+          <t>2 — Researcher</t>
         </is>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>Seaweed, Mollusk</t>
+          <t>Mollusk</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
@@ -31295,7 +31229,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>WQ 2.1.1 — Chlorophyll-a</t>
+          <t>WQ 1.3.1 — Rate of water filtration, WQ 1.1.1 — N and P bioextraction, WQ 1.2.1 — Dissolved oxygen</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -31305,7 +31239,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>Not species-specific</t>
+          <t>Multi-species / mixed</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
@@ -31330,7 +31264,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>Pigment HPLC, Water chemistry</t>
+          <t>Modelling</t>
         </is>
       </c>
       <c r="AH149" t="inlineStr">
@@ -31350,17 +31284,17 @@
       </c>
       <c r="AK149" s="16" t="inlineStr">
         <is>
-          <t>This intergovernmental SOP is the standard route to the chlorophyll-a indicator. Collect water (Niskin/bottle), filter onto GF/F, extract the pigment and determine chlorophyll-a spectrophotometrically or by HPLC (ISO 10260), or calibrate an in-situ fluorometer against these samples, all under defined quality assurance (accredited labs, reference checks). Follow it for comparable, eutrophication-grade chlorophyll data; the ICES TIMES procedure and UNESCO/SCOR pigment monographs are the underpinning analytical references, and satellite ocean-colour chlorophyll is the remote-sensing complement.</t>
+          <t>This is a user-friendly mechanistic model of suspension-feeding bivalves rather than a field method: given environmental drivers and stock, it predicts clearance/filtration rate, ammonium and faecal losses, oxygen uptake and growth for many species, from individual to culture-area scale. Use it to quantify the water-filtration service (and to complement bioextraction and dissolved-oxygen work) by parameterising and running scenarios; farm/bay carrying-capacity models (FARM, EcoWin) and Dame's depletion indices are the complementary frameworks.</t>
         </is>
       </c>
       <c r="AL149" s="17" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Ref</t>
         </is>
       </c>
       <c r="AM149" s="18" t="inlineStr">
         <is>
-          <t>jamp_2012</t>
+          <t>hawkins_2013</t>
         </is>
       </c>
       <c r="AN149" s="19" t="n"/>
@@ -31368,50 +31302,47 @@
       <c r="AP149" s="19" t="n"/>
       <c r="AQ149" s="16" t="inlineStr">
         <is>
-          <t>Standard Chlorophyll-a Determination SOP (JAMP)</t>
+          <t>ShellSIM Bivalve Filtration &amp; Growth Model (Reference)</t>
         </is>
       </c>
       <c r="AR149" s="16" t="inlineStr">
         <is>
-          <t>OSPAR Commission (JAMP); ICES</t>
+          <t>Hawkins, A.J.S.; et al. (ShellSIM)</t>
         </is>
       </c>
       <c r="AS149" s="16" t="inlineStr">
         <is>
-          <t>The ICES TIMES 'Standard procedure for the determination of chlorophyll a by spectroscopic methods' (Aminot &amp; Rey 2000) and the UNESCO/SCOR pigment monographs (Jeffrey et al. 1997) are the underpinning analytical references. Satellite ocean-colour chl-a is the remote-sensing complement.</t>
+          <t>Farm-/bay-scale carrying-capacity models (FARM, EcoWin) and the Dame depletion indices (clearance vs. residence vs. primary-production time) are the complementary frameworks for filtration-as-service. Modelling tool → T2.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Karlson, B., et al.</t>
+          <t>OSPAR Commission (JAMP)</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Microscopic and Molecular Methods for Quantitative Phytoplankton Analysis (IOC Manuals and Guides No. 55)</t>
+          <t>JAMP Eutrophication Monitoring Guidelines: Chlorophyll a in Water (with ICES TIMES chlorophyll procedure)</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>IOC Manuals and Guides, UNESCO</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>55</v>
+          <t>OSPAR Commission / ICES Techniques in Marine Environmental Sciences</t>
+        </is>
       </c>
       <c r="G150" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>UNESCO/IOC</t>
+          <t>OSPAR Commission</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Canonical manual for quantitative phytoplankton community analysis: sampling, microscopy/Utermöhl counts, and molecular (qPCR) methods. The standard route to the microorganism/plankton-community indicator.</t>
+          <t>Intergovernmental standardized procedure for chlorophyll-a determination (sampling, filtration, extraction, spectrophotometric/HPLC analysis; ISO 10260; in-situ fluorometer calibration). The standard route to the chlorophyll-a indicator.</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -31421,12 +31352,12 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Yes — documents sampling + enumeration/identification methods in replicable detail across microscopy and molecular approaches.</t>
+          <t>Yes — prescribes collection→filtration→extraction→analysis with QA (accredited labs, reference checks). Reproducible analytical SOP.</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>Partial — net-tow/bottle sampling farmer-doable; microscopy enumeration/ID and qPCR need a taxonomist/partner lab.</t>
+          <t>Partial — water sampling/filtration farmer-doable; spectrophotometric/HPLC analysis needs a partner lab (or a calibrated fluorometer + QC).</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -31436,12 +31367,12 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>Plankton net/Niskin, settling chambers, inverted microscope; (qPCR for molecular)</t>
+          <t>Niskin/bottle, filtration rig, GF/F filters; spectrophotometer/HPLC or calibrated fluorometer</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low–Medium</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -31451,12 +31382,12 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>Utermöhl counts; community composition; molecular enumeration</t>
+          <t>Standardized chl-a quantification; eutrophication assessment</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>Yes — Open (UNESCO/IOC PDF)</t>
+          <t>Yes — Open (OSPAR/JRC PDF)</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
@@ -31466,12 +31397,12 @@
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>https://unesdoc.unesco.org (IOC Manuals &amp; Guides 55, 2010)</t>
+          <t>https://mcc.jrc.ec.europa.eu/documents/OSPAR/Eutrophication_MonitoringGuidelinesch_%20a.pdf</t>
         </is>
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>The standard route to the phytoplankton/microorganism indicator; eDNA metabarcoding is the emerging molecular complement.</t>
+          <t>The standard analytical route to the chlorophyll-a indicator; satellite ocean-colour is the remote-sensing complement.</t>
         </is>
       </c>
       <c r="V150" t="inlineStr">
@@ -31496,7 +31427,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>WQ 2.1.2 — Microorganisms</t>
+          <t>WQ 2.1.1 — Chlorophyll-a</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -31531,7 +31462,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>Plankton sampling</t>
+          <t>Pigment HPLC, Water chemistry</t>
         </is>
       </c>
       <c r="AH150" t="inlineStr">
@@ -31551,7 +31482,7 @@
       </c>
       <c r="AK150" s="16" t="inlineStr">
         <is>
-          <t>This canonical manual is the standard route to the phytoplankton/microorganism indicator. Collect water with a net or Niskin, settle sub-samples in chambers and count/identify phytoplankton by inverted microscope (Utermohl method), or use molecular (qPCR) enumeration for the community. Follow it for replicable community composition and abundance; HELCOM species lists and the AQUACOSM SOP give a practical workflow, and eDNA metabarcoding is the emerging molecular complement.</t>
+          <t>This intergovernmental SOP is the standard route to the chlorophyll-a indicator. Collect water (Niskin/bottle), filter onto GF/F, extract the pigment and determine chlorophyll-a spectrophotometrically or by HPLC (ISO 10260), or calibrate an in-situ fluorometer against these samples, all under defined quality assurance (accredited labs, reference checks). Follow it for comparable, eutrophication-grade chlorophyll data; the ICES TIMES procedure and UNESCO/SCOR pigment monographs are the underpinning analytical references, and satellite ocean-colour chlorophyll is the remote-sensing complement.</t>
         </is>
       </c>
       <c r="AL150" s="17" t="inlineStr">
@@ -31561,7 +31492,7 @@
       </c>
       <c r="AM150" s="18" t="inlineStr">
         <is>
-          <t>karlson_2010</t>
+          <t>jamp_2012</t>
         </is>
       </c>
       <c r="AN150" s="19" t="n"/>
@@ -31569,47 +31500,50 @@
       <c r="AP150" s="19" t="n"/>
       <c r="AQ150" s="16" t="inlineStr">
         <is>
-          <t>Quantitative Phytoplankton Analysis Manual (Microscopy + Molecular)</t>
+          <t>Standard Chlorophyll-a Determination SOP (JAMP)</t>
         </is>
       </c>
       <c r="AR150" s="16" t="inlineStr">
         <is>
-          <t>Karlson, B.; Cusack, C.; Bresnan, E. (eds.) — UNESCO/IOC</t>
+          <t>OSPAR Commission (JAMP); ICES</t>
         </is>
       </c>
       <c r="AS150" s="16" t="inlineStr">
         <is>
-          <t>HELCOM Phytoplankton Expert Group species lists and the AQUACOSM phytoplankton SOP give the practical sampling/ID workflow. eDNA metabarcoding (row 24) is the emerging molecular complement.</t>
+          <t>The ICES TIMES 'Standard procedure for the determination of chlorophyll a by spectroscopic methods' (Aminot &amp; Rey 2000) and the UNESCO/SCOR pigment monographs (Jeffrey et al. 1997) are the underpinning analytical references. Satellite ocean-colour chl-a is the remote-sensing complement.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Global Ocean Acidification Observing Network (GOA-ON)</t>
+          <t>Karlson, B., et al.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Practical Best Practices for Ocean Acidification Monitoring (the 'OA Cookbook') + GOA-ON in a Box kit</t>
+          <t>Microscopic and Molecular Methods for Quantitative Phytoplankton Analysis (IOC Manuals and Guides No. 55)</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>GOA-ON (PubPub)</t>
-        </is>
+          <t>IOC Manuals and Guides, UNESCO</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>55</v>
       </c>
       <c r="G151" t="n">
-        <v>2024</v>
+        <v>2010</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Global Ocean Acidification Observing Network</t>
+          <t>UNESCO/IOC</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Practitioner-level SOPs for coastal carbonate-system monitoring (pH via spectrophotometry / iSAMI sensor, total alkalinity, CO2SYS), built around the low-cost GOA-ON in a Box kit and explicitly aimed at low-resource teams. The practical route to the pH / ocean-acidification indicator.</t>
+          <t>Canonical manual for quantitative phytoplankton community analysis: sampling, microscopy/Utermöhl counts, and molecular (qPCR) methods. The standard route to the microorganism/plankton-community indicator.</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -31619,12 +31553,12 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Yes — step-by-step SOPs (site selection, sampling, sensor operation, spectrophotometric pH with m-cresol purple, reference-material QC, CO2SYS) to weather-quality targets.</t>
+          <t>Yes — documents sampling + enumeration/identification methods in replicable detail across microscopy and molecular approaches.</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Partial — the in-a-Box kit lets a practitioner sample and measure pH; alkalinity titration, reference-material QC and CO2SYS still need training/partner support.</t>
+          <t>Partial — net-tow/bottle sampling farmer-doable; microscopy enumeration/ID and qPCR need a taxonomist/partner lab.</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -31634,7 +31568,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>GOA-ON in a Box kit, CTD-Diver, iSAMI pH sensor, spectrophotometer, reagents</t>
+          <t>Plankton net/Niskin, settling chambers, inverted microscope; (qPCR for molecular)</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -31644,17 +31578,17 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Multi-season (3–9 months)</t>
+          <t>Year-long study (12 months)</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>Carbonate-system computation (CO2SYS); QA against reference materials</t>
+          <t>Utermöhl counts; community composition; molecular enumeration</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>Yes — Open (PubPub)</t>
+          <t>Yes — Open (UNESCO/IOC PDF)</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
@@ -31664,12 +31598,12 @@
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>https://oceanacidificationcookbook.org</t>
+          <t>https://unesdoc.unesco.org (IOC Manuals &amp; Guides 55, 2010)</t>
         </is>
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>Built around the low-cost 'GOA-ON in a Box' kit and aimed at low-resource teams; the Dickson guide is the research-grade reference behind it.</t>
+          <t>The standard route to the phytoplankton/microorganism indicator; eDNA metabarcoding is the emerging molecular complement.</t>
         </is>
       </c>
       <c r="V151" t="inlineStr">
@@ -31684,17 +31618,17 @@
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>Seaweed</t>
+          <t>Seaweed, Mollusk</t>
         </is>
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>Climate Change</t>
+          <t>Water Quality</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>CC 2.1.1 — pH / ocean acidification</t>
+          <t>WQ 2.1.2 — Microorganisms</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -31729,7 +31663,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>Carbonate chemistry</t>
+          <t>Plankton sampling</t>
         </is>
       </c>
       <c r="AH151" t="inlineStr">
@@ -31749,7 +31683,7 @@
       </c>
       <c r="AK151" s="16" t="inlineStr">
         <is>
-          <t>This practitioner-level protocol lowers the barrier to carbonate-system (pH / ocean-acidification) monitoring, built around the low-cost 'GOA-ON in a Box' kit for low-resource teams. Follow its step-by-step SOPs: site selection, water sampling, sensor operation, spectrophotometric pH with m-cresol purple (or an iSAMI sensor) and total alkalinity, then compute the carbonate system with CO2SYS, with quality control against certified reference materials to weather-quality targets. It is the practical route to the pH indicator (and relevant to mollusc shell/carbonate contexts); the research-grade Dickson guide is the analytical reference behind it.</t>
+          <t>This canonical manual is the standard route to the phytoplankton/microorganism indicator. Collect water with a net or Niskin, settle sub-samples in chambers and count/identify phytoplankton by inverted microscope (Utermohl method), or use molecular (qPCR) enumeration for the community. Follow it for replicable community composition and abundance; HELCOM species lists and the AQUACOSM SOP give a practical workflow, and eDNA metabarcoding is the emerging molecular complement.</t>
         </is>
       </c>
       <c r="AL151" s="17" t="inlineStr">
@@ -31759,7 +31693,7 @@
       </c>
       <c r="AM151" s="18" t="inlineStr">
         <is>
-          <t>goaon_2024</t>
+          <t>karlson_2010</t>
         </is>
       </c>
       <c r="AN151" s="19" t="n"/>
@@ -31767,62 +31701,62 @@
       <c r="AP151" s="19" t="n"/>
       <c r="AQ151" s="16" t="inlineStr">
         <is>
-          <t>Low-Cost Ocean-Acidification Monitoring (GOA-ON Cookbook)</t>
+          <t>Quantitative Phytoplankton Analysis Manual (Microscopy + Molecular)</t>
         </is>
       </c>
       <c r="AR151" s="16" t="inlineStr">
         <is>
-          <t>Global Ocean Acidification Observing Network (GOA-ON)</t>
+          <t>Karlson, B.; Cusack, C.; Bresnan, E. (eds.) — UNESCO/IOC</t>
         </is>
       </c>
       <c r="AS151" s="16" t="inlineStr">
         <is>
-          <t>Lowers the OA-monitoring barrier dramatically vs. research-grade SOPs (next row). The EPA 'Guidelines for Measuring Changes in Seawater pH... Eastern US' (Pimenta &amp; Grear 2018) and the SDG 14.3.1 indicator methodology are companion references. Also relevant to mollusc shell/carbonate contexts.</t>
+          <t>HELCOM Phytoplankton Expert Group species lists and the AQUACOSM phytoplankton SOP give the practical sampling/ID workflow. eDNA metabarcoding (row 24) is the emerging molecular complement.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Dickson, A. G., et al.</t>
+          <t>Global Ocean Acidification Observing Network (GOA-ON)</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Guide to Best Practices for Ocean Acidification Research and Data Reporting (+ addendum)</t>
+          <t>Practical Best Practices for Ocean Acidification Monitoring (the 'OA Cookbook') + GOA-ON in a Box kit</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>GOA-ON / EU / IOCCP</t>
+          <t>GOA-ON (PubPub)</t>
         </is>
       </c>
       <c r="G152" t="n">
-        <v>2010</v>
+        <v>2024</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Publications Office of the European Union</t>
+          <t>Global Ocean Acidification Observing Network</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>The authoritative research-grade SOPs for seawater carbonate-system measurement and OA experimental design/data reporting — the analytical reference underpinning the OA Cookbook.</t>
+          <t>Practitioner-level SOPs for coastal carbonate-system monitoring (pH via spectrophotometry / iSAMI sensor, total alkalinity, CO2SYS), built around the low-cost GOA-ON in a Box kit and explicitly aimed at low-resource teams. The practical route to the pH / ocean-acidification indicator.</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Reference (authoritative SOP / usable design tool)</t>
+          <t>Protocol</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Adequate as the analytical gold-standard reference: defines high-accuracy pH/DIC/TA/pCO2 methods and reporting; a research programme is built from it.</t>
+          <t>Yes — step-by-step SOPs (site selection, sampling, sensor operation, spectrophotometric pH with m-cresol purple, reference-material QC, CO2SYS) to weather-quality targets.</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>No — research-grade carbonate chemistry throughout (CRM-traceable, high-precision instrumentation).</t>
+          <t>Partial — the in-a-Box kit lets a practitioner sample and measure pH; alkalinity titration, reference-material QC and CO2SYS still need training/partner support.</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -31832,27 +31766,27 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>Research-grade spectrophotometry/coulometry, certified reference materials</t>
+          <t>GOA-ON in a Box kit, CTD-Diver, iSAMI pH sensor, spectrophotometer, reagents</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Not time-specific</t>
+          <t>Multi-season (3–9 months)</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>High-accuracy carbonate-system SOPs; OA experimental design</t>
+          <t>Carbonate-system computation (CO2SYS); QA against reference materials</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>Yes — Open (PDF + addendum)</t>
+          <t>Yes — Open (PubPub)</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
@@ -31862,12 +31796,12 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>https://goa-on.org/resources/manuals.php</t>
+          <t>https://oceanacidificationcookbook.org</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>Pair it with the practitioner OA cookbook for low-cost field deployment.</t>
+          <t>Built around the low-cost 'GOA-ON in a Box' kit and aimed at low-resource teams; the Dickson guide is the research-grade reference behind it.</t>
         </is>
       </c>
       <c r="V152" t="inlineStr">
@@ -31877,12 +31811,12 @@
       </c>
       <c r="W152" s="7" t="inlineStr">
         <is>
-          <t>2 — Researcher</t>
+          <t>3 — Partnership</t>
         </is>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>Seaweed, Mollusk</t>
+          <t>Seaweed</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
@@ -31947,17 +31881,17 @@
       </c>
       <c r="AK152" s="16" t="inlineStr">
         <is>
-          <t>This is the authoritative research-grade reference for seawater carbonate-system measurement and ocean-acidification experimental design and data reporting - the analytical gold standard (high-accuracy pH, DIC, total alkalinity, pCO2) underpinning the practitioner OA cookbook. Use it to build a weather-quality ocean-acidification programme or to anchor methods; pair it with the cookbook for low-cost field deployment.</t>
+          <t>This practitioner-level protocol lowers the barrier to carbonate-system (pH / ocean-acidification) monitoring, built around the low-cost 'GOA-ON in a Box' kit for low-resource teams. Follow its step-by-step SOPs: site selection, water sampling, sensor operation, spectrophotometric pH with m-cresol purple (or an iSAMI sensor) and total alkalinity, then compute the carbonate system with CO2SYS, with quality control against certified reference materials to weather-quality targets. It is the practical route to the pH indicator (and relevant to mollusc shell/carbonate contexts); the research-grade Dickson guide is the analytical reference behind it.</t>
         </is>
       </c>
       <c r="AL152" s="17" t="inlineStr">
         <is>
-          <t>Ref</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="AM152" s="18" t="inlineStr">
         <is>
-          <t>dickson_2010</t>
+          <t>goaon_2024</t>
         </is>
       </c>
       <c r="AN152" s="19" t="n"/>
@@ -31965,62 +31899,62 @@
       <c r="AP152" s="19" t="n"/>
       <c r="AQ152" s="16" t="inlineStr">
         <is>
-          <t>Research-Grade Ocean-Acidification Measurement SOPs (Reference)</t>
+          <t>Low-Cost Ocean-Acidification Monitoring (GOA-ON Cookbook)</t>
         </is>
       </c>
       <c r="AR152" s="16" t="inlineStr">
         <is>
-          <t>Dickson, A.G.; Sabine, C.L.; Christian, J.R. (eds.); Riebesell, U.; et al.</t>
+          <t>Global Ocean Acidification Observing Network (GOA-ON)</t>
         </is>
       </c>
       <c r="AS152" s="16" t="inlineStr">
         <is>
-          <t>The reference standard for weather-quality OA data; pair with the practitioner-facing OA Cookbook (previous row) for field deployment. Tier T2 as a researcher-grade design tool.</t>
+          <t>Lowers the OA-monitoring barrier dramatically vs. research-grade SOPs (next row). The EPA 'Guidelines for Measuring Changes in Seawater pH... Eastern US' (Pimenta &amp; Grear 2018) and the SDG 14.3.1 indicator methodology are companion references. Also relevant to mollusc shell/carbonate contexts.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Verra</t>
+          <t>Dickson, A. G., et al.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Methodology Framework for Seaweed Carbon Projects (VCS M0172; incl. archived seaweed-aquaculture removals methodology)</t>
+          <t>Guide to Best Practices for Ocean Acidification Research and Data Reporting (+ addendum)</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Verra (Verified Carbon Standard)</t>
+          <t>GOA-ON / EU / IOCCP</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>2024</v>
+        <v>2010</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Verra</t>
+          <t>Publications Office of the European Union</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Carbon-crediting methodology framework for seaweed projects (in development). Its cradle-to-grave project-emissions accounting (LCA) maps to seaweed CC 1.2.1 (GHG); its core carbon-removal/sequestration crediting falls OUTSIDE the MEL indicator set (the framework deliberately excludes seaweed carbon sequestration as too uncertain to account).</t>
+          <t>The authoritative research-grade SOPs for seawater carbonate-system measurement and OA experimental design/data reporting — the analytical reference underpinning the OA Cookbook.</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Reference (carbon-accounting methodology framework)</t>
+          <t>Reference (authoritative SOP / usable design tool)</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Adequate only for the GHG-accounting (LCA) component vis-à-vis MEL; the sequestration/removals crediting it primarily addresses has no MEL indicator home (Sub-rule 1b note).</t>
+          <t>Adequate as the analytical gold-standard reference: defines high-accuracy pH/DIC/TA/pCO2 methods and reporting; a research programme is built from it.</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>No — project-level carbon MRV requires specialist accounting/verification.</t>
+          <t>No — research-grade carbonate chemistry throughout (CRM-traceable, high-precision instrumentation).</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -32030,7 +31964,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>LCA/MRV accounting (remote sensing, sampling, modelling)</t>
+          <t>Research-grade spectrophotometry/coulometry, certified reference materials</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -32040,32 +31974,32 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>One-time (no sampling — desk-based)</t>
+          <t>Not time-specific</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>Carbon-accounting methodology; net-removal computation</t>
+          <t>High-accuracy carbonate-system SOPs; OA experimental design</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>Yes — Open (Verra methodology page)</t>
+          <t>Yes — Open (PDF + addendum)</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>Abstract only</t>
+          <t>Abstract + Methods (fetched)</t>
         </is>
       </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>https://verra.org/methodologies/</t>
+          <t>https://goa-on.org/resources/manuals.php</t>
         </is>
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>MEL does not measure seaweed carbon sequestration - only the cradle-to-grave greenhouse-gas footprint overlaps; treat carbon-removal crediting as outside scope.</t>
+          <t>Pair it with the practitioner OA cookbook for low-cost field deployment.</t>
         </is>
       </c>
       <c r="V153" t="inlineStr">
@@ -32080,7 +32014,7 @@
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>Seaweed</t>
+          <t>Seaweed, Mollusk</t>
         </is>
       </c>
       <c r="Y153" t="inlineStr">
@@ -32090,7 +32024,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>CC 1.2.1 — Cradle-to-grave GHG emissions, Not in MEL framework</t>
+          <t>CC 2.1.1 — pH / ocean acidification</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -32125,7 +32059,7 @@
       </c>
       <c r="AG153" t="inlineStr">
         <is>
-          <t>Modelling, Remote sensing</t>
+          <t>Carbonate chemistry</t>
         </is>
       </c>
       <c r="AH153" t="inlineStr">
@@ -32145,7 +32079,7 @@
       </c>
       <c r="AK153" s="16" t="inlineStr">
         <is>
-          <t>This is an in-development carbon-crediting methodology framework for seaweed projects. Only its cradle-to-grave project-emissions (life-cycle) accounting maps to the seaweed GHG indicator; its core carbon-removal/sequestration crediting sits deliberately outside the MEL indicator set (the framework itself excludes seaweed carbon sequestration). It is included to flag that live grey-literature area - MEL measures only the cradle-to-grave GHG overlap, not sequestration MRV.</t>
+          <t>This is the authoritative research-grade reference for seawater carbonate-system measurement and ocean-acidification experimental design and data reporting - the analytical gold standard (high-accuracy pH, DIC, total alkalinity, pCO2) underpinning the practitioner OA cookbook. Use it to build a weather-quality ocean-acidification programme or to anchor methods; pair it with the cookbook for low-cost field deployment.</t>
         </is>
       </c>
       <c r="AL153" s="17" t="inlineStr">
@@ -32155,7 +32089,7 @@
       </c>
       <c r="AM153" s="18" t="inlineStr">
         <is>
-          <t>verra_2024</t>
+          <t>dickson_2010</t>
         </is>
       </c>
       <c r="AN153" s="19" t="n"/>
@@ -32163,67 +32097,62 @@
       <c r="AP153" s="19" t="n"/>
       <c r="AQ153" s="16" t="inlineStr">
         <is>
-          <t>Seaweed Carbon-Project Accounting Framework (GHG-Footprint Overlap Only)</t>
+          <t>Research-Grade Ocean-Acidification Measurement SOPs (Reference)</t>
         </is>
       </c>
       <c r="AR153" s="16" t="inlineStr">
         <is>
-          <t>Verra; Oceans 2050 (input)</t>
+          <t>Dickson, A.G.; Sabine, C.L.; Christian, J.R. (eds.); Riebesell, U.; et al.</t>
         </is>
       </c>
       <c r="AS153" s="16" t="inlineStr">
         <is>
-          <t>Included to flag a live grey-lit area (seaweed carbon MRV) that the MEL framework intentionally does NOT measure — only the cradle-to-grave GHG (CC 1.2.1) overlaps. The earlier standalone removals methodology was archived (June 2024); development moved into M0172. Tier T2.</t>
+          <t>The reference standard for weather-quality OA data; pair with the practitioner-facing OA Cookbook (previous row) for field deployment. Tier T2 as a researcher-grade design tool.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Pacific Northwest National Laboratory (PNNL)</t>
+          <t>Verra</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Macroalgae mCDR: LCA, Carbon Sequestration/Permanence and MRV Methods Review (PNNL-33997)</t>
+          <t>Methodology Framework for Seaweed Carbon Projects (VCS M0172; incl. archived seaweed-aquaculture removals methodology)</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>PNNL Technical Report</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>PNNL-33997</t>
+          <t>Verra (Verified Carbon Standard)</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>US DOE / Pacific Northwest National Laboratory</t>
+          <t>Verra</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Technical report reviewing LCA + monitoring/reporting/verification (MRV) methods for macroalgae carbon-dioxide removal (remote sensing, physical/sediment sampling, eDNA+coring for permanence, modelling, forensic carbon accounting). LCA/GHG-accounting maps to seaweed CC 1.2.1; the sequestration-permanence focus sits outside the MEL indicator set.</t>
+          <t>Carbon-crediting methodology framework for seaweed projects (in development). Its cradle-to-grave project-emissions accounting (LCA) maps to seaweed CC 1.2.1 (GHG); its core carbon-removal/sequestration crediting falls OUTSIDE the MEL indicator set (the framework deliberately excludes seaweed carbon sequestration as too uncertain to account).</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Reference (methods review / usable design tool)</t>
+          <t>Reference (carbon-accounting methodology framework)</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Adequate as an MRV methods inventory a programme is built from; not a single executable protocol. LCA component aligns to CC 1.2.1.</t>
+          <t>Adequate only for the GHG-accounting (LCA) component vis-à-vis MEL; the sequestration/removals crediting it primarily addresses has no MEL indicator home (Sub-rule 1b note).</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>No — carbon MRV/LCA is specialist throughout.</t>
+          <t>No — project-level carbon MRV requires specialist accounting/verification.</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -32233,7 +32162,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>LCA software, remote sensing, sediment coring, eDNA</t>
+          <t>LCA/MRV accounting (remote sensing, sampling, modelling)</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -32248,27 +32177,27 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>LCA; MRV method comparison</t>
+          <t>Carbon-accounting methodology; net-removal computation</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>Yes — Open (PNNL PDF)</t>
+          <t>Yes — Open (Verra methodology page)</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>Abstract + Methods (fetched)</t>
+          <t>Abstract only</t>
         </is>
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>https://www.pnnl.gov/main/publications/external/technical_reports/PNNL-33997.pdf</t>
+          <t>https://verra.org/methodologies/</t>
         </is>
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>Only the greenhouse-gas-footprint component maps to MEL; there are as yet no established MRV protocols for macroalgae carbon capture or permanence.</t>
+          <t>MEL does not measure seaweed carbon sequestration - only the cradle-to-grave greenhouse-gas footprint overlaps; treat carbon-removal crediting as outside scope.</t>
         </is>
       </c>
       <c r="V154" t="inlineStr">
@@ -32328,7 +32257,7 @@
       </c>
       <c r="AG154" t="inlineStr">
         <is>
-          <t>Modelling, Remote sensing, eDNA</t>
+          <t>Modelling, Remote sensing</t>
         </is>
       </c>
       <c r="AH154" t="inlineStr">
@@ -32348,7 +32277,7 @@
       </c>
       <c r="AK154" s="16" t="inlineStr">
         <is>
-          <t>This technical report reviews life-cycle-assessment and monitoring/reporting/verification methods for macroalgae carbon-dioxide removal (remote sensing, sediment sampling, eDNA-plus-coring for permanence, modelling, forensic carbon accounting). Within MEL scope only the LCA/GHG-accounting component maps to the seaweed GHG indicator; the sequestration/permanence side has no MEL home. Its honest takeaway is that there are as yet no established MRV protocols for macroalgae carbon capture or permanence.</t>
+          <t>This is an in-development carbon-crediting methodology framework for seaweed projects. Only its cradle-to-grave project-emissions (life-cycle) accounting maps to the seaweed GHG indicator; its core carbon-removal/sequestration crediting sits deliberately outside the MEL indicator set (the framework itself excludes seaweed carbon sequestration). It is included to flag that live grey-literature area - MEL measures only the cradle-to-grave GHG overlap, not sequestration MRV.</t>
         </is>
       </c>
       <c r="AL154" s="17" t="inlineStr">
@@ -32358,7 +32287,7 @@
       </c>
       <c r="AM154" s="18" t="inlineStr">
         <is>
-          <t>pnnl_2023</t>
+          <t>verra_2024</t>
         </is>
       </c>
       <c r="AN154" s="19" t="n"/>
@@ -32366,62 +32295,67 @@
       <c r="AP154" s="19" t="n"/>
       <c r="AQ154" s="16" t="inlineStr">
         <is>
-          <t>Macroalgae Carbon-Removal MRV Methods Review (Reference)</t>
+          <t>Seaweed Carbon-Project Accounting Framework (GHG-Footprint Overlap Only)</t>
         </is>
       </c>
       <c r="AR154" s="16" t="inlineStr">
         <is>
-          <t>Pacific Northwest National Laboratory (PNNL)</t>
+          <t>Verra; Oceans 2050 (input)</t>
         </is>
       </c>
       <c r="AS154" s="16" t="inlineStr">
         <is>
-          <t>Honest caveat across this literature: there are as yet no established MRV protocols for macroalgae carbon capture/permanence. The EDF 'Carbon Sequestration by Seaweed' report is a companion NGO context piece. Only the cradle-to-grave GHG (CC 1.2.1) overlaps MEL.</t>
+          <t>Included to flag a live grey-lit area (seaweed carbon MRV) that the MEL framework intentionally does NOT measure — only the cradle-to-grave GHG (CC 1.2.1) overlaps. The earlier standalone removals methodology was archived (June 2024); development moved into M0172. Tier T2.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ISO</t>
+          <t>Pacific Northwest National Laboratory (PNNL)</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Life-cycle assessment standards for cradle-to-grave GHG (ISO 14040 / ISO 14044; PAS 2050)</t>
+          <t>Macroalgae mCDR: LCA, Carbon Sequestration/Permanence and MRV Methods Review (PNNL-33997)</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ISO / BSI</t>
+          <t>PNNL Technical Report</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>PNNL-33997</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>International Organization for Standardization / BSI</t>
+          <t>US DOE / Pacific Northwest National Laboratory</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>The underlying standards for cradle-to-grave GHG/carbon-footprint accounting that operationalise the GHG-emissions indicator across all three sectors. Cradle-to-grave GHG = CC 1.1.1 (molluscs &amp; finfish) and CC 1.2.1 (seaweed).</t>
+          <t>Technical report reviewing LCA + monitoring/reporting/verification (MRV) methods for macroalgae carbon-dioxide removal (remote sensing, physical/sediment sampling, eDNA+coring for permanence, modelling, forensic carbon accounting). LCA/GHG-accounting maps to seaweed CC 1.2.1; the sequestration-permanence focus sits outside the MEL indicator set.</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Reference (standards / usable design tool)</t>
+          <t>Reference (methods review / usable design tool)</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Adequate as the methodological backbone for any aquaculture LCA/carbon-footprint; a footprint study is built from these standards (often with seafood-specific guidance).</t>
+          <t>Adequate as an MRV methods inventory a programme is built from; not a single executable protocol. LCA component aligns to CC 1.2.1.</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>No — LCA specialists.</t>
+          <t>No — carbon MRV/LCA is specialist throughout.</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -32431,12 +32365,12 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>LCA software + life-cycle inventory data</t>
+          <t>LCA software, remote sensing, sediment coring, eDNA</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>Medium–High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -32446,27 +32380,27 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>Life-cycle inventory + impact assessment (GWP)</t>
+          <t>LCA; MRV method comparison</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>No — Paywalled (ISO; PAS 2050 via BSI)</t>
+          <t>Yes — Open (PNNL PDF)</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>Title only (no abstract or DOI)</t>
+          <t>Abstract + Methods (fetched)</t>
         </is>
       </c>
       <c r="T155" t="inlineStr">
         <is>
-          <t>https://www.iso.org/standard/37456.html (ISO 14040)</t>
+          <t>https://www.pnnl.gov/main/publications/external/technical_reports/PNNL-33997.pdf</t>
         </is>
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>The methodological backbone for any aquaculture carbon-footprint study; note GHG is CC 1.1.1 for molluscs/finfish but CC 1.2.1 for seaweed.</t>
+          <t>Only the greenhouse-gas-footprint component maps to MEL; there are as yet no established MRV protocols for macroalgae carbon capture or permanence.</t>
         </is>
       </c>
       <c r="V155" t="inlineStr">
@@ -32481,7 +32415,7 @@
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>Seaweed, Mollusk, Finfish</t>
+          <t>Seaweed</t>
         </is>
       </c>
       <c r="Y155" t="inlineStr">
@@ -32491,7 +32425,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>CC 1.1.1 — Cradle-to-grave GHG, CC 1.2.1 — Cradle-to-grave GHG emissions</t>
+          <t>CC 1.2.1 — Cradle-to-grave GHG emissions, Not in MEL framework</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -32526,7 +32460,7 @@
       </c>
       <c r="AG155" t="inlineStr">
         <is>
-          <t>Modelling</t>
+          <t>Modelling, Remote sensing, eDNA</t>
         </is>
       </c>
       <c r="AH155" t="inlineStr">
@@ -32546,7 +32480,7 @@
       </c>
       <c r="AK155" s="16" t="inlineStr">
         <is>
-          <t>These are the underlying life-cycle-assessment standards (ISO 14040/14044, PAS 2050) that operationalise cradle-to-grave GHG / carbon-footprint accounting across all sectors. A footprint study is built from them - compile a life-cycle inventory and run impact assessment (global-warming potential) - typically with seafood-specific guidance layered on. Included so the GHG indicator has a methodological home; note the dual numbering (cradle-to-grave GHG is CC 1.1.1 for molluscs/finfish but CC 1.2.1 for seaweed). (Entry from general knowledge - consult the standards themselves for procedure.)</t>
+          <t>This technical report reviews life-cycle-assessment and monitoring/reporting/verification methods for macroalgae carbon-dioxide removal (remote sensing, sediment sampling, eDNA-plus-coring for permanence, modelling, forensic carbon accounting). Within MEL scope only the LCA/GHG-accounting component maps to the seaweed GHG indicator; the sequestration/permanence side has no MEL home. Its honest takeaway is that there are as yet no established MRV protocols for macroalgae carbon capture or permanence.</t>
         </is>
       </c>
       <c r="AL155" s="17" t="inlineStr">
@@ -32556,7 +32490,7 @@
       </c>
       <c r="AM155" s="18" t="inlineStr">
         <is>
-          <t>iso_2021</t>
+          <t>pnnl_2023</t>
         </is>
       </c>
       <c r="AN155" s="19" t="n"/>
@@ -32564,70 +32498,62 @@
       <c r="AP155" s="19" t="n"/>
       <c r="AQ155" s="16" t="inlineStr">
         <is>
-          <t>Life-Cycle Assessment Standards for GHG Footprinting (Reference)</t>
+          <t>Macroalgae Carbon-Removal MRV Methods Review (Reference)</t>
         </is>
       </c>
       <c r="AR155" s="16" t="inlineStr">
         <is>
-          <t>ISO; BSI (PAS 2050)</t>
+          <t>Pacific Northwest National Laboratory (PNNL)</t>
         </is>
       </c>
       <c r="AS155" s="16" t="inlineStr">
         <is>
-          <t>General-knowledge entry (not a fetched source this session); included so the cradle-to-grave GHG indicator has a protocol home. Seafood-specific LCA guidance and ASC/MSC footprint work build on these. Note the dual numbering: cradle-to-grave GHG = CC 1.1.1 for molluscs/finfish but CC 1.2.1 for seaweed.</t>
+          <t>Honest caveat across this literature: there are as yet no established MRV protocols for macroalgae carbon capture/permanence. The EDF 'Carbon Sequestration by Seaweed' report is a companion NGO context piece. Only the cradle-to-grave GHG (CC 1.2.1) overlaps MEL.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Gold, Z., et al.</t>
+          <t>ISO</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>A manager's guide to using eDNA metabarcoding in marine ecosystems</t>
+          <t>Life-cycle assessment standards for cradle-to-grave GHG (ISO 14040 / ISO 14044; PAS 2050)</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>PeerJ</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10</v>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>e14071</t>
+          <t>ISO / BSI</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>PeerJ</t>
+          <t>International Organization for Standardization / BSI</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Practitioner-/manager-facing guide to designing eDNA metabarcoding monitoring programmes (primer selection, reference databases, decontamination, pilot variance, archiving). Cross-cutting biodiversity tool serving epibiota, mobile fauna, community composition, and plankton indicators.</t>
+          <t>The underlying standards for cradle-to-grave GHG/carbon-footprint accounting that operationalise the GHG-emissions indicator across all three sectors. Cradle-to-grave GHG = CC 1.1.1 (molluscs &amp; finfish) and CC 1.2.1 (seaweed).</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Reference (usable design tool / manager guide)</t>
+          <t>Reference (standards / usable design tool)</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Adequate as a programme-design guide: five decision steps for a defensible eDNA monitoring programme; not itself a single bench protocol.</t>
+          <t>Adequate as the methodological backbone for any aquaculture LCA/carbon-footprint; a footprint study is built from these standards (often with seafood-specific guidance).</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>No — water sampling/filtration is simple, but the metabarcoding pipeline (extraction, PCR, sequencing, bioinformatics) is specialist throughout.</t>
+          <t>No — LCA specialists.</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -32637,42 +32563,42 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>Filtration kit; molecular lab (extraction, PCR, sequencing); bioinformatics</t>
+          <t>LCA software + life-cycle inventory data</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium–High</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Not time-specific</t>
+          <t>One-time (no sampling — desk-based)</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>Site-occupancy decontamination; metabarcoding bioinformatics</t>
+          <t>Life-cycle inventory + impact assessment (GWP)</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>Yes — Open (PeerJ, CC-BY)</t>
+          <t>No — Paywalled (ISO; PAS 2050 via BSI)</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>Abstract + Methods (fetched)</t>
+          <t>Title only (no abstract or DOI)</t>
         </is>
       </c>
       <c r="T156" t="inlineStr">
         <is>
-          <t>https://peerj.com/articles/14071/</t>
+          <t>https://www.iso.org/standard/37456.html (ISO 14040)</t>
         </is>
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>A programme-design guide; a Springer protocol chapter gives the bench SOP, and formal eDNA standardisation is still in progress.</t>
+          <t>The methodological backbone for any aquaculture carbon-footprint study; note GHG is CC 1.1.1 for molluscs/finfish but CC 1.2.1 for seaweed.</t>
         </is>
       </c>
       <c r="V156" t="inlineStr">
@@ -32692,12 +32618,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>Habitat &amp; Biodiversity, Water Quality</t>
+          <t>Climate Change</t>
         </is>
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 1.2.1 — Mobile fauna, H&amp;B 2.1.1 — Community composition, WQ 2.1.2 — Microorganisms</t>
+          <t>CC 1.1.1 — Cradle-to-grave GHG, CC 1.2.1 — Cradle-to-grave GHG emissions</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -32732,7 +32658,7 @@
       </c>
       <c r="AG156" t="inlineStr">
         <is>
-          <t>eDNA</t>
+          <t>Modelling</t>
         </is>
       </c>
       <c r="AH156" t="inlineStr">
@@ -32752,7 +32678,7 @@
       </c>
       <c r="AK156" s="16" t="inlineStr">
         <is>
-          <t>This manager-facing guide helps design a defensible eDNA metabarcoding monitoring programme - primer selection, reference databases, decontamination, pilot variance and archiving - as a cross-cutting biodiversity tool (epibiota, mobile fauna, community composition, plankton). Use it to plan the programme; a Springer protocol chapter gives the bench sampling/extraction SOP, and formal ISO/CEN eDNA standardisation is still in progress. It pairs with the MarineGEO fouling/ARMS and IOC phytoplankton methods.</t>
+          <t>These are the underlying life-cycle-assessment standards (ISO 14040/14044, PAS 2050) that operationalise cradle-to-grave GHG / carbon-footprint accounting across all sectors. A footprint study is built from them - compile a life-cycle inventory and run impact assessment (global-warming potential) - typically with seafood-specific guidance layered on. Included so the GHG indicator has a methodological home; note the dual numbering (cradle-to-grave GHG is CC 1.1.1 for molluscs/finfish but CC 1.2.1 for seaweed). (Entry from general knowledge - consult the standards themselves for procedure.)</t>
         </is>
       </c>
       <c r="AL156" s="17" t="inlineStr">
@@ -32762,7 +32688,7 @@
       </c>
       <c r="AM156" s="18" t="inlineStr">
         <is>
-          <t>gold_2022</t>
+          <t>iso_2021</t>
         </is>
       </c>
       <c r="AN156" s="19" t="n"/>
@@ -32770,15 +32696,221 @@
       <c r="AP156" s="19" t="n"/>
       <c r="AQ156" s="16" t="inlineStr">
         <is>
+          <t>Life-Cycle Assessment Standards for GHG Footprinting (Reference)</t>
+        </is>
+      </c>
+      <c r="AR156" s="16" t="inlineStr">
+        <is>
+          <t>ISO; BSI (PAS 2050)</t>
+        </is>
+      </c>
+      <c r="AS156" s="16" t="inlineStr">
+        <is>
+          <t>General-knowledge entry (not a fetched source this session); included so the cradle-to-grave GHG indicator has a protocol home. Seafood-specific LCA guidance and ASC/MSC footprint work build on these. Note the dual numbering: cradle-to-grave GHG = CC 1.1.1 for molluscs/finfish but CC 1.2.1 for seaweed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Gold, Z., et al.</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>A manager's guide to using eDNA metabarcoding in marine ecosystems</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>PeerJ</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>e14071</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>2022</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>PeerJ</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Practitioner-/manager-facing guide to designing eDNA metabarcoding monitoring programmes (primer selection, reference databases, decontamination, pilot variance, archiving). Cross-cutting biodiversity tool serving epibiota, mobile fauna, community composition, and plankton indicators.</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Reference (usable design tool / manager guide)</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Adequate as a programme-design guide: five decision steps for a defensible eDNA monitoring programme; not itself a single bench protocol.</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>No — water sampling/filtration is simple, but the metabarcoding pipeline (extraction, PCR, sequencing, bioinformatics) is specialist throughout.</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Filtration kit; molecular lab (extraction, PCR, sequencing); bioinformatics</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Not time-specific</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>Site-occupancy decontamination; metabarcoding bioinformatics</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>Yes — Open (PeerJ, CC-BY)</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>https://peerj.com/articles/14071/</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>A programme-design guide; a Springer protocol chapter gives the bench SOP, and formal eDNA standardisation is still in progress.</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W157" s="7" t="inlineStr">
+        <is>
+          <t>2 — Researcher</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Seaweed, Mollusk, Finfish</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>Habitat &amp; Biodiversity, Water Quality</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 1.2.1 — Mobile fauna, H&amp;B 2.1.1 — Community composition, WQ 2.1.2 — Microorganisms</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>Cross-zone / global</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>Not species-specific</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>Not depth-specific</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK157" s="16" t="inlineStr">
+        <is>
+          <t>This manager-facing guide helps design a defensible eDNA metabarcoding monitoring programme - primer selection, reference databases, decontamination, pilot variance and archiving - as a cross-cutting biodiversity tool (epibiota, mobile fauna, community composition, plankton). Use it to plan the programme; a Springer protocol chapter gives the bench sampling/extraction SOP, and formal ISO/CEN eDNA standardisation is still in progress. It pairs with the MarineGEO fouling/ARMS and IOC phytoplankton methods.</t>
+        </is>
+      </c>
+      <c r="AL157" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM157" s="18" t="inlineStr">
+        <is>
+          <t>gold_2022</t>
+        </is>
+      </c>
+      <c r="AN157" s="19" t="n"/>
+      <c r="AO157" s="19" t="n"/>
+      <c r="AP157" s="19" t="n"/>
+      <c r="AQ157" s="16" t="inlineStr">
+        <is>
           <t>Designing an eDNA Metabarcoding Monitoring Programme (Manager's Guide)</t>
         </is>
       </c>
-      <c r="AR156" s="16" t="inlineStr">
+      <c r="AR157" s="16" t="inlineStr">
         <is>
           <t>Gold, Z.; Sprague, J.; Kushner, D.J.; et al.</t>
         </is>
       </c>
-      <c r="AS156" s="16" t="inlineStr">
+      <c r="AS157" s="16" t="inlineStr">
         <is>
           <t>A Springer protocol chapter ('Environmental DNA from Marine Waters and Substrates: Protocols for Sampling and eDNA Extraction') gives the bench SOP; formal ISO/CEN eDNA standardisation is still in progress. Pairs with MarineGEO Fouling/ARMS (cryptobiota) and IOC phytoplankton. The framework already cites Mercaldo-Allen 2021 (eDNA at oyster cages).</t>
         </is>
@@ -32975,7 +33107,7 @@
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>Clear (visual methods feasible)</t>
+          <t>Turbid (visual methods limited)</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -33129,12 +33261,12 @@
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>Turbid (visual methods limited)</t>
+          <t>Clear (visual methods feasible)</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
         <is>
-          <t>Seaweed + finfish (IMTA)</t>
+          <t>Seaweed + finfish</t>
         </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
